--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
-  </si>
-  <si>
-    <t>04.09.202648</t>
-  </si>
-  <si>
-    <t>04.09.202649</t>
-  </si>
-  <si>
-    <t>04.09.202650</t>
-  </si>
-  <si>
-    <t>04.09.202651</t>
-  </si>
-  <si>
-    <t>04.09.202652</t>
-  </si>
-  <si>
-    <t>04.09.202653</t>
-  </si>
-  <si>
-    <t>04.09.202654</t>
-  </si>
-  <si>
-    <t>04.09.202655</t>
-  </si>
-  <si>
-    <t>04.09.202656</t>
-  </si>
-  <si>
-    <t>04.09.202657</t>
-  </si>
-  <si>
-    <t>04.09.202658</t>
-  </si>
-  <si>
-    <t>04.09.202659</t>
-  </si>
-  <si>
-    <t>04.09.202660</t>
-  </si>
-  <si>
-    <t>04.09.202661</t>
-  </si>
-  <si>
-    <t>04.09.202662</t>
-  </si>
-  <si>
-    <t>04.09.202663</t>
-  </si>
-  <si>
-    <t>04.09.202664</t>
-  </si>
-  <si>
-    <t>04.09.202665</t>
-  </si>
-  <si>
-    <t>04.09.202666</t>
-  </si>
-  <si>
-    <t>04.09.202667</t>
-  </si>
-  <si>
-    <t>04.09.202668</t>
-  </si>
-  <si>
-    <t>04.09.202669</t>
-  </si>
-  <si>
-    <t>04.09.202670</t>
-  </si>
-  <si>
-    <t>04.09.202671</t>
-  </si>
-  <si>
-    <t>04.09.202672</t>
-  </si>
-  <si>
-    <t>04.09.202673</t>
-  </si>
-  <si>
-    <t>04.09.202674</t>
-  </si>
-  <si>
-    <t>04.09.202675</t>
-  </si>
-  <si>
-    <t>04.09.202676</t>
-  </si>
-  <si>
-    <t>04.09.202677</t>
-  </si>
-  <si>
-    <t>04.09.202678</t>
-  </si>
-  <si>
-    <t>04.09.202679</t>
-  </si>
-  <si>
-    <t>04.09.202680</t>
-  </si>
-  <si>
-    <t>04.09.202681</t>
-  </si>
-  <si>
-    <t>04.09.202682</t>
-  </si>
-  <si>
-    <t>04.09.202683</t>
-  </si>
-  <si>
-    <t>04.09.202684</t>
-  </si>
-  <si>
-    <t>04.09.202685</t>
-  </si>
-  <si>
-    <t>04.09.202686</t>
-  </si>
-  <si>
-    <t>04.09.202687</t>
-  </si>
-  <si>
-    <t>04.09.202688</t>
-  </si>
-  <si>
-    <t>04.09.202689</t>
-  </si>
-  <si>
-    <t>04.09.202690</t>
-  </si>
-  <si>
-    <t>04.09.202691</t>
-  </si>
-  <si>
-    <t>04.09.202692</t>
-  </si>
-  <si>
-    <t>04.09.202693</t>
-  </si>
-  <si>
-    <t>04.09.202694</t>
-  </si>
-  <si>
-    <t>04.09.202695</t>
-  </si>
-  <si>
-    <t>04.09.202696</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
+  </si>
+  <si>
+    <t>13.09.202691</t>
+  </si>
+  <si>
+    <t>13.09.202692</t>
+  </si>
+  <si>
+    <t>13.09.202693</t>
+  </si>
+  <si>
+    <t>13.09.202694</t>
+  </si>
+  <si>
+    <t>13.09.202695</t>
+  </si>
+  <si>
+    <t>13.09.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>2502.926</v>
+        <v>2797.817</v>
       </c>
       <c r="C2">
-        <v>2502.926</v>
+        <v>2797.817</v>
       </c>
       <c r="D2">
-        <v>-36.241</v>
+        <v>-46.721</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>2134.163</v>
+        <v>4893.418</v>
       </c>
       <c r="C3">
-        <v>2134.163</v>
+        <v>4893.418</v>
       </c>
       <c r="D3">
-        <v>-36.743</v>
+        <v>-47.498</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>1538.197</v>
+        <v>1553.435</v>
       </c>
       <c r="C4">
-        <v>1538.197</v>
+        <v>1553.435</v>
       </c>
       <c r="D4">
-        <v>-51.71</v>
+        <v>-52.21</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>1548.876</v>
+        <v>1557.771</v>
       </c>
       <c r="C5">
-        <v>1548.876</v>
+        <v>1557.771</v>
       </c>
       <c r="D5">
-        <v>-46.084</v>
+        <v>-44.292</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>1449.301</v>
+        <v>1514.737</v>
       </c>
       <c r="C6">
-        <v>1449.301</v>
+        <v>1514.737</v>
       </c>
       <c r="D6">
-        <v>-27.787</v>
+        <v>-55.393</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>510</v>
+        <v>1484.602</v>
       </c>
       <c r="C7">
-        <v>510</v>
+        <v>1484.602</v>
       </c>
       <c r="D7">
-        <v>1.053</v>
+        <v>-55.334</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>1297.529</v>
+        <v>1440.382</v>
       </c>
       <c r="C8">
-        <v>1297.529</v>
+        <v>1440.382</v>
       </c>
       <c r="D8">
-        <v>-17.132</v>
+        <v>-69.895</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>510</v>
+        <v>1423.506</v>
       </c>
       <c r="C9">
-        <v>510</v>
+        <v>1423.506</v>
       </c>
       <c r="D9">
-        <v>5.626</v>
+        <v>-48.405</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1401.389</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1401.389</v>
       </c>
       <c r="D10">
-        <v>6.822</v>
+        <v>-26.72</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1457.487</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1457.487</v>
       </c>
       <c r="D11">
-        <v>2.997</v>
+        <v>-36.384</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>1275.035</v>
+        <v>1438.835</v>
       </c>
       <c r="C12">
-        <v>1275.035</v>
+        <v>1438.835</v>
       </c>
       <c r="D12">
-        <v>-17.826</v>
+        <v>-35.047</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>510</v>
+        <v>1402.718</v>
       </c>
       <c r="C13">
-        <v>510</v>
+        <v>1402.718</v>
       </c>
       <c r="D13">
-        <v>4.689</v>
+        <v>-35.414</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>1285.033</v>
+        <v>288.273</v>
       </c>
       <c r="C14">
-        <v>1285.033</v>
+        <v>288.273</v>
       </c>
       <c r="D14">
-        <v>-12.876</v>
+        <v>23.464</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>1195.637</v>
+        <v>294.114</v>
       </c>
       <c r="C15">
-        <v>1195.637</v>
+        <v>294.114</v>
       </c>
       <c r="D15">
-        <v>-1.682</v>
+        <v>24.603</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>1177.463</v>
+        <v>1277.82</v>
       </c>
       <c r="C16">
-        <v>1177.463</v>
+        <v>1277.82</v>
       </c>
       <c r="D16">
-        <v>-6.013</v>
+        <v>-11.242</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>1231.369</v>
+        <v>1256.854</v>
       </c>
       <c r="C17">
-        <v>1231.369</v>
+        <v>1256.854</v>
       </c>
       <c r="D17">
-        <v>-23.229</v>
+        <v>-26.353</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>1246.798</v>
+        <v>1274.534</v>
       </c>
       <c r="C18">
-        <v>1246.798</v>
+        <v>1274.534</v>
       </c>
       <c r="D18">
-        <v>-27.057</v>
+        <v>-21.184</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>1119.226</v>
+        <v>1282.844</v>
       </c>
       <c r="C19">
-        <v>1119.226</v>
+        <v>1282.844</v>
       </c>
       <c r="D19">
-        <v>-14.786</v>
+        <v>-12.624</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>507.857</v>
+        <v>1352.818</v>
       </c>
       <c r="C20">
-        <v>507.857</v>
+        <v>1352.818</v>
       </c>
       <c r="D20">
-        <v>34.448</v>
+        <v>-29.374</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>472.435</v>
+        <v>1284.139</v>
       </c>
       <c r="C21">
-        <v>472.435</v>
+        <v>1284.139</v>
       </c>
       <c r="D21">
-        <v>9.685</v>
+        <v>-15.78</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>437.58</v>
+        <v>1421.448</v>
       </c>
       <c r="C22">
-        <v>437.58</v>
+        <v>1421.448</v>
       </c>
       <c r="D22">
-        <v>3.682</v>
+        <v>-38.802</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>445.229</v>
+        <v>1299.921</v>
       </c>
       <c r="C23">
-        <v>445.229</v>
+        <v>1299.921</v>
       </c>
       <c r="D23">
-        <v>36.22</v>
+        <v>-16.488</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>461.351</v>
+        <v>446.882</v>
       </c>
       <c r="C24">
-        <v>461.351</v>
+        <v>446.882</v>
       </c>
       <c r="D24">
-        <v>11.408</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>404.254</v>
+        <v>307.085</v>
       </c>
       <c r="C25">
-        <v>404.254</v>
+        <v>307.085</v>
       </c>
       <c r="D25">
-        <v>9.769</v>
+        <v>22.792</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>376.287</v>
+        <v>1462.51</v>
       </c>
       <c r="C26">
-        <v>376.287</v>
+        <v>1462.51</v>
       </c>
       <c r="D26">
-        <v>36.868</v>
+        <v>-5.243</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>403.223</v>
+        <v>507</v>
       </c>
       <c r="C27">
-        <v>403.223</v>
+        <v>507</v>
       </c>
       <c r="D27">
-        <v>39.858</v>
+        <v>12.657</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>280.366</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>280.366</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>24.874</v>
+        <v>0.465</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>126.32</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>126.32</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>35.907</v>
+        <v>22.413</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>263.493</v>
+        <v>501</v>
       </c>
       <c r="C30">
-        <v>263.493</v>
+        <v>501</v>
       </c>
       <c r="D30">
-        <v>108.579</v>
+        <v>54.642</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>53.408</v>
+        <v>1198.552</v>
       </c>
       <c r="C31">
-        <v>53.408</v>
+        <v>1198.552</v>
       </c>
       <c r="D31">
-        <v>57.87</v>
+        <v>-2.412</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>219.408</v>
+        <v>1658.859</v>
       </c>
       <c r="C32">
-        <v>219.408</v>
+        <v>1658.859</v>
       </c>
       <c r="D32">
-        <v>57.931</v>
+        <v>-54.099</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>255.776</v>
+        <v>1526.385</v>
       </c>
       <c r="C33">
-        <v>255.776</v>
+        <v>1526.385</v>
       </c>
       <c r="D33">
-        <v>98.943</v>
+        <v>-143.819</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>260.293</v>
+        <v>3781.594</v>
       </c>
       <c r="C34">
-        <v>260.293</v>
+        <v>3781.594</v>
       </c>
       <c r="D34">
-        <v>169.313</v>
+        <v>-131.041</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>-1088.89</v>
+        <v>1373.954</v>
       </c>
       <c r="C35">
-        <v>-1088.89</v>
+        <v>1373.954</v>
       </c>
       <c r="D35">
-        <v>177.036</v>
+        <v>-131.459</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>251.189</v>
+        <v>1357.347</v>
       </c>
       <c r="C36">
-        <v>251.189</v>
+        <v>1357.347</v>
       </c>
       <c r="D36">
-        <v>91.494</v>
+        <v>-151.653</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>215.551</v>
+        <v>1356.353</v>
       </c>
       <c r="C37">
-        <v>215.551</v>
+        <v>1356.353</v>
       </c>
       <c r="D37">
-        <v>135.644</v>
+        <v>-184.264</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>26.542</v>
+        <v>1679.049</v>
       </c>
       <c r="C38">
-        <v>26.542</v>
+        <v>1679.049</v>
       </c>
       <c r="D38">
-        <v>98.986</v>
+        <v>-119.826</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>19.254</v>
+        <v>1184.514</v>
       </c>
       <c r="C39">
-        <v>19.254</v>
+        <v>1184.514</v>
       </c>
       <c r="D39">
-        <v>111.274</v>
+        <v>-166.363</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>11.698</v>
+        <v>1182.359</v>
       </c>
       <c r="C40">
-        <v>11.698</v>
+        <v>1182.359</v>
       </c>
       <c r="D40">
-        <v>112.23</v>
+        <v>-177.323</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>51.55</v>
+        <v>1181.726</v>
       </c>
       <c r="C41">
-        <v>51.55</v>
+        <v>1181.726</v>
       </c>
       <c r="D41">
-        <v>98.66800000000001</v>
+        <v>-193.43</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>43.339</v>
+        <v>968.9059999999999</v>
       </c>
       <c r="C42">
-        <v>43.339</v>
+        <v>968.9059999999999</v>
       </c>
       <c r="D42">
-        <v>80.992</v>
+        <v>-92.98399999999999</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>16.802</v>
+        <v>932.674</v>
       </c>
       <c r="C43">
-        <v>16.802</v>
+        <v>932.674</v>
       </c>
       <c r="D43">
-        <v>75.941</v>
+        <v>-133.768</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>36.424</v>
+        <v>951.448</v>
       </c>
       <c r="C44">
-        <v>36.424</v>
+        <v>951.448</v>
       </c>
       <c r="D44">
-        <v>102.473</v>
+        <v>-225.454</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>17.199</v>
+        <v>932.671</v>
       </c>
       <c r="C45">
-        <v>17.199</v>
+        <v>932.671</v>
       </c>
       <c r="D45">
-        <v>56.789</v>
+        <v>-219.283</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>818.851</v>
+        <v>651.48</v>
       </c>
       <c r="C46">
-        <v>818.851</v>
+        <v>651.48</v>
       </c>
       <c r="D46">
-        <v>-6.955</v>
+        <v>-188.827</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>818.426</v>
+        <v>647.803</v>
       </c>
       <c r="C47">
-        <v>818.426</v>
+        <v>647.803</v>
       </c>
       <c r="D47">
-        <v>-11.218</v>
+        <v>-236.593</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>1021.089</v>
+        <v>795.068</v>
       </c>
       <c r="C48">
-        <v>1021.089</v>
+        <v>795.068</v>
       </c>
       <c r="D48">
-        <v>-42.371</v>
+        <v>-213.857</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>201.134</v>
+        <v>660.991</v>
       </c>
       <c r="C49">
-        <v>201.134</v>
+        <v>660.991</v>
       </c>
       <c r="D49">
-        <v>3.693</v>
+        <v>-237.216</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>249.039</v>
+        <v>510.347</v>
       </c>
       <c r="C50">
-        <v>249.039</v>
+        <v>510.347</v>
       </c>
       <c r="D50">
-        <v>67.28100000000001</v>
+        <v>-231.127</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>251.576</v>
+        <v>625.446</v>
       </c>
       <c r="C51">
-        <v>251.576</v>
+        <v>625.446</v>
       </c>
       <c r="D51">
-        <v>59.898</v>
+        <v>-213.579</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>251.185</v>
+        <v>488.429</v>
       </c>
       <c r="C52">
-        <v>251.185</v>
+        <v>488.429</v>
       </c>
       <c r="D52">
-        <v>51.703</v>
+        <v>-186.602</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>251.624</v>
+        <v>488.069</v>
       </c>
       <c r="C53">
-        <v>251.624</v>
+        <v>488.069</v>
       </c>
       <c r="D53">
-        <v>48.758</v>
+        <v>-157.994</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>256.276</v>
+        <v>454.701</v>
       </c>
       <c r="C54">
-        <v>256.276</v>
+        <v>454.701</v>
       </c>
       <c r="D54">
-        <v>17.972</v>
+        <v>-48.521</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>261.49</v>
+        <v>456.402</v>
       </c>
       <c r="C55">
-        <v>261.49</v>
+        <v>456.402</v>
       </c>
       <c r="D55">
-        <v>50.867</v>
+        <v>-77.98</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>254.256</v>
+        <v>453.635</v>
       </c>
       <c r="C56">
-        <v>254.256</v>
+        <v>453.635</v>
       </c>
       <c r="D56">
-        <v>82.035</v>
+        <v>-43.354</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>256.796</v>
+        <v>453.32</v>
       </c>
       <c r="C57">
-        <v>256.796</v>
+        <v>453.32</v>
       </c>
       <c r="D57">
-        <v>50.753</v>
+        <v>-50.484</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>253.836</v>
+        <v>618.474</v>
       </c>
       <c r="C58">
-        <v>253.836</v>
+        <v>618.474</v>
       </c>
       <c r="D58">
-        <v>40.682</v>
+        <v>-48.823</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>252.198</v>
+        <v>623.86</v>
       </c>
       <c r="C59">
-        <v>252.198</v>
+        <v>623.86</v>
       </c>
       <c r="D59">
-        <v>32.51</v>
+        <v>-31.813</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>251</v>
+        <v>624.154</v>
       </c>
       <c r="C60">
-        <v>251</v>
+        <v>624.154</v>
       </c>
       <c r="D60">
-        <v>13.328</v>
+        <v>-22.028</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>31.245</v>
+        <v>-32.109</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>251.09</v>
+        <v>840.047</v>
       </c>
       <c r="C62">
-        <v>251.09</v>
+        <v>840.047</v>
       </c>
       <c r="D62">
-        <v>114.387</v>
+        <v>-48.717</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>253.1</v>
+        <v>841.395</v>
       </c>
       <c r="C63">
-        <v>253.1</v>
+        <v>841.395</v>
       </c>
       <c r="D63">
-        <v>53.283</v>
+        <v>-46.415</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>51</v>
+        <v>259.132</v>
       </c>
       <c r="C64">
-        <v>51</v>
+        <v>259.132</v>
       </c>
       <c r="D64">
-        <v>9.25</v>
+        <v>2.109</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>2232.804</v>
+        <v>903.28</v>
       </c>
       <c r="C65">
-        <v>2232.804</v>
+        <v>903.28</v>
       </c>
       <c r="D65">
-        <v>-19.983</v>
+        <v>-60.547</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>1403.275</v>
+        <v>1144.244</v>
       </c>
       <c r="C66">
-        <v>1403.275</v>
+        <v>1144.244</v>
       </c>
       <c r="D66">
-        <v>-14.286</v>
+        <v>-69.968</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>1547.921</v>
+        <v>1139.395</v>
       </c>
       <c r="C67">
-        <v>1547.921</v>
+        <v>1139.395</v>
       </c>
       <c r="D67">
-        <v>-67.298</v>
+        <v>-43.731</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>2009.766</v>
+        <v>1149.979</v>
       </c>
       <c r="C68">
-        <v>2009.766</v>
+        <v>1149.979</v>
       </c>
       <c r="D68">
-        <v>-76.09999999999999</v>
+        <v>-57.032</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>2314.136</v>
+        <v>1175.928</v>
       </c>
       <c r="C69">
-        <v>2314.136</v>
+        <v>1175.928</v>
       </c>
       <c r="D69">
-        <v>-69.224</v>
+        <v>-66.709</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>1758.383</v>
+        <v>1625.417</v>
       </c>
       <c r="C70">
-        <v>1758.383</v>
+        <v>1625.417</v>
       </c>
       <c r="D70">
-        <v>-8.141999999999999</v>
+        <v>-22.961</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>1792.065</v>
+        <v>1575.566</v>
       </c>
       <c r="C71">
-        <v>1792.065</v>
+        <v>1575.566</v>
       </c>
       <c r="D71">
-        <v>-39.908</v>
+        <v>-42.337</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>1762.498</v>
+        <v>1596.618</v>
       </c>
       <c r="C72">
-        <v>1762.498</v>
+        <v>1596.618</v>
       </c>
       <c r="D72">
-        <v>-47.147</v>
+        <v>-7.384</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>1862.914</v>
+        <v>1632.983</v>
       </c>
       <c r="C73">
-        <v>1862.914</v>
+        <v>1632.983</v>
       </c>
       <c r="D73">
-        <v>-57.481</v>
+        <v>-11.803</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>1964.81</v>
+        <v>2035.555</v>
       </c>
       <c r="C74">
-        <v>1964.81</v>
+        <v>2035.555</v>
       </c>
       <c r="D74">
-        <v>-40.835</v>
+        <v>-40.385</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>1973.905</v>
+        <v>1917.105</v>
       </c>
       <c r="C75">
-        <v>1973.905</v>
+        <v>1917.105</v>
       </c>
       <c r="D75">
-        <v>-53.293</v>
+        <v>-38.811</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>1972.717</v>
+        <v>3399.506</v>
       </c>
       <c r="C76">
-        <v>1972.717</v>
+        <v>3399.506</v>
       </c>
       <c r="D76">
-        <v>-43.278</v>
+        <v>-49.172</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>2126.323</v>
+        <v>2051.781</v>
       </c>
       <c r="C77">
-        <v>2126.323</v>
+        <v>2051.781</v>
       </c>
       <c r="D77">
-        <v>-69.34999999999999</v>
+        <v>-37.362</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>2002.816</v>
+        <v>1818.479</v>
       </c>
       <c r="C78">
-        <v>2002.816</v>
+        <v>1818.479</v>
       </c>
       <c r="D78">
-        <v>-60.838</v>
+        <v>-72.773</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>1994.399</v>
+        <v>1643.107</v>
       </c>
       <c r="C79">
-        <v>1994.399</v>
+        <v>1643.107</v>
       </c>
       <c r="D79">
-        <v>-36.928</v>
+        <v>-61.981</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>2234.504</v>
+        <v>1575.903</v>
       </c>
       <c r="C80">
-        <v>2234.504</v>
+        <v>1575.903</v>
       </c>
       <c r="D80">
-        <v>-69.383</v>
+        <v>-50.065</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>4326.697</v>
+        <v>1582.359</v>
       </c>
       <c r="C81">
-        <v>4326.697</v>
+        <v>1582.359</v>
       </c>
       <c r="D81">
-        <v>-57.308</v>
+        <v>-49.497</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>1824.08</v>
+        <v>1541.774</v>
       </c>
       <c r="C82">
-        <v>1824.08</v>
+        <v>1541.774</v>
       </c>
       <c r="D82">
-        <v>-17.67</v>
+        <v>-55.591</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>436.747</v>
+        <v>1585.518</v>
       </c>
       <c r="C83">
-        <v>436.747</v>
+        <v>1585.518</v>
       </c>
       <c r="D83">
-        <v>16.433</v>
+        <v>-82.009</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>465.199</v>
+        <v>1538.246</v>
       </c>
       <c r="C84">
-        <v>465.199</v>
+        <v>1538.246</v>
       </c>
       <c r="D84">
-        <v>2.108</v>
+        <v>-63.654</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>448.427</v>
+        <v>1545.642</v>
       </c>
       <c r="C85">
-        <v>448.427</v>
+        <v>1545.642</v>
       </c>
       <c r="D85">
-        <v>8.859999999999999</v>
+        <v>-34.903</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>1964.966</v>
+        <v>1509.08</v>
       </c>
       <c r="C86">
-        <v>1964.966</v>
+        <v>1509.08</v>
       </c>
       <c r="D86">
-        <v>-40.596</v>
+        <v>-21.437</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>1936.21</v>
+        <v>1511.044</v>
       </c>
       <c r="C87">
-        <v>1936.21</v>
+        <v>1511.044</v>
       </c>
       <c r="D87">
-        <v>-13.266</v>
+        <v>-34.707</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>1663.266</v>
+        <v>1363.404</v>
       </c>
       <c r="C88">
-        <v>1663.266</v>
+        <v>1363.404</v>
       </c>
       <c r="D88">
-        <v>-8.670999999999999</v>
+        <v>-10.049</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>1506.282</v>
+        <v>755</v>
       </c>
       <c r="C89">
-        <v>1506.282</v>
+        <v>755</v>
       </c>
       <c r="D89">
-        <v>-17.345</v>
+        <v>-4.051</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>2199.304</v>
+        <v>1446.729</v>
       </c>
       <c r="C90">
-        <v>2199.304</v>
+        <v>1446.729</v>
       </c>
       <c r="D90">
-        <v>-19.019</v>
+        <v>-11.032</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>359.258</v>
+        <v>1259.516</v>
       </c>
       <c r="C91">
-        <v>359.258</v>
+        <v>1259.516</v>
       </c>
       <c r="D91">
-        <v>19.407</v>
+        <v>-4.979</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>493.651</v>
+        <v>1590.998</v>
       </c>
       <c r="C92">
-        <v>493.651</v>
+        <v>1590.998</v>
       </c>
       <c r="D92">
-        <v>37.532</v>
+        <v>-17.637</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>477.487</v>
+        <v>1715.694</v>
       </c>
       <c r="C93">
-        <v>477.487</v>
+        <v>1715.694</v>
       </c>
       <c r="D93">
-        <v>30.976</v>
+        <v>-23.533</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>452.972</v>
+        <v>1521.352</v>
       </c>
       <c r="C94">
-        <v>452.972</v>
+        <v>1521.352</v>
       </c>
       <c r="D94">
-        <v>11.247</v>
+        <v>-17.993</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>480.228</v>
+        <v>1361.134</v>
       </c>
       <c r="C95">
-        <v>480.228</v>
+        <v>1361.134</v>
       </c>
       <c r="D95">
-        <v>15.084</v>
+        <v>-20.051</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>493.245</v>
+        <v>1440.926</v>
       </c>
       <c r="C96">
-        <v>493.245</v>
+        <v>1440.926</v>
       </c>
       <c r="D96">
-        <v>31.543</v>
+        <v>-4.023</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>1258.562</v>
+        <v>1219.097</v>
       </c>
       <c r="C97">
-        <v>1258.562</v>
+        <v>1219.097</v>
       </c>
       <c r="D97">
-        <v>-9.811999999999999</v>
+        <v>-6.818</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>2650.91</v>
+        <v>1199.096</v>
       </c>
       <c r="C98">
-        <v>2650.91</v>
+        <v>1199.096</v>
       </c>
       <c r="D98">
-        <v>-42.428</v>
+        <v>-32.249</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>3080.047</v>
+        <v>1196.651</v>
       </c>
       <c r="C99">
-        <v>3080.047</v>
+        <v>1196.651</v>
       </c>
       <c r="D99">
-        <v>-61.057</v>
+        <v>-22.075</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>1499.865</v>
+        <v>1341.595</v>
       </c>
       <c r="C100">
-        <v>1499.865</v>
+        <v>1341.595</v>
       </c>
       <c r="D100">
-        <v>-36.773</v>
+        <v>-27.43</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>1520.733</v>
+        <v>1000</v>
       </c>
       <c r="C101">
-        <v>1520.733</v>
+        <v>1000</v>
       </c>
       <c r="D101">
-        <v>-53.293</v>
+        <v>-4.19</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>1323.624</v>
+        <v>307.564</v>
       </c>
       <c r="C102">
-        <v>1323.624</v>
+        <v>307.564</v>
       </c>
       <c r="D102">
-        <v>-45.48</v>
+        <v>9.116</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>1320.626</v>
+        <v>217.676</v>
       </c>
       <c r="C103">
-        <v>1320.626</v>
+        <v>217.676</v>
       </c>
       <c r="D103">
-        <v>-44.038</v>
+        <v>35.498</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>1316.75</v>
+        <v>328.299</v>
       </c>
       <c r="C104">
-        <v>1316.75</v>
+        <v>328.299</v>
       </c>
       <c r="D104">
-        <v>-37.348</v>
+        <v>83.429</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>1198.429</v>
+        <v>272.65</v>
       </c>
       <c r="C105">
-        <v>1198.429</v>
+        <v>272.65</v>
       </c>
       <c r="D105">
-        <v>-23.243</v>
+        <v>52.417</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>1284.771</v>
+        <v>339.166</v>
       </c>
       <c r="C106">
-        <v>1284.771</v>
+        <v>339.166</v>
       </c>
       <c r="D106">
-        <v>-31.499</v>
+        <v>23.307</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>1296.216</v>
+        <v>510</v>
       </c>
       <c r="C107">
-        <v>1296.216</v>
+        <v>510</v>
       </c>
       <c r="D107">
-        <v>-33.211</v>
+        <v>17.685</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>1299</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1299</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>-13.864</v>
+        <v>10.586</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>1350.07</v>
+        <v>362.781</v>
       </c>
       <c r="C109">
-        <v>1350.07</v>
+        <v>362.781</v>
       </c>
       <c r="D109">
-        <v>-20.429</v>
+        <v>17.903</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>1372.645</v>
+        <v>1446.798</v>
       </c>
       <c r="C110">
-        <v>1372.645</v>
+        <v>1446.798</v>
       </c>
       <c r="D110">
-        <v>-49.142</v>
+        <v>-15.586</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>1379.147</v>
+        <v>1282.508</v>
       </c>
       <c r="C111">
-        <v>1379.147</v>
+        <v>1282.508</v>
       </c>
       <c r="D111">
-        <v>-49.527</v>
+        <v>-20.946</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>1297.904</v>
+        <v>1492.82</v>
       </c>
       <c r="C112">
-        <v>1297.904</v>
+        <v>1492.82</v>
       </c>
       <c r="D112">
-        <v>-26.54</v>
+        <v>-37.029</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>1394.198</v>
+        <v>1715.608</v>
       </c>
       <c r="C113">
-        <v>1394.198</v>
+        <v>1715.608</v>
       </c>
       <c r="D113">
-        <v>-26.271</v>
+        <v>-53.156</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>1370.348</v>
+        <v>1280.422</v>
       </c>
       <c r="C114">
-        <v>1370.348</v>
+        <v>1280.422</v>
       </c>
       <c r="D114">
-        <v>-52.982</v>
+        <v>-23.174</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>1549.101</v>
+        <v>1447.584</v>
       </c>
       <c r="C115">
-        <v>1549.101</v>
+        <v>1447.584</v>
       </c>
       <c r="D115">
-        <v>-35.982</v>
+        <v>-35.438</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>1284.308</v>
+        <v>1348.504</v>
       </c>
       <c r="C116">
-        <v>1284.308</v>
+        <v>1348.504</v>
       </c>
       <c r="D116">
-        <v>-15.501</v>
+        <v>-24.529</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>1291.554</v>
+        <v>5154.143</v>
       </c>
       <c r="C117">
-        <v>1291.554</v>
+        <v>5154.143</v>
       </c>
       <c r="D117">
-        <v>-25.05</v>
+        <v>-58.445</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>1493.894</v>
+        <v>1631.804</v>
       </c>
       <c r="C118">
-        <v>1493.894</v>
+        <v>1631.804</v>
       </c>
       <c r="D118">
-        <v>-52.716</v>
+        <v>-54.398</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>1435.931</v>
+        <v>1499.194</v>
       </c>
       <c r="C119">
-        <v>1435.931</v>
+        <v>1499.194</v>
       </c>
       <c r="D119">
-        <v>-38.818</v>
+        <v>-29.559</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>1463.179</v>
+        <v>1739.774</v>
       </c>
       <c r="C120">
-        <v>1463.179</v>
+        <v>1739.774</v>
       </c>
       <c r="D120">
-        <v>-35.069</v>
+        <v>-39.117</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>1418.457</v>
+        <v>1473.869</v>
       </c>
       <c r="C121">
-        <v>1418.457</v>
+        <v>1473.869</v>
       </c>
       <c r="D121">
-        <v>-43.033</v>
+        <v>-28.246</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>1615.944</v>
+        <v>510</v>
       </c>
       <c r="C122">
-        <v>1615.944</v>
+        <v>510</v>
       </c>
       <c r="D122">
-        <v>-5.533</v>
+        <v>30.067</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>1576.392</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1576.392</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>-26.047</v>
+        <v>59.985</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>1622.342</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1622.342</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>-27.155</v>
+        <v>52.927</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>1631.663</v>
+        <v>497.06</v>
       </c>
       <c r="C125">
-        <v>1631.663</v>
+        <v>497.06</v>
       </c>
       <c r="D125">
-        <v>-33.617</v>
+        <v>86.063</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>408.021</v>
+        <v>267.422</v>
       </c>
       <c r="C126">
-        <v>408.021</v>
+        <v>267.422</v>
       </c>
       <c r="D126">
-        <v>7.957</v>
+        <v>12.677</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>404.013</v>
+        <v>256.495</v>
       </c>
       <c r="C127">
-        <v>404.013</v>
+        <v>256.495</v>
       </c>
       <c r="D127">
-        <v>30.167</v>
+        <v>20.568</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>374.112</v>
+        <v>281.445</v>
       </c>
       <c r="C128">
-        <v>374.112</v>
+        <v>281.445</v>
       </c>
       <c r="D128">
-        <v>34.116</v>
+        <v>46.846</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>181.894</v>
+        <v>117.834</v>
       </c>
       <c r="C129">
-        <v>181.894</v>
+        <v>117.834</v>
       </c>
       <c r="D129">
-        <v>127.613</v>
+        <v>23.628</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>332.717</v>
+        <v>196.968</v>
       </c>
       <c r="C130">
-        <v>332.717</v>
+        <v>196.968</v>
       </c>
       <c r="D130">
-        <v>165.195</v>
+        <v>18.443</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>105.848</v>
+        <v>240.228</v>
       </c>
       <c r="C131">
-        <v>105.848</v>
+        <v>240.228</v>
       </c>
       <c r="D131">
-        <v>95.922</v>
+        <v>16.906</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B132">
-        <v>262.209</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>262.209</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>45.943</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B133">
-        <v>249.279</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>249.279</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>69.825</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B134">
-        <v>952.9640000000001</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>952.9640000000001</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>-33.191</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B135">
-        <v>251.049</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>251.049</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>11.714</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B136">
-        <v>251.349</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>251.349</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>53.928</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B137">
-        <v>42.751</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>42.751</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>82.902</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B138">
-        <v>104.21</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>104.21</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>89.848</v>
+        <v>0</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B139">
-        <v>-110.744</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>-110.744</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>66.167</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B140">
-        <v>-40.407</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>-40.407</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>104.978</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B141">
-        <v>94.324</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>94.324</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>100.116</v>
+        <v>0</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B142">
-        <v>6.668</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>6.668</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>93.97</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B143">
-        <v>34.829</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>34.829</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>78.08499999999999</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46269.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46269.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46269.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46269.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,868 +34,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
-  </si>
-  <si>
-    <t>20.09.202639</t>
-  </si>
-  <si>
-    <t>20.09.202640</t>
-  </si>
-  <si>
-    <t>20.09.202641</t>
-  </si>
-  <si>
-    <t>20.09.202642</t>
-  </si>
-  <si>
-    <t>20.09.202643</t>
-  </si>
-  <si>
-    <t>20.09.202644</t>
-  </si>
-  <si>
-    <t>20.09.202645</t>
-  </si>
-  <si>
-    <t>20.09.202646</t>
-  </si>
-  <si>
-    <t>20.09.202647</t>
-  </si>
-  <si>
-    <t>20.09.202648</t>
-  </si>
-  <si>
-    <t>20.09.202649</t>
-  </si>
-  <si>
-    <t>20.09.202650</t>
-  </si>
-  <si>
-    <t>20.09.202651</t>
-  </si>
-  <si>
-    <t>20.09.202652</t>
-  </si>
-  <si>
-    <t>20.09.202653</t>
-  </si>
-  <si>
-    <t>20.09.202654</t>
-  </si>
-  <si>
-    <t>20.09.202655</t>
-  </si>
-  <si>
-    <t>20.09.202656</t>
-  </si>
-  <si>
-    <t>20.09.202657</t>
-  </si>
-  <si>
-    <t>20.09.202658</t>
-  </si>
-  <si>
-    <t>20.09.202659</t>
-  </si>
-  <si>
-    <t>20.09.202660</t>
-  </si>
-  <si>
-    <t>20.09.202661</t>
-  </si>
-  <si>
-    <t>20.09.202662</t>
-  </si>
-  <si>
-    <t>20.09.202663</t>
-  </si>
-  <si>
-    <t>20.09.202664</t>
-  </si>
-  <si>
-    <t>20.09.202665</t>
-  </si>
-  <si>
-    <t>20.09.202666</t>
-  </si>
-  <si>
-    <t>20.09.202667</t>
-  </si>
-  <si>
-    <t>20.09.202668</t>
-  </si>
-  <si>
-    <t>20.09.202669</t>
-  </si>
-  <si>
-    <t>20.09.202670</t>
-  </si>
-  <si>
-    <t>20.09.202671</t>
-  </si>
-  <si>
-    <t>20.09.202672</t>
-  </si>
-  <si>
-    <t>20.09.202673</t>
-  </si>
-  <si>
-    <t>20.09.202674</t>
-  </si>
-  <si>
-    <t>20.09.202675</t>
-  </si>
-  <si>
-    <t>20.09.202676</t>
-  </si>
-  <si>
-    <t>20.09.202677</t>
-  </si>
-  <si>
-    <t>20.09.202678</t>
-  </si>
-  <si>
-    <t>20.09.202679</t>
-  </si>
-  <si>
-    <t>20.09.202680</t>
-  </si>
-  <si>
-    <t>20.09.202681</t>
-  </si>
-  <si>
-    <t>20.09.202682</t>
-  </si>
-  <si>
-    <t>20.09.202683</t>
-  </si>
-  <si>
-    <t>20.09.202684</t>
-  </si>
-  <si>
-    <t>20.09.202685</t>
-  </si>
-  <si>
-    <t>20.09.202686</t>
-  </si>
-  <si>
-    <t>20.09.202687</t>
-  </si>
-  <si>
-    <t>20.09.202688</t>
-  </si>
-  <si>
-    <t>20.09.202689</t>
-  </si>
-  <si>
-    <t>20.09.202690</t>
-  </si>
-  <si>
-    <t>20.09.202691</t>
-  </si>
-  <si>
-    <t>20.09.202692</t>
-  </si>
-  <si>
-    <t>20.09.202693</t>
-  </si>
-  <si>
-    <t>20.09.202694</t>
-  </si>
-  <si>
-    <t>20.09.202695</t>
-  </si>
-  <si>
-    <t>20.09.202696</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
+  </si>
+  <si>
+    <t>30.09.202640</t>
+  </si>
+  <si>
+    <t>30.09.202641</t>
+  </si>
+  <si>
+    <t>30.09.202642</t>
+  </si>
+  <si>
+    <t>30.09.202643</t>
+  </si>
+  <si>
+    <t>30.09.202644</t>
+  </si>
+  <si>
+    <t>30.09.202645</t>
+  </si>
+  <si>
+    <t>30.09.202646</t>
+  </si>
+  <si>
+    <t>30.09.202647</t>
+  </si>
+  <si>
+    <t>30.09.202648</t>
+  </si>
+  <si>
+    <t>30.09.202649</t>
+  </si>
+  <si>
+    <t>30.09.202650</t>
+  </si>
+  <si>
+    <t>30.09.202651</t>
+  </si>
+  <si>
+    <t>30.09.202652</t>
+  </si>
+  <si>
+    <t>30.09.202653</t>
+  </si>
+  <si>
+    <t>30.09.202654</t>
+  </si>
+  <si>
+    <t>30.09.202655</t>
+  </si>
+  <si>
+    <t>30.09.202656</t>
+  </si>
+  <si>
+    <t>30.09.202657</t>
+  </si>
+  <si>
+    <t>30.09.202658</t>
+  </si>
+  <si>
+    <t>30.09.202659</t>
+  </si>
+  <si>
+    <t>30.09.202660</t>
+  </si>
+  <si>
+    <t>30.09.202661</t>
+  </si>
+  <si>
+    <t>30.09.202662</t>
+  </si>
+  <si>
+    <t>30.09.202663</t>
+  </si>
+  <si>
+    <t>30.09.202664</t>
+  </si>
+  <si>
+    <t>30.09.202665</t>
+  </si>
+  <si>
+    <t>30.09.202666</t>
+  </si>
+  <si>
+    <t>30.09.202667</t>
+  </si>
+  <si>
+    <t>30.09.202668</t>
+  </si>
+  <si>
+    <t>30.09.202669</t>
+  </si>
+  <si>
+    <t>30.09.202670</t>
+  </si>
+  <si>
+    <t>30.09.202671</t>
+  </si>
+  <si>
+    <t>30.09.202672</t>
+  </si>
+  <si>
+    <t>30.09.202673</t>
+  </si>
+  <si>
+    <t>30.09.202674</t>
+  </si>
+  <si>
+    <t>30.09.202675</t>
+  </si>
+  <si>
+    <t>30.09.202676</t>
+  </si>
+  <si>
+    <t>30.09.202677</t>
+  </si>
+  <si>
+    <t>30.09.202678</t>
+  </si>
+  <si>
+    <t>30.09.202679</t>
+  </si>
+  <si>
+    <t>30.09.202680</t>
+  </si>
+  <si>
+    <t>30.09.202681</t>
+  </si>
+  <si>
+    <t>30.09.202682</t>
+  </si>
+  <si>
+    <t>30.09.202683</t>
+  </si>
+  <si>
+    <t>30.09.202684</t>
+  </si>
+  <si>
+    <t>30.09.202685</t>
+  </si>
+  <si>
+    <t>30.09.202686</t>
+  </si>
+  <si>
+    <t>30.09.202687</t>
+  </si>
+  <si>
+    <t>30.09.202688</t>
+  </si>
+  <si>
+    <t>30.09.202689</t>
+  </si>
+  <si>
+    <t>30.09.202690</t>
+  </si>
+  <si>
+    <t>30.09.202691</t>
+  </si>
+  <si>
+    <t>30.09.202692</t>
+  </si>
+  <si>
+    <t>30.09.202693</t>
+  </si>
+  <si>
+    <t>30.09.202694</t>
+  </si>
+  <si>
+    <t>30.09.202695</t>
+  </si>
+  <si>
+    <t>30.09.202696</t>
   </si>
 </sst>
 </file>
@@ -1282,16 +1282,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>383.906</v>
+        <v>204.406</v>
       </c>
       <c r="C2">
-        <v>383.906</v>
+        <v>204.406</v>
       </c>
       <c r="D2">
-        <v>21.613</v>
+        <v>39.851</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1302,16 +1302,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>447.299</v>
+        <v>261</v>
       </c>
       <c r="C3">
-        <v>447.299</v>
+        <v>261</v>
       </c>
       <c r="D3">
-        <v>7.92</v>
+        <v>17.854</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>445.216</v>
+        <v>262.022</v>
       </c>
       <c r="C4">
-        <v>445.216</v>
+        <v>262.022</v>
       </c>
       <c r="D4">
-        <v>24.917</v>
+        <v>20.834</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1342,16 +1342,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>415.256</v>
+        <v>1100</v>
       </c>
       <c r="C5">
-        <v>415.256</v>
+        <v>1100</v>
       </c>
       <c r="D5">
-        <v>27.56</v>
+        <v>-5.189</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>1196.456</v>
+        <v>1091.423</v>
       </c>
       <c r="C6">
-        <v>1196.456</v>
+        <v>1091.423</v>
       </c>
       <c r="D6">
-        <v>-3.922</v>
+        <v>-17.469</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1382,16 +1382,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>1196.219</v>
+        <v>1183.131</v>
       </c>
       <c r="C7">
-        <v>1196.219</v>
+        <v>1183.131</v>
       </c>
       <c r="D7">
-        <v>-1.854</v>
+        <v>-36.317</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1402,16 +1402,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>1208.649</v>
+        <v>1000</v>
       </c>
       <c r="C8">
-        <v>1208.649</v>
+        <v>1000</v>
       </c>
       <c r="D8">
-        <v>-22.079</v>
+        <v>-27.208</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1422,16 +1422,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>1195.602</v>
+        <v>1043.836</v>
       </c>
       <c r="C9">
-        <v>1195.602</v>
+        <v>1043.836</v>
       </c>
       <c r="D9">
-        <v>-13.442</v>
+        <v>-8.683999999999999</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
         <v>501</v>
@@ -1451,7 +1451,7 @@
         <v>501</v>
       </c>
       <c r="D10">
-        <v>15.668</v>
+        <v>6.811</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1462,16 +1462,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>1199.277</v>
+        <v>320.567</v>
       </c>
       <c r="C11">
-        <v>1199.277</v>
+        <v>320.567</v>
       </c>
       <c r="D11">
-        <v>-10.655</v>
+        <v>14.725</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1482,16 +1482,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>1192.892</v>
+        <v>280</v>
       </c>
       <c r="C12">
-        <v>1192.892</v>
+        <v>280</v>
       </c>
       <c r="D12">
-        <v>-1.219</v>
+        <v>10.933</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1502,16 +1502,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>1188.53</v>
+        <v>251.309</v>
       </c>
       <c r="C13">
-        <v>1188.53</v>
+        <v>251.309</v>
       </c>
       <c r="D13">
-        <v>-4.039</v>
+        <v>32.738</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1522,16 +1522,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>1189.035</v>
+        <v>318.632</v>
       </c>
       <c r="C14">
-        <v>1189.035</v>
+        <v>318.632</v>
       </c>
       <c r="D14">
-        <v>1.967</v>
+        <v>62.18</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1542,16 +1542,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>1271.148</v>
+        <v>481.322</v>
       </c>
       <c r="C15">
-        <v>1271.148</v>
+        <v>481.322</v>
       </c>
       <c r="D15">
-        <v>-18.248</v>
+        <v>62.041</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1562,16 +1562,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>2014.582</v>
+        <v>501</v>
       </c>
       <c r="C16">
-        <v>2014.582</v>
+        <v>501</v>
       </c>
       <c r="D16">
-        <v>-43.518</v>
+        <v>54.553</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1582,16 +1582,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>3448.448</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>3448.448</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>-37.437</v>
+        <v>77.396</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1602,16 +1602,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>1265.457</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1265.457</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>-15.516</v>
+        <v>101.631</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1622,16 +1622,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>1949.675</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>1949.675</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>-37.691</v>
+        <v>26.764</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>3414.41</v>
+        <v>501</v>
       </c>
       <c r="C20">
-        <v>3414.41</v>
+        <v>501</v>
       </c>
       <c r="D20">
-        <v>-41.808</v>
+        <v>10.77</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1662,16 +1662,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>2436.759</v>
+        <v>261.029</v>
       </c>
       <c r="C21">
-        <v>2436.759</v>
+        <v>261.029</v>
       </c>
       <c r="D21">
-        <v>-46.02</v>
+        <v>2.48</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1682,16 +1682,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>1488.739</v>
+        <v>501</v>
       </c>
       <c r="C22">
-        <v>1488.739</v>
+        <v>501</v>
       </c>
       <c r="D22">
-        <v>-67.742</v>
+        <v>18.654</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1702,16 +1702,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>3467.402</v>
+        <v>1083.313</v>
       </c>
       <c r="C23">
-        <v>3467.402</v>
+        <v>1083.313</v>
       </c>
       <c r="D23">
-        <v>-54.796</v>
+        <v>-22.519</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1722,16 +1722,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>1628.848</v>
+        <v>1285.806</v>
       </c>
       <c r="C24">
-        <v>1628.848</v>
+        <v>1285.806</v>
       </c>
       <c r="D24">
-        <v>-30.95</v>
+        <v>-19.038</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1742,16 +1742,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>1518.965</v>
+        <v>1416.599</v>
       </c>
       <c r="C25">
-        <v>1518.965</v>
+        <v>1416.599</v>
       </c>
       <c r="D25">
-        <v>-26.417</v>
+        <v>-23.443</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1762,16 +1762,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>1666.03</v>
+        <v>1616.526</v>
       </c>
       <c r="C26">
-        <v>1666.03</v>
+        <v>1616.526</v>
       </c>
       <c r="D26">
-        <v>-23.899</v>
+        <v>-6.428</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>1714.737</v>
+        <v>1678.886</v>
       </c>
       <c r="C27">
-        <v>1714.737</v>
+        <v>1678.886</v>
       </c>
       <c r="D27">
-        <v>-33.897</v>
+        <v>-28.95</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>1671.256</v>
+        <v>1556.085</v>
       </c>
       <c r="C28">
-        <v>1671.256</v>
+        <v>1556.085</v>
       </c>
       <c r="D28">
-        <v>-33.932</v>
+        <v>-27.948</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1822,16 +1822,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>1405.192</v>
+        <v>1492.206</v>
       </c>
       <c r="C29">
-        <v>1405.192</v>
+        <v>1492.206</v>
       </c>
       <c r="D29">
-        <v>1.212</v>
+        <v>-5.702</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1842,16 +1842,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>6369.259</v>
+        <v>1552.917</v>
       </c>
       <c r="C30">
-        <v>6369.259</v>
+        <v>1552.917</v>
       </c>
       <c r="D30">
-        <v>-80.423</v>
+        <v>-7.481</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1862,16 +1862,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>6999</v>
+        <v>501</v>
       </c>
       <c r="C31">
-        <v>6999</v>
+        <v>501</v>
       </c>
       <c r="D31">
-        <v>-125.322</v>
+        <v>30.193</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1882,16 +1882,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>3177.23</v>
+        <v>491.421</v>
       </c>
       <c r="C32">
-        <v>3177.23</v>
+        <v>491.421</v>
       </c>
       <c r="D32">
-        <v>-95.38</v>
+        <v>68.18899999999999</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1902,16 +1902,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>147.935</v>
+        <v>339.1</v>
       </c>
       <c r="C33">
-        <v>147.935</v>
+        <v>339.1</v>
       </c>
       <c r="D33">
-        <v>7.991</v>
+        <v>170.88</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1922,16 +1922,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>1541.788</v>
+        <v>245.069</v>
       </c>
       <c r="C34">
-        <v>1541.788</v>
+        <v>245.069</v>
       </c>
       <c r="D34">
-        <v>-10.689</v>
+        <v>152.052</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1942,16 +1942,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>459.967</v>
+        <v>-121.75</v>
       </c>
       <c r="C35">
-        <v>459.967</v>
+        <v>-121.75</v>
       </c>
       <c r="D35">
-        <v>35.071</v>
+        <v>142.146</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1962,16 +1962,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>330.253</v>
+        <v>-65.167</v>
       </c>
       <c r="C36">
-        <v>330.253</v>
+        <v>-65.167</v>
       </c>
       <c r="D36">
-        <v>10.701</v>
+        <v>101.716</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1982,16 +1982,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>1214.64</v>
+        <v>-75.062</v>
       </c>
       <c r="C37">
-        <v>1214.64</v>
+        <v>-75.062</v>
       </c>
       <c r="D37">
-        <v>-26.875</v>
+        <v>162.57</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -2002,16 +2002,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>1217.488</v>
+        <v>-94.93899999999999</v>
       </c>
       <c r="C38">
-        <v>1217.488</v>
+        <v>-94.93899999999999</v>
       </c>
       <c r="D38">
-        <v>-22.958</v>
+        <v>143.942</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -2022,16 +2022,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>1149.492</v>
+        <v>-212.048</v>
       </c>
       <c r="C39">
-        <v>1149.492</v>
+        <v>-212.048</v>
       </c>
       <c r="D39">
-        <v>-12.807</v>
+        <v>88.148</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -2042,16 +2042,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>1427.021</v>
+        <v>-227.264</v>
       </c>
       <c r="C40">
-        <v>1427.021</v>
+        <v>-227.264</v>
       </c>
       <c r="D40">
-        <v>-50.351</v>
+        <v>84.089</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -2062,16 +2062,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>699</v>
+        <v>-186.934</v>
       </c>
       <c r="C41">
-        <v>699</v>
+        <v>-186.934</v>
       </c>
       <c r="D41">
-        <v>-33.057</v>
+        <v>100.098</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -2082,16 +2082,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-254.299</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>-254.299</v>
       </c>
       <c r="D42">
-        <v>-107.075</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -2102,16 +2102,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>-275.864</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>-275.864</v>
       </c>
       <c r="D43">
-        <v>-60.103</v>
+        <v>94.92100000000001</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -2122,16 +2122,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>981.587</v>
+        <v>-257.042</v>
       </c>
       <c r="C44">
-        <v>981.587</v>
+        <v>-257.042</v>
       </c>
       <c r="D44">
-        <v>-32.08</v>
+        <v>108.504</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -2142,16 +2142,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>976.772</v>
+        <v>-234.809</v>
       </c>
       <c r="C45">
-        <v>976.772</v>
+        <v>-234.809</v>
       </c>
       <c r="D45">
-        <v>-49.871</v>
+        <v>127.97</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>201.109</v>
+        <v>-264.099</v>
       </c>
       <c r="C46">
-        <v>201.109</v>
+        <v>-264.099</v>
       </c>
       <c r="D46">
-        <v>10.098</v>
+        <v>107.485</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2182,16 +2182,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>87.065</v>
+        <v>-280.884</v>
       </c>
       <c r="C47">
-        <v>87.065</v>
+        <v>-280.884</v>
       </c>
       <c r="D47">
-        <v>31.188</v>
+        <v>84.587</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2202,16 +2202,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>-5.828</v>
+        <v>-267.697</v>
       </c>
       <c r="C48">
-        <v>-5.828</v>
+        <v>-267.697</v>
       </c>
       <c r="D48">
-        <v>79.872</v>
+        <v>88.947</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2222,16 +2222,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>31.627</v>
+        <v>-252.31</v>
       </c>
       <c r="C49">
-        <v>31.627</v>
+        <v>-252.31</v>
       </c>
       <c r="D49">
-        <v>37.169</v>
+        <v>105.148</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>3.447</v>
+        <v>-278.033</v>
       </c>
       <c r="C50">
-        <v>3.447</v>
+        <v>-278.033</v>
       </c>
       <c r="D50">
-        <v>45.594</v>
+        <v>87.95699999999999</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2262,16 +2262,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>-2236.088</v>
+        <v>-290</v>
       </c>
       <c r="C51">
-        <v>-2236.088</v>
+        <v>-290</v>
       </c>
       <c r="D51">
-        <v>86.806</v>
+        <v>73.68600000000001</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2282,16 +2282,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>-5890.837</v>
+        <v>-61.996</v>
       </c>
       <c r="C52">
-        <v>-5890.837</v>
+        <v>-61.996</v>
       </c>
       <c r="D52">
-        <v>78.578</v>
+        <v>71.351</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2302,16 +2302,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>10.496</v>
+        <v>189.275</v>
       </c>
       <c r="C53">
-        <v>10.496</v>
+        <v>189.275</v>
       </c>
       <c r="D53">
-        <v>8.209</v>
+        <v>94.038</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2322,16 +2322,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>775.49</v>
+        <v>-73.69499999999999</v>
       </c>
       <c r="C54">
-        <v>775.49</v>
+        <v>-73.69499999999999</v>
       </c>
       <c r="D54">
-        <v>-109.763</v>
+        <v>79.023</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2342,16 +2342,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>650</v>
+        <v>-97.467</v>
       </c>
       <c r="C55">
-        <v>650</v>
+        <v>-97.467</v>
       </c>
       <c r="D55">
-        <v>-6.546</v>
+        <v>52.551</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2362,16 +2362,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>664.848</v>
+        <v>-79.377</v>
       </c>
       <c r="C56">
-        <v>664.848</v>
+        <v>-79.377</v>
       </c>
       <c r="D56">
-        <v>-7.059</v>
+        <v>106.184</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2382,16 +2382,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>478.155</v>
+        <v>-90.277</v>
       </c>
       <c r="C57">
-        <v>478.155</v>
+        <v>-90.277</v>
       </c>
       <c r="D57">
-        <v>-11.47</v>
+        <v>66.696</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2402,16 +2402,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>500</v>
+        <v>-1182.508</v>
       </c>
       <c r="C58">
-        <v>500</v>
+        <v>-1182.508</v>
       </c>
       <c r="D58">
-        <v>-24.52</v>
+        <v>91.86199999999999</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2422,16 +2422,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>633.806</v>
+        <v>-71.462</v>
       </c>
       <c r="C59">
-        <v>633.806</v>
+        <v>-71.462</v>
       </c>
       <c r="D59">
-        <v>-0.413</v>
+        <v>103.546</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2442,16 +2442,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>251</v>
+        <v>-87</v>
       </c>
       <c r="C60">
-        <v>251</v>
+        <v>-87</v>
       </c>
       <c r="D60">
-        <v>7.377</v>
+        <v>43.843</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2462,16 +2462,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>72.702</v>
+        <v>145.406</v>
       </c>
       <c r="C61">
-        <v>72.702</v>
+        <v>145.406</v>
       </c>
       <c r="D61">
-        <v>22.084</v>
+        <v>69.175</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2482,16 +2482,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>203.308</v>
+        <v>61.255</v>
       </c>
       <c r="C62">
-        <v>203.308</v>
+        <v>61.255</v>
       </c>
       <c r="D62">
-        <v>12.63</v>
+        <v>60.254</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2502,16 +2502,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>600</v>
+        <v>206.82</v>
       </c>
       <c r="C63">
-        <v>600</v>
+        <v>206.82</v>
       </c>
       <c r="D63">
-        <v>-3.439</v>
+        <v>34.22</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2522,16 +2522,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>94.095</v>
+        <v>1989.689</v>
       </c>
       <c r="C64">
-        <v>94.095</v>
+        <v>1989.689</v>
       </c>
       <c r="D64">
-        <v>26.99</v>
+        <v>-45.036</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2542,16 +2542,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>630.242</v>
+        <v>1217.382</v>
       </c>
       <c r="C65">
-        <v>630.242</v>
+        <v>1217.382</v>
       </c>
       <c r="D65">
-        <v>-11.206</v>
+        <v>-41.644</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2562,16 +2562,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>992.096</v>
+        <v>1568.28</v>
       </c>
       <c r="C66">
-        <v>992.096</v>
+        <v>1568.28</v>
       </c>
       <c r="D66">
-        <v>-8.833</v>
+        <v>-32.305</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>984.769</v>
+        <v>1592.927</v>
       </c>
       <c r="C67">
-        <v>984.769</v>
+        <v>1592.927</v>
       </c>
       <c r="D67">
-        <v>-26.635</v>
+        <v>-31.548</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2602,16 +2602,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>1538.825</v>
+        <v>2113.135</v>
       </c>
       <c r="C68">
-        <v>1538.825</v>
+        <v>2113.135</v>
       </c>
       <c r="D68">
-        <v>-26.436</v>
+        <v>-24.434</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2622,16 +2622,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>1701.55</v>
+        <v>4082.985</v>
       </c>
       <c r="C69">
-        <v>1701.55</v>
+        <v>4082.985</v>
       </c>
       <c r="D69">
-        <v>-32.919</v>
+        <v>-40.294</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2642,16 +2642,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>1795.93</v>
+        <v>501</v>
       </c>
       <c r="C70">
-        <v>1795.93</v>
+        <v>501</v>
       </c>
       <c r="D70">
-        <v>6.094</v>
+        <v>82.953</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>1893.672</v>
+        <v>368.083</v>
       </c>
       <c r="C71">
-        <v>1893.672</v>
+        <v>368.083</v>
       </c>
       <c r="D71">
-        <v>-52.454</v>
+        <v>50.729</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2682,16 +2682,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>1659.481</v>
+        <v>501</v>
       </c>
       <c r="C72">
-        <v>1659.481</v>
+        <v>501</v>
       </c>
       <c r="D72">
-        <v>-50.59</v>
+        <v>9.884</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>1716.927</v>
+        <v>1532.835</v>
       </c>
       <c r="C73">
-        <v>1716.927</v>
+        <v>1532.835</v>
       </c>
       <c r="D73">
-        <v>-67.756</v>
+        <v>-7.159</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2722,16 +2722,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>1378.875</v>
+        <v>2124.455</v>
       </c>
       <c r="C74">
-        <v>1378.875</v>
+        <v>2124.455</v>
       </c>
       <c r="D74">
-        <v>-26.493</v>
+        <v>-33.804</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2742,16 +2742,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>1724.197</v>
+        <v>2218.418</v>
       </c>
       <c r="C75">
-        <v>1724.197</v>
+        <v>2218.418</v>
       </c>
       <c r="D75">
-        <v>-16.061</v>
+        <v>-29.186</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2762,16 +2762,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>1673.842</v>
+        <v>2408.923</v>
       </c>
       <c r="C76">
-        <v>1673.842</v>
+        <v>2408.923</v>
       </c>
       <c r="D76">
-        <v>-35.202</v>
+        <v>-33.91</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2782,16 +2782,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>504.596</v>
+        <v>2018.034</v>
       </c>
       <c r="C77">
-        <v>504.596</v>
+        <v>2018.034</v>
       </c>
       <c r="D77">
-        <v>9.933</v>
+        <v>-6.233</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2802,16 +2802,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>522</v>
+        <v>1639.428</v>
       </c>
       <c r="C78">
-        <v>522</v>
+        <v>1639.428</v>
       </c>
       <c r="D78">
-        <v>1.208</v>
+        <v>-3.003</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2822,16 +2822,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>504.267</v>
+        <v>1584.231</v>
       </c>
       <c r="C79">
-        <v>504.267</v>
+        <v>1584.231</v>
       </c>
       <c r="D79">
-        <v>30.904</v>
+        <v>-0.193</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2842,16 +2842,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>510.744</v>
+        <v>567.308</v>
       </c>
       <c r="C80">
-        <v>510.744</v>
+        <v>567.308</v>
       </c>
       <c r="D80">
-        <v>42.637</v>
+        <v>21.163</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2862,16 +2862,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>515.244</v>
+        <v>506.262</v>
       </c>
       <c r="C81">
-        <v>515.244</v>
+        <v>506.262</v>
       </c>
       <c r="D81">
-        <v>57.399</v>
+        <v>30.681</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2882,16 +2882,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>507.629</v>
+        <v>580.097</v>
       </c>
       <c r="C82">
-        <v>507.629</v>
+        <v>580.097</v>
       </c>
       <c r="D82">
-        <v>56.801</v>
+        <v>10.45</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2902,16 +2902,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>503.331</v>
+        <v>2207.333</v>
       </c>
       <c r="C83">
-        <v>503.331</v>
+        <v>2207.333</v>
       </c>
       <c r="D83">
-        <v>30.452</v>
+        <v>-1.779</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2922,16 +2922,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>501.111</v>
+        <v>614.313</v>
       </c>
       <c r="C84">
-        <v>501.111</v>
+        <v>614.313</v>
       </c>
       <c r="D84">
-        <v>9.763999999999999</v>
+        <v>16.985</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2942,16 +2942,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>1000</v>
+        <v>473.66</v>
       </c>
       <c r="C85">
-        <v>1000</v>
+        <v>473.66</v>
       </c>
       <c r="D85">
-        <v>-21.972</v>
+        <v>0.246</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2962,16 +2962,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>1860.526</v>
+        <v>1000</v>
       </c>
       <c r="C86">
-        <v>1860.526</v>
+        <v>1000</v>
       </c>
       <c r="D86">
-        <v>-33.979</v>
+        <v>-17.556</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2982,16 +2982,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>1617.253</v>
+        <v>320.865</v>
       </c>
       <c r="C87">
-        <v>1617.253</v>
+        <v>320.865</v>
       </c>
       <c r="D87">
-        <v>-37.758</v>
+        <v>8.227</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -3002,16 +3002,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>1601.5</v>
+        <v>334.093</v>
       </c>
       <c r="C88">
-        <v>1601.5</v>
+        <v>334.093</v>
       </c>
       <c r="D88">
-        <v>-36.077</v>
+        <v>32.149</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -3022,16 +3022,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>1617.424</v>
+        <v>-1550.257</v>
       </c>
       <c r="C89">
-        <v>1617.424</v>
+        <v>-1550.257</v>
       </c>
       <c r="D89">
-        <v>-40.412</v>
+        <v>40.223</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -3042,16 +3042,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>1225.127</v>
+        <v>-1268.241</v>
       </c>
       <c r="C90">
-        <v>1225.127</v>
+        <v>-1268.241</v>
       </c>
       <c r="D90">
-        <v>-43.363</v>
+        <v>23.741</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -3062,16 +3062,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>1627.378</v>
+        <v>309.245</v>
       </c>
       <c r="C91">
-        <v>1627.378</v>
+        <v>309.245</v>
       </c>
       <c r="D91">
-        <v>-39.514</v>
+        <v>15.445</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -3082,16 +3082,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>1696.313</v>
+        <v>268.481</v>
       </c>
       <c r="C92">
-        <v>1696.313</v>
+        <v>268.481</v>
       </c>
       <c r="D92">
-        <v>-45.85</v>
+        <v>13.862</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -3102,16 +3102,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>1623.276</v>
+        <v>312.504</v>
       </c>
       <c r="C93">
-        <v>1623.276</v>
+        <v>312.504</v>
       </c>
       <c r="D93">
-        <v>-45.121</v>
+        <v>5.312</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -3122,16 +3122,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>6821.961</v>
+        <v>325.486</v>
       </c>
       <c r="C94">
-        <v>6821.961</v>
+        <v>325.486</v>
       </c>
       <c r="D94">
-        <v>-76.867</v>
+        <v>7.918</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -3142,16 +3142,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>6999</v>
+        <v>430.377</v>
       </c>
       <c r="C95">
-        <v>6999</v>
+        <v>430.377</v>
       </c>
       <c r="D95">
-        <v>-87.64</v>
+        <v>3.777</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>2327.909</v>
+        <v>435.302</v>
       </c>
       <c r="C96">
-        <v>2327.909</v>
+        <v>435.302</v>
       </c>
       <c r="D96">
-        <v>-84.176</v>
+        <v>0.848</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3182,16 +3182,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>1583.141</v>
+        <v>999</v>
       </c>
       <c r="C97">
-        <v>1583.141</v>
+        <v>999</v>
       </c>
       <c r="D97">
-        <v>-31.675</v>
+        <v>-15.8</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3202,16 +3202,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>1597.647</v>
+        <v>1021.862</v>
       </c>
       <c r="C98">
-        <v>1597.647</v>
+        <v>1021.862</v>
       </c>
       <c r="D98">
-        <v>-16.039</v>
+        <v>-15.195</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>700</v>
+        <v>1186.244</v>
       </c>
       <c r="C99">
-        <v>700</v>
+        <v>1186.244</v>
       </c>
       <c r="D99">
-        <v>13.225</v>
+        <v>-14.29</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3242,16 +3242,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>1424.795</v>
+        <v>1184.049</v>
       </c>
       <c r="C100">
-        <v>1424.795</v>
+        <v>1184.049</v>
       </c>
       <c r="D100">
-        <v>-23.48</v>
+        <v>-4.988</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3262,16 +3262,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>644.49</v>
+        <v>446.114</v>
       </c>
       <c r="C101">
-        <v>644.49</v>
+        <v>446.114</v>
       </c>
       <c r="D101">
-        <v>6.564</v>
+        <v>9.766999999999999</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3282,16 +3282,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>700</v>
+        <v>437.144</v>
       </c>
       <c r="C102">
-        <v>700</v>
+        <v>437.144</v>
       </c>
       <c r="D102">
-        <v>17.193</v>
+        <v>10.184</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3302,16 +3302,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>581.25</v>
+        <v>1135.207</v>
       </c>
       <c r="C103">
-        <v>581.25</v>
+        <v>1135.207</v>
       </c>
       <c r="D103">
-        <v>4.377</v>
+        <v>-12.836</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3322,16 +3322,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>700</v>
+        <v>1094.071</v>
       </c>
       <c r="C104">
-        <v>700</v>
+        <v>1094.071</v>
       </c>
       <c r="D104">
-        <v>9.286</v>
+        <v>-3.514</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>1186.918</v>
+        <v>477.836</v>
       </c>
       <c r="C105">
-        <v>1186.918</v>
+        <v>477.836</v>
       </c>
       <c r="D105">
-        <v>-1.003</v>
+        <v>20.968</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3362,16 +3362,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>700</v>
+        <v>1197.17</v>
       </c>
       <c r="C106">
-        <v>700</v>
+        <v>1197.17</v>
       </c>
       <c r="D106">
-        <v>33.071</v>
+        <v>-9.686</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3382,16 +3382,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1176.573</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1176.573</v>
       </c>
       <c r="D107">
-        <v>10.509</v>
+        <v>-1.85</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3402,16 +3402,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>685.8819999999999</v>
+        <v>577.732</v>
       </c>
       <c r="C108">
-        <v>685.8819999999999</v>
+        <v>577.732</v>
       </c>
       <c r="D108">
-        <v>10.725</v>
+        <v>-6.855</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3422,16 +3422,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>700</v>
+        <v>352.809</v>
       </c>
       <c r="C109">
-        <v>700</v>
+        <v>352.809</v>
       </c>
       <c r="D109">
-        <v>7.918</v>
+        <v>-16.864</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3442,16 +3442,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>502.752</v>
+        <v>1196.477</v>
       </c>
       <c r="C110">
-        <v>502.752</v>
+        <v>1196.477</v>
       </c>
       <c r="D110">
-        <v>10.183</v>
+        <v>-23.913</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>520.811</v>
+        <v>1326.679</v>
       </c>
       <c r="C111">
-        <v>520.811</v>
+        <v>1326.679</v>
       </c>
       <c r="D111">
-        <v>6.246</v>
+        <v>-12.681</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3482,16 +3482,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>517.024</v>
+        <v>1455.426</v>
       </c>
       <c r="C112">
-        <v>517.024</v>
+        <v>1455.426</v>
       </c>
       <c r="D112">
-        <v>10.022</v>
+        <v>-25.659</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3502,16 +3502,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>1126.904</v>
+        <v>501</v>
       </c>
       <c r="C113">
-        <v>1126.904</v>
+        <v>501</v>
       </c>
       <c r="D113">
-        <v>-6.028</v>
+        <v>12.831</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3522,16 +3522,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>-14.602</v>
+        <v>20.735</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3542,16 +3542,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>1205.084</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>1205.084</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>-2.936</v>
+        <v>9.337999999999999</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3562,16 +3562,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>1199.056</v>
+        <v>1235.131</v>
       </c>
       <c r="C116">
-        <v>1199.056</v>
+        <v>1235.131</v>
       </c>
       <c r="D116">
-        <v>-4.756</v>
+        <v>-16.062</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3582,16 +3582,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>1179.481</v>
+        <v>501</v>
       </c>
       <c r="C117">
-        <v>1179.481</v>
+        <v>501</v>
       </c>
       <c r="D117">
-        <v>-1.082</v>
+        <v>5.304</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3602,16 +3602,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>1165.999</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1165.999</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>-23.465</v>
+        <v>40.591</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>1485.165</v>
+        <v>1186.894</v>
       </c>
       <c r="C119">
-        <v>1485.165</v>
+        <v>1186.894</v>
       </c>
       <c r="D119">
-        <v>-43.071</v>
+        <v>-2.83</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3642,16 +3642,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>1414.536</v>
+        <v>1381.732</v>
       </c>
       <c r="C120">
-        <v>1414.536</v>
+        <v>1381.732</v>
       </c>
       <c r="D120">
-        <v>-33.915</v>
+        <v>-25.774</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3662,16 +3662,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>1324.15</v>
+        <v>1446.135</v>
       </c>
       <c r="C121">
-        <v>1324.15</v>
+        <v>1446.135</v>
       </c>
       <c r="D121">
-        <v>-31.444</v>
+        <v>-10.609</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>1221.968</v>
+        <v>1591.451</v>
       </c>
       <c r="C122">
-        <v>1221.968</v>
+        <v>1591.451</v>
       </c>
       <c r="D122">
-        <v>-10.494</v>
+        <v>-2.55</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3702,16 +3702,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>1204.057</v>
+        <v>1629.024</v>
       </c>
       <c r="C123">
-        <v>1204.057</v>
+        <v>1629.024</v>
       </c>
       <c r="D123">
-        <v>-8.313000000000001</v>
+        <v>-38.819</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3722,16 +3722,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>1197.869</v>
+        <v>1739.29</v>
       </c>
       <c r="C124">
-        <v>1197.869</v>
+        <v>1739.29</v>
       </c>
       <c r="D124">
-        <v>-22.471</v>
+        <v>-50.671</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3742,16 +3742,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>375.251</v>
+        <v>1677.504</v>
       </c>
       <c r="C125">
-        <v>375.251</v>
+        <v>1677.504</v>
       </c>
       <c r="D125">
-        <v>1.53</v>
+        <v>-48.724</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3762,16 +3762,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>1445.356</v>
+        <v>2324.027</v>
       </c>
       <c r="C126">
-        <v>1445.356</v>
+        <v>2324.027</v>
       </c>
       <c r="D126">
-        <v>-43.736</v>
+        <v>-48.677</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>1108.835</v>
+        <v>5051.227</v>
       </c>
       <c r="C127">
-        <v>1108.835</v>
+        <v>5051.227</v>
       </c>
       <c r="D127">
-        <v>-63.984</v>
+        <v>-45.565</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3802,16 +3802,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>1166.912</v>
+        <v>1130.792</v>
       </c>
       <c r="C128">
-        <v>1166.912</v>
+        <v>1130.792</v>
       </c>
       <c r="D128">
-        <v>-25.78</v>
+        <v>-3.891</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3822,16 +3822,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>1146.104</v>
+        <v>357.621</v>
       </c>
       <c r="C129">
-        <v>1146.104</v>
+        <v>357.621</v>
       </c>
       <c r="D129">
-        <v>-8.695</v>
+        <v>41.817</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3842,16 +3842,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>1380.76</v>
+        <v>500.897</v>
       </c>
       <c r="C130">
-        <v>1380.76</v>
+        <v>500.897</v>
       </c>
       <c r="D130">
-        <v>-66.541</v>
+        <v>40.698</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3862,16 +3862,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>1103.217</v>
+        <v>275.952</v>
       </c>
       <c r="C131">
-        <v>1103.217</v>
+        <v>275.952</v>
       </c>
       <c r="D131">
-        <v>-40.774</v>
+        <v>56.73</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3882,16 +3882,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>1316.674</v>
+        <v>197.046</v>
       </c>
       <c r="C132">
-        <v>1316.674</v>
+        <v>197.046</v>
       </c>
       <c r="D132">
-        <v>-41.162</v>
+        <v>26.725</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3902,16 +3902,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>1000</v>
+        <v>292.295</v>
       </c>
       <c r="C133">
-        <v>1000</v>
+        <v>292.295</v>
       </c>
       <c r="D133">
-        <v>-8.116</v>
+        <v>120.332</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3922,16 +3922,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>218.729</v>
+        <v>261.241</v>
       </c>
       <c r="C134">
-        <v>218.729</v>
+        <v>261.241</v>
       </c>
       <c r="D134">
-        <v>26.546</v>
+        <v>66.489</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3942,16 +3942,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>808.353</v>
+        <v>261.055</v>
       </c>
       <c r="C135">
-        <v>808.353</v>
+        <v>261.055</v>
       </c>
       <c r="D135">
-        <v>-7.961</v>
+        <v>26.369</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3962,16 +3962,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>700</v>
+        <v>261.047</v>
       </c>
       <c r="C136">
-        <v>700</v>
+        <v>261.047</v>
       </c>
       <c r="D136">
-        <v>-0.965</v>
+        <v>32.734</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3982,16 +3982,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>146.067</v>
+        <v>360</v>
       </c>
       <c r="C137">
-        <v>146.067</v>
+        <v>360</v>
       </c>
       <c r="D137">
-        <v>9.952</v>
+        <v>123.811</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -4002,16 +4002,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>136.929</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>136.929</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>39.606</v>
+        <v>62.098</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>157.147</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>157.147</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>19.72</v>
+        <v>54.869</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -4042,16 +4042,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>600</v>
+        <v>79.467</v>
       </c>
       <c r="C140">
-        <v>600</v>
+        <v>79.467</v>
       </c>
       <c r="D140">
-        <v>-0.042</v>
+        <v>162.999</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -4062,16 +4062,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
-        <v>46.135</v>
+        <v>205.022</v>
       </c>
       <c r="C141">
-        <v>46.135</v>
+        <v>205.022</v>
       </c>
       <c r="D141">
-        <v>20.398</v>
+        <v>85.514</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -4082,16 +4082,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>81.952</v>
+        <v>74.245</v>
       </c>
       <c r="C142">
-        <v>81.952</v>
+        <v>74.245</v>
       </c>
       <c r="D142">
-        <v>15.626</v>
+        <v>77.163</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -4102,16 +4102,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>220.624</v>
+        <v>26.693</v>
       </c>
       <c r="C143">
-        <v>220.624</v>
+        <v>26.693</v>
       </c>
       <c r="D143">
-        <v>11.654</v>
+        <v>80.645</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -4122,16 +4122,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>222.433</v>
+        <v>15.221</v>
       </c>
       <c r="C144">
-        <v>222.433</v>
+        <v>15.221</v>
       </c>
       <c r="D144">
-        <v>24.809</v>
+        <v>141.354</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -4142,16 +4142,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>238.131</v>
+        <v>17.584</v>
       </c>
       <c r="C145">
-        <v>238.131</v>
+        <v>17.584</v>
       </c>
       <c r="D145">
-        <v>8.81</v>
+        <v>143.422</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -4162,16 +4162,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>144.734</v>
+        <v>4.176</v>
       </c>
       <c r="C146">
-        <v>144.734</v>
+        <v>4.176</v>
       </c>
       <c r="D146">
-        <v>19.109</v>
+        <v>132.788</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4182,16 +4182,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>197.344</v>
+        <v>52.348</v>
       </c>
       <c r="C147">
-        <v>197.344</v>
+        <v>52.348</v>
       </c>
       <c r="D147">
-        <v>47.531</v>
+        <v>67.754</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4202,16 +4202,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>251</v>
+        <v>13.383</v>
       </c>
       <c r="C148">
-        <v>251</v>
+        <v>13.383</v>
       </c>
       <c r="D148">
-        <v>24.003</v>
+        <v>114.844</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4222,16 +4222,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>453.409</v>
+        <v>9.859</v>
       </c>
       <c r="C149">
-        <v>453.409</v>
+        <v>9.859</v>
       </c>
       <c r="D149">
-        <v>-13.803</v>
+        <v>21.108</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4242,16 +4242,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>738.972</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>738.972</v>
+        <v>2</v>
       </c>
       <c r="D150">
-        <v>-18.307</v>
+        <v>32.048</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4262,16 +4262,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>828.376</v>
+        <v>201.278</v>
       </c>
       <c r="C151">
-        <v>828.376</v>
+        <v>201.278</v>
       </c>
       <c r="D151">
-        <v>-13.511</v>
+        <v>82.315</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4282,16 +4282,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>251</v>
+        <v>201.68</v>
       </c>
       <c r="C152">
-        <v>251</v>
+        <v>201.68</v>
       </c>
       <c r="D152">
-        <v>43.506</v>
+        <v>133.037</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4302,16 +4302,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>182.771</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>182.771</v>
       </c>
       <c r="D153">
-        <v>47.576</v>
+        <v>97.991</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4322,16 +4322,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>208.649</v>
+        <v>-2234.168</v>
       </c>
       <c r="C154">
-        <v>208.649</v>
+        <v>-2234.168</v>
       </c>
       <c r="D154">
-        <v>10.522</v>
+        <v>118.295</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4342,16 +4342,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>89.045</v>
+        <v>202.183</v>
       </c>
       <c r="C155">
-        <v>89.045</v>
+        <v>202.183</v>
       </c>
       <c r="D155">
-        <v>53.483</v>
+        <v>80.34399999999999</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4362,16 +4362,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>26.909</v>
+        <v>203.521</v>
       </c>
       <c r="C156">
-        <v>26.909</v>
+        <v>203.521</v>
       </c>
       <c r="D156">
-        <v>25.323</v>
+        <v>63.333</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4382,16 +4382,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>-6.131</v>
+        <v>202.02</v>
       </c>
       <c r="C157">
-        <v>-6.131</v>
+        <v>202.02</v>
       </c>
       <c r="D157">
-        <v>34.897</v>
+        <v>45.716</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>-83.70999999999999</v>
+        <v>-945.2619999999999</v>
       </c>
       <c r="C158">
-        <v>-83.70999999999999</v>
+        <v>-945.2619999999999</v>
       </c>
       <c r="D158">
-        <v>82.402</v>
+        <v>92.879</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4422,16 +4422,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>-2464.559</v>
+        <v>199.883</v>
       </c>
       <c r="C159">
-        <v>-2464.559</v>
+        <v>199.883</v>
       </c>
       <c r="D159">
-        <v>38.806</v>
+        <v>98.203</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4442,16 +4442,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>-63.295</v>
+        <v>188.746</v>
       </c>
       <c r="C160">
-        <v>-63.295</v>
+        <v>188.746</v>
       </c>
       <c r="D160">
-        <v>72.438</v>
+        <v>98.342</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4462,16 +4462,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>-291.314</v>
+        <v>201.171</v>
       </c>
       <c r="C161">
-        <v>-291.314</v>
+        <v>201.171</v>
       </c>
       <c r="D161">
-        <v>98.459</v>
+        <v>38.438</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4482,16 +4482,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>-87.46599999999999</v>
+        <v>1348.567</v>
       </c>
       <c r="C162">
-        <v>-87.46599999999999</v>
+        <v>1348.567</v>
       </c>
       <c r="D162">
-        <v>57.849</v>
+        <v>-54.599</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4502,16 +4502,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>-446.646</v>
+        <v>2774.972</v>
       </c>
       <c r="C163">
-        <v>-446.646</v>
+        <v>2774.972</v>
       </c>
       <c r="D163">
-        <v>54.59</v>
+        <v>-70.148</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4522,16 +4522,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>362</v>
+        <v>5644.058</v>
       </c>
       <c r="C164">
-        <v>362</v>
+        <v>5644.058</v>
       </c>
       <c r="D164">
-        <v>54.372</v>
+        <v>-64.934</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4542,16 +4542,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>1580.278</v>
+        <v>2676.904</v>
       </c>
       <c r="C165">
-        <v>1580.278</v>
+        <v>2676.904</v>
       </c>
       <c r="D165">
-        <v>-13.094</v>
+        <v>-110.235</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4562,16 +4562,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>1701.612</v>
+        <v>2155.103</v>
       </c>
       <c r="C166">
-        <v>1701.612</v>
+        <v>2155.103</v>
       </c>
       <c r="D166">
-        <v>-15.777</v>
+        <v>-180.169</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4582,16 +4582,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>2113.422</v>
+        <v>2568.742</v>
       </c>
       <c r="C167">
-        <v>2113.422</v>
+        <v>2568.742</v>
       </c>
       <c r="D167">
-        <v>-46.058</v>
+        <v>-155.306</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4602,16 +4602,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>3913.008</v>
+        <v>1787.788</v>
       </c>
       <c r="C168">
-        <v>3913.008</v>
+        <v>1787.788</v>
       </c>
       <c r="D168">
-        <v>-65.59099999999999</v>
+        <v>-181.23</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4622,16 +4622,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>2433.978</v>
+        <v>1595.783</v>
       </c>
       <c r="C169">
-        <v>2433.978</v>
+        <v>1595.783</v>
       </c>
       <c r="D169">
-        <v>-55.909</v>
+        <v>-145.281</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4642,16 +4642,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>1792.997</v>
+        <v>1692.629</v>
       </c>
       <c r="C170">
-        <v>1792.997</v>
+        <v>1692.629</v>
       </c>
       <c r="D170">
-        <v>-25.061</v>
+        <v>-60.514</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4662,16 +4662,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>1844.747</v>
+        <v>1692.373</v>
       </c>
       <c r="C171">
-        <v>1844.747</v>
+        <v>1692.373</v>
       </c>
       <c r="D171">
-        <v>-19.047</v>
+        <v>-96.726</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4682,16 +4682,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>1743.95</v>
+        <v>1693.345</v>
       </c>
       <c r="C172">
-        <v>1743.95</v>
+        <v>1693.345</v>
       </c>
       <c r="D172">
-        <v>5.877</v>
+        <v>-47.878</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4702,16 +4702,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>1750.741</v>
+        <v>1692.179</v>
       </c>
       <c r="C173">
-        <v>1750.741</v>
+        <v>1692.179</v>
       </c>
       <c r="D173">
-        <v>-23.848</v>
+        <v>-61.677</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4722,16 +4722,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>1476.728</v>
+        <v>1758.22</v>
       </c>
       <c r="C174">
-        <v>1476.728</v>
+        <v>1758.22</v>
       </c>
       <c r="D174">
-        <v>-10.72</v>
+        <v>-91.79300000000001</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4742,16 +4742,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>501.315</v>
+        <v>1761.018</v>
       </c>
       <c r="C175">
-        <v>501.315</v>
+        <v>1761.018</v>
       </c>
       <c r="D175">
-        <v>26.181</v>
+        <v>-37.987</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4762,16 +4762,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>536.312</v>
+        <v>1761.16</v>
       </c>
       <c r="C176">
-        <v>536.312</v>
+        <v>1761.16</v>
       </c>
       <c r="D176">
-        <v>40.306</v>
+        <v>-2.139</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4782,16 +4782,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>533.153</v>
+        <v>228.5</v>
       </c>
       <c r="C177">
-        <v>533.153</v>
+        <v>228.5</v>
       </c>
       <c r="D177">
-        <v>35.973</v>
+        <v>25.916</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4802,16 +4802,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>501</v>
+        <v>445.838</v>
       </c>
       <c r="C178">
-        <v>501</v>
+        <v>445.838</v>
       </c>
       <c r="D178">
-        <v>19.064</v>
+        <v>88.946</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4822,16 +4822,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>606.3</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>606.3</v>
       </c>
       <c r="D179">
-        <v>7.504</v>
+        <v>122.944</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4842,16 +4842,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>1508.572</v>
+        <v>601</v>
       </c>
       <c r="C180">
-        <v>1508.572</v>
+        <v>601</v>
       </c>
       <c r="D180">
-        <v>-8.083</v>
+        <v>118.072</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4862,16 +4862,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>1565.675</v>
+        <v>27.339</v>
       </c>
       <c r="C181">
-        <v>1565.675</v>
+        <v>27.339</v>
       </c>
       <c r="D181">
-        <v>-9.606999999999999</v>
+        <v>60.249</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4882,16 +4882,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>501</v>
+        <v>-312.077</v>
       </c>
       <c r="C182">
-        <v>501</v>
+        <v>-312.077</v>
       </c>
       <c r="D182">
-        <v>1.834</v>
+        <v>25.383</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4902,16 +4902,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>134.812</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>134.812</v>
       </c>
       <c r="D183">
-        <v>12.93</v>
+        <v>45.066</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4922,16 +4922,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>35.61</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>35.61</v>
       </c>
       <c r="D184">
-        <v>7.753</v>
+        <v>64.928</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4942,16 +4942,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>178.144</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>178.144</v>
       </c>
       <c r="D185">
-        <v>2.975</v>
+        <v>89.227</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4962,16 +4962,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>1482.722</v>
+        <v>262.457</v>
       </c>
       <c r="C186">
-        <v>1482.722</v>
+        <v>262.457</v>
       </c>
       <c r="D186">
-        <v>-11.071</v>
+        <v>22.183</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4982,16 +4982,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>501</v>
+        <v>208.959</v>
       </c>
       <c r="C187">
-        <v>501</v>
+        <v>208.959</v>
       </c>
       <c r="D187">
-        <v>5.48</v>
+        <v>25.488</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -5002,16 +5002,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>215.901</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>215.901</v>
       </c>
       <c r="D188">
-        <v>1.444</v>
+        <v>37.652</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -5022,16 +5022,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>1394.934</v>
+        <v>211.251</v>
       </c>
       <c r="C189">
-        <v>1394.934</v>
+        <v>211.251</v>
       </c>
       <c r="D189">
-        <v>-1.577</v>
+        <v>62.947</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -5042,16 +5042,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>1433.848</v>
+        <v>202.775</v>
       </c>
       <c r="C190">
-        <v>1433.848</v>
+        <v>202.775</v>
       </c>
       <c r="D190">
-        <v>-19.105</v>
+        <v>78.502</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -5062,16 +5062,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>1520.882</v>
+        <v>208.772</v>
       </c>
       <c r="C191">
-        <v>1520.882</v>
+        <v>208.772</v>
       </c>
       <c r="D191">
-        <v>-28.666</v>
+        <v>46.271</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -5082,16 +5082,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>1479.578</v>
+        <v>209.336</v>
       </c>
       <c r="C192">
-        <v>1479.578</v>
+        <v>209.336</v>
       </c>
       <c r="D192">
-        <v>-38.969</v>
+        <v>14.759</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -5102,16 +5102,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>2143.907</v>
+        <v>1179.098</v>
       </c>
       <c r="C193">
-        <v>2143.907</v>
+        <v>1179.098</v>
       </c>
       <c r="D193">
-        <v>-48.488</v>
+        <v>-30.023</v>
       </c>
       <c r="E193">
         <v>96</v>
@@ -5122,16 +5122,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>1425.529</v>
+        <v>1000</v>
       </c>
       <c r="C194">
-        <v>1425.529</v>
+        <v>1000</v>
       </c>
       <c r="D194">
-        <v>-4.877</v>
+        <v>-23.219</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -5142,16 +5142,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>1367.989</v>
+        <v>501</v>
       </c>
       <c r="C195">
-        <v>1367.989</v>
+        <v>501</v>
       </c>
       <c r="D195">
-        <v>-22.75</v>
+        <v>9.744</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -5162,16 +5162,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>1348.979</v>
+        <v>1192.479</v>
       </c>
       <c r="C196">
-        <v>1348.979</v>
+        <v>1192.479</v>
       </c>
       <c r="D196">
-        <v>-34.211</v>
+        <v>-0.34</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -5182,16 +5182,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>1282.544</v>
+        <v>1000</v>
       </c>
       <c r="C197">
-        <v>1282.544</v>
+        <v>1000</v>
       </c>
       <c r="D197">
-        <v>-6.106</v>
+        <v>2.998</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -5202,16 +5202,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>1473.568</v>
+        <v>1585.627</v>
       </c>
       <c r="C198">
-        <v>1473.568</v>
+        <v>1585.627</v>
       </c>
       <c r="D198">
-        <v>-34.711</v>
+        <v>-31.371</v>
       </c>
       <c r="E198">
         <v>5</v>
@@ -5222,16 +5222,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>1455.254</v>
+        <v>1158.437</v>
       </c>
       <c r="C199">
-        <v>1455.254</v>
+        <v>1158.437</v>
       </c>
       <c r="D199">
-        <v>-17.48</v>
+        <v>-5.558</v>
       </c>
       <c r="E199">
         <v>6</v>
@@ -5242,16 +5242,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>1139.165</v>
+        <v>1441.179</v>
       </c>
       <c r="C200">
-        <v>1139.165</v>
+        <v>1441.179</v>
       </c>
       <c r="D200">
-        <v>-24.848</v>
+        <v>-43.768</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -5262,16 +5262,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>1276.88</v>
+        <v>1501.966</v>
       </c>
       <c r="C201">
-        <v>1276.88</v>
+        <v>1501.966</v>
       </c>
       <c r="D201">
-        <v>-34.994</v>
+        <v>-55.813</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5282,16 +5282,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>1306.227</v>
+        <v>1857.03</v>
       </c>
       <c r="C202">
-        <v>1306.227</v>
+        <v>1857.03</v>
       </c>
       <c r="D202">
-        <v>-36.393</v>
+        <v>-30.919</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -5302,16 +5302,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>1344.157</v>
+        <v>1129.19</v>
       </c>
       <c r="C203">
-        <v>1344.157</v>
+        <v>1129.19</v>
       </c>
       <c r="D203">
-        <v>-39.378</v>
+        <v>-20.796</v>
       </c>
       <c r="E203">
         <v>10</v>
@@ -5322,16 +5322,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>1412.68</v>
+        <v>1293.584</v>
       </c>
       <c r="C204">
-        <v>1412.68</v>
+        <v>1293.584</v>
       </c>
       <c r="D204">
-        <v>-17.25</v>
+        <v>-76.181</v>
       </c>
       <c r="E204">
         <v>11</v>
@@ -5342,16 +5342,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>1275.652</v>
+        <v>1545.809</v>
       </c>
       <c r="C205">
-        <v>1275.652</v>
+        <v>1545.809</v>
       </c>
       <c r="D205">
-        <v>-10.117</v>
+        <v>-50.163</v>
       </c>
       <c r="E205">
         <v>12</v>
@@ -5362,16 +5362,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>501</v>
+        <v>1198.339</v>
       </c>
       <c r="C206">
-        <v>501</v>
+        <v>1198.339</v>
       </c>
       <c r="D206">
-        <v>9.773</v>
+        <v>-37.548</v>
       </c>
       <c r="E206">
         <v>13</v>
@@ -5382,16 +5382,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>497.405</v>
+        <v>1013.517</v>
       </c>
       <c r="C207">
-        <v>497.405</v>
+        <v>1013.517</v>
       </c>
       <c r="D207">
-        <v>23.289</v>
+        <v>-42.168</v>
       </c>
       <c r="E207">
         <v>14</v>
@@ -5402,16 +5402,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>449.709</v>
+        <v>1530.882</v>
       </c>
       <c r="C208">
-        <v>449.709</v>
+        <v>1530.882</v>
       </c>
       <c r="D208">
-        <v>45.651</v>
+        <v>-67.02800000000001</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5422,16 +5422,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>381.244</v>
+        <v>1722.401</v>
       </c>
       <c r="C209">
-        <v>381.244</v>
+        <v>1722.401</v>
       </c>
       <c r="D209">
-        <v>35.733</v>
+        <v>-97.07299999999999</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5442,16 +5442,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>378.139</v>
+        <v>2795.175</v>
       </c>
       <c r="C210">
-        <v>378.139</v>
+        <v>2795.175</v>
       </c>
       <c r="D210">
-        <v>52.299</v>
+        <v>-56.586</v>
       </c>
       <c r="E210">
         <v>17</v>
@@ -5462,16 +5462,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>501</v>
+        <v>1356.156</v>
       </c>
       <c r="C211">
-        <v>501</v>
+        <v>1356.156</v>
       </c>
       <c r="D211">
-        <v>43.574</v>
+        <v>-34.921</v>
       </c>
       <c r="E211">
         <v>18</v>
@@ -5482,16 +5482,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>414.502</v>
+        <v>1683.919</v>
       </c>
       <c r="C212">
-        <v>414.502</v>
+        <v>1683.919</v>
       </c>
       <c r="D212">
-        <v>26.906</v>
+        <v>-41.586</v>
       </c>
       <c r="E212">
         <v>19</v>
@@ -5502,16 +5502,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>501</v>
+        <v>1316.962</v>
       </c>
       <c r="C213">
-        <v>501</v>
+        <v>1316.962</v>
       </c>
       <c r="D213">
-        <v>26.074</v>
+        <v>-27.913</v>
       </c>
       <c r="E213">
         <v>20</v>
@@ -5522,16 +5522,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>1239.196</v>
+        <v>501</v>
       </c>
       <c r="C214">
-        <v>1239.196</v>
+        <v>501</v>
       </c>
       <c r="D214">
-        <v>-12.707</v>
+        <v>36.744</v>
       </c>
       <c r="E214">
         <v>21</v>
@@ -5542,16 +5542,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>1194.992</v>
+        <v>424.316</v>
       </c>
       <c r="C215">
-        <v>1194.992</v>
+        <v>424.316</v>
       </c>
       <c r="D215">
-        <v>-16.667</v>
+        <v>25.314</v>
       </c>
       <c r="E215">
         <v>22</v>
@@ -5562,16 +5562,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>1151.092</v>
+        <v>1344.781</v>
       </c>
       <c r="C216">
-        <v>1151.092</v>
+        <v>1344.781</v>
       </c>
       <c r="D216">
-        <v>-25.976</v>
+        <v>-15.84</v>
       </c>
       <c r="E216">
         <v>23</v>
@@ -5582,16 +5582,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>1182.586</v>
+        <v>3338.989</v>
       </c>
       <c r="C217">
-        <v>1182.586</v>
+        <v>3338.989</v>
       </c>
       <c r="D217">
-        <v>-22.528</v>
+        <v>-53.647</v>
       </c>
       <c r="E217">
         <v>24</v>
@@ -5602,16 +5602,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>1197.15</v>
+        <v>2422.004</v>
       </c>
       <c r="C218">
-        <v>1197.15</v>
+        <v>2422.004</v>
       </c>
       <c r="D218">
-        <v>-13.458</v>
+        <v>-24.456</v>
       </c>
       <c r="E218">
         <v>25</v>
@@ -5622,16 +5622,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>1199.012</v>
+        <v>3578.498</v>
       </c>
       <c r="C219">
-        <v>1199.012</v>
+        <v>3578.498</v>
       </c>
       <c r="D219">
-        <v>-5.813</v>
+        <v>-50.416</v>
       </c>
       <c r="E219">
         <v>26</v>
@@ -5642,16 +5642,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>1186.483</v>
+        <v>2890.208</v>
       </c>
       <c r="C220">
-        <v>1186.483</v>
+        <v>2890.208</v>
       </c>
       <c r="D220">
-        <v>2.114</v>
+        <v>-90.533</v>
       </c>
       <c r="E220">
         <v>27</v>
@@ -5662,16 +5662,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>410.877</v>
+        <v>2004.076</v>
       </c>
       <c r="C221">
-        <v>410.877</v>
+        <v>2004.076</v>
       </c>
       <c r="D221">
-        <v>68.515</v>
+        <v>-79.32899999999999</v>
       </c>
       <c r="E221">
         <v>28</v>
@@ -5682,16 +5682,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>1367.139</v>
+        <v>6744.078</v>
       </c>
       <c r="C222">
-        <v>1367.139</v>
+        <v>6744.078</v>
       </c>
       <c r="D222">
-        <v>-26.521</v>
+        <v>-89.45399999999999</v>
       </c>
       <c r="E222">
         <v>29</v>
@@ -5702,16 +5702,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>366.21</v>
+        <v>5505.847</v>
       </c>
       <c r="C223">
-        <v>366.21</v>
+        <v>5505.847</v>
       </c>
       <c r="D223">
-        <v>1.837</v>
+        <v>-119.057</v>
       </c>
       <c r="E223">
         <v>30</v>
@@ -5722,16 +5722,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>239.594</v>
+        <v>3308.894</v>
       </c>
       <c r="C224">
-        <v>239.594</v>
+        <v>3308.894</v>
       </c>
       <c r="D224">
-        <v>13.345</v>
+        <v>-127.804</v>
       </c>
       <c r="E224">
         <v>31</v>
@@ -5742,16 +5742,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>73.765</v>
+        <v>4633.329</v>
       </c>
       <c r="C225">
-        <v>73.765</v>
+        <v>4633.329</v>
       </c>
       <c r="D225">
-        <v>24.871</v>
+        <v>-142.701</v>
       </c>
       <c r="E225">
         <v>32</v>
@@ -5762,16 +5762,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>36.263</v>
+        <v>1517.511</v>
       </c>
       <c r="C226">
-        <v>36.263</v>
+        <v>1517.511</v>
       </c>
       <c r="D226">
-        <v>12.483</v>
+        <v>-163.924</v>
       </c>
       <c r="E226">
         <v>33</v>
@@ -5782,16 +5782,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>903.968</v>
+        <v>1467.55</v>
       </c>
       <c r="C227">
-        <v>903.968</v>
+        <v>1467.55</v>
       </c>
       <c r="D227">
-        <v>-38.492</v>
+        <v>-135.887</v>
       </c>
       <c r="E227">
         <v>34</v>
@@ -5802,16 +5802,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>700</v>
+        <v>1524.565</v>
       </c>
       <c r="C228">
-        <v>700</v>
+        <v>1524.565</v>
       </c>
       <c r="D228">
-        <v>-51.208</v>
+        <v>-118.42</v>
       </c>
       <c r="E228">
         <v>35</v>
@@ -5822,16 +5822,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>1461.208</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>1461.208</v>
       </c>
       <c r="D229">
-        <v>-13.807</v>
+        <v>-68.19499999999999</v>
       </c>
       <c r="E229">
         <v>36</v>
@@ -5842,16 +5842,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>251</v>
+        <v>908.519</v>
       </c>
       <c r="C230">
-        <v>251</v>
+        <v>908.519</v>
       </c>
       <c r="D230">
-        <v>0.207</v>
+        <v>-133.349</v>
       </c>
       <c r="E230">
         <v>37</v>
@@ -5862,16 +5862,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>700</v>
+        <v>749.898</v>
       </c>
       <c r="C231">
-        <v>700</v>
+        <v>749.898</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>-44.366</v>
       </c>
       <c r="E231">
         <v>38</v>
@@ -5882,16 +5882,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>750.33</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>750.33</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>-14.122</v>
       </c>
       <c r="E232">
         <v>39</v>
@@ -5902,7 +5902,7 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -6262,7 +6262,7 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -6522,7 +6522,7 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -6882,7 +6882,7 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -6922,7 +6922,7 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2">
-        <v>46285.95833333334</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2">
-        <v>46285.96875</v>
+        <v>46295.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2">
-        <v>46285.97916666666</v>
+        <v>46295.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2">
-        <v>46285.98958333334</v>
+        <v>46295.98958333334</v>
       </c>
       <c r="B289">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,868 +34,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
-  </si>
-  <si>
-    <t>30.09.202640</t>
-  </si>
-  <si>
-    <t>30.09.202641</t>
-  </si>
-  <si>
-    <t>30.09.202642</t>
-  </si>
-  <si>
-    <t>30.09.202643</t>
-  </si>
-  <si>
-    <t>30.09.202644</t>
-  </si>
-  <si>
-    <t>30.09.202645</t>
-  </si>
-  <si>
-    <t>30.09.202646</t>
-  </si>
-  <si>
-    <t>30.09.202647</t>
-  </si>
-  <si>
-    <t>30.09.202648</t>
-  </si>
-  <si>
-    <t>30.09.202649</t>
-  </si>
-  <si>
-    <t>30.09.202650</t>
-  </si>
-  <si>
-    <t>30.09.202651</t>
-  </si>
-  <si>
-    <t>30.09.202652</t>
-  </si>
-  <si>
-    <t>30.09.202653</t>
-  </si>
-  <si>
-    <t>30.09.202654</t>
-  </si>
-  <si>
-    <t>30.09.202655</t>
-  </si>
-  <si>
-    <t>30.09.202656</t>
-  </si>
-  <si>
-    <t>30.09.202657</t>
-  </si>
-  <si>
-    <t>30.09.202658</t>
-  </si>
-  <si>
-    <t>30.09.202659</t>
-  </si>
-  <si>
-    <t>30.09.202660</t>
-  </si>
-  <si>
-    <t>30.09.202661</t>
-  </si>
-  <si>
-    <t>30.09.202662</t>
-  </si>
-  <si>
-    <t>30.09.202663</t>
-  </si>
-  <si>
-    <t>30.09.202664</t>
-  </si>
-  <si>
-    <t>30.09.202665</t>
-  </si>
-  <si>
-    <t>30.09.202666</t>
-  </si>
-  <si>
-    <t>30.09.202667</t>
-  </si>
-  <si>
-    <t>30.09.202668</t>
-  </si>
-  <si>
-    <t>30.09.202669</t>
-  </si>
-  <si>
-    <t>30.09.202670</t>
-  </si>
-  <si>
-    <t>30.09.202671</t>
-  </si>
-  <si>
-    <t>30.09.202672</t>
-  </si>
-  <si>
-    <t>30.09.202673</t>
-  </si>
-  <si>
-    <t>30.09.202674</t>
-  </si>
-  <si>
-    <t>30.09.202675</t>
-  </si>
-  <si>
-    <t>30.09.202676</t>
-  </si>
-  <si>
-    <t>30.09.202677</t>
-  </si>
-  <si>
-    <t>30.09.202678</t>
-  </si>
-  <si>
-    <t>30.09.202679</t>
-  </si>
-  <si>
-    <t>30.09.202680</t>
-  </si>
-  <si>
-    <t>30.09.202681</t>
-  </si>
-  <si>
-    <t>30.09.202682</t>
-  </si>
-  <si>
-    <t>30.09.202683</t>
-  </si>
-  <si>
-    <t>30.09.202684</t>
-  </si>
-  <si>
-    <t>30.09.202685</t>
-  </si>
-  <si>
-    <t>30.09.202686</t>
-  </si>
-  <si>
-    <t>30.09.202687</t>
-  </si>
-  <si>
-    <t>30.09.202688</t>
-  </si>
-  <si>
-    <t>30.09.202689</t>
-  </si>
-  <si>
-    <t>30.09.202690</t>
-  </si>
-  <si>
-    <t>30.09.202691</t>
-  </si>
-  <si>
-    <t>30.09.202692</t>
-  </si>
-  <si>
-    <t>30.09.202693</t>
-  </si>
-  <si>
-    <t>30.09.202694</t>
-  </si>
-  <si>
-    <t>30.09.202695</t>
-  </si>
-  <si>
-    <t>30.09.202696</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1282,16 +1282,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
-        <v>204.406</v>
+        <v>-31.271</v>
       </c>
       <c r="C2">
-        <v>204.406</v>
+        <v>-31.271</v>
       </c>
       <c r="D2">
-        <v>39.851</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1302,16 +1302,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>261</v>
+        <v>234.808</v>
       </c>
       <c r="C3">
-        <v>261</v>
+        <v>234.808</v>
       </c>
       <c r="D3">
-        <v>17.854</v>
+        <v>55.613</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1322,16 +1322,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>262.022</v>
+        <v>218.007</v>
       </c>
       <c r="C4">
-        <v>262.022</v>
+        <v>218.007</v>
       </c>
       <c r="D4">
-        <v>20.834</v>
+        <v>45.122</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1342,16 +1342,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>1100</v>
+        <v>218.444</v>
       </c>
       <c r="C5">
-        <v>1100</v>
+        <v>218.444</v>
       </c>
       <c r="D5">
-        <v>-5.189</v>
+        <v>49.258</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>1091.423</v>
+        <v>232.402</v>
       </c>
       <c r="C6">
-        <v>1091.423</v>
+        <v>232.402</v>
       </c>
       <c r="D6">
-        <v>-17.469</v>
+        <v>50.054</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1382,16 +1382,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>1183.131</v>
+        <v>218.725</v>
       </c>
       <c r="C7">
-        <v>1183.131</v>
+        <v>218.725</v>
       </c>
       <c r="D7">
-        <v>-36.317</v>
+        <v>63.19</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1402,16 +1402,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>1000</v>
+        <v>239.23</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>239.23</v>
       </c>
       <c r="D8">
-        <v>-27.208</v>
+        <v>62.505</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1422,16 +1422,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>1043.836</v>
+        <v>208.185</v>
       </c>
       <c r="C9">
-        <v>1043.836</v>
+        <v>208.185</v>
       </c>
       <c r="D9">
-        <v>-8.683999999999999</v>
+        <v>42.75</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1442,16 +1442,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>501</v>
+        <v>204.72</v>
       </c>
       <c r="C10">
-        <v>501</v>
+        <v>204.72</v>
       </c>
       <c r="D10">
-        <v>6.811</v>
+        <v>17.505</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1462,16 +1462,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>320.567</v>
+        <v>200</v>
       </c>
       <c r="C11">
-        <v>320.567</v>
+        <v>200</v>
       </c>
       <c r="D11">
-        <v>14.725</v>
+        <v>10.989</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1482,16 +1482,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>280</v>
+        <v>1183.078</v>
       </c>
       <c r="C12">
-        <v>280</v>
+        <v>1183.078</v>
       </c>
       <c r="D12">
-        <v>10.933</v>
+        <v>-1.237</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1502,16 +1502,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>251.309</v>
+        <v>1416.921</v>
       </c>
       <c r="C13">
-        <v>251.309</v>
+        <v>1416.921</v>
       </c>
       <c r="D13">
-        <v>32.738</v>
+        <v>-9.31</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1522,16 +1522,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>318.632</v>
+        <v>261</v>
       </c>
       <c r="C14">
-        <v>318.632</v>
+        <v>261</v>
       </c>
       <c r="D14">
-        <v>62.18</v>
+        <v>0.755</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1542,16 +1542,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>481.322</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>481.322</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>62.041</v>
+        <v>4.244</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1562,16 +1562,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>501</v>
+        <v>1380.096</v>
       </c>
       <c r="C16">
-        <v>501</v>
+        <v>1380.096</v>
       </c>
       <c r="D16">
-        <v>54.553</v>
+        <v>-38.685</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1582,16 +1582,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1422.579</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1422.579</v>
       </c>
       <c r="D17">
-        <v>77.396</v>
+        <v>-29.857</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1602,16 +1602,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>362.092</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>362.092</v>
       </c>
       <c r="D18">
-        <v>101.631</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1622,16 +1622,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>269.617</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>269.617</v>
       </c>
       <c r="D19">
-        <v>26.764</v>
+        <v>21.536</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
-        <v>501</v>
+        <v>253.484</v>
       </c>
       <c r="C20">
-        <v>501</v>
+        <v>253.484</v>
       </c>
       <c r="D20">
-        <v>10.77</v>
+        <v>30.082</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1662,16 +1662,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>261.029</v>
+        <v>252.78</v>
       </c>
       <c r="C21">
-        <v>261.029</v>
+        <v>252.78</v>
       </c>
       <c r="D21">
-        <v>2.48</v>
+        <v>60.462</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1682,16 +1682,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
-        <v>501</v>
+        <v>283.06</v>
       </c>
       <c r="C22">
-        <v>501</v>
+        <v>283.06</v>
       </c>
       <c r="D22">
-        <v>18.654</v>
+        <v>66.247</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1702,16 +1702,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>1083.313</v>
+        <v>318.638</v>
       </c>
       <c r="C23">
-        <v>1083.313</v>
+        <v>318.638</v>
       </c>
       <c r="D23">
-        <v>-22.519</v>
+        <v>36.045</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1722,16 +1722,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>1285.806</v>
+        <v>259.14</v>
       </c>
       <c r="C24">
-        <v>1285.806</v>
+        <v>259.14</v>
       </c>
       <c r="D24">
-        <v>-19.038</v>
+        <v>40.878</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1742,16 +1742,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>1416.599</v>
+        <v>407.464</v>
       </c>
       <c r="C25">
-        <v>1416.599</v>
+        <v>407.464</v>
       </c>
       <c r="D25">
-        <v>-23.443</v>
+        <v>36.526</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1762,16 +1762,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
-        <v>1616.526</v>
+        <v>382.411</v>
       </c>
       <c r="C26">
-        <v>1616.526</v>
+        <v>382.411</v>
       </c>
       <c r="D26">
-        <v>-6.428</v>
+        <v>88.569</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1782,16 +1782,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
-        <v>1678.886</v>
+        <v>312.498</v>
       </c>
       <c r="C27">
-        <v>1678.886</v>
+        <v>312.498</v>
       </c>
       <c r="D27">
-        <v>-28.95</v>
+        <v>37.213</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>1556.085</v>
+        <v>400.431</v>
       </c>
       <c r="C28">
-        <v>1556.085</v>
+        <v>400.431</v>
       </c>
       <c r="D28">
-        <v>-27.948</v>
+        <v>67.44199999999999</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1822,16 +1822,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
-        <v>1492.206</v>
+        <v>343.133</v>
       </c>
       <c r="C29">
-        <v>1492.206</v>
+        <v>343.133</v>
       </c>
       <c r="D29">
-        <v>-5.702</v>
+        <v>83.339</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1842,16 +1842,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
-        <v>1552.917</v>
+        <v>297.251</v>
       </c>
       <c r="C30">
-        <v>1552.917</v>
+        <v>297.251</v>
       </c>
       <c r="D30">
-        <v>-7.481</v>
+        <v>51.054</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1862,16 +1862,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
-        <v>501</v>
+        <v>316.506</v>
       </c>
       <c r="C31">
-        <v>501</v>
+        <v>316.506</v>
       </c>
       <c r="D31">
-        <v>30.193</v>
+        <v>42.296</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1882,16 +1882,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
-        <v>491.421</v>
+        <v>284.518</v>
       </c>
       <c r="C32">
-        <v>491.421</v>
+        <v>284.518</v>
       </c>
       <c r="D32">
-        <v>68.18899999999999</v>
+        <v>60.474</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1902,16 +1902,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
-        <v>339.1</v>
+        <v>256.846</v>
       </c>
       <c r="C33">
-        <v>339.1</v>
+        <v>256.846</v>
       </c>
       <c r="D33">
-        <v>170.88</v>
+        <v>133.275</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1922,16 +1922,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>245.069</v>
+        <v>260.932</v>
       </c>
       <c r="C34">
-        <v>245.069</v>
+        <v>260.932</v>
       </c>
       <c r="D34">
-        <v>152.052</v>
+        <v>13.463</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1942,16 +1942,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>-121.75</v>
+        <v>2272.529</v>
       </c>
       <c r="C35">
-        <v>-121.75</v>
+        <v>2272.529</v>
       </c>
       <c r="D35">
-        <v>142.146</v>
+        <v>-36.007</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1962,16 +1962,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>-65.167</v>
+        <v>262.281</v>
       </c>
       <c r="C36">
-        <v>-65.167</v>
+        <v>262.281</v>
       </c>
       <c r="D36">
-        <v>101.716</v>
+        <v>16.846</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1982,16 +1982,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
-        <v>-75.062</v>
+        <v>-82.58199999999999</v>
       </c>
       <c r="C37">
-        <v>-75.062</v>
+        <v>-82.58199999999999</v>
       </c>
       <c r="D37">
-        <v>162.57</v>
+        <v>57.961</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -2002,16 +2002,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
-        <v>-94.93899999999999</v>
+        <v>52.988</v>
       </c>
       <c r="C38">
-        <v>-94.93899999999999</v>
+        <v>52.988</v>
       </c>
       <c r="D38">
-        <v>143.942</v>
+        <v>25.503</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -2022,16 +2022,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>-212.048</v>
+        <v>-281.747</v>
       </c>
       <c r="C39">
-        <v>-212.048</v>
+        <v>-281.747</v>
       </c>
       <c r="D39">
-        <v>88.148</v>
+        <v>65.861</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -2042,16 +2042,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>-227.264</v>
+        <v>-615.252</v>
       </c>
       <c r="C40">
-        <v>-227.264</v>
+        <v>-615.252</v>
       </c>
       <c r="D40">
-        <v>84.089</v>
+        <v>113.556</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -2062,16 +2062,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
-        <v>-186.934</v>
+        <v>-86.636</v>
       </c>
       <c r="C41">
-        <v>-186.934</v>
+        <v>-86.636</v>
       </c>
       <c r="D41">
-        <v>100.098</v>
+        <v>226.388</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -2082,16 +2082,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>-254.299</v>
+        <v>-218.689</v>
       </c>
       <c r="C42">
-        <v>-254.299</v>
+        <v>-218.689</v>
       </c>
       <c r="D42">
-        <v>98</v>
+        <v>138.93</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -2102,16 +2102,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>-275.864</v>
+        <v>-283.873</v>
       </c>
       <c r="C43">
-        <v>-275.864</v>
+        <v>-283.873</v>
       </c>
       <c r="D43">
-        <v>94.92100000000001</v>
+        <v>84.233</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -2122,16 +2122,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
-        <v>-257.042</v>
+        <v>-251.213</v>
       </c>
       <c r="C44">
-        <v>-257.042</v>
+        <v>-251.213</v>
       </c>
       <c r="D44">
-        <v>108.504</v>
+        <v>162.517</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -2142,16 +2142,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
-        <v>-234.809</v>
+        <v>-278.337</v>
       </c>
       <c r="C45">
-        <v>-234.809</v>
+        <v>-278.337</v>
       </c>
       <c r="D45">
-        <v>127.97</v>
+        <v>166.613</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>-264.099</v>
+        <v>-271.292</v>
       </c>
       <c r="C46">
-        <v>-264.099</v>
+        <v>-271.292</v>
       </c>
       <c r="D46">
-        <v>107.485</v>
+        <v>120.277</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2182,16 +2182,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>-280.884</v>
+        <v>-266.248</v>
       </c>
       <c r="C47">
-        <v>-280.884</v>
+        <v>-266.248</v>
       </c>
       <c r="D47">
-        <v>84.587</v>
+        <v>139.53</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2202,16 +2202,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>-267.697</v>
+        <v>-285.187</v>
       </c>
       <c r="C48">
-        <v>-267.697</v>
+        <v>-285.187</v>
       </c>
       <c r="D48">
-        <v>88.947</v>
+        <v>159.873</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2222,16 +2222,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>-252.31</v>
+        <v>-268.689</v>
       </c>
       <c r="C49">
-        <v>-252.31</v>
+        <v>-268.689</v>
       </c>
       <c r="D49">
-        <v>105.148</v>
+        <v>140.446</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2242,16 +2242,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>-278.033</v>
+        <v>-308.047</v>
       </c>
       <c r="C50">
-        <v>-278.033</v>
+        <v>-308.047</v>
       </c>
       <c r="D50">
-        <v>87.95699999999999</v>
+        <v>157.08</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2262,16 +2262,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>-290</v>
+        <v>-268.067</v>
       </c>
       <c r="C51">
-        <v>-290</v>
+        <v>-268.067</v>
       </c>
       <c r="D51">
-        <v>73.68600000000001</v>
+        <v>141.083</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2282,16 +2282,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
-        <v>-61.996</v>
+        <v>-269.996</v>
       </c>
       <c r="C52">
-        <v>-61.996</v>
+        <v>-269.996</v>
       </c>
       <c r="D52">
-        <v>71.351</v>
+        <v>166.76</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2302,16 +2302,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
-        <v>189.275</v>
+        <v>-270.308</v>
       </c>
       <c r="C53">
-        <v>189.275</v>
+        <v>-270.308</v>
       </c>
       <c r="D53">
-        <v>94.038</v>
+        <v>148.979</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2322,16 +2322,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
-        <v>-73.69499999999999</v>
+        <v>-280.059</v>
       </c>
       <c r="C54">
-        <v>-73.69499999999999</v>
+        <v>-280.059</v>
       </c>
       <c r="D54">
-        <v>79.023</v>
+        <v>153.104</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2342,16 +2342,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
-        <v>-97.467</v>
+        <v>-272.466</v>
       </c>
       <c r="C55">
-        <v>-97.467</v>
+        <v>-272.466</v>
       </c>
       <c r="D55">
-        <v>52.551</v>
+        <v>144.438</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2362,16 +2362,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
-        <v>-79.377</v>
+        <v>-287.168</v>
       </c>
       <c r="C56">
-        <v>-79.377</v>
+        <v>-287.168</v>
       </c>
       <c r="D56">
-        <v>106.184</v>
+        <v>114.963</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2382,16 +2382,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
-        <v>-90.277</v>
+        <v>-284.63</v>
       </c>
       <c r="C57">
-        <v>-90.277</v>
+        <v>-284.63</v>
       </c>
       <c r="D57">
-        <v>66.696</v>
+        <v>115.383</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2402,16 +2402,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
-        <v>-1182.508</v>
+        <v>-369.875</v>
       </c>
       <c r="C58">
-        <v>-1182.508</v>
+        <v>-369.875</v>
       </c>
       <c r="D58">
-        <v>91.86199999999999</v>
+        <v>179.42</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2422,16 +2422,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
-        <v>-71.462</v>
+        <v>-289.931</v>
       </c>
       <c r="C59">
-        <v>-71.462</v>
+        <v>-289.931</v>
       </c>
       <c r="D59">
-        <v>103.546</v>
+        <v>128.418</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2442,16 +2442,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>-87</v>
+        <v>-290</v>
       </c>
       <c r="C60">
-        <v>-87</v>
+        <v>-290</v>
       </c>
       <c r="D60">
-        <v>43.843</v>
+        <v>93.66800000000001</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2462,16 +2462,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
-        <v>145.406</v>
+        <v>-282.009</v>
       </c>
       <c r="C61">
-        <v>145.406</v>
+        <v>-282.009</v>
       </c>
       <c r="D61">
-        <v>69.175</v>
+        <v>142.383</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2482,16 +2482,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
-        <v>61.255</v>
+        <v>-2140.926</v>
       </c>
       <c r="C62">
-        <v>61.255</v>
+        <v>-2140.926</v>
       </c>
       <c r="D62">
-        <v>60.254</v>
+        <v>145.914</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2502,16 +2502,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>206.82</v>
+        <v>-350.9</v>
       </c>
       <c r="C63">
-        <v>206.82</v>
+        <v>-350.9</v>
       </c>
       <c r="D63">
-        <v>34.22</v>
+        <v>111.356</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2522,16 +2522,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>1989.689</v>
+        <v>-277.288</v>
       </c>
       <c r="C64">
-        <v>1989.689</v>
+        <v>-277.288</v>
       </c>
       <c r="D64">
-        <v>-45.036</v>
+        <v>142.561</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2542,16 +2542,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>1217.382</v>
+        <v>-289.506</v>
       </c>
       <c r="C65">
-        <v>1217.382</v>
+        <v>-289.506</v>
       </c>
       <c r="D65">
-        <v>-41.644</v>
+        <v>101.633</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2562,16 +2562,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>1568.28</v>
+        <v>-285.798</v>
       </c>
       <c r="C66">
-        <v>1568.28</v>
+        <v>-285.798</v>
       </c>
       <c r="D66">
-        <v>-32.305</v>
+        <v>225.22</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>1592.927</v>
+        <v>-289.125</v>
       </c>
       <c r="C67">
-        <v>1592.927</v>
+        <v>-289.125</v>
       </c>
       <c r="D67">
-        <v>-31.548</v>
+        <v>131.283</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2602,16 +2602,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>2113.135</v>
+        <v>-289.317</v>
       </c>
       <c r="C68">
-        <v>2113.135</v>
+        <v>-289.317</v>
       </c>
       <c r="D68">
-        <v>-24.434</v>
+        <v>131.471</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2622,16 +2622,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>4082.985</v>
+        <v>-289.639</v>
       </c>
       <c r="C69">
-        <v>4082.985</v>
+        <v>-289.639</v>
       </c>
       <c r="D69">
-        <v>-40.294</v>
+        <v>50.192</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2642,16 +2642,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>501</v>
+        <v>200.28</v>
       </c>
       <c r="C70">
-        <v>501</v>
+        <v>200.28</v>
       </c>
       <c r="D70">
-        <v>82.953</v>
+        <v>67.252</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>368.083</v>
+        <v>4493.602</v>
       </c>
       <c r="C71">
-        <v>368.083</v>
+        <v>4493.602</v>
       </c>
       <c r="D71">
-        <v>50.729</v>
+        <v>-26.077</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2682,16 +2682,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
-        <v>501</v>
+        <v>1547.234</v>
       </c>
       <c r="C72">
-        <v>501</v>
+        <v>1547.234</v>
       </c>
       <c r="D72">
-        <v>9.884</v>
+        <v>-20.598</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2702,16 +2702,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>1532.835</v>
+        <v>1150.493</v>
       </c>
       <c r="C73">
-        <v>1532.835</v>
+        <v>1150.493</v>
       </c>
       <c r="D73">
-        <v>-7.159</v>
+        <v>-40.261</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2722,16 +2722,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>2124.455</v>
+        <v>1935.902</v>
       </c>
       <c r="C74">
-        <v>2124.455</v>
+        <v>1935.902</v>
       </c>
       <c r="D74">
-        <v>-33.804</v>
+        <v>-10.265</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2742,16 +2742,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>2218.418</v>
+        <v>1764.966</v>
       </c>
       <c r="C75">
-        <v>2218.418</v>
+        <v>1764.966</v>
       </c>
       <c r="D75">
-        <v>-29.186</v>
+        <v>-14.92</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2762,16 +2762,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>2408.923</v>
+        <v>3990.666</v>
       </c>
       <c r="C76">
-        <v>2408.923</v>
+        <v>3990.666</v>
       </c>
       <c r="D76">
-        <v>-33.91</v>
+        <v>-59.827</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2782,16 +2782,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
-        <v>2018.034</v>
+        <v>2263.897</v>
       </c>
       <c r="C77">
-        <v>2018.034</v>
+        <v>2263.897</v>
       </c>
       <c r="D77">
-        <v>-6.233</v>
+        <v>-33.487</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2802,16 +2802,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
-        <v>1639.428</v>
+        <v>501</v>
       </c>
       <c r="C78">
-        <v>1639.428</v>
+        <v>501</v>
       </c>
       <c r="D78">
-        <v>-3.003</v>
+        <v>22.782</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2822,16 +2822,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>1584.231</v>
+        <v>1611.713</v>
       </c>
       <c r="C79">
-        <v>1584.231</v>
+        <v>1611.713</v>
       </c>
       <c r="D79">
-        <v>-0.193</v>
+        <v>-19.178</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2842,16 +2842,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>567.308</v>
+        <v>1743.082</v>
       </c>
       <c r="C80">
-        <v>567.308</v>
+        <v>1743.082</v>
       </c>
       <c r="D80">
-        <v>21.163</v>
+        <v>-34.837</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2862,16 +2862,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>506.262</v>
+        <v>2121.247</v>
       </c>
       <c r="C81">
-        <v>506.262</v>
+        <v>2121.247</v>
       </c>
       <c r="D81">
-        <v>30.681</v>
+        <v>-34.502</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2882,16 +2882,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
-        <v>580.097</v>
+        <v>2044.589</v>
       </c>
       <c r="C82">
-        <v>580.097</v>
+        <v>2044.589</v>
       </c>
       <c r="D82">
-        <v>10.45</v>
+        <v>-20.668</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2902,16 +2902,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>2207.333</v>
+        <v>1749.118</v>
       </c>
       <c r="C83">
-        <v>2207.333</v>
+        <v>1749.118</v>
       </c>
       <c r="D83">
-        <v>-1.779</v>
+        <v>-34.556</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2922,16 +2922,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
-        <v>614.313</v>
+        <v>1767.026</v>
       </c>
       <c r="C84">
-        <v>614.313</v>
+        <v>1767.026</v>
       </c>
       <c r="D84">
-        <v>16.985</v>
+        <v>-19.958</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2942,16 +2942,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>473.66</v>
+        <v>1584.367</v>
       </c>
       <c r="C85">
-        <v>473.66</v>
+        <v>1584.367</v>
       </c>
       <c r="D85">
-        <v>0.246</v>
+        <v>-24.885</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2962,16 +2962,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>1000</v>
+        <v>1147.347</v>
       </c>
       <c r="C86">
-        <v>1000</v>
+        <v>1147.347</v>
       </c>
       <c r="D86">
-        <v>-17.556</v>
+        <v>-44.96</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2982,16 +2982,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>320.865</v>
+        <v>1182.276</v>
       </c>
       <c r="C87">
-        <v>320.865</v>
+        <v>1182.276</v>
       </c>
       <c r="D87">
-        <v>8.227</v>
+        <v>-34.66</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -3002,16 +3002,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>334.093</v>
+        <v>1437.874</v>
       </c>
       <c r="C88">
-        <v>334.093</v>
+        <v>1437.874</v>
       </c>
       <c r="D88">
-        <v>32.149</v>
+        <v>-10.691</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -3022,16 +3022,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>-1550.257</v>
+        <v>1187.293</v>
       </c>
       <c r="C89">
-        <v>-1550.257</v>
+        <v>1187.293</v>
       </c>
       <c r="D89">
-        <v>40.223</v>
+        <v>-4.339</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -3042,16 +3042,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
-        <v>-1268.241</v>
+        <v>1529.2</v>
       </c>
       <c r="C90">
-        <v>-1268.241</v>
+        <v>1529.2</v>
       </c>
       <c r="D90">
-        <v>23.741</v>
+        <v>-7.274</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -3062,16 +3062,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
-        <v>309.245</v>
+        <v>353.473</v>
       </c>
       <c r="C91">
-        <v>309.245</v>
+        <v>353.473</v>
       </c>
       <c r="D91">
-        <v>15.445</v>
+        <v>10.689</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -3082,16 +3082,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
-        <v>268.481</v>
+        <v>286.566</v>
       </c>
       <c r="C92">
-        <v>268.481</v>
+        <v>286.566</v>
       </c>
       <c r="D92">
-        <v>13.862</v>
+        <v>12.93</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -3102,16 +3102,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
-        <v>312.504</v>
+        <v>142.904</v>
       </c>
       <c r="C93">
-        <v>312.504</v>
+        <v>142.904</v>
       </c>
       <c r="D93">
-        <v>5.312</v>
+        <v>32.767</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -3122,16 +3122,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
-        <v>325.486</v>
+        <v>86.002</v>
       </c>
       <c r="C94">
-        <v>325.486</v>
+        <v>86.002</v>
       </c>
       <c r="D94">
-        <v>7.918</v>
+        <v>51.775</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -3142,16 +3142,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
-        <v>430.377</v>
+        <v>-12.28</v>
       </c>
       <c r="C95">
-        <v>430.377</v>
+        <v>-12.28</v>
       </c>
       <c r="D95">
-        <v>3.777</v>
+        <v>83.39400000000001</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
-        <v>435.302</v>
+        <v>81.577</v>
       </c>
       <c r="C96">
-        <v>435.302</v>
+        <v>81.577</v>
       </c>
       <c r="D96">
-        <v>0.848</v>
+        <v>86.179</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3182,16 +3182,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>999</v>
+        <v>105.458</v>
       </c>
       <c r="C97">
-        <v>999</v>
+        <v>105.458</v>
       </c>
       <c r="D97">
-        <v>-15.8</v>
+        <v>77.191</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3202,16 +3202,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>1021.862</v>
+        <v>-75.328</v>
       </c>
       <c r="C98">
-        <v>1021.862</v>
+        <v>-75.328</v>
       </c>
       <c r="D98">
-        <v>-15.195</v>
+        <v>34.786</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>1186.244</v>
+        <v>-72.346</v>
       </c>
       <c r="C99">
-        <v>1186.244</v>
+        <v>-72.346</v>
       </c>
       <c r="D99">
-        <v>-14.29</v>
+        <v>49.235</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3242,16 +3242,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>1184.049</v>
+        <v>-98.872</v>
       </c>
       <c r="C100">
-        <v>1184.049</v>
+        <v>-98.872</v>
       </c>
       <c r="D100">
-        <v>-4.988</v>
+        <v>25.869</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3262,16 +3262,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
-        <v>446.114</v>
+        <v>-98.361</v>
       </c>
       <c r="C101">
-        <v>446.114</v>
+        <v>-98.361</v>
       </c>
       <c r="D101">
-        <v>9.766999999999999</v>
+        <v>28.743</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3282,16 +3282,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
-        <v>437.144</v>
+        <v>-82.184</v>
       </c>
       <c r="C102">
-        <v>437.144</v>
+        <v>-82.184</v>
       </c>
       <c r="D102">
-        <v>10.184</v>
+        <v>32.506</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3302,16 +3302,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
-        <v>1135.207</v>
+        <v>-42.577</v>
       </c>
       <c r="C103">
-        <v>1135.207</v>
+        <v>-42.577</v>
       </c>
       <c r="D103">
-        <v>-12.836</v>
+        <v>54.865</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3322,16 +3322,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
-        <v>1094.071</v>
+        <v>-57.986</v>
       </c>
       <c r="C104">
-        <v>1094.071</v>
+        <v>-57.986</v>
       </c>
       <c r="D104">
-        <v>-3.514</v>
+        <v>39.506</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
-        <v>477.836</v>
+        <v>-98.712</v>
       </c>
       <c r="C105">
-        <v>477.836</v>
+        <v>-98.712</v>
       </c>
       <c r="D105">
-        <v>20.968</v>
+        <v>24.109</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3362,16 +3362,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
-        <v>1197.17</v>
+        <v>1007.143</v>
       </c>
       <c r="C106">
-        <v>1197.17</v>
+        <v>1007.143</v>
       </c>
       <c r="D106">
-        <v>-9.686</v>
+        <v>-0.32</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3382,16 +3382,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
-        <v>1176.573</v>
+        <v>-98.93600000000001</v>
       </c>
       <c r="C107">
-        <v>1176.573</v>
+        <v>-98.93600000000001</v>
       </c>
       <c r="D107">
-        <v>-1.85</v>
+        <v>2.97</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3402,16 +3402,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
-        <v>577.732</v>
+        <v>-93.892</v>
       </c>
       <c r="C108">
-        <v>577.732</v>
+        <v>-93.892</v>
       </c>
       <c r="D108">
-        <v>-6.855</v>
+        <v>36.259</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3422,16 +3422,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
-        <v>352.809</v>
+        <v>-98.72799999999999</v>
       </c>
       <c r="C109">
-        <v>352.809</v>
+        <v>-98.72799999999999</v>
       </c>
       <c r="D109">
-        <v>-16.864</v>
+        <v>2.307</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3442,16 +3442,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
-        <v>1196.477</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>1196.477</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>-23.913</v>
+        <v>5.235</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
-        <v>1326.679</v>
+        <v>1221.727</v>
       </c>
       <c r="C111">
-        <v>1326.679</v>
+        <v>1221.727</v>
       </c>
       <c r="D111">
-        <v>-12.681</v>
+        <v>-13.584</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3482,16 +3482,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
-        <v>1455.426</v>
+        <v>246.679</v>
       </c>
       <c r="C112">
-        <v>1455.426</v>
+        <v>246.679</v>
       </c>
       <c r="D112">
-        <v>-25.659</v>
+        <v>12.17</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3502,16 +3502,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
-        <v>501</v>
+        <v>240.996</v>
       </c>
       <c r="C113">
-        <v>501</v>
+        <v>240.996</v>
       </c>
       <c r="D113">
-        <v>12.831</v>
+        <v>22.168</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3522,16 +3522,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>219.289</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>219.289</v>
       </c>
       <c r="D114">
-        <v>20.735</v>
+        <v>59.642</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3542,16 +3542,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>229.412</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>229.412</v>
       </c>
       <c r="D115">
-        <v>9.337999999999999</v>
+        <v>41.456</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3562,16 +3562,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>1235.131</v>
+        <v>239.633</v>
       </c>
       <c r="C116">
-        <v>1235.131</v>
+        <v>239.633</v>
       </c>
       <c r="D116">
-        <v>-16.062</v>
+        <v>45.187</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3582,16 +3582,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>501</v>
+        <v>9.863</v>
       </c>
       <c r="C117">
-        <v>501</v>
+        <v>9.863</v>
       </c>
       <c r="D117">
-        <v>5.304</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3602,16 +3602,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>1438.751</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1438.751</v>
       </c>
       <c r="D118">
-        <v>40.591</v>
+        <v>-14.401</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3622,16 +3622,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>1186.894</v>
+        <v>1330.428</v>
       </c>
       <c r="C119">
-        <v>1186.894</v>
+        <v>1330.428</v>
       </c>
       <c r="D119">
-        <v>-2.83</v>
+        <v>-15.894</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3642,16 +3642,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>1381.732</v>
+        <v>501</v>
       </c>
       <c r="C120">
-        <v>1381.732</v>
+        <v>501</v>
       </c>
       <c r="D120">
-        <v>-25.774</v>
+        <v>46.765</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3662,16 +3662,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
-        <v>1446.135</v>
+        <v>1398.776</v>
       </c>
       <c r="C121">
-        <v>1446.135</v>
+        <v>1398.776</v>
       </c>
       <c r="D121">
-        <v>-10.609</v>
+        <v>-12.04</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
-        <v>1591.451</v>
+        <v>419.088</v>
       </c>
       <c r="C122">
-        <v>1591.451</v>
+        <v>419.088</v>
       </c>
       <c r="D122">
-        <v>-2.55</v>
+        <v>2.17</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3702,16 +3702,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>1629.024</v>
+        <v>1448.702</v>
       </c>
       <c r="C123">
-        <v>1629.024</v>
+        <v>1448.702</v>
       </c>
       <c r="D123">
-        <v>-38.819</v>
+        <v>-0.346</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3722,16 +3722,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>1739.29</v>
+        <v>365.601</v>
       </c>
       <c r="C124">
-        <v>1739.29</v>
+        <v>365.601</v>
       </c>
       <c r="D124">
-        <v>-50.671</v>
+        <v>37.987</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3742,16 +3742,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>1677.504</v>
+        <v>501</v>
       </c>
       <c r="C125">
-        <v>1677.504</v>
+        <v>501</v>
       </c>
       <c r="D125">
-        <v>-48.724</v>
+        <v>39.29</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3762,16 +3762,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>2324.027</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>2324.027</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>-48.677</v>
+        <v>39.047</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>5051.227</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>5051.227</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>-45.565</v>
+        <v>26.247</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3802,16 +3802,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>1130.792</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>1130.792</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>-3.891</v>
+        <v>27.082</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3822,16 +3822,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
-        <v>357.621</v>
+        <v>360.616</v>
       </c>
       <c r="C129">
-        <v>357.621</v>
+        <v>360.616</v>
       </c>
       <c r="D129">
-        <v>41.817</v>
+        <v>37.563</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3842,16 +3842,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>500.897</v>
+        <v>4705.021</v>
       </c>
       <c r="C130">
-        <v>500.897</v>
+        <v>4705.021</v>
       </c>
       <c r="D130">
-        <v>40.698</v>
+        <v>-32.568</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3862,16 +3862,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
-        <v>275.952</v>
+        <v>1612.998</v>
       </c>
       <c r="C131">
-        <v>275.952</v>
+        <v>1612.998</v>
       </c>
       <c r="D131">
-        <v>56.73</v>
+        <v>-4.121</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3882,16 +3882,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
-        <v>197.046</v>
+        <v>206.952</v>
       </c>
       <c r="C132">
-        <v>197.046</v>
+        <v>206.952</v>
       </c>
       <c r="D132">
-        <v>26.725</v>
+        <v>28.473</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3902,16 +3902,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
-        <v>292.295</v>
+        <v>22.389</v>
       </c>
       <c r="C133">
-        <v>292.295</v>
+        <v>22.389</v>
       </c>
       <c r="D133">
-        <v>120.332</v>
+        <v>62.997</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3922,16 +3922,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>261.241</v>
+        <v>1536.56</v>
       </c>
       <c r="C134">
-        <v>261.241</v>
+        <v>1536.56</v>
       </c>
       <c r="D134">
-        <v>66.489</v>
+        <v>-79.212</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3942,16 +3942,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
-        <v>261.055</v>
+        <v>68.28400000000001</v>
       </c>
       <c r="C135">
-        <v>261.055</v>
+        <v>68.28400000000001</v>
       </c>
       <c r="D135">
-        <v>26.369</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3962,16 +3962,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
-        <v>261.047</v>
+        <v>17.006</v>
       </c>
       <c r="C136">
-        <v>261.047</v>
+        <v>17.006</v>
       </c>
       <c r="D136">
-        <v>32.734</v>
+        <v>56.579</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3982,16 +3982,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
-        <v>360</v>
+        <v>144.936</v>
       </c>
       <c r="C137">
-        <v>360</v>
+        <v>144.936</v>
       </c>
       <c r="D137">
-        <v>123.811</v>
+        <v>88.91200000000001</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -4002,16 +4002,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>-77.712</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>-77.712</v>
       </c>
       <c r="D138">
-        <v>62.098</v>
+        <v>34.579</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>-89.917</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-89.917</v>
       </c>
       <c r="D139">
-        <v>54.869</v>
+        <v>54.887</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -4042,16 +4042,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
-        <v>79.467</v>
+        <v>-2457.607</v>
       </c>
       <c r="C140">
-        <v>79.467</v>
+        <v>-2457.607</v>
       </c>
       <c r="D140">
-        <v>162.999</v>
+        <v>158.192</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -4062,16 +4062,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
-        <v>205.022</v>
+        <v>-570.112</v>
       </c>
       <c r="C141">
-        <v>205.022</v>
+        <v>-570.112</v>
       </c>
       <c r="D141">
-        <v>85.514</v>
+        <v>140.677</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -4082,16 +4082,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
-        <v>74.245</v>
+        <v>-97.93899999999999</v>
       </c>
       <c r="C142">
-        <v>74.245</v>
+        <v>-97.93899999999999</v>
       </c>
       <c r="D142">
-        <v>77.163</v>
+        <v>69.203</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -4102,16 +4102,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
-        <v>26.693</v>
+        <v>10.528</v>
       </c>
       <c r="C143">
-        <v>26.693</v>
+        <v>10.528</v>
       </c>
       <c r="D143">
-        <v>80.645</v>
+        <v>73.38500000000001</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -4122,16 +4122,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>15.221</v>
+        <v>-66.432</v>
       </c>
       <c r="C144">
-        <v>15.221</v>
+        <v>-66.432</v>
       </c>
       <c r="D144">
-        <v>141.354</v>
+        <v>58.221</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -4142,16 +4142,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
-        <v>17.584</v>
+        <v>-17.2</v>
       </c>
       <c r="C145">
-        <v>17.584</v>
+        <v>-17.2</v>
       </c>
       <c r="D145">
-        <v>143.422</v>
+        <v>79.86199999999999</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -4162,16 +4162,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
-        <v>4.176</v>
+        <v>12.993</v>
       </c>
       <c r="C146">
-        <v>4.176</v>
+        <v>12.993</v>
       </c>
       <c r="D146">
-        <v>132.788</v>
+        <v>60.84</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4182,16 +4182,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>52.348</v>
+        <v>699.7089999999999</v>
       </c>
       <c r="C147">
-        <v>52.348</v>
+        <v>699.7089999999999</v>
       </c>
       <c r="D147">
-        <v>67.754</v>
+        <v>-9.718</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4202,16 +4202,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
-        <v>13.383</v>
+        <v>92.93600000000001</v>
       </c>
       <c r="C148">
-        <v>13.383</v>
+        <v>92.93600000000001</v>
       </c>
       <c r="D148">
-        <v>114.844</v>
+        <v>57.287</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4222,16 +4222,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>9.859</v>
+        <v>-163.593</v>
       </c>
       <c r="C149">
-        <v>9.859</v>
+        <v>-163.593</v>
       </c>
       <c r="D149">
-        <v>21.108</v>
+        <v>65.211</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4242,16 +4242,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>12.518</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>12.518</v>
       </c>
       <c r="D150">
-        <v>32.048</v>
+        <v>20.118</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4262,16 +4262,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>201.278</v>
+        <v>17.056</v>
       </c>
       <c r="C151">
-        <v>201.278</v>
+        <v>17.056</v>
       </c>
       <c r="D151">
-        <v>82.315</v>
+        <v>28.881</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4282,16 +4282,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
-        <v>201.68</v>
+        <v>120.707</v>
       </c>
       <c r="C152">
-        <v>201.68</v>
+        <v>120.707</v>
       </c>
       <c r="D152">
-        <v>133.037</v>
+        <v>47.566</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4302,16 +4302,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
-        <v>182.771</v>
+        <v>-4.358</v>
       </c>
       <c r="C153">
-        <v>182.771</v>
+        <v>-4.358</v>
       </c>
       <c r="D153">
-        <v>97.991</v>
+        <v>57.673</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4322,16 +4322,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
-        <v>-2234.168</v>
+        <v>-51.751</v>
       </c>
       <c r="C154">
-        <v>-2234.168</v>
+        <v>-51.751</v>
       </c>
       <c r="D154">
-        <v>118.295</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4342,16 +4342,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
-        <v>202.183</v>
+        <v>5.696</v>
       </c>
       <c r="C155">
-        <v>202.183</v>
+        <v>5.696</v>
       </c>
       <c r="D155">
-        <v>80.34399999999999</v>
+        <v>66.099</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4362,16 +4362,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
-        <v>203.521</v>
+        <v>260.839</v>
       </c>
       <c r="C156">
-        <v>203.521</v>
+        <v>260.839</v>
       </c>
       <c r="D156">
-        <v>63.333</v>
+        <v>60.095</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4382,16 +4382,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
-        <v>202.02</v>
+        <v>260.943</v>
       </c>
       <c r="C157">
-        <v>202.02</v>
+        <v>260.943</v>
       </c>
       <c r="D157">
-        <v>45.716</v>
+        <v>64.15300000000001</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4402,16 +4402,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
-        <v>-945.2619999999999</v>
+        <v>259.479</v>
       </c>
       <c r="C158">
-        <v>-945.2619999999999</v>
+        <v>259.479</v>
       </c>
       <c r="D158">
-        <v>92.879</v>
+        <v>63.866</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4422,16 +4422,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
-        <v>199.883</v>
+        <v>2.945</v>
       </c>
       <c r="C159">
-        <v>199.883</v>
+        <v>2.945</v>
       </c>
       <c r="D159">
-        <v>98.203</v>
+        <v>59.821</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4442,16 +4442,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>188.746</v>
+        <v>-100</v>
       </c>
       <c r="C160">
-        <v>188.746</v>
+        <v>-100</v>
       </c>
       <c r="D160">
-        <v>98.342</v>
+        <v>43.742</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4462,16 +4462,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>201.171</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>201.171</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>38.438</v>
+        <v>27.91</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4482,16 +4482,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>1348.567</v>
+        <v>-73.628</v>
       </c>
       <c r="C162">
-        <v>1348.567</v>
+        <v>-73.628</v>
       </c>
       <c r="D162">
-        <v>-54.599</v>
+        <v>66.545</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4502,16 +4502,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>2774.972</v>
+        <v>-289.756</v>
       </c>
       <c r="C163">
-        <v>2774.972</v>
+        <v>-289.756</v>
       </c>
       <c r="D163">
-        <v>-70.148</v>
+        <v>62.289</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4522,16 +4522,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>5644.058</v>
+        <v>-108</v>
       </c>
       <c r="C164">
-        <v>5644.058</v>
+        <v>-108</v>
       </c>
       <c r="D164">
-        <v>-64.934</v>
+        <v>43.615</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4542,16 +4542,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>2676.904</v>
+        <v>1962.205</v>
       </c>
       <c r="C165">
-        <v>2676.904</v>
+        <v>1962.205</v>
       </c>
       <c r="D165">
-        <v>-110.235</v>
+        <v>-15.175</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4562,16 +4562,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>2155.103</v>
+        <v>271</v>
       </c>
       <c r="C166">
-        <v>2155.103</v>
+        <v>271</v>
       </c>
       <c r="D166">
-        <v>-180.169</v>
+        <v>50.289</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4582,16 +4582,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>2568.742</v>
+        <v>1723.735</v>
       </c>
       <c r="C167">
-        <v>2568.742</v>
+        <v>1723.735</v>
       </c>
       <c r="D167">
-        <v>-155.306</v>
+        <v>-21.571</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4602,16 +4602,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>1787.788</v>
+        <v>360</v>
       </c>
       <c r="C168">
-        <v>1787.788</v>
+        <v>360</v>
       </c>
       <c r="D168">
-        <v>-181.23</v>
+        <v>5.929</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4622,16 +4622,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
-        <v>1595.783</v>
+        <v>502</v>
       </c>
       <c r="C169">
-        <v>1595.783</v>
+        <v>502</v>
       </c>
       <c r="D169">
-        <v>-145.281</v>
+        <v>0.199</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4642,16 +4642,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
-        <v>1692.629</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>1692.629</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>-60.514</v>
+        <v>45.052</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4662,16 +4662,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
-        <v>1692.373</v>
+        <v>494.43</v>
       </c>
       <c r="C171">
-        <v>1692.373</v>
+        <v>494.43</v>
       </c>
       <c r="D171">
-        <v>-96.726</v>
+        <v>69.34699999999999</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4682,16 +4682,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
-        <v>1693.345</v>
+        <v>284.108</v>
       </c>
       <c r="C172">
-        <v>1693.345</v>
+        <v>284.108</v>
       </c>
       <c r="D172">
-        <v>-47.878</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4702,16 +4702,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
-        <v>1692.179</v>
+        <v>276.546</v>
       </c>
       <c r="C173">
-        <v>1692.179</v>
+        <v>276.546</v>
       </c>
       <c r="D173">
-        <v>-61.677</v>
+        <v>111.532</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4722,16 +4722,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
-        <v>1758.22</v>
+        <v>271.314</v>
       </c>
       <c r="C174">
-        <v>1758.22</v>
+        <v>271.314</v>
       </c>
       <c r="D174">
-        <v>-91.79300000000001</v>
+        <v>94.477</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4742,16 +4742,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>1761.018</v>
+        <v>269</v>
       </c>
       <c r="C175">
-        <v>1761.018</v>
+        <v>269</v>
       </c>
       <c r="D175">
-        <v>-37.987</v>
+        <v>37.172</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4762,16 +4762,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
-        <v>1761.16</v>
+        <v>269.048</v>
       </c>
       <c r="C176">
-        <v>1761.16</v>
+        <v>269.048</v>
       </c>
       <c r="D176">
-        <v>-2.139</v>
+        <v>59.36</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4782,16 +4782,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>228.5</v>
+        <v>269</v>
       </c>
       <c r="C177">
-        <v>228.5</v>
+        <v>269</v>
       </c>
       <c r="D177">
-        <v>25.916</v>
+        <v>25.46</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4802,16 +4802,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>445.838</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>445.838</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>88.946</v>
+        <v>13.761</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4822,16 +4822,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>606.3</v>
+        <v>0</v>
       </c>
       <c r="C179">
-        <v>606.3</v>
+        <v>0</v>
       </c>
       <c r="D179">
-        <v>122.944</v>
+        <v>1.937</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4842,16 +4842,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>601</v>
+        <v>1737.724</v>
       </c>
       <c r="C180">
-        <v>601</v>
+        <v>1737.724</v>
       </c>
       <c r="D180">
-        <v>118.072</v>
+        <v>-14.592</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4862,16 +4862,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>27.339</v>
+        <v>1516.961</v>
       </c>
       <c r="C181">
-        <v>27.339</v>
+        <v>1516.961</v>
       </c>
       <c r="D181">
-        <v>60.249</v>
+        <v>-15.491</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4882,16 +4882,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>-312.077</v>
+        <v>1244.498</v>
       </c>
       <c r="C182">
-        <v>-312.077</v>
+        <v>1244.498</v>
       </c>
       <c r="D182">
-        <v>25.383</v>
+        <v>-38.305</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4902,16 +4902,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>134.812</v>
+        <v>1275.644</v>
       </c>
       <c r="C183">
-        <v>134.812</v>
+        <v>1275.644</v>
       </c>
       <c r="D183">
-        <v>45.066</v>
+        <v>-47.325</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4922,16 +4922,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>35.61</v>
+        <v>1379.523</v>
       </c>
       <c r="C184">
-        <v>35.61</v>
+        <v>1379.523</v>
       </c>
       <c r="D184">
-        <v>64.928</v>
+        <v>-20.863</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4942,16 +4942,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
-        <v>178.144</v>
+        <v>50.045</v>
       </c>
       <c r="C185">
-        <v>178.144</v>
+        <v>50.045</v>
       </c>
       <c r="D185">
-        <v>89.227</v>
+        <v>2.977</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4962,16 +4962,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>262.457</v>
+        <v>1489.952</v>
       </c>
       <c r="C186">
-        <v>262.457</v>
+        <v>1489.952</v>
       </c>
       <c r="D186">
-        <v>22.183</v>
+        <v>-23.147</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4982,16 +4982,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>208.959</v>
+        <v>1514.958</v>
       </c>
       <c r="C187">
-        <v>208.959</v>
+        <v>1514.958</v>
       </c>
       <c r="D187">
-        <v>25.488</v>
+        <v>-19.412</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -5002,16 +5002,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>215.901</v>
+        <v>501</v>
       </c>
       <c r="C188">
-        <v>215.901</v>
+        <v>501</v>
       </c>
       <c r="D188">
-        <v>37.652</v>
+        <v>12.383</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -5022,16 +5022,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
-        <v>211.251</v>
+        <v>0</v>
       </c>
       <c r="C189">
-        <v>211.251</v>
+        <v>0</v>
       </c>
       <c r="D189">
-        <v>62.947</v>
+        <v>10.568</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -5042,16 +5042,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
-        <v>202.775</v>
+        <v>1304.461</v>
       </c>
       <c r="C190">
-        <v>202.775</v>
+        <v>1304.461</v>
       </c>
       <c r="D190">
-        <v>78.502</v>
+        <v>1.426</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -5062,16 +5062,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
-        <v>208.772</v>
+        <v>1167.048</v>
       </c>
       <c r="C191">
-        <v>208.772</v>
+        <v>1167.048</v>
       </c>
       <c r="D191">
-        <v>46.271</v>
+        <v>-7.897</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -5082,16 +5082,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
-        <v>209.336</v>
+        <v>430.259</v>
       </c>
       <c r="C192">
-        <v>209.336</v>
+        <v>430.259</v>
       </c>
       <c r="D192">
-        <v>14.759</v>
+        <v>24.73</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -5102,16 +5102,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>1179.098</v>
+        <v>357.118</v>
       </c>
       <c r="C193">
-        <v>1179.098</v>
+        <v>357.118</v>
       </c>
       <c r="D193">
-        <v>-30.023</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E193">
         <v>96</v>
@@ -5122,16 +5122,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>1000</v>
+        <v>360.899</v>
       </c>
       <c r="C194">
-        <v>1000</v>
+        <v>360.899</v>
       </c>
       <c r="D194">
-        <v>-23.219</v>
+        <v>39.941</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -5142,16 +5142,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
-        <v>501</v>
+        <v>1181.061</v>
       </c>
       <c r="C195">
-        <v>501</v>
+        <v>1181.061</v>
       </c>
       <c r="D195">
-        <v>9.744</v>
+        <v>1.983</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -5162,16 +5162,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
-        <v>1192.479</v>
+        <v>501</v>
       </c>
       <c r="C196">
-        <v>1192.479</v>
+        <v>501</v>
       </c>
       <c r="D196">
-        <v>-0.34</v>
+        <v>14.447</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -5182,16 +5182,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C197">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D197">
-        <v>2.998</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -5202,16 +5202,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>1585.627</v>
+        <v>1187.868</v>
       </c>
       <c r="C198">
-        <v>1585.627</v>
+        <v>1187.868</v>
       </c>
       <c r="D198">
-        <v>-31.371</v>
+        <v>-0.249</v>
       </c>
       <c r="E198">
         <v>5</v>
@@ -5222,16 +5222,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>1158.437</v>
+        <v>1227.207</v>
       </c>
       <c r="C199">
-        <v>1158.437</v>
+        <v>1227.207</v>
       </c>
       <c r="D199">
-        <v>-5.558</v>
+        <v>-25.348</v>
       </c>
       <c r="E199">
         <v>6</v>
@@ -5242,16 +5242,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>1441.179</v>
+        <v>1273.864</v>
       </c>
       <c r="C200">
-        <v>1441.179</v>
+        <v>1273.864</v>
       </c>
       <c r="D200">
-        <v>-43.768</v>
+        <v>-57.613</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -5262,16 +5262,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>1501.966</v>
+        <v>1388.725</v>
       </c>
       <c r="C201">
-        <v>1501.966</v>
+        <v>1388.725</v>
       </c>
       <c r="D201">
-        <v>-55.813</v>
+        <v>-6.366</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5282,16 +5282,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>1857.03</v>
+        <v>1325.643</v>
       </c>
       <c r="C202">
-        <v>1857.03</v>
+        <v>1325.643</v>
       </c>
       <c r="D202">
-        <v>-30.919</v>
+        <v>-21.299</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -5302,16 +5302,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>1129.19</v>
+        <v>1392.43</v>
       </c>
       <c r="C203">
-        <v>1129.19</v>
+        <v>1392.43</v>
       </c>
       <c r="D203">
-        <v>-20.796</v>
+        <v>-48.195</v>
       </c>
       <c r="E203">
         <v>10</v>
@@ -5322,16 +5322,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>1293.584</v>
+        <v>1368.11</v>
       </c>
       <c r="C204">
-        <v>1293.584</v>
+        <v>1368.11</v>
       </c>
       <c r="D204">
-        <v>-76.181</v>
+        <v>-39.962</v>
       </c>
       <c r="E204">
         <v>11</v>
@@ -5342,16 +5342,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>1545.809</v>
+        <v>1362.75</v>
       </c>
       <c r="C205">
-        <v>1545.809</v>
+        <v>1362.75</v>
       </c>
       <c r="D205">
-        <v>-50.163</v>
+        <v>-20.402</v>
       </c>
       <c r="E205">
         <v>12</v>
@@ -5362,16 +5362,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
-        <v>1198.339</v>
+        <v>1525.137</v>
       </c>
       <c r="C206">
-        <v>1198.339</v>
+        <v>1525.137</v>
       </c>
       <c r="D206">
-        <v>-37.548</v>
+        <v>-40.875</v>
       </c>
       <c r="E206">
         <v>13</v>
@@ -5382,16 +5382,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
-        <v>1013.517</v>
+        <v>1744.492</v>
       </c>
       <c r="C207">
-        <v>1013.517</v>
+        <v>1744.492</v>
       </c>
       <c r="D207">
-        <v>-42.168</v>
+        <v>-58.291</v>
       </c>
       <c r="E207">
         <v>14</v>
@@ -5402,16 +5402,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>1530.882</v>
+        <v>2638.804</v>
       </c>
       <c r="C208">
-        <v>1530.882</v>
+        <v>2638.804</v>
       </c>
       <c r="D208">
-        <v>-67.02800000000001</v>
+        <v>-65.776</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5422,16 +5422,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
-        <v>1722.401</v>
+        <v>1605.154</v>
       </c>
       <c r="C209">
-        <v>1722.401</v>
+        <v>1605.154</v>
       </c>
       <c r="D209">
-        <v>-97.07299999999999</v>
+        <v>-43.546</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5442,16 +5442,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
-        <v>2795.175</v>
+        <v>1594.546</v>
       </c>
       <c r="C210">
-        <v>2795.175</v>
+        <v>1594.546</v>
       </c>
       <c r="D210">
-        <v>-56.586</v>
+        <v>-56.16</v>
       </c>
       <c r="E210">
         <v>17</v>
@@ -5462,16 +5462,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
-        <v>1356.156</v>
+        <v>1310.551</v>
       </c>
       <c r="C211">
-        <v>1356.156</v>
+        <v>1310.551</v>
       </c>
       <c r="D211">
-        <v>-34.921</v>
+        <v>-29.6</v>
       </c>
       <c r="E211">
         <v>18</v>
@@ -5482,16 +5482,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>1683.919</v>
+        <v>1311.192</v>
       </c>
       <c r="C212">
-        <v>1683.919</v>
+        <v>1311.192</v>
       </c>
       <c r="D212">
-        <v>-41.586</v>
+        <v>-31.798</v>
       </c>
       <c r="E212">
         <v>19</v>
@@ -5502,16 +5502,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>1316.962</v>
+        <v>1339.499</v>
       </c>
       <c r="C213">
-        <v>1316.962</v>
+        <v>1339.499</v>
       </c>
       <c r="D213">
-        <v>-27.913</v>
+        <v>-92.3</v>
       </c>
       <c r="E213">
         <v>20</v>
@@ -5522,16 +5522,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>501</v>
+        <v>1334.311</v>
       </c>
       <c r="C214">
-        <v>501</v>
+        <v>1334.311</v>
       </c>
       <c r="D214">
-        <v>36.744</v>
+        <v>-30.189</v>
       </c>
       <c r="E214">
         <v>21</v>
@@ -5542,16 +5542,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>424.316</v>
+        <v>1326.286</v>
       </c>
       <c r="C215">
-        <v>424.316</v>
+        <v>1326.286</v>
       </c>
       <c r="D215">
-        <v>25.314</v>
+        <v>-32.7</v>
       </c>
       <c r="E215">
         <v>22</v>
@@ -5562,16 +5562,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>1344.781</v>
+        <v>1342.461</v>
       </c>
       <c r="C216">
-        <v>1344.781</v>
+        <v>1342.461</v>
       </c>
       <c r="D216">
-        <v>-15.84</v>
+        <v>-9.17</v>
       </c>
       <c r="E216">
         <v>23</v>
@@ -5582,16 +5582,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>3338.989</v>
+        <v>1342.83</v>
       </c>
       <c r="C217">
-        <v>3338.989</v>
+        <v>1342.83</v>
       </c>
       <c r="D217">
-        <v>-53.647</v>
+        <v>-8.798999999999999</v>
       </c>
       <c r="E217">
         <v>24</v>
@@ -5602,16 +5602,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>2422.004</v>
+        <v>1483.597</v>
       </c>
       <c r="C218">
-        <v>2422.004</v>
+        <v>1483.597</v>
       </c>
       <c r="D218">
-        <v>-24.456</v>
+        <v>-15.654</v>
       </c>
       <c r="E218">
         <v>25</v>
@@ -5622,16 +5622,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>3578.498</v>
+        <v>1345.909</v>
       </c>
       <c r="C219">
-        <v>3578.498</v>
+        <v>1345.909</v>
       </c>
       <c r="D219">
-        <v>-50.416</v>
+        <v>-7.882</v>
       </c>
       <c r="E219">
         <v>26</v>
@@ -5642,16 +5642,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>2890.208</v>
+        <v>1481.582</v>
       </c>
       <c r="C220">
-        <v>2890.208</v>
+        <v>1481.582</v>
       </c>
       <c r="D220">
-        <v>-90.533</v>
+        <v>-15.264</v>
       </c>
       <c r="E220">
         <v>27</v>
@@ -5662,16 +5662,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>2004.076</v>
+        <v>1399.042</v>
       </c>
       <c r="C221">
-        <v>2004.076</v>
+        <v>1399.042</v>
       </c>
       <c r="D221">
-        <v>-79.32899999999999</v>
+        <v>6.221</v>
       </c>
       <c r="E221">
         <v>28</v>
@@ -5682,16 +5682,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>6744.078</v>
+        <v>501</v>
       </c>
       <c r="C222">
-        <v>6744.078</v>
+        <v>501</v>
       </c>
       <c r="D222">
-        <v>-89.45399999999999</v>
+        <v>14.781</v>
       </c>
       <c r="E222">
         <v>29</v>
@@ -5702,16 +5702,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>5505.847</v>
+        <v>427.687</v>
       </c>
       <c r="C223">
-        <v>5505.847</v>
+        <v>427.687</v>
       </c>
       <c r="D223">
-        <v>-119.057</v>
+        <v>28.648</v>
       </c>
       <c r="E223">
         <v>30</v>
@@ -5722,16 +5722,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>3308.894</v>
+        <v>97.134</v>
       </c>
       <c r="C224">
-        <v>3308.894</v>
+        <v>97.134</v>
       </c>
       <c r="D224">
-        <v>-127.804</v>
+        <v>35.467</v>
       </c>
       <c r="E224">
         <v>31</v>
@@ -5742,16 +5742,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>4633.329</v>
+        <v>135.876</v>
       </c>
       <c r="C225">
-        <v>4633.329</v>
+        <v>135.876</v>
       </c>
       <c r="D225">
-        <v>-142.701</v>
+        <v>28.933</v>
       </c>
       <c r="E225">
         <v>32</v>
@@ -5762,16 +5762,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>1517.511</v>
+        <v>0</v>
       </c>
       <c r="C226">
-        <v>1517.511</v>
+        <v>0</v>
       </c>
       <c r="D226">
-        <v>-163.924</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>33</v>
@@ -5782,16 +5782,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B227">
-        <v>1467.55</v>
+        <v>0</v>
       </c>
       <c r="C227">
-        <v>1467.55</v>
+        <v>0</v>
       </c>
       <c r="D227">
-        <v>-135.887</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>34</v>
@@ -5802,16 +5802,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B228">
-        <v>1524.565</v>
+        <v>0</v>
       </c>
       <c r="C228">
-        <v>1524.565</v>
+        <v>0</v>
       </c>
       <c r="D228">
-        <v>-118.42</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>35</v>
@@ -5822,16 +5822,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B229">
-        <v>1461.208</v>
+        <v>0</v>
       </c>
       <c r="C229">
-        <v>1461.208</v>
+        <v>0</v>
       </c>
       <c r="D229">
-        <v>-68.19499999999999</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>36</v>
@@ -5842,16 +5842,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B230">
-        <v>908.519</v>
+        <v>0</v>
       </c>
       <c r="C230">
-        <v>908.519</v>
+        <v>0</v>
       </c>
       <c r="D230">
-        <v>-133.349</v>
+        <v>0</v>
       </c>
       <c r="E230">
         <v>37</v>
@@ -5862,16 +5862,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B231">
-        <v>749.898</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>749.898</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>-44.366</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>38</v>
@@ -5882,16 +5882,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B232">
-        <v>750.33</v>
+        <v>0</v>
       </c>
       <c r="C232">
-        <v>750.33</v>
+        <v>0</v>
       </c>
       <c r="D232">
-        <v>-14.122</v>
+        <v>0</v>
       </c>
       <c r="E232">
         <v>39</v>
@@ -5902,7 +5902,7 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -6262,7 +6262,7 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -6522,7 +6522,7 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -6622,7 +6622,7 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -6882,7 +6882,7 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -6922,7 +6922,7 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2">
-        <v>46295.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2">
-        <v>46295.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2">
-        <v>46295.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2">
-        <v>46295.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B289">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,582 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>01.10.20261</t>
-  </si>
-  <si>
-    <t>01.10.20262</t>
-  </si>
-  <si>
-    <t>01.10.20263</t>
-  </si>
-  <si>
-    <t>01.10.20264</t>
-  </si>
-  <si>
-    <t>01.10.20265</t>
-  </si>
-  <si>
-    <t>01.10.20266</t>
-  </si>
-  <si>
-    <t>01.10.20267</t>
-  </si>
-  <si>
-    <t>01.10.20268</t>
-  </si>
-  <si>
-    <t>01.10.20269</t>
-  </si>
-  <si>
-    <t>01.10.202610</t>
-  </si>
-  <si>
-    <t>01.10.202611</t>
-  </si>
-  <si>
-    <t>01.10.202612</t>
-  </si>
-  <si>
-    <t>01.10.202613</t>
-  </si>
-  <si>
-    <t>01.10.202614</t>
-  </si>
-  <si>
-    <t>01.10.202615</t>
-  </si>
-  <si>
-    <t>01.10.202616</t>
-  </si>
-  <si>
-    <t>01.10.202617</t>
-  </si>
-  <si>
-    <t>01.10.202618</t>
-  </si>
-  <si>
-    <t>01.10.202619</t>
-  </si>
-  <si>
-    <t>01.10.202620</t>
-  </si>
-  <si>
-    <t>01.10.202621</t>
-  </si>
-  <si>
-    <t>01.10.202622</t>
-  </si>
-  <si>
-    <t>01.10.202623</t>
-  </si>
-  <si>
-    <t>01.10.202624</t>
-  </si>
-  <si>
-    <t>01.10.202625</t>
-  </si>
-  <si>
-    <t>01.10.202626</t>
-  </si>
-  <si>
-    <t>01.10.202627</t>
-  </si>
-  <si>
-    <t>01.10.202628</t>
-  </si>
-  <si>
-    <t>01.10.202629</t>
-  </si>
-  <si>
-    <t>01.10.202630</t>
-  </si>
-  <si>
-    <t>01.10.202631</t>
-  </si>
-  <si>
-    <t>01.10.202632</t>
-  </si>
-  <si>
-    <t>01.10.202633</t>
-  </si>
-  <si>
-    <t>01.10.202634</t>
-  </si>
-  <si>
-    <t>01.10.202635</t>
-  </si>
-  <si>
-    <t>01.10.202636</t>
-  </si>
-  <si>
-    <t>01.10.202637</t>
-  </si>
-  <si>
-    <t>01.10.202638</t>
-  </si>
-  <si>
-    <t>01.10.202639</t>
-  </si>
-  <si>
-    <t>01.10.202640</t>
-  </si>
-  <si>
-    <t>01.10.202641</t>
-  </si>
-  <si>
-    <t>01.10.202642</t>
-  </si>
-  <si>
-    <t>01.10.202643</t>
-  </si>
-  <si>
-    <t>01.10.202644</t>
-  </si>
-  <si>
-    <t>01.10.202645</t>
-  </si>
-  <si>
-    <t>01.10.202646</t>
-  </si>
-  <si>
-    <t>01.10.202647</t>
-  </si>
-  <si>
-    <t>01.10.202648</t>
-  </si>
-  <si>
-    <t>01.10.202649</t>
-  </si>
-  <si>
-    <t>01.10.202650</t>
-  </si>
-  <si>
-    <t>01.10.202651</t>
-  </si>
-  <si>
-    <t>01.10.202652</t>
-  </si>
-  <si>
-    <t>01.10.202653</t>
-  </si>
-  <si>
-    <t>01.10.202654</t>
-  </si>
-  <si>
-    <t>01.10.202655</t>
-  </si>
-  <si>
-    <t>01.10.202656</t>
-  </si>
-  <si>
-    <t>01.10.202657</t>
-  </si>
-  <si>
-    <t>01.10.202658</t>
-  </si>
-  <si>
-    <t>01.10.202659</t>
-  </si>
-  <si>
-    <t>01.10.202660</t>
-  </si>
-  <si>
-    <t>01.10.202661</t>
-  </si>
-  <si>
-    <t>01.10.202662</t>
-  </si>
-  <si>
-    <t>01.10.202663</t>
-  </si>
-  <si>
-    <t>01.10.202664</t>
-  </si>
-  <si>
-    <t>01.10.202665</t>
-  </si>
-  <si>
-    <t>01.10.202666</t>
-  </si>
-  <si>
-    <t>01.10.202667</t>
-  </si>
-  <si>
-    <t>01.10.202668</t>
-  </si>
-  <si>
-    <t>01.10.202669</t>
-  </si>
-  <si>
-    <t>01.10.202670</t>
-  </si>
-  <si>
-    <t>01.10.202671</t>
-  </si>
-  <si>
-    <t>01.10.202672</t>
-  </si>
-  <si>
-    <t>01.10.202673</t>
-  </si>
-  <si>
-    <t>01.10.202674</t>
-  </si>
-  <si>
-    <t>01.10.202675</t>
-  </si>
-  <si>
-    <t>01.10.202676</t>
-  </si>
-  <si>
-    <t>01.10.202677</t>
-  </si>
-  <si>
-    <t>01.10.202678</t>
-  </si>
-  <si>
-    <t>01.10.202679</t>
-  </si>
-  <si>
-    <t>01.10.202680</t>
-  </si>
-  <si>
-    <t>01.10.202681</t>
-  </si>
-  <si>
-    <t>01.10.202682</t>
-  </si>
-  <si>
-    <t>01.10.202683</t>
-  </si>
-  <si>
-    <t>01.10.202684</t>
-  </si>
-  <si>
-    <t>01.10.202685</t>
-  </si>
-  <si>
-    <t>01.10.202686</t>
-  </si>
-  <si>
-    <t>01.10.202687</t>
-  </si>
-  <si>
-    <t>01.10.202688</t>
-  </si>
-  <si>
-    <t>01.10.202689</t>
-  </si>
-  <si>
-    <t>01.10.202690</t>
-  </si>
-  <si>
-    <t>01.10.202691</t>
-  </si>
-  <si>
-    <t>01.10.202692</t>
-  </si>
-  <si>
-    <t>01.10.202693</t>
-  </si>
-  <si>
-    <t>01.10.202694</t>
-  </si>
-  <si>
-    <t>01.10.202695</t>
-  </si>
-  <si>
-    <t>01.10.202696</t>
-  </si>
-  <si>
-    <t>02.10.20261</t>
-  </si>
-  <si>
-    <t>02.10.20262</t>
-  </si>
-  <si>
-    <t>02.10.20263</t>
-  </si>
-  <si>
-    <t>02.10.20264</t>
-  </si>
-  <si>
-    <t>02.10.20265</t>
-  </si>
-  <si>
-    <t>02.10.20266</t>
-  </si>
-  <si>
-    <t>02.10.20267</t>
-  </si>
-  <si>
-    <t>02.10.20268</t>
-  </si>
-  <si>
-    <t>02.10.20269</t>
-  </si>
-  <si>
-    <t>02.10.202610</t>
-  </si>
-  <si>
-    <t>02.10.202611</t>
-  </si>
-  <si>
-    <t>02.10.202612</t>
-  </si>
-  <si>
-    <t>02.10.202613</t>
-  </si>
-  <si>
-    <t>02.10.202614</t>
-  </si>
-  <si>
-    <t>02.10.202615</t>
-  </si>
-  <si>
-    <t>02.10.202616</t>
-  </si>
-  <si>
-    <t>02.10.202617</t>
-  </si>
-  <si>
-    <t>02.10.202618</t>
-  </si>
-  <si>
-    <t>02.10.202619</t>
-  </si>
-  <si>
-    <t>02.10.202620</t>
-  </si>
-  <si>
-    <t>02.10.202621</t>
-  </si>
-  <si>
-    <t>02.10.202622</t>
-  </si>
-  <si>
-    <t>02.10.202623</t>
-  </si>
-  <si>
-    <t>02.10.202624</t>
-  </si>
-  <si>
-    <t>02.10.202625</t>
-  </si>
-  <si>
-    <t>02.10.202626</t>
-  </si>
-  <si>
-    <t>02.10.202627</t>
-  </si>
-  <si>
-    <t>02.10.202628</t>
-  </si>
-  <si>
-    <t>02.10.202629</t>
-  </si>
-  <si>
-    <t>02.10.202630</t>
-  </si>
-  <si>
-    <t>02.10.202631</t>
-  </si>
-  <si>
-    <t>02.10.202632</t>
-  </si>
-  <si>
-    <t>02.10.202633</t>
-  </si>
-  <si>
-    <t>02.10.202634</t>
-  </si>
-  <si>
-    <t>02.10.202635</t>
-  </si>
-  <si>
-    <t>02.10.202636</t>
-  </si>
-  <si>
-    <t>02.10.202637</t>
-  </si>
-  <si>
-    <t>02.10.202638</t>
-  </si>
-  <si>
-    <t>02.10.202639</t>
-  </si>
-  <si>
-    <t>02.10.202640</t>
-  </si>
-  <si>
-    <t>02.10.202641</t>
-  </si>
-  <si>
-    <t>02.10.202642</t>
-  </si>
-  <si>
-    <t>02.10.202643</t>
-  </si>
-  <si>
-    <t>02.10.202644</t>
-  </si>
-  <si>
-    <t>02.10.202645</t>
-  </si>
-  <si>
-    <t>02.10.202646</t>
-  </si>
-  <si>
-    <t>02.10.202647</t>
-  </si>
-  <si>
-    <t>02.10.202648</t>
-  </si>
-  <si>
-    <t>02.10.202649</t>
-  </si>
-  <si>
-    <t>02.10.202650</t>
-  </si>
-  <si>
-    <t>02.10.202651</t>
-  </si>
-  <si>
-    <t>02.10.202652</t>
-  </si>
-  <si>
-    <t>02.10.202653</t>
-  </si>
-  <si>
-    <t>02.10.202654</t>
-  </si>
-  <si>
-    <t>02.10.202655</t>
-  </si>
-  <si>
-    <t>02.10.202656</t>
-  </si>
-  <si>
-    <t>02.10.202657</t>
-  </si>
-  <si>
-    <t>02.10.202658</t>
-  </si>
-  <si>
-    <t>02.10.202659</t>
-  </si>
-  <si>
-    <t>02.10.202660</t>
-  </si>
-  <si>
-    <t>02.10.202661</t>
-  </si>
-  <si>
-    <t>02.10.202662</t>
-  </si>
-  <si>
-    <t>02.10.202663</t>
-  </si>
-  <si>
-    <t>02.10.202664</t>
-  </si>
-  <si>
-    <t>02.10.202665</t>
-  </si>
-  <si>
-    <t>02.10.202666</t>
-  </si>
-  <si>
-    <t>02.10.202667</t>
-  </si>
-  <si>
-    <t>02.10.202668</t>
-  </si>
-  <si>
-    <t>02.10.202669</t>
-  </si>
-  <si>
-    <t>02.10.202670</t>
-  </si>
-  <si>
-    <t>02.10.202671</t>
-  </si>
-  <si>
-    <t>02.10.202672</t>
-  </si>
-  <si>
-    <t>02.10.202673</t>
-  </si>
-  <si>
-    <t>02.10.202674</t>
-  </si>
-  <si>
-    <t>02.10.202675</t>
-  </si>
-  <si>
-    <t>02.10.202676</t>
-  </si>
-  <si>
-    <t>02.10.202677</t>
-  </si>
-  <si>
-    <t>02.10.202678</t>
-  </si>
-  <si>
-    <t>02.10.202679</t>
-  </si>
-  <si>
-    <t>02.10.202680</t>
-  </si>
-  <si>
-    <t>02.10.202681</t>
-  </si>
-  <si>
-    <t>02.10.202682</t>
-  </si>
-  <si>
-    <t>02.10.202683</t>
-  </si>
-  <si>
-    <t>02.10.202684</t>
-  </si>
-  <si>
-    <t>02.10.202685</t>
-  </si>
-  <si>
-    <t>02.10.202686</t>
-  </si>
-  <si>
-    <t>02.10.202687</t>
-  </si>
-  <si>
-    <t>02.10.202688</t>
-  </si>
-  <si>
-    <t>02.10.202689</t>
-  </si>
-  <si>
-    <t>02.10.202690</t>
-  </si>
-  <si>
-    <t>02.10.202691</t>
-  </si>
-  <si>
-    <t>02.10.202692</t>
-  </si>
-  <si>
-    <t>02.10.202693</t>
-  </si>
-  <si>
-    <t>02.10.202694</t>
-  </si>
-  <si>
-    <t>02.10.202695</t>
-  </si>
-  <si>
-    <t>02.10.202696</t>
-  </si>
-  <si>
     <t>03.10.20261</t>
   </si>
   <si>
@@ -896,6 +320,294 @@
   </si>
   <si>
     <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F289"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1282,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>-31.271</v>
+        <v>360.899</v>
       </c>
       <c r="C2">
-        <v>-31.271</v>
+        <v>360.899</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>39.941</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1302,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46296.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>234.808</v>
+        <v>1181.061</v>
       </c>
       <c r="C3">
-        <v>234.808</v>
+        <v>1181.061</v>
       </c>
       <c r="D3">
-        <v>55.613</v>
+        <v>1.983</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1322,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46296.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>218.007</v>
+        <v>501</v>
       </c>
       <c r="C4">
-        <v>218.007</v>
+        <v>501</v>
       </c>
       <c r="D4">
-        <v>45.122</v>
+        <v>14.447</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1342,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46296.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>218.444</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>218.444</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>49.258</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1362,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46296.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>232.402</v>
+        <v>1187.868</v>
       </c>
       <c r="C6">
-        <v>232.402</v>
+        <v>1187.868</v>
       </c>
       <c r="D6">
-        <v>50.054</v>
+        <v>-0.249</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1382,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46296.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>218.725</v>
+        <v>1227.207</v>
       </c>
       <c r="C7">
-        <v>218.725</v>
+        <v>1227.207</v>
       </c>
       <c r="D7">
-        <v>63.19</v>
+        <v>-25.348</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1402,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46296.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>239.23</v>
+        <v>1273.864</v>
       </c>
       <c r="C8">
-        <v>239.23</v>
+        <v>1273.864</v>
       </c>
       <c r="D8">
-        <v>62.505</v>
+        <v>-57.613</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1422,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46296.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>208.185</v>
+        <v>1388.725</v>
       </c>
       <c r="C9">
-        <v>208.185</v>
+        <v>1388.725</v>
       </c>
       <c r="D9">
-        <v>42.75</v>
+        <v>-6.366</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1442,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46296.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>204.72</v>
+        <v>1325.643</v>
       </c>
       <c r="C10">
-        <v>204.72</v>
+        <v>1325.643</v>
       </c>
       <c r="D10">
-        <v>17.505</v>
+        <v>-21.299</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1462,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46296.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>200</v>
+        <v>1392.43</v>
       </c>
       <c r="C11">
-        <v>200</v>
+        <v>1392.43</v>
       </c>
       <c r="D11">
-        <v>10.989</v>
+        <v>-48.195</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1482,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46296.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>1183.078</v>
+        <v>1368.11</v>
       </c>
       <c r="C12">
-        <v>1183.078</v>
+        <v>1368.11</v>
       </c>
       <c r="D12">
-        <v>-1.237</v>
+        <v>-39.962</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1502,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46296.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>1416.921</v>
+        <v>1362.75</v>
       </c>
       <c r="C13">
-        <v>1416.921</v>
+        <v>1362.75</v>
       </c>
       <c r="D13">
-        <v>-9.31</v>
+        <v>-20.402</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1522,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46296.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>261</v>
+        <v>1525.137</v>
       </c>
       <c r="C14">
-        <v>261</v>
+        <v>1525.137</v>
       </c>
       <c r="D14">
-        <v>0.755</v>
+        <v>-40.875</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1542,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46296.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>1744.492</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1744.492</v>
       </c>
       <c r="D15">
-        <v>4.244</v>
+        <v>-58.291</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1562,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46296.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>1380.096</v>
+        <v>2638.804</v>
       </c>
       <c r="C16">
-        <v>1380.096</v>
+        <v>2638.804</v>
       </c>
       <c r="D16">
-        <v>-38.685</v>
+        <v>-65.776</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1582,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46296.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>1422.579</v>
+        <v>1605.154</v>
       </c>
       <c r="C17">
-        <v>1422.579</v>
+        <v>1605.154</v>
       </c>
       <c r="D17">
-        <v>-29.857</v>
+        <v>-43.546</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1602,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46296.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>362.092</v>
+        <v>1594.546</v>
       </c>
       <c r="C18">
-        <v>362.092</v>
+        <v>1594.546</v>
       </c>
       <c r="D18">
-        <v>8.826000000000001</v>
+        <v>-56.16</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1622,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46296.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>269.617</v>
+        <v>1310.551</v>
       </c>
       <c r="C19">
-        <v>269.617</v>
+        <v>1310.551</v>
       </c>
       <c r="D19">
-        <v>21.536</v>
+        <v>-29.6</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1642,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46296.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>253.484</v>
+        <v>1311.192</v>
       </c>
       <c r="C20">
-        <v>253.484</v>
+        <v>1311.192</v>
       </c>
       <c r="D20">
-        <v>30.082</v>
+        <v>-31.798</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1662,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46296.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>252.78</v>
+        <v>1339.499</v>
       </c>
       <c r="C21">
-        <v>252.78</v>
+        <v>1339.499</v>
       </c>
       <c r="D21">
-        <v>60.462</v>
+        <v>-92.3</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1682,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46296.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>283.06</v>
+        <v>1334.311</v>
       </c>
       <c r="C22">
-        <v>283.06</v>
+        <v>1334.311</v>
       </c>
       <c r="D22">
-        <v>66.247</v>
+        <v>-30.189</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1702,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46296.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>318.638</v>
+        <v>1326.286</v>
       </c>
       <c r="C23">
-        <v>318.638</v>
+        <v>1326.286</v>
       </c>
       <c r="D23">
-        <v>36.045</v>
+        <v>-32.7</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1722,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46296.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>259.14</v>
+        <v>1342.461</v>
       </c>
       <c r="C24">
-        <v>259.14</v>
+        <v>1342.461</v>
       </c>
       <c r="D24">
-        <v>40.878</v>
+        <v>-9.17</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1742,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46296.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>407.464</v>
+        <v>1342.83</v>
       </c>
       <c r="C25">
-        <v>407.464</v>
+        <v>1342.83</v>
       </c>
       <c r="D25">
-        <v>36.526</v>
+        <v>-8.798999999999999</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1762,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46296.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>382.411</v>
+        <v>1483.597</v>
       </c>
       <c r="C26">
-        <v>382.411</v>
+        <v>1483.597</v>
       </c>
       <c r="D26">
-        <v>88.569</v>
+        <v>-15.654</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1782,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46296.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>312.498</v>
+        <v>1345.909</v>
       </c>
       <c r="C27">
-        <v>312.498</v>
+        <v>1345.909</v>
       </c>
       <c r="D27">
-        <v>37.213</v>
+        <v>-7.882</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1802,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46296.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>400.431</v>
+        <v>1481.582</v>
       </c>
       <c r="C28">
-        <v>400.431</v>
+        <v>1481.582</v>
       </c>
       <c r="D28">
-        <v>67.44199999999999</v>
+        <v>-15.264</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1822,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46296.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>343.133</v>
+        <v>1399.042</v>
       </c>
       <c r="C29">
-        <v>343.133</v>
+        <v>1399.042</v>
       </c>
       <c r="D29">
-        <v>83.339</v>
+        <v>6.221</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1842,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46296.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>297.251</v>
+        <v>501</v>
       </c>
       <c r="C30">
-        <v>297.251</v>
+        <v>501</v>
       </c>
       <c r="D30">
-        <v>51.054</v>
+        <v>14.781</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1862,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46296.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>316.506</v>
+        <v>427.687</v>
       </c>
       <c r="C31">
-        <v>316.506</v>
+        <v>427.687</v>
       </c>
       <c r="D31">
-        <v>42.296</v>
+        <v>28.648</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1882,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46296.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>284.518</v>
+        <v>97.134</v>
       </c>
       <c r="C32">
-        <v>284.518</v>
+        <v>97.134</v>
       </c>
       <c r="D32">
-        <v>60.474</v>
+        <v>35.467</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1902,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46296.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>256.846</v>
+        <v>135.876</v>
       </c>
       <c r="C33">
-        <v>256.846</v>
+        <v>135.876</v>
       </c>
       <c r="D33">
-        <v>133.275</v>
+        <v>28.933</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1922,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46296.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>260.932</v>
+        <v>328.61</v>
       </c>
       <c r="C34">
-        <v>260.932</v>
+        <v>328.61</v>
       </c>
       <c r="D34">
-        <v>13.463</v>
+        <v>27.055</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1942,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46296.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>2272.529</v>
+        <v>102.936</v>
       </c>
       <c r="C35">
-        <v>2272.529</v>
+        <v>102.936</v>
       </c>
       <c r="D35">
-        <v>-36.007</v>
+        <v>39.925</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1962,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46296.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>262.281</v>
+        <v>217.81</v>
       </c>
       <c r="C36">
-        <v>262.281</v>
+        <v>217.81</v>
       </c>
       <c r="D36">
-        <v>16.846</v>
+        <v>13.139</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1982,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46296.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>-82.58199999999999</v>
+        <v>376.993</v>
       </c>
       <c r="C37">
-        <v>-82.58199999999999</v>
+        <v>376.993</v>
       </c>
       <c r="D37">
-        <v>57.961</v>
+        <v>25.7</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -2002,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46296.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>52.988</v>
+        <v>717.571</v>
       </c>
       <c r="C38">
-        <v>52.988</v>
+        <v>717.571</v>
       </c>
       <c r="D38">
-        <v>25.503</v>
+        <v>-0.85</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -2022,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46296.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>-281.747</v>
+        <v>929.418</v>
       </c>
       <c r="C39">
-        <v>-281.747</v>
+        <v>929.418</v>
       </c>
       <c r="D39">
-        <v>65.861</v>
+        <v>-57.287</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -2042,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46296.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>-615.252</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>-615.252</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>113.556</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -2062,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46296.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>-86.636</v>
+        <v>1058.121</v>
       </c>
       <c r="C41">
-        <v>-86.636</v>
+        <v>1058.121</v>
       </c>
       <c r="D41">
-        <v>226.388</v>
+        <v>-20.161</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -2082,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46296.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>-218.689</v>
+        <v>251.178</v>
       </c>
       <c r="C42">
-        <v>-218.689</v>
+        <v>251.178</v>
       </c>
       <c r="D42">
-        <v>138.93</v>
+        <v>5.615</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -2102,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46296.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>-283.873</v>
+        <v>127.712</v>
       </c>
       <c r="C43">
-        <v>-283.873</v>
+        <v>127.712</v>
       </c>
       <c r="D43">
-        <v>84.233</v>
+        <v>14.369</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -2122,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46296.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>-251.213</v>
+        <v>217.25</v>
       </c>
       <c r="C44">
-        <v>-251.213</v>
+        <v>217.25</v>
       </c>
       <c r="D44">
-        <v>162.517</v>
+        <v>8.318</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -2142,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46296.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>-278.337</v>
+        <v>122.913</v>
       </c>
       <c r="C45">
-        <v>-278.337</v>
+        <v>122.913</v>
       </c>
       <c r="D45">
-        <v>166.613</v>
+        <v>39.282</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -2162,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46296.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>-271.292</v>
+        <v>193.921</v>
       </c>
       <c r="C46">
-        <v>-271.292</v>
+        <v>193.921</v>
       </c>
       <c r="D46">
-        <v>120.277</v>
+        <v>22.032</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2182,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46296.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>-266.248</v>
+        <v>-130.066</v>
       </c>
       <c r="C47">
-        <v>-266.248</v>
+        <v>-130.066</v>
       </c>
       <c r="D47">
-        <v>139.53</v>
+        <v>28.399</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2202,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46296.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>-285.187</v>
+        <v>77.456</v>
       </c>
       <c r="C48">
-        <v>-285.187</v>
+        <v>77.456</v>
       </c>
       <c r="D48">
-        <v>159.873</v>
+        <v>19.198</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2222,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46296.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>-268.689</v>
+        <v>70.63200000000001</v>
       </c>
       <c r="C49">
-        <v>-268.689</v>
+        <v>70.63200000000001</v>
       </c>
       <c r="D49">
-        <v>140.446</v>
+        <v>5.233</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2242,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46296.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>-308.047</v>
+        <v>-67.762</v>
       </c>
       <c r="C50">
-        <v>-308.047</v>
+        <v>-67.762</v>
       </c>
       <c r="D50">
-        <v>157.08</v>
+        <v>30.98</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2262,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46296.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>-268.067</v>
+        <v>20.858</v>
       </c>
       <c r="C51">
-        <v>-268.067</v>
+        <v>20.858</v>
       </c>
       <c r="D51">
-        <v>141.083</v>
+        <v>17.458</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2282,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46296.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>-269.996</v>
+        <v>110.214</v>
       </c>
       <c r="C52">
-        <v>-269.996</v>
+        <v>110.214</v>
       </c>
       <c r="D52">
-        <v>166.76</v>
+        <v>17.805</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2302,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46296.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>-270.308</v>
+        <v>207.922</v>
       </c>
       <c r="C53">
-        <v>-270.308</v>
+        <v>207.922</v>
       </c>
       <c r="D53">
-        <v>148.979</v>
+        <v>8.401</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2322,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46296.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>-280.059</v>
+        <v>221.176</v>
       </c>
       <c r="C54">
-        <v>-280.059</v>
+        <v>221.176</v>
       </c>
       <c r="D54">
-        <v>153.104</v>
+        <v>7.042</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2342,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46296.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>-272.466</v>
+        <v>698.849</v>
       </c>
       <c r="C55">
-        <v>-272.466</v>
+        <v>698.849</v>
       </c>
       <c r="D55">
-        <v>144.438</v>
+        <v>-4.311</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2362,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46296.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>-287.168</v>
+        <v>183.48</v>
       </c>
       <c r="C56">
-        <v>-287.168</v>
+        <v>183.48</v>
       </c>
       <c r="D56">
-        <v>114.963</v>
+        <v>23.68</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2382,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46296.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>-284.63</v>
+        <v>700</v>
       </c>
       <c r="C57">
-        <v>-284.63</v>
+        <v>700</v>
       </c>
       <c r="D57">
-        <v>115.383</v>
+        <v>-14.402</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2402,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46296.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>-369.875</v>
+        <v>162.642</v>
       </c>
       <c r="C58">
-        <v>-369.875</v>
+        <v>162.642</v>
       </c>
       <c r="D58">
-        <v>179.42</v>
+        <v>7.824</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2422,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46296.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>-289.931</v>
+        <v>700</v>
       </c>
       <c r="C59">
-        <v>-289.931</v>
+        <v>700</v>
       </c>
       <c r="D59">
-        <v>128.418</v>
+        <v>-0.113</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2442,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46296.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>-290</v>
+        <v>-177.934</v>
       </c>
       <c r="C60">
-        <v>-290</v>
+        <v>-177.934</v>
       </c>
       <c r="D60">
-        <v>93.66800000000001</v>
+        <v>37.829</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2462,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46296.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>-282.009</v>
+        <v>179.234</v>
       </c>
       <c r="C61">
-        <v>-282.009</v>
+        <v>179.234</v>
       </c>
       <c r="D61">
-        <v>142.383</v>
+        <v>4.513</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2482,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46296.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>-2140.926</v>
+        <v>87.407</v>
       </c>
       <c r="C62">
-        <v>-2140.926</v>
+        <v>87.407</v>
       </c>
       <c r="D62">
-        <v>145.914</v>
+        <v>29.809</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2502,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46296.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>-350.9</v>
+        <v>44.691</v>
       </c>
       <c r="C63">
-        <v>-350.9</v>
+        <v>44.691</v>
       </c>
       <c r="D63">
-        <v>111.356</v>
+        <v>49.358</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2522,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46296.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>-277.288</v>
+        <v>252.287</v>
       </c>
       <c r="C64">
-        <v>-277.288</v>
+        <v>252.287</v>
       </c>
       <c r="D64">
-        <v>142.561</v>
+        <v>58.916</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2542,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46296.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>-289.506</v>
+        <v>252.824</v>
       </c>
       <c r="C65">
-        <v>-289.506</v>
+        <v>252.824</v>
       </c>
       <c r="D65">
-        <v>101.633</v>
+        <v>2.277</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2562,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46296.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>-285.798</v>
+        <v>1797.148</v>
       </c>
       <c r="C66">
-        <v>-285.798</v>
+        <v>1797.148</v>
       </c>
       <c r="D66">
-        <v>225.22</v>
+        <v>-19.305</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2582,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46296.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>-289.125</v>
+        <v>2132.44</v>
       </c>
       <c r="C67">
-        <v>-289.125</v>
+        <v>2132.44</v>
       </c>
       <c r="D67">
-        <v>131.283</v>
+        <v>-2.602</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2602,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46296.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>-289.317</v>
+        <v>1614.752</v>
       </c>
       <c r="C68">
-        <v>-289.317</v>
+        <v>1614.752</v>
       </c>
       <c r="D68">
-        <v>131.471</v>
+        <v>4.219</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2622,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46296.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>-289.639</v>
+        <v>1580.514</v>
       </c>
       <c r="C69">
-        <v>-289.639</v>
+        <v>1580.514</v>
       </c>
       <c r="D69">
-        <v>50.192</v>
+        <v>-11.161</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2642,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46296.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>200.28</v>
+        <v>457.223</v>
       </c>
       <c r="C70">
-        <v>200.28</v>
+        <v>457.223</v>
       </c>
       <c r="D70">
-        <v>67.252</v>
+        <v>40.836</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2662,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46296.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>4493.602</v>
+        <v>501</v>
       </c>
       <c r="C71">
-        <v>4493.602</v>
+        <v>501</v>
       </c>
       <c r="D71">
-        <v>-26.077</v>
+        <v>21.891</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2682,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46296.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>1547.234</v>
+        <v>439.075</v>
       </c>
       <c r="C72">
-        <v>1547.234</v>
+        <v>439.075</v>
       </c>
       <c r="D72">
-        <v>-20.598</v>
+        <v>29.922</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2702,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46296.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>1150.493</v>
+        <v>510</v>
       </c>
       <c r="C73">
-        <v>1150.493</v>
+        <v>510</v>
       </c>
       <c r="D73">
-        <v>-40.261</v>
+        <v>32.812</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2722,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46296.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>1935.902</v>
+        <v>397.507</v>
       </c>
       <c r="C74">
-        <v>1935.902</v>
+        <v>397.507</v>
       </c>
       <c r="D74">
-        <v>-10.265</v>
+        <v>37.412</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2742,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46296.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>1764.966</v>
+        <v>359.748</v>
       </c>
       <c r="C75">
-        <v>1764.966</v>
+        <v>359.748</v>
       </c>
       <c r="D75">
-        <v>-14.92</v>
+        <v>31.709</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2762,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46296.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>3990.666</v>
+        <v>503</v>
       </c>
       <c r="C76">
-        <v>3990.666</v>
+        <v>503</v>
       </c>
       <c r="D76">
-        <v>-59.827</v>
+        <v>9.359</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2782,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46296.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>2263.897</v>
+        <v>501.483</v>
       </c>
       <c r="C77">
-        <v>2263.897</v>
+        <v>501.483</v>
       </c>
       <c r="D77">
-        <v>-33.487</v>
+        <v>13.677</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2802,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46296.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C78">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D78">
-        <v>22.782</v>
+        <v>10.254</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2822,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46296.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>1611.713</v>
+        <v>458.089</v>
       </c>
       <c r="C79">
-        <v>1611.713</v>
+        <v>458.089</v>
       </c>
       <c r="D79">
-        <v>-19.178</v>
+        <v>13.588</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2842,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46296.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>1743.082</v>
+        <v>422.117</v>
       </c>
       <c r="C80">
-        <v>1743.082</v>
+        <v>422.117</v>
       </c>
       <c r="D80">
-        <v>-34.837</v>
+        <v>18.549</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2862,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46296.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>2121.247</v>
+        <v>465.061</v>
       </c>
       <c r="C81">
-        <v>2121.247</v>
+        <v>465.061</v>
       </c>
       <c r="D81">
-        <v>-34.502</v>
+        <v>17.165</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2882,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46296.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>2044.589</v>
+        <v>445.096</v>
       </c>
       <c r="C82">
-        <v>2044.589</v>
+        <v>445.096</v>
       </c>
       <c r="D82">
-        <v>-20.668</v>
+        <v>14.5</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2902,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46296.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>1749.118</v>
+        <v>480.444</v>
       </c>
       <c r="C83">
-        <v>1749.118</v>
+        <v>480.444</v>
       </c>
       <c r="D83">
-        <v>-34.556</v>
+        <v>-19.267</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2922,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46296.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>1767.026</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1767.026</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>-19.958</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2942,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46296.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>1584.367</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>1584.367</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>-24.885</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2962,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46296.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>1147.347</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>1147.347</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>-44.96</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2982,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46296.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>1182.276</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>1182.276</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>-34.66</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -3002,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46296.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>1437.874</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1437.874</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>-10.691</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -3022,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46296.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>1187.293</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1187.293</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>-4.339</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -3042,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46296.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>1529.2</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1529.2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>-7.274</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -3062,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46296.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>353.473</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>353.473</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>10.689</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -3082,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46296.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>286.566</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>286.566</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>12.93</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -3102,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46296.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>142.904</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>142.904</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>32.767</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -3122,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46296.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B94">
-        <v>86.002</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>86.002</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>51.775</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -3142,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46296.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B95">
-        <v>-12.28</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>-12.28</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>83.39400000000001</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -3162,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46296.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B96">
-        <v>81.577</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>81.577</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>86.179</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3182,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46296.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>105.458</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>105.458</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>77.191</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3202,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B98">
-        <v>-75.328</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>-75.328</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>34.786</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3222,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46297.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>-72.346</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>-72.346</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>49.235</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3242,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46297.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B100">
-        <v>-98.872</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>-98.872</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>25.869</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3262,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46297.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B101">
-        <v>-98.361</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>-98.361</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>28.743</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3282,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46297.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B102">
-        <v>-82.184</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>-82.184</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>32.506</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3302,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46297.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B103">
-        <v>-42.577</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>-42.577</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>54.865</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3322,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46297.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B104">
-        <v>-57.986</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>-57.986</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>39.506</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3342,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46297.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B105">
-        <v>-98.712</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>-98.712</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>24.109</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3362,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46297.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B106">
-        <v>1007.143</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>1007.143</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3382,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46297.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B107">
-        <v>-98.93600000000001</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>-98.93600000000001</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3402,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46297.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>-93.892</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>-93.892</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>36.259</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3422,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46297.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>-98.72799999999999</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>-98.72799999999999</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>2.307</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3442,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46297.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>5.235</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3462,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46297.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B111">
-        <v>1221.727</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1221.727</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>-13.584</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3482,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46297.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B112">
-        <v>246.679</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>246.679</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>12.17</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3502,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46297.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B113">
-        <v>240.996</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>240.996</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>22.168</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3522,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46297.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B114">
-        <v>219.289</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>219.289</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>59.642</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3542,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46297.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B115">
-        <v>229.412</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>229.412</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>41.456</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3562,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46297.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B116">
-        <v>239.633</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>239.633</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>45.187</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3582,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46297.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B117">
-        <v>9.863</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>9.863</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3602,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46297.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>1438.751</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1438.751</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>-14.401</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3622,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46297.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>1330.428</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>1330.428</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>-15.894</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3642,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46297.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>46.765</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3662,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46297.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>1398.776</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1398.776</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>-12.04</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3682,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46297.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>419.088</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>419.088</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3702,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46297.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>1448.702</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1448.702</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>-0.346</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3722,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46297.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>365.601</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>365.601</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>37.987</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3742,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46297.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>39.29</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3762,7 +3474,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46297.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3771,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>39.047</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3782,7 +3494,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46297.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3791,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>26.247</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3802,7 +3514,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46297.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3811,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>27.082</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3822,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46297.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>360.616</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>360.616</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>37.563</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3842,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46297.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>4705.021</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>4705.021</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>-32.568</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3862,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46297.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>1612.998</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1612.998</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>-4.121</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3882,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46297.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>206.952</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>206.952</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>28.473</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3902,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46297.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>22.389</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>22.389</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>62.997</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3922,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46297.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>1536.56</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1536.56</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>-79.212</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3942,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46297.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>68.28400000000001</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>68.28400000000001</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>9.157999999999999</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3962,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46297.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>17.006</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>17.006</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>56.579</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3982,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46297.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>144.936</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>144.936</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>88.91200000000001</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -4002,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46297.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>-77.712</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>-77.712</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>34.579</v>
+        <v>0</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -4022,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46297.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>-89.917</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>-89.917</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>54.887</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -4042,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46297.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>-2457.607</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>-2457.607</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>158.192</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -4062,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46297.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>-570.112</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>-570.112</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>140.677</v>
+        <v>0</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -4082,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46297.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>-97.93899999999999</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>-97.93899999999999</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>69.203</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -4102,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46297.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>10.528</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>10.528</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>73.38500000000001</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -4122,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46297.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>-66.432</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>-66.432</v>
+        <v>0</v>
       </c>
       <c r="D144">
-        <v>58.221</v>
+        <v>0</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -4142,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46297.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>-17.2</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>-17.2</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>79.86199999999999</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -4162,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46297.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>12.993</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>12.993</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>60.84</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4182,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46297.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>699.7089999999999</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>699.7089999999999</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>-9.718</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4202,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46297.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>92.93600000000001</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>92.93600000000001</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>57.287</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4222,16 +3934,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46297.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>-163.593</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>-163.593</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>65.211</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4242,16 +3954,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46297.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>12.518</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>12.518</v>
+        <v>0</v>
       </c>
       <c r="D150">
-        <v>20.118</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4262,16 +3974,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46297.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>17.056</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>17.056</v>
+        <v>0</v>
       </c>
       <c r="D151">
-        <v>28.881</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4282,16 +3994,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46297.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>120.707</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>120.707</v>
+        <v>0</v>
       </c>
       <c r="D152">
-        <v>47.566</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4302,16 +4014,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46297.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>-4.358</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>-4.358</v>
+        <v>0</v>
       </c>
       <c r="D153">
-        <v>57.673</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4322,16 +4034,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46297.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>-51.751</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>-51.751</v>
+        <v>0</v>
       </c>
       <c r="D154">
-        <v>75.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4342,16 +4054,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46297.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>5.696</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>5.696</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>66.099</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4362,16 +4074,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46297.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>260.839</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>260.839</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>60.095</v>
+        <v>0</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4382,16 +4094,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46297.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>260.943</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>260.943</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>64.15300000000001</v>
+        <v>0</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4402,16 +4114,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46297.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>259.479</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>259.479</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>63.866</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4422,16 +4134,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46297.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>2.945</v>
+        <v>0</v>
       </c>
       <c r="C159">
-        <v>2.945</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>59.821</v>
+        <v>0</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4442,16 +4154,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46297.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="C160">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>43.742</v>
+        <v>0</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4462,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46297.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4471,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>27.91</v>
+        <v>0</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4482,16 +4194,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46297.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>-73.628</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>-73.628</v>
+        <v>0</v>
       </c>
       <c r="D162">
-        <v>66.545</v>
+        <v>0</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4502,16 +4214,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46297.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>-289.756</v>
+        <v>0</v>
       </c>
       <c r="C163">
-        <v>-289.756</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>62.289</v>
+        <v>0</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4522,16 +4234,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46297.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>-108</v>
+        <v>0</v>
       </c>
       <c r="C164">
-        <v>-108</v>
+        <v>0</v>
       </c>
       <c r="D164">
-        <v>43.615</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4542,16 +4254,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46297.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>1962.205</v>
+        <v>0</v>
       </c>
       <c r="C165">
-        <v>1962.205</v>
+        <v>0</v>
       </c>
       <c r="D165">
-        <v>-15.175</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4562,16 +4274,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46297.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>50.289</v>
+        <v>0</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4582,16 +4294,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46297.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>1723.735</v>
+        <v>0</v>
       </c>
       <c r="C167">
-        <v>1723.735</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>-21.571</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4602,16 +4314,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46297.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="C168">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D168">
-        <v>5.929</v>
+        <v>0</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4622,16 +4334,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46297.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4642,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46297.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4651,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>45.052</v>
+        <v>0</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4662,16 +4374,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46297.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>494.43</v>
+        <v>0</v>
       </c>
       <c r="C171">
-        <v>494.43</v>
+        <v>0</v>
       </c>
       <c r="D171">
-        <v>69.34699999999999</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4682,16 +4394,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46297.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>284.108</v>
+        <v>0</v>
       </c>
       <c r="C172">
-        <v>284.108</v>
+        <v>0</v>
       </c>
       <c r="D172">
-        <v>81.43000000000001</v>
+        <v>0</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4702,16 +4414,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46297.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>276.546</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>276.546</v>
+        <v>0</v>
       </c>
       <c r="D173">
-        <v>111.532</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4722,16 +4434,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46297.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>271.314</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>271.314</v>
+        <v>0</v>
       </c>
       <c r="D174">
-        <v>94.477</v>
+        <v>0</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4742,16 +4454,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46297.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="C175">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="D175">
-        <v>37.172</v>
+        <v>0</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4762,16 +4474,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46297.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>269.048</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>269.048</v>
+        <v>0</v>
       </c>
       <c r="D176">
-        <v>59.36</v>
+        <v>0</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4782,16 +4494,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46297.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="D177">
-        <v>25.46</v>
+        <v>0</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4802,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46297.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4811,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>13.761</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4822,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46297.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4831,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>1.937</v>
+        <v>0</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4842,16 +4554,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46297.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>1737.724</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>1737.724</v>
+        <v>0</v>
       </c>
       <c r="D180">
-        <v>-14.592</v>
+        <v>0</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4862,16 +4574,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46297.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>1516.961</v>
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>1516.961</v>
+        <v>0</v>
       </c>
       <c r="D181">
-        <v>-15.491</v>
+        <v>0</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4882,16 +4594,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46297.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>1244.498</v>
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>1244.498</v>
+        <v>0</v>
       </c>
       <c r="D182">
-        <v>-38.305</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4902,16 +4614,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46297.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>1275.644</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>1275.644</v>
+        <v>0</v>
       </c>
       <c r="D183">
-        <v>-47.325</v>
+        <v>0</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4922,16 +4634,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46297.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>1379.523</v>
+        <v>0</v>
       </c>
       <c r="C184">
-        <v>1379.523</v>
+        <v>0</v>
       </c>
       <c r="D184">
-        <v>-20.863</v>
+        <v>0</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4942,16 +4654,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46297.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>50.045</v>
+        <v>0</v>
       </c>
       <c r="C185">
-        <v>50.045</v>
+        <v>0</v>
       </c>
       <c r="D185">
-        <v>2.977</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4962,16 +4674,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46297.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>1489.952</v>
+        <v>0</v>
       </c>
       <c r="C186">
-        <v>1489.952</v>
+        <v>0</v>
       </c>
       <c r="D186">
-        <v>-23.147</v>
+        <v>0</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4982,16 +4694,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46297.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>1514.958</v>
+        <v>0</v>
       </c>
       <c r="C187">
-        <v>1514.958</v>
+        <v>0</v>
       </c>
       <c r="D187">
-        <v>-19.412</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -5002,16 +4714,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46297.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="D188">
-        <v>12.383</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -5022,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46297.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -5031,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>10.568</v>
+        <v>0</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -5042,16 +4754,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46297.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="B190">
-        <v>1304.461</v>
+        <v>0</v>
       </c>
       <c r="C190">
-        <v>1304.461</v>
+        <v>0</v>
       </c>
       <c r="D190">
-        <v>1.426</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -5062,16 +4774,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46297.96875</v>
+        <v>46299.96875</v>
       </c>
       <c r="B191">
-        <v>1167.048</v>
+        <v>0</v>
       </c>
       <c r="C191">
-        <v>1167.048</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>-7.897</v>
+        <v>0</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -5082,16 +4794,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46297.97916666666</v>
+        <v>46299.97916666666</v>
       </c>
       <c r="B192">
-        <v>430.259</v>
+        <v>0</v>
       </c>
       <c r="C192">
-        <v>430.259</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>24.73</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -5102,1942 +4814,22 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46297.98958333334</v>
+        <v>46299.98958333334</v>
       </c>
       <c r="B193">
-        <v>357.118</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>357.118</v>
+        <v>0</v>
       </c>
       <c r="D193">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" s="2">
-        <v>46298</v>
-      </c>
-      <c r="B194">
-        <v>360.899</v>
-      </c>
-      <c r="C194">
-        <v>360.899</v>
-      </c>
-      <c r="D194">
-        <v>39.941</v>
-      </c>
-      <c r="E194">
-        <v>1</v>
-      </c>
-      <c r="F194" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" s="2">
-        <v>46298.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>1181.061</v>
-      </c>
-      <c r="C195">
-        <v>1181.061</v>
-      </c>
-      <c r="D195">
-        <v>1.983</v>
-      </c>
-      <c r="E195">
-        <v>2</v>
-      </c>
-      <c r="F195" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" s="2">
-        <v>46298.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>501</v>
-      </c>
-      <c r="C196">
-        <v>501</v>
-      </c>
-      <c r="D196">
-        <v>14.447</v>
-      </c>
-      <c r="E196">
-        <v>3</v>
-      </c>
-      <c r="F196" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" s="2">
-        <v>46298.03125</v>
-      </c>
-      <c r="B197">
-        <v>0</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
-      <c r="D197">
-        <v>8.000999999999999</v>
-      </c>
-      <c r="E197">
-        <v>4</v>
-      </c>
-      <c r="F197" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" s="2">
-        <v>46298.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>1187.868</v>
-      </c>
-      <c r="C198">
-        <v>1187.868</v>
-      </c>
-      <c r="D198">
-        <v>-0.249</v>
-      </c>
-      <c r="E198">
-        <v>5</v>
-      </c>
-      <c r="F198" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" s="2">
-        <v>46298.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>1227.207</v>
-      </c>
-      <c r="C199">
-        <v>1227.207</v>
-      </c>
-      <c r="D199">
-        <v>-25.348</v>
-      </c>
-      <c r="E199">
-        <v>6</v>
-      </c>
-      <c r="F199" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" s="2">
-        <v>46298.0625</v>
-      </c>
-      <c r="B200">
-        <v>1273.864</v>
-      </c>
-      <c r="C200">
-        <v>1273.864</v>
-      </c>
-      <c r="D200">
-        <v>-57.613</v>
-      </c>
-      <c r="E200">
-        <v>7</v>
-      </c>
-      <c r="F200" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201" s="2">
-        <v>46298.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>1388.725</v>
-      </c>
-      <c r="C201">
-        <v>1388.725</v>
-      </c>
-      <c r="D201">
-        <v>-6.366</v>
-      </c>
-      <c r="E201">
-        <v>8</v>
-      </c>
-      <c r="F201" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" s="2">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>1325.643</v>
-      </c>
-      <c r="C202">
-        <v>1325.643</v>
-      </c>
-      <c r="D202">
-        <v>-21.299</v>
-      </c>
-      <c r="E202">
-        <v>9</v>
-      </c>
-      <c r="F202" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" s="2">
-        <v>46298.09375</v>
-      </c>
-      <c r="B203">
-        <v>1392.43</v>
-      </c>
-      <c r="C203">
-        <v>1392.43</v>
-      </c>
-      <c r="D203">
-        <v>-48.195</v>
-      </c>
-      <c r="E203">
-        <v>10</v>
-      </c>
-      <c r="F203" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" s="2">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>1368.11</v>
-      </c>
-      <c r="C204">
-        <v>1368.11</v>
-      </c>
-      <c r="D204">
-        <v>-39.962</v>
-      </c>
-      <c r="E204">
-        <v>11</v>
-      </c>
-      <c r="F204" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" s="2">
-        <v>46298.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>1362.75</v>
-      </c>
-      <c r="C205">
-        <v>1362.75</v>
-      </c>
-      <c r="D205">
-        <v>-20.402</v>
-      </c>
-      <c r="E205">
-        <v>12</v>
-      </c>
-      <c r="F205" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206" s="2">
-        <v>46298.125</v>
-      </c>
-      <c r="B206">
-        <v>1525.137</v>
-      </c>
-      <c r="C206">
-        <v>1525.137</v>
-      </c>
-      <c r="D206">
-        <v>-40.875</v>
-      </c>
-      <c r="E206">
-        <v>13</v>
-      </c>
-      <c r="F206" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207" s="2">
-        <v>46298.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>1744.492</v>
-      </c>
-      <c r="C207">
-        <v>1744.492</v>
-      </c>
-      <c r="D207">
-        <v>-58.291</v>
-      </c>
-      <c r="E207">
-        <v>14</v>
-      </c>
-      <c r="F207" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208" s="2">
-        <v>46298.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>2638.804</v>
-      </c>
-      <c r="C208">
-        <v>2638.804</v>
-      </c>
-      <c r="D208">
-        <v>-65.776</v>
-      </c>
-      <c r="E208">
-        <v>15</v>
-      </c>
-      <c r="F208" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" s="2">
-        <v>46298.15625</v>
-      </c>
-      <c r="B209">
-        <v>1605.154</v>
-      </c>
-      <c r="C209">
-        <v>1605.154</v>
-      </c>
-      <c r="D209">
-        <v>-43.546</v>
-      </c>
-      <c r="E209">
-        <v>16</v>
-      </c>
-      <c r="F209" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" s="2">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>1594.546</v>
-      </c>
-      <c r="C210">
-        <v>1594.546</v>
-      </c>
-      <c r="D210">
-        <v>-56.16</v>
-      </c>
-      <c r="E210">
-        <v>17</v>
-      </c>
-      <c r="F210" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" s="2">
-        <v>46298.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>1310.551</v>
-      </c>
-      <c r="C211">
-        <v>1310.551</v>
-      </c>
-      <c r="D211">
-        <v>-29.6</v>
-      </c>
-      <c r="E211">
-        <v>18</v>
-      </c>
-      <c r="F211" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" s="2">
-        <v>46298.1875</v>
-      </c>
-      <c r="B212">
-        <v>1311.192</v>
-      </c>
-      <c r="C212">
-        <v>1311.192</v>
-      </c>
-      <c r="D212">
-        <v>-31.798</v>
-      </c>
-      <c r="E212">
-        <v>19</v>
-      </c>
-      <c r="F212" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" s="2">
-        <v>46298.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>1339.499</v>
-      </c>
-      <c r="C213">
-        <v>1339.499</v>
-      </c>
-      <c r="D213">
-        <v>-92.3</v>
-      </c>
-      <c r="E213">
-        <v>20</v>
-      </c>
-      <c r="F213" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" s="2">
-        <v>46298.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>1334.311</v>
-      </c>
-      <c r="C214">
-        <v>1334.311</v>
-      </c>
-      <c r="D214">
-        <v>-30.189</v>
-      </c>
-      <c r="E214">
-        <v>21</v>
-      </c>
-      <c r="F214" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215" s="2">
-        <v>46298.21875</v>
-      </c>
-      <c r="B215">
-        <v>1326.286</v>
-      </c>
-      <c r="C215">
-        <v>1326.286</v>
-      </c>
-      <c r="D215">
-        <v>-32.7</v>
-      </c>
-      <c r="E215">
-        <v>22</v>
-      </c>
-      <c r="F215" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216" s="2">
-        <v>46298.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>1342.461</v>
-      </c>
-      <c r="C216">
-        <v>1342.461</v>
-      </c>
-      <c r="D216">
-        <v>-9.17</v>
-      </c>
-      <c r="E216">
-        <v>23</v>
-      </c>
-      <c r="F216" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217" s="2">
-        <v>46298.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>1342.83</v>
-      </c>
-      <c r="C217">
-        <v>1342.83</v>
-      </c>
-      <c r="D217">
-        <v>-8.798999999999999</v>
-      </c>
-      <c r="E217">
-        <v>24</v>
-      </c>
-      <c r="F217" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218" s="2">
-        <v>46298.25</v>
-      </c>
-      <c r="B218">
-        <v>1483.597</v>
-      </c>
-      <c r="C218">
-        <v>1483.597</v>
-      </c>
-      <c r="D218">
-        <v>-15.654</v>
-      </c>
-      <c r="E218">
-        <v>25</v>
-      </c>
-      <c r="F218" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219" s="2">
-        <v>46298.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>1345.909</v>
-      </c>
-      <c r="C219">
-        <v>1345.909</v>
-      </c>
-      <c r="D219">
-        <v>-7.882</v>
-      </c>
-      <c r="E219">
-        <v>26</v>
-      </c>
-      <c r="F219" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220" s="2">
-        <v>46298.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>1481.582</v>
-      </c>
-      <c r="C220">
-        <v>1481.582</v>
-      </c>
-      <c r="D220">
-        <v>-15.264</v>
-      </c>
-      <c r="E220">
-        <v>27</v>
-      </c>
-      <c r="F220" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221" s="2">
-        <v>46298.28125</v>
-      </c>
-      <c r="B221">
-        <v>1399.042</v>
-      </c>
-      <c r="C221">
-        <v>1399.042</v>
-      </c>
-      <c r="D221">
-        <v>6.221</v>
-      </c>
-      <c r="E221">
-        <v>28</v>
-      </c>
-      <c r="F221" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222" s="2">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>501</v>
-      </c>
-      <c r="C222">
-        <v>501</v>
-      </c>
-      <c r="D222">
-        <v>14.781</v>
-      </c>
-      <c r="E222">
-        <v>29</v>
-      </c>
-      <c r="F222" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223" s="2">
-        <v>46298.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>427.687</v>
-      </c>
-      <c r="C223">
-        <v>427.687</v>
-      </c>
-      <c r="D223">
-        <v>28.648</v>
-      </c>
-      <c r="E223">
-        <v>30</v>
-      </c>
-      <c r="F223" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224" s="2">
-        <v>46298.3125</v>
-      </c>
-      <c r="B224">
-        <v>97.134</v>
-      </c>
-      <c r="C224">
-        <v>97.134</v>
-      </c>
-      <c r="D224">
-        <v>35.467</v>
-      </c>
-      <c r="E224">
-        <v>31</v>
-      </c>
-      <c r="F224" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225" s="2">
-        <v>46298.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>135.876</v>
-      </c>
-      <c r="C225">
-        <v>135.876</v>
-      </c>
-      <c r="D225">
-        <v>28.933</v>
-      </c>
-      <c r="E225">
-        <v>32</v>
-      </c>
-      <c r="F225" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226" s="2">
-        <v>46298.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>0</v>
-      </c>
-      <c r="C226">
-        <v>0</v>
-      </c>
-      <c r="D226">
-        <v>0</v>
-      </c>
-      <c r="E226">
-        <v>33</v>
-      </c>
-      <c r="F226" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227" s="2">
-        <v>46298.34375</v>
-      </c>
-      <c r="B227">
-        <v>0</v>
-      </c>
-      <c r="C227">
-        <v>0</v>
-      </c>
-      <c r="D227">
-        <v>0</v>
-      </c>
-      <c r="E227">
-        <v>34</v>
-      </c>
-      <c r="F227" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228" s="2">
-        <v>46298.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>0</v>
-      </c>
-      <c r="C228">
-        <v>0</v>
-      </c>
-      <c r="D228">
-        <v>0</v>
-      </c>
-      <c r="E228">
-        <v>35</v>
-      </c>
-      <c r="F228" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229" s="2">
-        <v>46298.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>0</v>
-      </c>
-      <c r="C229">
-        <v>0</v>
-      </c>
-      <c r="D229">
-        <v>0</v>
-      </c>
-      <c r="E229">
-        <v>36</v>
-      </c>
-      <c r="F229" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230" s="2">
-        <v>46298.375</v>
-      </c>
-      <c r="B230">
-        <v>0</v>
-      </c>
-      <c r="C230">
-        <v>0</v>
-      </c>
-      <c r="D230">
-        <v>0</v>
-      </c>
-      <c r="E230">
-        <v>37</v>
-      </c>
-      <c r="F230" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231" s="2">
-        <v>46298.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>0</v>
-      </c>
-      <c r="C231">
-        <v>0</v>
-      </c>
-      <c r="D231">
-        <v>0</v>
-      </c>
-      <c r="E231">
-        <v>38</v>
-      </c>
-      <c r="F231" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232" s="2">
-        <v>46298.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>0</v>
-      </c>
-      <c r="C232">
-        <v>0</v>
-      </c>
-      <c r="D232">
-        <v>0</v>
-      </c>
-      <c r="E232">
-        <v>39</v>
-      </c>
-      <c r="F232" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233" s="2">
-        <v>46298.40625</v>
-      </c>
-      <c r="B233">
-        <v>0</v>
-      </c>
-      <c r="C233">
-        <v>0</v>
-      </c>
-      <c r="D233">
-        <v>0</v>
-      </c>
-      <c r="E233">
-        <v>40</v>
-      </c>
-      <c r="F233" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234" s="2">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>0</v>
-      </c>
-      <c r="C234">
-        <v>0</v>
-      </c>
-      <c r="D234">
-        <v>0</v>
-      </c>
-      <c r="E234">
-        <v>41</v>
-      </c>
-      <c r="F234" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235" s="2">
-        <v>46298.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>0</v>
-      </c>
-      <c r="C235">
-        <v>0</v>
-      </c>
-      <c r="D235">
-        <v>0</v>
-      </c>
-      <c r="E235">
-        <v>42</v>
-      </c>
-      <c r="F235" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236" s="2">
-        <v>46298.4375</v>
-      </c>
-      <c r="B236">
-        <v>0</v>
-      </c>
-      <c r="C236">
-        <v>0</v>
-      </c>
-      <c r="D236">
-        <v>0</v>
-      </c>
-      <c r="E236">
-        <v>43</v>
-      </c>
-      <c r="F236" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237" s="2">
-        <v>46298.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>0</v>
-      </c>
-      <c r="C237">
-        <v>0</v>
-      </c>
-      <c r="D237">
-        <v>0</v>
-      </c>
-      <c r="E237">
-        <v>44</v>
-      </c>
-      <c r="F237" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238" s="2">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>0</v>
-      </c>
-      <c r="C238">
-        <v>0</v>
-      </c>
-      <c r="D238">
-        <v>0</v>
-      </c>
-      <c r="E238">
-        <v>45</v>
-      </c>
-      <c r="F238" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239" s="2">
-        <v>46298.46875</v>
-      </c>
-      <c r="B239">
-        <v>0</v>
-      </c>
-      <c r="C239">
-        <v>0</v>
-      </c>
-      <c r="D239">
-        <v>0</v>
-      </c>
-      <c r="E239">
-        <v>46</v>
-      </c>
-      <c r="F239" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240" s="2">
-        <v>46298.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>0</v>
-      </c>
-      <c r="C240">
-        <v>0</v>
-      </c>
-      <c r="D240">
-        <v>0</v>
-      </c>
-      <c r="E240">
-        <v>47</v>
-      </c>
-      <c r="F240" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241" s="2">
-        <v>46298.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>0</v>
-      </c>
-      <c r="C241">
-        <v>0</v>
-      </c>
-      <c r="D241">
-        <v>0</v>
-      </c>
-      <c r="E241">
-        <v>48</v>
-      </c>
-      <c r="F241" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242" s="2">
-        <v>46298.5</v>
-      </c>
-      <c r="B242">
-        <v>0</v>
-      </c>
-      <c r="C242">
-        <v>0</v>
-      </c>
-      <c r="D242">
-        <v>0</v>
-      </c>
-      <c r="E242">
-        <v>49</v>
-      </c>
-      <c r="F242" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243" s="2">
-        <v>46298.51041666666</v>
-      </c>
-      <c r="B243">
-        <v>0</v>
-      </c>
-      <c r="C243">
-        <v>0</v>
-      </c>
-      <c r="D243">
-        <v>0</v>
-      </c>
-      <c r="E243">
-        <v>50</v>
-      </c>
-      <c r="F243" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244" s="2">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="B244">
-        <v>0</v>
-      </c>
-      <c r="C244">
-        <v>0</v>
-      </c>
-      <c r="D244">
-        <v>0</v>
-      </c>
-      <c r="E244">
-        <v>51</v>
-      </c>
-      <c r="F244" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245" s="2">
-        <v>46298.53125</v>
-      </c>
-      <c r="B245">
-        <v>0</v>
-      </c>
-      <c r="C245">
-        <v>0</v>
-      </c>
-      <c r="D245">
-        <v>0</v>
-      </c>
-      <c r="E245">
-        <v>52</v>
-      </c>
-      <c r="F245" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246" s="2">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="B246">
-        <v>0</v>
-      </c>
-      <c r="C246">
-        <v>0</v>
-      </c>
-      <c r="D246">
-        <v>0</v>
-      </c>
-      <c r="E246">
-        <v>53</v>
-      </c>
-      <c r="F246" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247" s="2">
-        <v>46298.55208333334</v>
-      </c>
-      <c r="B247">
-        <v>0</v>
-      </c>
-      <c r="C247">
-        <v>0</v>
-      </c>
-      <c r="D247">
-        <v>0</v>
-      </c>
-      <c r="E247">
-        <v>54</v>
-      </c>
-      <c r="F247" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248" s="2">
-        <v>46298.5625</v>
-      </c>
-      <c r="B248">
-        <v>0</v>
-      </c>
-      <c r="C248">
-        <v>0</v>
-      </c>
-      <c r="D248">
-        <v>0</v>
-      </c>
-      <c r="E248">
-        <v>55</v>
-      </c>
-      <c r="F248" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249" s="2">
-        <v>46298.57291666666</v>
-      </c>
-      <c r="B249">
-        <v>0</v>
-      </c>
-      <c r="C249">
-        <v>0</v>
-      </c>
-      <c r="D249">
-        <v>0</v>
-      </c>
-      <c r="E249">
-        <v>56</v>
-      </c>
-      <c r="F249" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250" s="2">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="B250">
-        <v>0</v>
-      </c>
-      <c r="C250">
-        <v>0</v>
-      </c>
-      <c r="D250">
-        <v>0</v>
-      </c>
-      <c r="E250">
-        <v>57</v>
-      </c>
-      <c r="F250" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251" s="2">
-        <v>46298.59375</v>
-      </c>
-      <c r="B251">
-        <v>0</v>
-      </c>
-      <c r="C251">
-        <v>0</v>
-      </c>
-      <c r="D251">
-        <v>0</v>
-      </c>
-      <c r="E251">
-        <v>58</v>
-      </c>
-      <c r="F251" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252" s="2">
-        <v>46298.60416666666</v>
-      </c>
-      <c r="B252">
-        <v>0</v>
-      </c>
-      <c r="C252">
-        <v>0</v>
-      </c>
-      <c r="D252">
-        <v>0</v>
-      </c>
-      <c r="E252">
-        <v>59</v>
-      </c>
-      <c r="F252" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253" s="2">
-        <v>46298.61458333334</v>
-      </c>
-      <c r="B253">
-        <v>0</v>
-      </c>
-      <c r="C253">
-        <v>0</v>
-      </c>
-      <c r="D253">
-        <v>0</v>
-      </c>
-      <c r="E253">
-        <v>60</v>
-      </c>
-      <c r="F253" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254" s="2">
-        <v>46298.625</v>
-      </c>
-      <c r="B254">
-        <v>0</v>
-      </c>
-      <c r="C254">
-        <v>0</v>
-      </c>
-      <c r="D254">
-        <v>0</v>
-      </c>
-      <c r="E254">
-        <v>61</v>
-      </c>
-      <c r="F254" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255" s="2">
-        <v>46298.63541666666</v>
-      </c>
-      <c r="B255">
-        <v>0</v>
-      </c>
-      <c r="C255">
-        <v>0</v>
-      </c>
-      <c r="D255">
-        <v>0</v>
-      </c>
-      <c r="E255">
-        <v>62</v>
-      </c>
-      <c r="F255" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256" s="2">
-        <v>46298.64583333334</v>
-      </c>
-      <c r="B256">
-        <v>0</v>
-      </c>
-      <c r="C256">
-        <v>0</v>
-      </c>
-      <c r="D256">
-        <v>0</v>
-      </c>
-      <c r="E256">
-        <v>63</v>
-      </c>
-      <c r="F256" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257" s="2">
-        <v>46298.65625</v>
-      </c>
-      <c r="B257">
-        <v>0</v>
-      </c>
-      <c r="C257">
-        <v>0</v>
-      </c>
-      <c r="D257">
-        <v>0</v>
-      </c>
-      <c r="E257">
-        <v>64</v>
-      </c>
-      <c r="F257" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258" s="2">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="B258">
-        <v>0</v>
-      </c>
-      <c r="C258">
-        <v>0</v>
-      </c>
-      <c r="D258">
-        <v>0</v>
-      </c>
-      <c r="E258">
-        <v>65</v>
-      </c>
-      <c r="F258" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259" s="2">
-        <v>46298.67708333334</v>
-      </c>
-      <c r="B259">
-        <v>0</v>
-      </c>
-      <c r="C259">
-        <v>0</v>
-      </c>
-      <c r="D259">
-        <v>0</v>
-      </c>
-      <c r="E259">
-        <v>66</v>
-      </c>
-      <c r="F259" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260" s="2">
-        <v>46298.6875</v>
-      </c>
-      <c r="B260">
-        <v>0</v>
-      </c>
-      <c r="C260">
-        <v>0</v>
-      </c>
-      <c r="D260">
-        <v>0</v>
-      </c>
-      <c r="E260">
-        <v>67</v>
-      </c>
-      <c r="F260" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261" s="2">
-        <v>46298.69791666666</v>
-      </c>
-      <c r="B261">
-        <v>0</v>
-      </c>
-      <c r="C261">
-        <v>0</v>
-      </c>
-      <c r="D261">
-        <v>0</v>
-      </c>
-      <c r="E261">
-        <v>68</v>
-      </c>
-      <c r="F261" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262" s="2">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="B262">
-        <v>0</v>
-      </c>
-      <c r="C262">
-        <v>0</v>
-      </c>
-      <c r="D262">
-        <v>0</v>
-      </c>
-      <c r="E262">
-        <v>69</v>
-      </c>
-      <c r="F262" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263" s="2">
-        <v>46298.71875</v>
-      </c>
-      <c r="B263">
-        <v>0</v>
-      </c>
-      <c r="C263">
-        <v>0</v>
-      </c>
-      <c r="D263">
-        <v>0</v>
-      </c>
-      <c r="E263">
-        <v>70</v>
-      </c>
-      <c r="F263" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" s="2">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="B264">
-        <v>0</v>
-      </c>
-      <c r="C264">
-        <v>0</v>
-      </c>
-      <c r="D264">
-        <v>0</v>
-      </c>
-      <c r="E264">
-        <v>71</v>
-      </c>
-      <c r="F264" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265" s="2">
-        <v>46298.73958333334</v>
-      </c>
-      <c r="B265">
-        <v>0</v>
-      </c>
-      <c r="C265">
-        <v>0</v>
-      </c>
-      <c r="D265">
-        <v>0</v>
-      </c>
-      <c r="E265">
-        <v>72</v>
-      </c>
-      <c r="F265" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266" s="2">
-        <v>46298.75</v>
-      </c>
-      <c r="B266">
-        <v>0</v>
-      </c>
-      <c r="C266">
-        <v>0</v>
-      </c>
-      <c r="D266">
-        <v>0</v>
-      </c>
-      <c r="E266">
-        <v>73</v>
-      </c>
-      <c r="F266" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267" s="2">
-        <v>46298.76041666666</v>
-      </c>
-      <c r="B267">
-        <v>0</v>
-      </c>
-      <c r="C267">
-        <v>0</v>
-      </c>
-      <c r="D267">
-        <v>0</v>
-      </c>
-      <c r="E267">
-        <v>74</v>
-      </c>
-      <c r="F267" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
-      <c r="A268" s="2">
-        <v>46298.77083333334</v>
-      </c>
-      <c r="B268">
-        <v>0</v>
-      </c>
-      <c r="C268">
-        <v>0</v>
-      </c>
-      <c r="D268">
-        <v>0</v>
-      </c>
-      <c r="E268">
-        <v>75</v>
-      </c>
-      <c r="F268" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269" s="2">
-        <v>46298.78125</v>
-      </c>
-      <c r="B269">
-        <v>0</v>
-      </c>
-      <c r="C269">
-        <v>0</v>
-      </c>
-      <c r="D269">
-        <v>0</v>
-      </c>
-      <c r="E269">
-        <v>76</v>
-      </c>
-      <c r="F269" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" s="2">
-        <v>46298.79166666666</v>
-      </c>
-      <c r="B270">
-        <v>0</v>
-      </c>
-      <c r="C270">
-        <v>0</v>
-      </c>
-      <c r="D270">
-        <v>0</v>
-      </c>
-      <c r="E270">
-        <v>77</v>
-      </c>
-      <c r="F270" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271" s="2">
-        <v>46298.80208333334</v>
-      </c>
-      <c r="B271">
-        <v>0</v>
-      </c>
-      <c r="C271">
-        <v>0</v>
-      </c>
-      <c r="D271">
-        <v>0</v>
-      </c>
-      <c r="E271">
-        <v>78</v>
-      </c>
-      <c r="F271" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="A272" s="2">
-        <v>46298.8125</v>
-      </c>
-      <c r="B272">
-        <v>0</v>
-      </c>
-      <c r="C272">
-        <v>0</v>
-      </c>
-      <c r="D272">
-        <v>0</v>
-      </c>
-      <c r="E272">
-        <v>79</v>
-      </c>
-      <c r="F272" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273" s="2">
-        <v>46298.82291666666</v>
-      </c>
-      <c r="B273">
-        <v>0</v>
-      </c>
-      <c r="C273">
-        <v>0</v>
-      </c>
-      <c r="D273">
-        <v>0</v>
-      </c>
-      <c r="E273">
-        <v>80</v>
-      </c>
-      <c r="F273" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
-      <c r="A274" s="2">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="B274">
-        <v>0</v>
-      </c>
-      <c r="C274">
-        <v>0</v>
-      </c>
-      <c r="D274">
-        <v>0</v>
-      </c>
-      <c r="E274">
-        <v>81</v>
-      </c>
-      <c r="F274" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
-      <c r="A275" s="2">
-        <v>46298.84375</v>
-      </c>
-      <c r="B275">
-        <v>0</v>
-      </c>
-      <c r="C275">
-        <v>0</v>
-      </c>
-      <c r="D275">
-        <v>0</v>
-      </c>
-      <c r="E275">
-        <v>82</v>
-      </c>
-      <c r="F275" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
-      <c r="A276" s="2">
-        <v>46298.85416666666</v>
-      </c>
-      <c r="B276">
-        <v>0</v>
-      </c>
-      <c r="C276">
-        <v>0</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-      <c r="E276">
-        <v>83</v>
-      </c>
-      <c r="F276" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
-      <c r="A277" s="2">
-        <v>46298.86458333334</v>
-      </c>
-      <c r="B277">
-        <v>0</v>
-      </c>
-      <c r="C277">
-        <v>0</v>
-      </c>
-      <c r="D277">
-        <v>0</v>
-      </c>
-      <c r="E277">
-        <v>84</v>
-      </c>
-      <c r="F277" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
-      <c r="A278" s="2">
-        <v>46298.875</v>
-      </c>
-      <c r="B278">
-        <v>0</v>
-      </c>
-      <c r="C278">
-        <v>0</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278">
-        <v>85</v>
-      </c>
-      <c r="F278" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
-      <c r="A279" s="2">
-        <v>46298.88541666666</v>
-      </c>
-      <c r="B279">
-        <v>0</v>
-      </c>
-      <c r="C279">
-        <v>0</v>
-      </c>
-      <c r="D279">
-        <v>0</v>
-      </c>
-      <c r="E279">
-        <v>86</v>
-      </c>
-      <c r="F279" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
-      <c r="A280" s="2">
-        <v>46298.89583333334</v>
-      </c>
-      <c r="B280">
-        <v>0</v>
-      </c>
-      <c r="C280">
-        <v>0</v>
-      </c>
-      <c r="D280">
-        <v>0</v>
-      </c>
-      <c r="E280">
-        <v>87</v>
-      </c>
-      <c r="F280" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
-      <c r="A281" s="2">
-        <v>46298.90625</v>
-      </c>
-      <c r="B281">
-        <v>0</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
-      </c>
-      <c r="D281">
-        <v>0</v>
-      </c>
-      <c r="E281">
-        <v>88</v>
-      </c>
-      <c r="F281" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
-      <c r="A282" s="2">
-        <v>46298.91666666666</v>
-      </c>
-      <c r="B282">
-        <v>0</v>
-      </c>
-      <c r="C282">
-        <v>0</v>
-      </c>
-      <c r="D282">
-        <v>0</v>
-      </c>
-      <c r="E282">
-        <v>89</v>
-      </c>
-      <c r="F282" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
-      <c r="A283" s="2">
-        <v>46298.92708333334</v>
-      </c>
-      <c r="B283">
-        <v>0</v>
-      </c>
-      <c r="C283">
-        <v>0</v>
-      </c>
-      <c r="D283">
-        <v>0</v>
-      </c>
-      <c r="E283">
-        <v>90</v>
-      </c>
-      <c r="F283" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
-      <c r="A284" s="2">
-        <v>46298.9375</v>
-      </c>
-      <c r="B284">
-        <v>0</v>
-      </c>
-      <c r="C284">
-        <v>0</v>
-      </c>
-      <c r="D284">
-        <v>0</v>
-      </c>
-      <c r="E284">
-        <v>91</v>
-      </c>
-      <c r="F284" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
-      <c r="A285" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B285">
-        <v>0</v>
-      </c>
-      <c r="C285">
-        <v>0</v>
-      </c>
-      <c r="D285">
-        <v>0</v>
-      </c>
-      <c r="E285">
-        <v>92</v>
-      </c>
-      <c r="F285" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
-      <c r="A286" s="2">
-        <v>46298.95833333334</v>
-      </c>
-      <c r="B286">
-        <v>0</v>
-      </c>
-      <c r="C286">
-        <v>0</v>
-      </c>
-      <c r="D286">
-        <v>0</v>
-      </c>
-      <c r="E286">
-        <v>93</v>
-      </c>
-      <c r="F286" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
-      <c r="A287" s="2">
-        <v>46298.96875</v>
-      </c>
-      <c r="B287">
-        <v>0</v>
-      </c>
-      <c r="C287">
-        <v>0</v>
-      </c>
-      <c r="D287">
-        <v>0</v>
-      </c>
-      <c r="E287">
-        <v>94</v>
-      </c>
-      <c r="F287" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
-      <c r="A288" s="2">
-        <v>46298.97916666666</v>
-      </c>
-      <c r="B288">
-        <v>0</v>
-      </c>
-      <c r="C288">
-        <v>0</v>
-      </c>
-      <c r="D288">
-        <v>0</v>
-      </c>
-      <c r="E288">
-        <v>95</v>
-      </c>
-      <c r="F288" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
-      <c r="A289" s="2">
-        <v>46298.98958333334</v>
-      </c>
-      <c r="B289">
-        <v>0</v>
-      </c>
-      <c r="C289">
-        <v>0</v>
-      </c>
-      <c r="D289">
-        <v>0</v>
-      </c>
-      <c r="E289">
-        <v>96</v>
-      </c>
-      <c r="F289" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="486">
   <si>
     <t>Timestamp</t>
   </si>
@@ -608,6 +608,870 @@
   </si>
   <si>
     <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
+  </si>
+  <si>
+    <t>07.10.202642</t>
+  </si>
+  <si>
+    <t>07.10.202643</t>
+  </si>
+  <si>
+    <t>07.10.202644</t>
+  </si>
+  <si>
+    <t>07.10.202645</t>
+  </si>
+  <si>
+    <t>07.10.202646</t>
+  </si>
+  <si>
+    <t>07.10.202647</t>
+  </si>
+  <si>
+    <t>07.10.202648</t>
+  </si>
+  <si>
+    <t>07.10.202649</t>
+  </si>
+  <si>
+    <t>07.10.202650</t>
+  </si>
+  <si>
+    <t>07.10.202651</t>
+  </si>
+  <si>
+    <t>07.10.202652</t>
+  </si>
+  <si>
+    <t>07.10.202653</t>
+  </si>
+  <si>
+    <t>07.10.202654</t>
+  </si>
+  <si>
+    <t>07.10.202655</t>
+  </si>
+  <si>
+    <t>07.10.202656</t>
+  </si>
+  <si>
+    <t>07.10.202657</t>
+  </si>
+  <si>
+    <t>07.10.202658</t>
+  </si>
+  <si>
+    <t>07.10.202659</t>
+  </si>
+  <si>
+    <t>07.10.202660</t>
+  </si>
+  <si>
+    <t>07.10.202661</t>
+  </si>
+  <si>
+    <t>07.10.202662</t>
+  </si>
+  <si>
+    <t>07.10.202663</t>
+  </si>
+  <si>
+    <t>07.10.202664</t>
+  </si>
+  <si>
+    <t>07.10.202665</t>
+  </si>
+  <si>
+    <t>07.10.202666</t>
+  </si>
+  <si>
+    <t>07.10.202667</t>
+  </si>
+  <si>
+    <t>07.10.202668</t>
+  </si>
+  <si>
+    <t>07.10.202669</t>
+  </si>
+  <si>
+    <t>07.10.202670</t>
+  </si>
+  <si>
+    <t>07.10.202671</t>
+  </si>
+  <si>
+    <t>07.10.202672</t>
+  </si>
+  <si>
+    <t>07.10.202673</t>
+  </si>
+  <si>
+    <t>07.10.202674</t>
+  </si>
+  <si>
+    <t>07.10.202675</t>
+  </si>
+  <si>
+    <t>07.10.202676</t>
+  </si>
+  <si>
+    <t>07.10.202677</t>
+  </si>
+  <si>
+    <t>07.10.202678</t>
+  </si>
+  <si>
+    <t>07.10.202679</t>
+  </si>
+  <si>
+    <t>07.10.202680</t>
+  </si>
+  <si>
+    <t>07.10.202681</t>
+  </si>
+  <si>
+    <t>07.10.202682</t>
+  </si>
+  <si>
+    <t>07.10.202683</t>
+  </si>
+  <si>
+    <t>07.10.202684</t>
+  </si>
+  <si>
+    <t>07.10.202685</t>
+  </si>
+  <si>
+    <t>07.10.202686</t>
+  </si>
+  <si>
+    <t>07.10.202687</t>
+  </si>
+  <si>
+    <t>07.10.202688</t>
+  </si>
+  <si>
+    <t>07.10.202689</t>
+  </si>
+  <si>
+    <t>07.10.202690</t>
+  </si>
+  <si>
+    <t>07.10.202691</t>
+  </si>
+  <si>
+    <t>07.10.202692</t>
+  </si>
+  <si>
+    <t>07.10.202693</t>
+  </si>
+  <si>
+    <t>07.10.202694</t>
+  </si>
+  <si>
+    <t>07.10.202695</t>
+  </si>
+  <si>
+    <t>07.10.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4832,6 +5696,5766 @@
         <v>197</v>
       </c>
     </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>525</v>
+      </c>
+      <c r="C328">
+        <v>525</v>
+      </c>
+      <c r="D328">
+        <v>9.144</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>395.594</v>
+      </c>
+      <c r="C329">
+        <v>395.594</v>
+      </c>
+      <c r="D329">
+        <v>21.834</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>1367.799</v>
+      </c>
+      <c r="C330">
+        <v>1367.799</v>
+      </c>
+      <c r="D330">
+        <v>-24.221</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>1167.137</v>
+      </c>
+      <c r="C331">
+        <v>1167.137</v>
+      </c>
+      <c r="D331">
+        <v>-16.429</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>961.8</v>
+      </c>
+      <c r="C332">
+        <v>961.8</v>
+      </c>
+      <c r="D332">
+        <v>-6.76</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>434.538</v>
+      </c>
+      <c r="C333">
+        <v>434.538</v>
+      </c>
+      <c r="D333">
+        <v>27.58</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>436.389</v>
+      </c>
+      <c r="C334">
+        <v>436.389</v>
+      </c>
+      <c r="D334">
+        <v>13.36</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>543.044</v>
+      </c>
+      <c r="C335">
+        <v>543.044</v>
+      </c>
+      <c r="D335">
+        <v>27.315</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>536.371</v>
+      </c>
+      <c r="C336">
+        <v>536.371</v>
+      </c>
+      <c r="D336">
+        <v>4.442</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>349.853</v>
+      </c>
+      <c r="C337">
+        <v>349.853</v>
+      </c>
+      <c r="D337">
+        <v>55.528</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>155.226</v>
+      </c>
+      <c r="C338">
+        <v>155.226</v>
+      </c>
+      <c r="D338">
+        <v>49.218</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>321.594</v>
+      </c>
+      <c r="C339">
+        <v>321.594</v>
+      </c>
+      <c r="D339">
+        <v>10.2</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>548.819</v>
+      </c>
+      <c r="C340">
+        <v>548.819</v>
+      </c>
+      <c r="D340">
+        <v>9.065</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>303.946</v>
+      </c>
+      <c r="C342">
+        <v>303.946</v>
+      </c>
+      <c r="D342">
+        <v>11.869</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>408.182</v>
+      </c>
+      <c r="C343">
+        <v>408.182</v>
+      </c>
+      <c r="D343">
+        <v>20.411</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>976.962</v>
+      </c>
+      <c r="C344">
+        <v>976.962</v>
+      </c>
+      <c r="D344">
+        <v>-4.756</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>978.215</v>
+      </c>
+      <c r="C345">
+        <v>978.215</v>
+      </c>
+      <c r="D345">
+        <v>-18.693</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>341.665</v>
+      </c>
+      <c r="C346">
+        <v>341.665</v>
+      </c>
+      <c r="D346">
+        <v>33.436</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>551</v>
+      </c>
+      <c r="C348">
+        <v>551</v>
+      </c>
+      <c r="D348">
+        <v>25.434</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>462.556</v>
+      </c>
+      <c r="C349">
+        <v>462.556</v>
+      </c>
+      <c r="D349">
+        <v>41.016</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>-4437.793</v>
+      </c>
+      <c r="C350">
+        <v>-4437.793</v>
+      </c>
+      <c r="D350">
+        <v>80.745</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>-322.603</v>
+      </c>
+      <c r="C351">
+        <v>-322.603</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>139.972</v>
+      </c>
+      <c r="C352">
+        <v>139.972</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>2.721</v>
+      </c>
+      <c r="C353">
+        <v>2.721</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>-490.123</v>
+      </c>
+      <c r="C354">
+        <v>-490.123</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>-34.062</v>
+      </c>
+      <c r="C355">
+        <v>-34.062</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>1.749</v>
+      </c>
+      <c r="C356">
+        <v>1.749</v>
+      </c>
+      <c r="D356">
+        <v>89.855</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>8.414999999999999</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>273</v>
+      </c>
+      <c r="C358">
+        <v>273</v>
+      </c>
+      <c r="D358">
+        <v>66.877</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>4.147</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>438</v>
+      </c>
+      <c r="C360">
+        <v>438</v>
+      </c>
+      <c r="D360">
+        <v>32.847</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>420.857</v>
+      </c>
+      <c r="C361">
+        <v>420.857</v>
+      </c>
+      <c r="D361">
+        <v>66.69</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>566.429</v>
+      </c>
+      <c r="C362">
+        <v>566.429</v>
+      </c>
+      <c r="D362">
+        <v>4.989</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>2257.208</v>
+      </c>
+      <c r="C363">
+        <v>2257.208</v>
+      </c>
+      <c r="D363">
+        <v>-15.157</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>3269.254</v>
+      </c>
+      <c r="C364">
+        <v>3269.254</v>
+      </c>
+      <c r="D364">
+        <v>-28.563</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>3266.817</v>
+      </c>
+      <c r="C365">
+        <v>3266.817</v>
+      </c>
+      <c r="D365">
+        <v>-30.708</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>2373.278</v>
+      </c>
+      <c r="C366">
+        <v>2373.278</v>
+      </c>
+      <c r="D366">
+        <v>-40.561</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>2405.178</v>
+      </c>
+      <c r="C367">
+        <v>2405.178</v>
+      </c>
+      <c r="D367">
+        <v>-11.181</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>626.2380000000001</v>
+      </c>
+      <c r="C368">
+        <v>626.2380000000001</v>
+      </c>
+      <c r="D368">
+        <v>22.746</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>610.423</v>
+      </c>
+      <c r="C369">
+        <v>610.423</v>
+      </c>
+      <c r="D369">
+        <v>3.603</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>609.962</v>
+      </c>
+      <c r="C370">
+        <v>609.962</v>
+      </c>
+      <c r="D370">
+        <v>5.445</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>610</v>
+      </c>
+      <c r="C371">
+        <v>610</v>
+      </c>
+      <c r="D371">
+        <v>15.974</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>33.99</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>575.352</v>
+      </c>
+      <c r="C373">
+        <v>575.352</v>
+      </c>
+      <c r="D373">
+        <v>36.342</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>555.237</v>
+      </c>
+      <c r="C374">
+        <v>555.237</v>
+      </c>
+      <c r="D374">
+        <v>1.29</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>480.726</v>
+      </c>
+      <c r="C375">
+        <v>480.726</v>
+      </c>
+      <c r="D375">
+        <v>3.638</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>489.529</v>
+      </c>
+      <c r="C376">
+        <v>489.529</v>
+      </c>
+      <c r="D376">
+        <v>13.821</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>377.928</v>
+      </c>
+      <c r="C377">
+        <v>377.928</v>
+      </c>
+      <c r="D377">
+        <v>3.242</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>1449.347</v>
+      </c>
+      <c r="C378">
+        <v>1449.347</v>
+      </c>
+      <c r="D378">
+        <v>-11.313</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>1685.062</v>
+      </c>
+      <c r="C379">
+        <v>1685.062</v>
+      </c>
+      <c r="D379">
+        <v>-14.552</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>497.813</v>
+      </c>
+      <c r="C380">
+        <v>497.813</v>
+      </c>
+      <c r="D380">
+        <v>3.03</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>336.344</v>
+      </c>
+      <c r="C381">
+        <v>336.344</v>
+      </c>
+      <c r="D381">
+        <v>18.361</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>1578.692</v>
+      </c>
+      <c r="C382">
+        <v>1578.692</v>
+      </c>
+      <c r="D382">
+        <v>-22.947</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>1397.774</v>
+      </c>
+      <c r="C383">
+        <v>1397.774</v>
+      </c>
+      <c r="D383">
+        <v>-0.996</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>1175.385</v>
+      </c>
+      <c r="C384">
+        <v>1175.385</v>
+      </c>
+      <c r="D384">
+        <v>-13.195</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1276.579</v>
+      </c>
+      <c r="C385">
+        <v>1276.579</v>
+      </c>
+      <c r="D385">
+        <v>-3.675</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>1678.859</v>
+      </c>
+      <c r="C386">
+        <v>1678.859</v>
+      </c>
+      <c r="D386">
+        <v>-30.334</v>
+      </c>
+      <c r="E386">
+        <v>1</v>
+      </c>
+      <c r="F386" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>1798.85</v>
+      </c>
+      <c r="C387">
+        <v>1798.85</v>
+      </c>
+      <c r="D387">
+        <v>-33.33</v>
+      </c>
+      <c r="E387">
+        <v>2</v>
+      </c>
+      <c r="F387" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>1626.006</v>
+      </c>
+      <c r="C388">
+        <v>1626.006</v>
+      </c>
+      <c r="D388">
+        <v>-44.472</v>
+      </c>
+      <c r="E388">
+        <v>3</v>
+      </c>
+      <c r="F388" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>1643.442</v>
+      </c>
+      <c r="C389">
+        <v>1643.442</v>
+      </c>
+      <c r="D389">
+        <v>-63.025</v>
+      </c>
+      <c r="E389">
+        <v>4</v>
+      </c>
+      <c r="F389" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>1624.72</v>
+      </c>
+      <c r="C390">
+        <v>1624.72</v>
+      </c>
+      <c r="D390">
+        <v>-52.517</v>
+      </c>
+      <c r="E390">
+        <v>5</v>
+      </c>
+      <c r="F390" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>1553.459</v>
+      </c>
+      <c r="C391">
+        <v>1553.459</v>
+      </c>
+      <c r="D391">
+        <v>-17.561</v>
+      </c>
+      <c r="E391">
+        <v>6</v>
+      </c>
+      <c r="F391" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>1532.427</v>
+      </c>
+      <c r="C392">
+        <v>1532.427</v>
+      </c>
+      <c r="D392">
+        <v>-35.121</v>
+      </c>
+      <c r="E392">
+        <v>7</v>
+      </c>
+      <c r="F392" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>1540.979</v>
+      </c>
+      <c r="C393">
+        <v>1540.979</v>
+      </c>
+      <c r="D393">
+        <v>-18.829</v>
+      </c>
+      <c r="E393">
+        <v>8</v>
+      </c>
+      <c r="F393" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>1509.89</v>
+      </c>
+      <c r="C394">
+        <v>1509.89</v>
+      </c>
+      <c r="D394">
+        <v>-17.549</v>
+      </c>
+      <c r="E394">
+        <v>9</v>
+      </c>
+      <c r="F394" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>1652.068</v>
+      </c>
+      <c r="C395">
+        <v>1652.068</v>
+      </c>
+      <c r="D395">
+        <v>-30.729</v>
+      </c>
+      <c r="E395">
+        <v>10</v>
+      </c>
+      <c r="F395" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>1380.121</v>
+      </c>
+      <c r="C396">
+        <v>1380.121</v>
+      </c>
+      <c r="D396">
+        <v>-9.476000000000001</v>
+      </c>
+      <c r="E396">
+        <v>11</v>
+      </c>
+      <c r="F396" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>1287.163</v>
+      </c>
+      <c r="C397">
+        <v>1287.163</v>
+      </c>
+      <c r="D397">
+        <v>-7</v>
+      </c>
+      <c r="E397">
+        <v>12</v>
+      </c>
+      <c r="F397" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>1365.638</v>
+      </c>
+      <c r="C398">
+        <v>1365.638</v>
+      </c>
+      <c r="D398">
+        <v>-10.508</v>
+      </c>
+      <c r="E398">
+        <v>13</v>
+      </c>
+      <c r="F398" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>1415.123</v>
+      </c>
+      <c r="C399">
+        <v>1415.123</v>
+      </c>
+      <c r="D399">
+        <v>-21.301</v>
+      </c>
+      <c r="E399">
+        <v>14</v>
+      </c>
+      <c r="F399" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>1364.463</v>
+      </c>
+      <c r="C400">
+        <v>1364.463</v>
+      </c>
+      <c r="D400">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="E400">
+        <v>15</v>
+      </c>
+      <c r="F400" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>1478.298</v>
+      </c>
+      <c r="C401">
+        <v>1478.298</v>
+      </c>
+      <c r="D401">
+        <v>-25.368</v>
+      </c>
+      <c r="E401">
+        <v>16</v>
+      </c>
+      <c r="F401" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>1420.438</v>
+      </c>
+      <c r="C402">
+        <v>1420.438</v>
+      </c>
+      <c r="D402">
+        <v>-7.155</v>
+      </c>
+      <c r="E402">
+        <v>17</v>
+      </c>
+      <c r="F402" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>1657.8</v>
+      </c>
+      <c r="C403">
+        <v>1657.8</v>
+      </c>
+      <c r="D403">
+        <v>-33.377</v>
+      </c>
+      <c r="E403">
+        <v>18</v>
+      </c>
+      <c r="F403" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>1540.548</v>
+      </c>
+      <c r="C404">
+        <v>1540.548</v>
+      </c>
+      <c r="D404">
+        <v>-20.912</v>
+      </c>
+      <c r="E404">
+        <v>19</v>
+      </c>
+      <c r="F404" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>2722.19</v>
+      </c>
+      <c r="C405">
+        <v>2722.19</v>
+      </c>
+      <c r="D405">
+        <v>-39.146</v>
+      </c>
+      <c r="E405">
+        <v>20</v>
+      </c>
+      <c r="F405" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>1684.118</v>
+      </c>
+      <c r="C406">
+        <v>1684.118</v>
+      </c>
+      <c r="D406">
+        <v>-9.603999999999999</v>
+      </c>
+      <c r="E406">
+        <v>21</v>
+      </c>
+      <c r="F406" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>1580.93</v>
+      </c>
+      <c r="C407">
+        <v>1580.93</v>
+      </c>
+      <c r="D407">
+        <v>-8.468</v>
+      </c>
+      <c r="E407">
+        <v>22</v>
+      </c>
+      <c r="F407" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>2093.89</v>
+      </c>
+      <c r="C408">
+        <v>2093.89</v>
+      </c>
+      <c r="D408">
+        <v>-25.279</v>
+      </c>
+      <c r="E408">
+        <v>23</v>
+      </c>
+      <c r="F408" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>1839.397</v>
+      </c>
+      <c r="C409">
+        <v>1839.397</v>
+      </c>
+      <c r="D409">
+        <v>-21.866</v>
+      </c>
+      <c r="E409">
+        <v>24</v>
+      </c>
+      <c r="F409" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>2070.268</v>
+      </c>
+      <c r="C410">
+        <v>2070.268</v>
+      </c>
+      <c r="D410">
+        <v>-22.007</v>
+      </c>
+      <c r="E410">
+        <v>25</v>
+      </c>
+      <c r="F410" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>2186.154</v>
+      </c>
+      <c r="C411">
+        <v>2186.154</v>
+      </c>
+      <c r="D411">
+        <v>-57.598</v>
+      </c>
+      <c r="E411">
+        <v>26</v>
+      </c>
+      <c r="F411" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>1888.714</v>
+      </c>
+      <c r="C412">
+        <v>1888.714</v>
+      </c>
+      <c r="D412">
+        <v>-37.875</v>
+      </c>
+      <c r="E412">
+        <v>27</v>
+      </c>
+      <c r="F412" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>1716.145</v>
+      </c>
+      <c r="C413">
+        <v>1716.145</v>
+      </c>
+      <c r="D413">
+        <v>-22.918</v>
+      </c>
+      <c r="E413">
+        <v>28</v>
+      </c>
+      <c r="F413" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>6031.961</v>
+      </c>
+      <c r="C414">
+        <v>6031.961</v>
+      </c>
+      <c r="D414">
+        <v>-63.792</v>
+      </c>
+      <c r="E414">
+        <v>29</v>
+      </c>
+      <c r="F414" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>2206.775</v>
+      </c>
+      <c r="C415">
+        <v>2206.775</v>
+      </c>
+      <c r="D415">
+        <v>-36.547</v>
+      </c>
+      <c r="E415">
+        <v>30</v>
+      </c>
+      <c r="F415" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>490.346</v>
+      </c>
+      <c r="C416">
+        <v>490.346</v>
+      </c>
+      <c r="D416">
+        <v>8.122999999999999</v>
+      </c>
+      <c r="E416">
+        <v>31</v>
+      </c>
+      <c r="F416" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>126.251</v>
+      </c>
+      <c r="C417">
+        <v>126.251</v>
+      </c>
+      <c r="D417">
+        <v>47.549</v>
+      </c>
+      <c r="E417">
+        <v>32</v>
+      </c>
+      <c r="F417" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1424.766</v>
+      </c>
+      <c r="C418">
+        <v>1424.766</v>
+      </c>
+      <c r="D418">
+        <v>-5.006</v>
+      </c>
+      <c r="E418">
+        <v>33</v>
+      </c>
+      <c r="F418" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>192.455</v>
+      </c>
+      <c r="C419">
+        <v>192.455</v>
+      </c>
+      <c r="D419">
+        <v>41.158</v>
+      </c>
+      <c r="E419">
+        <v>34</v>
+      </c>
+      <c r="F419" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>164.233</v>
+      </c>
+      <c r="C420">
+        <v>164.233</v>
+      </c>
+      <c r="D420">
+        <v>23.525</v>
+      </c>
+      <c r="E420">
+        <v>35</v>
+      </c>
+      <c r="F420" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>294.9</v>
+      </c>
+      <c r="C421">
+        <v>294.9</v>
+      </c>
+      <c r="D421">
+        <v>17.577</v>
+      </c>
+      <c r="E421">
+        <v>36</v>
+      </c>
+      <c r="F421" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>285.226</v>
+      </c>
+      <c r="C422">
+        <v>285.226</v>
+      </c>
+      <c r="D422">
+        <v>12.468</v>
+      </c>
+      <c r="E422">
+        <v>37</v>
+      </c>
+      <c r="F422" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>380</v>
+      </c>
+      <c r="C423">
+        <v>380</v>
+      </c>
+      <c r="D423">
+        <v>18.252</v>
+      </c>
+      <c r="E423">
+        <v>38</v>
+      </c>
+      <c r="F423" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>366.051</v>
+      </c>
+      <c r="C424">
+        <v>366.051</v>
+      </c>
+      <c r="D424">
+        <v>13.678</v>
+      </c>
+      <c r="E424">
+        <v>39</v>
+      </c>
+      <c r="F424" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>376.125</v>
+      </c>
+      <c r="C425">
+        <v>376.125</v>
+      </c>
+      <c r="D425">
+        <v>35.346</v>
+      </c>
+      <c r="E425">
+        <v>40</v>
+      </c>
+      <c r="F425" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>41</v>
+      </c>
+      <c r="F426" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>42</v>
+      </c>
+      <c r="F427" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>43</v>
+      </c>
+      <c r="F428" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+      <c r="E429">
+        <v>44</v>
+      </c>
+      <c r="F429" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>0</v>
+      </c>
+      <c r="E430">
+        <v>45</v>
+      </c>
+      <c r="F430" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>0</v>
+      </c>
+      <c r="E431">
+        <v>46</v>
+      </c>
+      <c r="F431" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432">
+        <v>47</v>
+      </c>
+      <c r="F432" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>48</v>
+      </c>
+      <c r="F433" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>0</v>
+      </c>
+      <c r="E434">
+        <v>49</v>
+      </c>
+      <c r="F434" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+      <c r="E435">
+        <v>50</v>
+      </c>
+      <c r="F435" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+      <c r="E436">
+        <v>51</v>
+      </c>
+      <c r="F436" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>0</v>
+      </c>
+      <c r="E437">
+        <v>52</v>
+      </c>
+      <c r="F437" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>0</v>
+      </c>
+      <c r="E438">
+        <v>53</v>
+      </c>
+      <c r="F438" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>0</v>
+      </c>
+      <c r="E439">
+        <v>54</v>
+      </c>
+      <c r="F439" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>0</v>
+      </c>
+      <c r="E440">
+        <v>55</v>
+      </c>
+      <c r="F440" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>0</v>
+      </c>
+      <c r="E441">
+        <v>56</v>
+      </c>
+      <c r="F441" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+      <c r="E442">
+        <v>57</v>
+      </c>
+      <c r="F442" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>0</v>
+      </c>
+      <c r="E443">
+        <v>58</v>
+      </c>
+      <c r="F443" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>0</v>
+      </c>
+      <c r="E444">
+        <v>59</v>
+      </c>
+      <c r="F444" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
+      <c r="E445">
+        <v>60</v>
+      </c>
+      <c r="F445" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>0</v>
+      </c>
+      <c r="E446">
+        <v>61</v>
+      </c>
+      <c r="F446" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>0</v>
+      </c>
+      <c r="E447">
+        <v>62</v>
+      </c>
+      <c r="F447" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+      <c r="E448">
+        <v>63</v>
+      </c>
+      <c r="F448" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>0</v>
+      </c>
+      <c r="E449">
+        <v>64</v>
+      </c>
+      <c r="F449" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>0</v>
+      </c>
+      <c r="E450">
+        <v>65</v>
+      </c>
+      <c r="F450" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>0</v>
+      </c>
+      <c r="E451">
+        <v>66</v>
+      </c>
+      <c r="F451" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>0</v>
+      </c>
+      <c r="E452">
+        <v>67</v>
+      </c>
+      <c r="F452" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>0</v>
+      </c>
+      <c r="E453">
+        <v>68</v>
+      </c>
+      <c r="F453" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>0</v>
+      </c>
+      <c r="E454">
+        <v>69</v>
+      </c>
+      <c r="F454" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+      <c r="E455">
+        <v>70</v>
+      </c>
+      <c r="F455" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>71</v>
+      </c>
+      <c r="F456" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+      <c r="E457">
+        <v>72</v>
+      </c>
+      <c r="F457" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+      <c r="E458">
+        <v>73</v>
+      </c>
+      <c r="F458" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+      <c r="E459">
+        <v>74</v>
+      </c>
+      <c r="F459" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460">
+        <v>75</v>
+      </c>
+      <c r="F460" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>0</v>
+      </c>
+      <c r="E461">
+        <v>76</v>
+      </c>
+      <c r="F461" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+      <c r="E462">
+        <v>77</v>
+      </c>
+      <c r="F462" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463">
+        <v>78</v>
+      </c>
+      <c r="F463" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+      <c r="E464">
+        <v>79</v>
+      </c>
+      <c r="F464" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465">
+        <v>80</v>
+      </c>
+      <c r="F465" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466">
+        <v>81</v>
+      </c>
+      <c r="F466" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+      <c r="E467">
+        <v>82</v>
+      </c>
+      <c r="F467" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+      <c r="E468">
+        <v>83</v>
+      </c>
+      <c r="F468" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+      <c r="E469">
+        <v>84</v>
+      </c>
+      <c r="F469" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <v>85</v>
+      </c>
+      <c r="F470" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+      <c r="E471">
+        <v>86</v>
+      </c>
+      <c r="F471" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
+      <c r="A472" s="2">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+      <c r="E472">
+        <v>87</v>
+      </c>
+      <c r="F472" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" s="2">
+        <v>46302.90625</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+      <c r="E473">
+        <v>88</v>
+      </c>
+      <c r="F473" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474" s="2">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+      <c r="E474">
+        <v>89</v>
+      </c>
+      <c r="F474" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" s="2">
+        <v>46302.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <v>90</v>
+      </c>
+      <c r="F475" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" s="2">
+        <v>46302.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>0</v>
+      </c>
+      <c r="E476">
+        <v>91</v>
+      </c>
+      <c r="F476" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" s="2">
+        <v>46302.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>0</v>
+      </c>
+      <c r="E477">
+        <v>92</v>
+      </c>
+      <c r="F477" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478" s="2">
+        <v>46302.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>0</v>
+      </c>
+      <c r="E478">
+        <v>93</v>
+      </c>
+      <c r="F478" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479" s="2">
+        <v>46302.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>0</v>
+      </c>
+      <c r="E479">
+        <v>94</v>
+      </c>
+      <c r="F479" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480" s="2">
+        <v>46302.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+      <c r="E480">
+        <v>95</v>
+      </c>
+      <c r="F480" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6">
+      <c r="A481" s="2">
+        <v>46302.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+      <c r="E481">
+        <v>96</v>
+      </c>
+      <c r="F481" t="s">
+        <v>485</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>1678.859</v>
+        <v>562.295</v>
       </c>
       <c r="C2">
-        <v>1678.859</v>
+        <v>562.295</v>
       </c>
       <c r="D2">
-        <v>-30.334</v>
+        <v>7.367</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>1798.85</v>
+        <v>605</v>
       </c>
       <c r="C3">
-        <v>1798.85</v>
+        <v>605</v>
       </c>
       <c r="D3">
-        <v>-33.33</v>
+        <v>9.551</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>1626.006</v>
+        <v>1032.564</v>
       </c>
       <c r="C4">
-        <v>1626.006</v>
+        <v>1032.564</v>
       </c>
       <c r="D4">
-        <v>-44.472</v>
+        <v>-12.846</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>1643.442</v>
+        <v>1510.645</v>
       </c>
       <c r="C5">
-        <v>1643.442</v>
+        <v>1510.645</v>
       </c>
       <c r="D5">
-        <v>-63.025</v>
+        <v>-13.904</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>1624.72</v>
+        <v>601.16</v>
       </c>
       <c r="C6">
-        <v>1624.72</v>
+        <v>601.16</v>
       </c>
       <c r="D6">
-        <v>-52.517</v>
+        <v>21.71</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>1553.459</v>
+        <v>602.223</v>
       </c>
       <c r="C7">
-        <v>1553.459</v>
+        <v>602.223</v>
       </c>
       <c r="D7">
-        <v>-17.561</v>
+        <v>25.853</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>1532.427</v>
+        <v>1158.879</v>
       </c>
       <c r="C8">
-        <v>1532.427</v>
+        <v>1158.879</v>
       </c>
       <c r="D8">
-        <v>-35.121</v>
+        <v>-6.145</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>1540.979</v>
+        <v>1343.916</v>
       </c>
       <c r="C9">
-        <v>1540.979</v>
+        <v>1343.916</v>
       </c>
       <c r="D9">
-        <v>-18.829</v>
+        <v>-17.752</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>1509.89</v>
+        <v>1413.056</v>
       </c>
       <c r="C10">
-        <v>1509.89</v>
+        <v>1413.056</v>
       </c>
       <c r="D10">
-        <v>-17.549</v>
+        <v>-27.552</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>1652.068</v>
+        <v>1742.969</v>
       </c>
       <c r="C11">
-        <v>1652.068</v>
+        <v>1742.969</v>
       </c>
       <c r="D11">
-        <v>-30.729</v>
+        <v>-32.638</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>1380.121</v>
+        <v>1633.449</v>
       </c>
       <c r="C12">
-        <v>1380.121</v>
+        <v>1633.449</v>
       </c>
       <c r="D12">
-        <v>-9.476000000000001</v>
+        <v>-33.394</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>1287.163</v>
+        <v>1522.331</v>
       </c>
       <c r="C13">
-        <v>1287.163</v>
+        <v>1522.331</v>
       </c>
       <c r="D13">
-        <v>-7</v>
+        <v>-28.679</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>1365.638</v>
+        <v>1470.989</v>
       </c>
       <c r="C14">
-        <v>1365.638</v>
+        <v>1470.989</v>
       </c>
       <c r="D14">
-        <v>-10.508</v>
+        <v>-23.848</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>1415.123</v>
+        <v>1485.859</v>
       </c>
       <c r="C15">
-        <v>1415.123</v>
+        <v>1485.859</v>
       </c>
       <c r="D15">
-        <v>-21.301</v>
+        <v>-45.023</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>1364.463</v>
+        <v>1611.406</v>
       </c>
       <c r="C16">
-        <v>1364.463</v>
+        <v>1611.406</v>
       </c>
       <c r="D16">
-        <v>-9.380000000000001</v>
+        <v>-26.001</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>1478.298</v>
+        <v>1729.39</v>
       </c>
       <c r="C17">
-        <v>1478.298</v>
+        <v>1729.39</v>
       </c>
       <c r="D17">
-        <v>-25.368</v>
+        <v>-30.675</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>1420.438</v>
+        <v>1290.807</v>
       </c>
       <c r="C18">
-        <v>1420.438</v>
+        <v>1290.807</v>
       </c>
       <c r="D18">
-        <v>-7.155</v>
+        <v>-20.761</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>1657.8</v>
+        <v>1391.495</v>
       </c>
       <c r="C19">
-        <v>1657.8</v>
+        <v>1391.495</v>
       </c>
       <c r="D19">
-        <v>-33.377</v>
+        <v>-23.683</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>1540.548</v>
+        <v>1175.15</v>
       </c>
       <c r="C20">
-        <v>1540.548</v>
+        <v>1175.15</v>
       </c>
       <c r="D20">
-        <v>-20.912</v>
+        <v>-30.451</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>2722.19</v>
+        <v>1246.458</v>
       </c>
       <c r="C21">
-        <v>2722.19</v>
+        <v>1246.458</v>
       </c>
       <c r="D21">
-        <v>-39.146</v>
+        <v>-29.638</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>1684.118</v>
+        <v>1319.886</v>
       </c>
       <c r="C22">
-        <v>1684.118</v>
+        <v>1319.886</v>
       </c>
       <c r="D22">
-        <v>-9.603999999999999</v>
+        <v>-22.956</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>1580.93</v>
+        <v>1195.457</v>
       </c>
       <c r="C23">
-        <v>1580.93</v>
+        <v>1195.457</v>
       </c>
       <c r="D23">
-        <v>-8.468</v>
+        <v>-7.891</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>2093.89</v>
+        <v>1668.3</v>
       </c>
       <c r="C24">
-        <v>2093.89</v>
+        <v>1668.3</v>
       </c>
       <c r="D24">
-        <v>-25.279</v>
+        <v>-27.599</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>1839.397</v>
+        <v>1506.273</v>
       </c>
       <c r="C25">
-        <v>1839.397</v>
+        <v>1506.273</v>
       </c>
       <c r="D25">
-        <v>-21.866</v>
+        <v>-6.823</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>2070.268</v>
+        <v>1774.641</v>
       </c>
       <c r="C26">
-        <v>2070.268</v>
+        <v>1774.641</v>
       </c>
       <c r="D26">
-        <v>-22.007</v>
+        <v>-17.159</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>2186.154</v>
+        <v>1784.375</v>
       </c>
       <c r="C27">
-        <v>2186.154</v>
+        <v>1784.375</v>
       </c>
       <c r="D27">
-        <v>-57.598</v>
+        <v>-20.483</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>1888.714</v>
+        <v>1820.379</v>
       </c>
       <c r="C28">
-        <v>1888.714</v>
+        <v>1820.379</v>
       </c>
       <c r="D28">
-        <v>-37.875</v>
+        <v>-5.544</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>1716.145</v>
+        <v>605</v>
       </c>
       <c r="C29">
-        <v>1716.145</v>
+        <v>605</v>
       </c>
       <c r="D29">
-        <v>-22.918</v>
+        <v>0.112</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>6031.961</v>
+        <v>1738.492</v>
       </c>
       <c r="C30">
-        <v>6031.961</v>
+        <v>1738.492</v>
       </c>
       <c r="D30">
-        <v>-63.792</v>
+        <v>-51.751</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>2206.775</v>
+        <v>1740.837</v>
       </c>
       <c r="C31">
-        <v>2206.775</v>
+        <v>1740.837</v>
       </c>
       <c r="D31">
-        <v>-36.547</v>
+        <v>-50.496</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>490.346</v>
+        <v>1756.296</v>
       </c>
       <c r="C32">
-        <v>490.346</v>
+        <v>1756.296</v>
       </c>
       <c r="D32">
-        <v>8.122999999999999</v>
+        <v>-28.042</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>126.251</v>
+        <v>1793.18</v>
       </c>
       <c r="C33">
-        <v>126.251</v>
+        <v>1793.18</v>
       </c>
       <c r="D33">
-        <v>47.549</v>
+        <v>-40.614</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>1424.766</v>
+        <v>1559.127</v>
       </c>
       <c r="C34">
-        <v>1424.766</v>
+        <v>1559.127</v>
       </c>
       <c r="D34">
-        <v>-5.006</v>
+        <v>-147.022</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>192.455</v>
+        <v>1572.406</v>
       </c>
       <c r="C35">
-        <v>192.455</v>
+        <v>1572.406</v>
       </c>
       <c r="D35">
-        <v>41.158</v>
+        <v>-120.177</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>164.233</v>
+        <v>1632.394</v>
       </c>
       <c r="C36">
-        <v>164.233</v>
+        <v>1632.394</v>
       </c>
       <c r="D36">
-        <v>23.525</v>
+        <v>-95.262</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>294.9</v>
+        <v>1571.259</v>
       </c>
       <c r="C37">
-        <v>294.9</v>
+        <v>1571.259</v>
       </c>
       <c r="D37">
-        <v>17.577</v>
+        <v>-0.014</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>285.226</v>
+        <v>1429.383</v>
       </c>
       <c r="C38">
-        <v>285.226</v>
+        <v>1429.383</v>
       </c>
       <c r="D38">
-        <v>12.468</v>
+        <v>-50.172</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>380</v>
+        <v>1430.02</v>
       </c>
       <c r="C39">
-        <v>380</v>
+        <v>1430.02</v>
       </c>
       <c r="D39">
-        <v>18.252</v>
+        <v>-6.302</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>366.051</v>
+        <v>1406.579</v>
       </c>
       <c r="C40">
-        <v>366.051</v>
+        <v>1406.579</v>
       </c>
       <c r="D40">
-        <v>13.678</v>
+        <v>-4.27</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>376.125</v>
+        <v>385.47</v>
       </c>
       <c r="C41">
-        <v>376.125</v>
+        <v>385.47</v>
       </c>
       <c r="D41">
-        <v>35.346</v>
+        <v>19.906</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>380.595</v>
+        <v>999.625</v>
       </c>
       <c r="C42">
-        <v>380.595</v>
+        <v>999.625</v>
       </c>
       <c r="D42">
-        <v>4.962</v>
+        <v>-0.767</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>252.575</v>
+        <v>587.7430000000001</v>
       </c>
       <c r="C43">
-        <v>252.575</v>
+        <v>587.7430000000001</v>
       </c>
       <c r="D43">
-        <v>20.053</v>
+        <v>8.605</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>380.013</v>
+        <v>394.41</v>
       </c>
       <c r="C44">
-        <v>380.013</v>
+        <v>394.41</v>
       </c>
       <c r="D44">
-        <v>4.635</v>
+        <v>16.344</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>29.691</v>
+        <v>491.2</v>
       </c>
       <c r="C45">
-        <v>29.691</v>
+        <v>491.2</v>
       </c>
       <c r="D45">
-        <v>45.879</v>
+        <v>51.954</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>139.506</v>
+        <v>445.223</v>
       </c>
       <c r="C46">
-        <v>139.506</v>
+        <v>445.223</v>
       </c>
       <c r="D46">
-        <v>10.596</v>
+        <v>53.567</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>309.995</v>
+        <v>353.761</v>
       </c>
       <c r="C47">
-        <v>309.995</v>
+        <v>353.761</v>
       </c>
       <c r="D47">
-        <v>44.048</v>
+        <v>47.517</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>302.044</v>
+        <v>321.397</v>
       </c>
       <c r="C48">
-        <v>302.044</v>
+        <v>321.397</v>
       </c>
       <c r="D48">
-        <v>60.957</v>
+        <v>27.03</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>308.546</v>
+        <v>424.482</v>
       </c>
       <c r="C49">
-        <v>308.546</v>
+        <v>424.482</v>
       </c>
       <c r="D49">
-        <v>12.373</v>
+        <v>5.277</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>191.753</v>
+        <v>363.239</v>
       </c>
       <c r="C50">
-        <v>191.753</v>
+        <v>363.239</v>
       </c>
       <c r="D50">
-        <v>27.679</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>337.929</v>
+        <v>700</v>
       </c>
       <c r="C51">
-        <v>337.929</v>
+        <v>700</v>
       </c>
       <c r="D51">
-        <v>12.744</v>
+        <v>-12.157</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>358.597</v>
+        <v>726.126</v>
       </c>
       <c r="C52">
-        <v>358.597</v>
+        <v>726.126</v>
       </c>
       <c r="D52">
-        <v>2.095</v>
+        <v>-24.043</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>336.453</v>
+        <v>1047.736</v>
       </c>
       <c r="C53">
-        <v>336.453</v>
+        <v>1047.736</v>
       </c>
       <c r="D53">
-        <v>8.250999999999999</v>
+        <v>-5.728</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>250.093</v>
+        <v>959.27</v>
       </c>
       <c r="C54">
-        <v>250.093</v>
+        <v>959.27</v>
       </c>
       <c r="D54">
-        <v>0.658</v>
+        <v>-5.743</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>1037.065</v>
+        <v>334.944</v>
       </c>
       <c r="C55">
-        <v>1037.065</v>
+        <v>334.944</v>
       </c>
       <c r="D55">
-        <v>-26.24</v>
+        <v>23.198</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>1105.336</v>
+        <v>384.586</v>
       </c>
       <c r="C56">
-        <v>1105.336</v>
+        <v>384.586</v>
       </c>
       <c r="D56">
-        <v>-2.371</v>
+        <v>22.813</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>1180.577</v>
+        <v>354.63</v>
       </c>
       <c r="C57">
-        <v>1180.577</v>
+        <v>354.63</v>
       </c>
       <c r="D57">
-        <v>-10.337</v>
+        <v>14.146</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>381</v>
+        <v>227.413</v>
       </c>
       <c r="C58">
-        <v>381</v>
+        <v>227.413</v>
       </c>
       <c r="D58">
-        <v>8.246</v>
+        <v>7.312</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>400</v>
+        <v>318.294</v>
       </c>
       <c r="C59">
-        <v>400</v>
+        <v>318.294</v>
       </c>
       <c r="D59">
-        <v>22.892</v>
+        <v>24.498</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>450</v>
+        <v>331.591</v>
       </c>
       <c r="C60">
-        <v>450</v>
+        <v>331.591</v>
       </c>
       <c r="D60">
-        <v>8.461</v>
+        <v>40.314</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>368.205</v>
+        <v>426</v>
       </c>
       <c r="C61">
-        <v>368.205</v>
+        <v>426</v>
       </c>
       <c r="D61">
-        <v>14.472</v>
+        <v>11.328</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>328.569</v>
+        <v>404.88</v>
       </c>
       <c r="C62">
-        <v>328.569</v>
+        <v>404.88</v>
       </c>
       <c r="D62">
-        <v>46.006</v>
+        <v>85.307</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>468.76</v>
+        <v>147.917</v>
       </c>
       <c r="C63">
-        <v>468.76</v>
+        <v>147.917</v>
       </c>
       <c r="D63">
-        <v>21.969</v>
+        <v>53.426</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>447.94</v>
+        <v>256.257</v>
       </c>
       <c r="C64">
-        <v>447.94</v>
+        <v>256.257</v>
       </c>
       <c r="D64">
-        <v>13.678</v>
+        <v>20.421</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>422.415</v>
+        <v>256</v>
       </c>
       <c r="C65">
-        <v>422.415</v>
+        <v>256</v>
       </c>
       <c r="D65">
-        <v>19.41</v>
+        <v>6.145</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>112.086</v>
+        <v>1481.764</v>
       </c>
       <c r="C66">
-        <v>112.086</v>
+        <v>1481.764</v>
       </c>
       <c r="D66">
-        <v>16.295</v>
+        <v>13.723</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>1444.456</v>
+        <v>1662.066</v>
       </c>
       <c r="C67">
-        <v>1444.456</v>
+        <v>1662.066</v>
       </c>
       <c r="D67">
-        <v>-1.994</v>
+        <v>-8.884</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>1674.737</v>
+        <v>2157.882</v>
       </c>
       <c r="C68">
-        <v>1674.737</v>
+        <v>2157.882</v>
       </c>
       <c r="D68">
-        <v>-4.975</v>
+        <v>-34.947</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>2033.379</v>
+        <v>1722.852</v>
       </c>
       <c r="C69">
-        <v>2033.379</v>
+        <v>1722.852</v>
       </c>
       <c r="D69">
-        <v>-28.764</v>
+        <v>-61.721</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>1708.318</v>
+        <v>1800.5</v>
       </c>
       <c r="C70">
-        <v>1708.318</v>
+        <v>1800.5</v>
       </c>
       <c r="D70">
-        <v>-0.997</v>
+        <v>-31.878</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>1751.733</v>
+        <v>1772.951</v>
       </c>
       <c r="C71">
-        <v>1751.733</v>
+        <v>1772.951</v>
       </c>
       <c r="D71">
-        <v>-32.931</v>
+        <v>-76.758</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>1587.227</v>
+        <v>1741.541</v>
       </c>
       <c r="C72">
-        <v>1587.227</v>
+        <v>1741.541</v>
       </c>
       <c r="D72">
-        <v>-7.78</v>
+        <v>-77.07899999999999</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>602</v>
+        <v>1740.447</v>
       </c>
       <c r="C73">
-        <v>602</v>
+        <v>1740.447</v>
       </c>
       <c r="D73">
-        <v>6.411</v>
+        <v>-102.295</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1719.256</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1719.256</v>
       </c>
       <c r="D74">
-        <v>53.298</v>
+        <v>-52.524</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>568.006</v>
+        <v>1732.089</v>
       </c>
       <c r="C75">
-        <v>568.006</v>
+        <v>1732.089</v>
       </c>
       <c r="D75">
-        <v>43.422</v>
+        <v>-26.469</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>602</v>
+        <v>650</v>
       </c>
       <c r="C76">
-        <v>602</v>
+        <v>650</v>
       </c>
       <c r="D76">
-        <v>16.918</v>
+        <v>3.964</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>8.795999999999999</v>
+        <v>44.13</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>3.081</v>
+        <v>42.809</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>7.002</v>
+        <v>46.024</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>278.654</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>278.654</v>
       </c>
       <c r="D80">
-        <v>6.97</v>
+        <v>29.173</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>1163.089</v>
+        <v>284.075</v>
       </c>
       <c r="C81">
-        <v>1163.089</v>
+        <v>284.075</v>
       </c>
       <c r="D81">
-        <v>-22.705</v>
+        <v>18.75</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>2771.276</v>
+        <v>1679.725</v>
       </c>
       <c r="C82">
-        <v>2771.276</v>
+        <v>1679.725</v>
       </c>
       <c r="D82">
-        <v>-41.665</v>
+        <v>-17.024</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>3032.812</v>
+        <v>1534.78</v>
       </c>
       <c r="C83">
-        <v>3032.812</v>
+        <v>1534.78</v>
       </c>
       <c r="D83">
-        <v>-66.322</v>
+        <v>-49.458</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>1993.802</v>
+        <v>1310.617</v>
       </c>
       <c r="C84">
-        <v>1993.802</v>
+        <v>1310.617</v>
       </c>
       <c r="D84">
-        <v>-27.228</v>
+        <v>-34.663</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1181.523</v>
+        <v>1480.335</v>
       </c>
       <c r="C85">
-        <v>1181.523</v>
+        <v>1480.335</v>
       </c>
       <c r="D85">
-        <v>-7.374</v>
+        <v>-3.444</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1857.639</v>
+        <v>1513.824</v>
       </c>
       <c r="C86">
-        <v>1857.639</v>
+        <v>1513.824</v>
       </c>
       <c r="D86">
-        <v>-13.144</v>
+        <v>-16.67</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>464.765</v>
+        <v>647.23</v>
       </c>
       <c r="C87">
-        <v>464.765</v>
+        <v>647.23</v>
       </c>
       <c r="D87">
-        <v>27.028</v>
+        <v>5.415</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>576.587</v>
+        <v>896.381</v>
       </c>
       <c r="C88">
-        <v>576.587</v>
+        <v>896.381</v>
       </c>
       <c r="D88">
-        <v>23.005</v>
+        <v>18.992</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>524.992</v>
+        <v>539.866</v>
       </c>
       <c r="C89">
-        <v>524.992</v>
+        <v>539.866</v>
       </c>
       <c r="D89">
-        <v>9.77</v>
+        <v>22.7</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>549.303</v>
+        <v>1392.312</v>
       </c>
       <c r="C90">
-        <v>549.303</v>
+        <v>1392.312</v>
       </c>
       <c r="D90">
-        <v>15.571</v>
+        <v>-8.829000000000001</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>603.809</v>
+        <v>1369.085</v>
       </c>
       <c r="C91">
-        <v>603.809</v>
+        <v>1369.085</v>
       </c>
       <c r="D91">
-        <v>9.728999999999999</v>
+        <v>-13.998</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1194.308</v>
+        <v>1554.984</v>
       </c>
       <c r="C92">
-        <v>1194.308</v>
+        <v>1554.984</v>
       </c>
       <c r="D92">
-        <v>-7.165</v>
+        <v>-19.27</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>408.362</v>
+        <v>1778.546</v>
       </c>
       <c r="C93">
-        <v>408.362</v>
+        <v>1778.546</v>
       </c>
       <c r="D93">
-        <v>2.511</v>
+        <v>-13.822</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>394.349</v>
+        <v>1459.414</v>
       </c>
       <c r="C94">
-        <v>394.349</v>
+        <v>1459.414</v>
       </c>
       <c r="D94">
-        <v>24.544</v>
+        <v>-15.46</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>601.5</v>
+        <v>1365.919</v>
       </c>
       <c r="C95">
-        <v>601.5</v>
+        <v>1365.919</v>
       </c>
       <c r="D95">
-        <v>14.662</v>
+        <v>-1.225</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1352.789</v>
+        <v>625.229</v>
       </c>
       <c r="C96">
-        <v>1352.789</v>
+        <v>625.229</v>
       </c>
       <c r="D96">
-        <v>-2.102</v>
+        <v>2.621</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1257.116</v>
+        <v>1185.28</v>
       </c>
       <c r="C97">
-        <v>1257.116</v>
+        <v>1185.28</v>
       </c>
       <c r="D97">
-        <v>-7.954</v>
+        <v>-5.607</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>562.295</v>
+        <v>1189.414</v>
       </c>
       <c r="C98">
-        <v>562.295</v>
+        <v>1189.414</v>
       </c>
       <c r="D98">
-        <v>7.367</v>
+        <v>6.727</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>605</v>
+        <v>1197.919</v>
       </c>
       <c r="C99">
-        <v>605</v>
+        <v>1197.919</v>
       </c>
       <c r="D99">
-        <v>9.551</v>
+        <v>-0.594</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1032.564</v>
+        <v>1212.581</v>
       </c>
       <c r="C100">
-        <v>1032.564</v>
+        <v>1212.581</v>
       </c>
       <c r="D100">
-        <v>-12.846</v>
+        <v>3.793</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1510.645</v>
+        <v>576.062</v>
       </c>
       <c r="C101">
-        <v>1510.645</v>
+        <v>576.062</v>
       </c>
       <c r="D101">
-        <v>-13.904</v>
+        <v>6.776</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>601.16</v>
+        <v>1398.409</v>
       </c>
       <c r="C102">
-        <v>601.16</v>
+        <v>1398.409</v>
       </c>
       <c r="D102">
-        <v>21.71</v>
+        <v>-11.349</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>602.223</v>
+        <v>1282.675</v>
       </c>
       <c r="C103">
-        <v>602.223</v>
+        <v>1282.675</v>
       </c>
       <c r="D103">
-        <v>25.853</v>
+        <v>-2.047</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>1158.879</v>
+        <v>1710.128</v>
       </c>
       <c r="C104">
-        <v>1158.879</v>
+        <v>1710.128</v>
       </c>
       <c r="D104">
-        <v>-6.145</v>
+        <v>-30.428</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>1343.916</v>
+        <v>1624.357</v>
       </c>
       <c r="C105">
-        <v>1343.916</v>
+        <v>1624.357</v>
       </c>
       <c r="D105">
-        <v>-17.752</v>
+        <v>-17.68</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>1413.056</v>
+        <v>1289.337</v>
       </c>
       <c r="C106">
-        <v>1413.056</v>
+        <v>1289.337</v>
       </c>
       <c r="D106">
-        <v>-27.552</v>
+        <v>-18.223</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>1742.969</v>
+        <v>1530.773</v>
       </c>
       <c r="C107">
-        <v>1742.969</v>
+        <v>1530.773</v>
       </c>
       <c r="D107">
-        <v>-32.638</v>
+        <v>-23.219</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>1633.449</v>
+        <v>1676.315</v>
       </c>
       <c r="C108">
-        <v>1633.449</v>
+        <v>1676.315</v>
       </c>
       <c r="D108">
-        <v>-33.394</v>
+        <v>-23.034</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>1522.331</v>
+        <v>2889.547</v>
       </c>
       <c r="C109">
-        <v>1522.331</v>
+        <v>2889.547</v>
       </c>
       <c r="D109">
-        <v>-28.679</v>
+        <v>-39.953</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>1470.989</v>
+        <v>6675.689</v>
       </c>
       <c r="C110">
-        <v>1470.989</v>
+        <v>6675.689</v>
       </c>
       <c r="D110">
-        <v>-23.848</v>
+        <v>-53.128</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>1485.859</v>
+        <v>1778.315</v>
       </c>
       <c r="C111">
-        <v>1485.859</v>
+        <v>1778.315</v>
       </c>
       <c r="D111">
-        <v>-45.023</v>
+        <v>-76.47499999999999</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>1611.406</v>
+        <v>1580.683</v>
       </c>
       <c r="C112">
-        <v>1611.406</v>
+        <v>1580.683</v>
       </c>
       <c r="D112">
-        <v>-26.001</v>
+        <v>-59.522</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>1729.39</v>
+        <v>2082.256</v>
       </c>
       <c r="C113">
-        <v>1729.39</v>
+        <v>2082.256</v>
       </c>
       <c r="D113">
-        <v>-30.675</v>
+        <v>-86.377</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>1290.807</v>
+        <v>1603.593</v>
       </c>
       <c r="C114">
-        <v>1290.807</v>
+        <v>1603.593</v>
       </c>
       <c r="D114">
-        <v>-20.761</v>
+        <v>-24.885</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>1391.495</v>
+        <v>1605.088</v>
       </c>
       <c r="C115">
-        <v>1391.495</v>
+        <v>1605.088</v>
       </c>
       <c r="D115">
-        <v>-23.683</v>
+        <v>-44.922</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>1175.15</v>
+        <v>1619.1</v>
       </c>
       <c r="C116">
-        <v>1175.15</v>
+        <v>1619.1</v>
       </c>
       <c r="D116">
-        <v>-30.451</v>
+        <v>-18.935</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>1246.458</v>
+        <v>1600.85</v>
       </c>
       <c r="C117">
-        <v>1246.458</v>
+        <v>1600.85</v>
       </c>
       <c r="D117">
-        <v>-29.638</v>
+        <v>-31.027</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>1319.886</v>
+        <v>1857.021</v>
       </c>
       <c r="C118">
-        <v>1319.886</v>
+        <v>1857.021</v>
       </c>
       <c r="D118">
-        <v>-22.956</v>
+        <v>-49.41</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>1195.457</v>
+        <v>2137.141</v>
       </c>
       <c r="C119">
-        <v>1195.457</v>
+        <v>2137.141</v>
       </c>
       <c r="D119">
-        <v>-7.891</v>
+        <v>-72.113</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>1668.3</v>
+        <v>1896.678</v>
       </c>
       <c r="C120">
-        <v>1668.3</v>
+        <v>1896.678</v>
       </c>
       <c r="D120">
-        <v>-27.599</v>
+        <v>-35.84</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>1506.273</v>
+        <v>1877.101</v>
       </c>
       <c r="C121">
-        <v>1506.273</v>
+        <v>1877.101</v>
       </c>
       <c r="D121">
-        <v>-6.823</v>
+        <v>-43.871</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>1774.641</v>
+        <v>2039.275</v>
       </c>
       <c r="C122">
-        <v>1774.641</v>
+        <v>2039.275</v>
       </c>
       <c r="D122">
-        <v>-17.159</v>
+        <v>-20.874</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>1784.375</v>
+        <v>621</v>
       </c>
       <c r="C123">
-        <v>1784.375</v>
+        <v>621</v>
       </c>
       <c r="D123">
-        <v>-20.483</v>
+        <v>25.274</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>1820.379</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1820.379</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>-5.544</v>
+        <v>37.772</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0.112</v>
+        <v>10.666</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>1738.492</v>
+        <v>753.125</v>
       </c>
       <c r="C126">
-        <v>1738.492</v>
+        <v>753.125</v>
       </c>
       <c r="D126">
-        <v>-51.751</v>
+        <v>19.861</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>1740.837</v>
+        <v>755</v>
       </c>
       <c r="C127">
-        <v>1740.837</v>
+        <v>755</v>
       </c>
       <c r="D127">
-        <v>-50.496</v>
+        <v>0.623</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>1756.296</v>
+        <v>753.648</v>
       </c>
       <c r="C128">
-        <v>1756.296</v>
+        <v>753.648</v>
       </c>
       <c r="D128">
-        <v>-28.042</v>
+        <v>41.176</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>1793.18</v>
+        <v>766.667</v>
       </c>
       <c r="C129">
-        <v>1793.18</v>
+        <v>766.667</v>
       </c>
       <c r="D129">
-        <v>-40.614</v>
+        <v>7.312</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>1559.127</v>
+        <v>3114.377</v>
       </c>
       <c r="C130">
-        <v>1559.127</v>
+        <v>3114.377</v>
       </c>
       <c r="D130">
-        <v>-147.022</v>
+        <v>-38.566</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>1572.406</v>
+        <v>4633.006</v>
       </c>
       <c r="C131">
-        <v>1572.406</v>
+        <v>4633.006</v>
       </c>
       <c r="D131">
-        <v>-120.177</v>
+        <v>-26.901</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>1632.394</v>
+        <v>636.206</v>
       </c>
       <c r="C132">
-        <v>1632.394</v>
+        <v>636.206</v>
       </c>
       <c r="D132">
-        <v>-95.262</v>
+        <v>4.051</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>1571.259</v>
+        <v>528.413</v>
       </c>
       <c r="C133">
-        <v>1571.259</v>
+        <v>528.413</v>
       </c>
       <c r="D133">
-        <v>-0.014</v>
+        <v>16.123</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>-50.172</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -608,6 +320,870 @@
   </si>
   <si>
     <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
+  </si>
+  <si>
+    <t>12.10.202639</t>
+  </si>
+  <si>
+    <t>12.10.202640</t>
+  </si>
+  <si>
+    <t>12.10.202641</t>
+  </si>
+  <si>
+    <t>12.10.202642</t>
+  </si>
+  <si>
+    <t>12.10.202643</t>
+  </si>
+  <si>
+    <t>12.10.202644</t>
+  </si>
+  <si>
+    <t>12.10.202645</t>
+  </si>
+  <si>
+    <t>12.10.202646</t>
+  </si>
+  <si>
+    <t>12.10.202647</t>
+  </si>
+  <si>
+    <t>12.10.202648</t>
+  </si>
+  <si>
+    <t>12.10.202649</t>
+  </si>
+  <si>
+    <t>12.10.202650</t>
+  </si>
+  <si>
+    <t>12.10.202651</t>
+  </si>
+  <si>
+    <t>12.10.202652</t>
+  </si>
+  <si>
+    <t>12.10.202653</t>
+  </si>
+  <si>
+    <t>12.10.202654</t>
+  </si>
+  <si>
+    <t>12.10.202655</t>
+  </si>
+  <si>
+    <t>12.10.202656</t>
+  </si>
+  <si>
+    <t>12.10.202657</t>
+  </si>
+  <si>
+    <t>12.10.202658</t>
+  </si>
+  <si>
+    <t>12.10.202659</t>
+  </si>
+  <si>
+    <t>12.10.202660</t>
+  </si>
+  <si>
+    <t>12.10.202661</t>
+  </si>
+  <si>
+    <t>12.10.202662</t>
+  </si>
+  <si>
+    <t>12.10.202663</t>
+  </si>
+  <si>
+    <t>12.10.202664</t>
+  </si>
+  <si>
+    <t>12.10.202665</t>
+  </si>
+  <si>
+    <t>12.10.202666</t>
+  </si>
+  <si>
+    <t>12.10.202667</t>
+  </si>
+  <si>
+    <t>12.10.202668</t>
+  </si>
+  <si>
+    <t>12.10.202669</t>
+  </si>
+  <si>
+    <t>12.10.202670</t>
+  </si>
+  <si>
+    <t>12.10.202671</t>
+  </si>
+  <si>
+    <t>12.10.202672</t>
+  </si>
+  <si>
+    <t>12.10.202673</t>
+  </si>
+  <si>
+    <t>12.10.202674</t>
+  </si>
+  <si>
+    <t>12.10.202675</t>
+  </si>
+  <si>
+    <t>12.10.202676</t>
+  </si>
+  <si>
+    <t>12.10.202677</t>
+  </si>
+  <si>
+    <t>12.10.202678</t>
+  </si>
+  <si>
+    <t>12.10.202679</t>
+  </si>
+  <si>
+    <t>12.10.202680</t>
+  </si>
+  <si>
+    <t>12.10.202681</t>
+  </si>
+  <si>
+    <t>12.10.202682</t>
+  </si>
+  <si>
+    <t>12.10.202683</t>
+  </si>
+  <si>
+    <t>12.10.202684</t>
+  </si>
+  <si>
+    <t>12.10.202685</t>
+  </si>
+  <si>
+    <t>12.10.202686</t>
+  </si>
+  <si>
+    <t>12.10.202687</t>
+  </si>
+  <si>
+    <t>12.10.202688</t>
+  </si>
+  <si>
+    <t>12.10.202689</t>
+  </si>
+  <si>
+    <t>12.10.202690</t>
+  </si>
+  <si>
+    <t>12.10.202691</t>
+  </si>
+  <si>
+    <t>12.10.202692</t>
+  </si>
+  <si>
+    <t>12.10.202693</t>
+  </si>
+  <si>
+    <t>12.10.202694</t>
+  </si>
+  <si>
+    <t>12.10.202695</t>
+  </si>
+  <si>
+    <t>12.10.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +1570,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>562.295</v>
+        <v>1189.414</v>
       </c>
       <c r="C2">
-        <v>562.295</v>
+        <v>1189.414</v>
       </c>
       <c r="D2">
-        <v>7.367</v>
+        <v>6.727</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1590,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>605</v>
+        <v>1197.919</v>
       </c>
       <c r="C3">
-        <v>605</v>
+        <v>1197.919</v>
       </c>
       <c r="D3">
-        <v>9.551</v>
+        <v>-0.594</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1610,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>1032.564</v>
+        <v>1212.581</v>
       </c>
       <c r="C4">
-        <v>1032.564</v>
+        <v>1212.581</v>
       </c>
       <c r="D4">
-        <v>-12.846</v>
+        <v>3.793</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1630,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>1510.645</v>
+        <v>576.062</v>
       </c>
       <c r="C5">
-        <v>1510.645</v>
+        <v>576.062</v>
       </c>
       <c r="D5">
-        <v>-13.904</v>
+        <v>6.776</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>601.16</v>
+        <v>1398.409</v>
       </c>
       <c r="C6">
-        <v>601.16</v>
+        <v>1398.409</v>
       </c>
       <c r="D6">
-        <v>21.71</v>
+        <v>-11.349</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>602.223</v>
+        <v>1282.675</v>
       </c>
       <c r="C7">
-        <v>602.223</v>
+        <v>1282.675</v>
       </c>
       <c r="D7">
-        <v>25.853</v>
+        <v>-2.047</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>1158.879</v>
+        <v>1710.128</v>
       </c>
       <c r="C8">
-        <v>1158.879</v>
+        <v>1710.128</v>
       </c>
       <c r="D8">
-        <v>-6.145</v>
+        <v>-30.428</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>1343.916</v>
+        <v>1624.357</v>
       </c>
       <c r="C9">
-        <v>1343.916</v>
+        <v>1624.357</v>
       </c>
       <c r="D9">
-        <v>-17.752</v>
+        <v>-17.68</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>1413.056</v>
+        <v>1289.337</v>
       </c>
       <c r="C10">
-        <v>1413.056</v>
+        <v>1289.337</v>
       </c>
       <c r="D10">
-        <v>-27.552</v>
+        <v>-18.223</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>1742.969</v>
+        <v>1530.773</v>
       </c>
       <c r="C11">
-        <v>1742.969</v>
+        <v>1530.773</v>
       </c>
       <c r="D11">
-        <v>-32.638</v>
+        <v>-23.219</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>1633.449</v>
+        <v>1676.315</v>
       </c>
       <c r="C12">
-        <v>1633.449</v>
+        <v>1676.315</v>
       </c>
       <c r="D12">
-        <v>-33.394</v>
+        <v>-23.034</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>1522.331</v>
+        <v>2889.547</v>
       </c>
       <c r="C13">
-        <v>1522.331</v>
+        <v>2889.547</v>
       </c>
       <c r="D13">
-        <v>-28.679</v>
+        <v>-39.953</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>1470.989</v>
+        <v>6675.689</v>
       </c>
       <c r="C14">
-        <v>1470.989</v>
+        <v>6675.689</v>
       </c>
       <c r="D14">
-        <v>-23.848</v>
+        <v>-53.128</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>1485.859</v>
+        <v>1778.315</v>
       </c>
       <c r="C15">
-        <v>1485.859</v>
+        <v>1778.315</v>
       </c>
       <c r="D15">
-        <v>-45.023</v>
+        <v>-76.47499999999999</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>1611.406</v>
+        <v>1580.683</v>
       </c>
       <c r="C16">
-        <v>1611.406</v>
+        <v>1580.683</v>
       </c>
       <c r="D16">
-        <v>-26.001</v>
+        <v>-59.522</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>1729.39</v>
+        <v>2082.256</v>
       </c>
       <c r="C17">
-        <v>1729.39</v>
+        <v>2082.256</v>
       </c>
       <c r="D17">
-        <v>-30.675</v>
+        <v>-86.377</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>1290.807</v>
+        <v>1603.593</v>
       </c>
       <c r="C18">
-        <v>1290.807</v>
+        <v>1603.593</v>
       </c>
       <c r="D18">
-        <v>-20.761</v>
+        <v>-24.885</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>1391.495</v>
+        <v>1605.088</v>
       </c>
       <c r="C19">
-        <v>1391.495</v>
+        <v>1605.088</v>
       </c>
       <c r="D19">
-        <v>-23.683</v>
+        <v>-44.922</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>1175.15</v>
+        <v>1619.1</v>
       </c>
       <c r="C20">
-        <v>1175.15</v>
+        <v>1619.1</v>
       </c>
       <c r="D20">
-        <v>-30.451</v>
+        <v>-18.935</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>1246.458</v>
+        <v>1600.85</v>
       </c>
       <c r="C21">
-        <v>1246.458</v>
+        <v>1600.85</v>
       </c>
       <c r="D21">
-        <v>-29.638</v>
+        <v>-31.027</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>1319.886</v>
+        <v>1857.021</v>
       </c>
       <c r="C22">
-        <v>1319.886</v>
+        <v>1857.021</v>
       </c>
       <c r="D22">
-        <v>-22.956</v>
+        <v>-49.41</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>1195.457</v>
+        <v>2137.141</v>
       </c>
       <c r="C23">
-        <v>1195.457</v>
+        <v>2137.141</v>
       </c>
       <c r="D23">
-        <v>-7.891</v>
+        <v>-72.113</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>1668.3</v>
+        <v>1896.678</v>
       </c>
       <c r="C24">
-        <v>1668.3</v>
+        <v>1896.678</v>
       </c>
       <c r="D24">
-        <v>-27.599</v>
+        <v>-35.84</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>1506.273</v>
+        <v>1877.101</v>
       </c>
       <c r="C25">
-        <v>1506.273</v>
+        <v>1877.101</v>
       </c>
       <c r="D25">
-        <v>-6.823</v>
+        <v>-43.871</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>1774.641</v>
+        <v>2039.275</v>
       </c>
       <c r="C26">
-        <v>1774.641</v>
+        <v>2039.275</v>
       </c>
       <c r="D26">
-        <v>-17.159</v>
+        <v>-20.874</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>1784.375</v>
+        <v>621</v>
       </c>
       <c r="C27">
-        <v>1784.375</v>
+        <v>621</v>
       </c>
       <c r="D27">
-        <v>-20.483</v>
+        <v>25.274</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>1820.379</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1820.379</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>-5.544</v>
+        <v>37.772</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>0.112</v>
+        <v>10.666</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>1738.492</v>
+        <v>753.125</v>
       </c>
       <c r="C30">
-        <v>1738.492</v>
+        <v>753.125</v>
       </c>
       <c r="D30">
-        <v>-51.751</v>
+        <v>19.861</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>1740.837</v>
+        <v>755</v>
       </c>
       <c r="C31">
-        <v>1740.837</v>
+        <v>755</v>
       </c>
       <c r="D31">
-        <v>-50.496</v>
+        <v>0.623</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>1756.296</v>
+        <v>753.648</v>
       </c>
       <c r="C32">
-        <v>1756.296</v>
+        <v>753.648</v>
       </c>
       <c r="D32">
-        <v>-28.042</v>
+        <v>41.176</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>1793.18</v>
+        <v>766.667</v>
       </c>
       <c r="C33">
-        <v>1793.18</v>
+        <v>766.667</v>
       </c>
       <c r="D33">
-        <v>-40.614</v>
+        <v>7.312</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>1559.127</v>
+        <v>3114.377</v>
       </c>
       <c r="C34">
-        <v>1559.127</v>
+        <v>3114.377</v>
       </c>
       <c r="D34">
-        <v>-147.022</v>
+        <v>-38.566</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>1572.406</v>
+        <v>4633.006</v>
       </c>
       <c r="C35">
-        <v>1572.406</v>
+        <v>4633.006</v>
       </c>
       <c r="D35">
-        <v>-120.177</v>
+        <v>-26.901</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>1632.394</v>
+        <v>636.206</v>
       </c>
       <c r="C36">
-        <v>1632.394</v>
+        <v>636.206</v>
       </c>
       <c r="D36">
-        <v>-95.262</v>
+        <v>4.051</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>1571.259</v>
+        <v>528.413</v>
       </c>
       <c r="C37">
-        <v>1571.259</v>
+        <v>528.413</v>
       </c>
       <c r="D37">
-        <v>-0.014</v>
+        <v>16.123</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>1429.383</v>
+        <v>3539.682</v>
       </c>
       <c r="C38">
-        <v>1429.383</v>
+        <v>3539.682</v>
       </c>
       <c r="D38">
-        <v>-50.172</v>
+        <v>-25.359</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>1430.02</v>
+        <v>2192.194</v>
       </c>
       <c r="C39">
-        <v>1430.02</v>
+        <v>2192.194</v>
       </c>
       <c r="D39">
-        <v>-6.302</v>
+        <v>-15.284</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>1406.579</v>
+        <v>1196.403</v>
       </c>
       <c r="C40">
-        <v>1406.579</v>
+        <v>1196.403</v>
       </c>
       <c r="D40">
-        <v>-4.27</v>
+        <v>-24.1</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>385.47</v>
+        <v>649.567</v>
       </c>
       <c r="C41">
-        <v>385.47</v>
+        <v>649.567</v>
       </c>
       <c r="D41">
-        <v>19.906</v>
+        <v>0.448</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>999.625</v>
+        <v>738.824</v>
       </c>
       <c r="C42">
-        <v>999.625</v>
+        <v>738.824</v>
       </c>
       <c r="D42">
-        <v>-0.767</v>
+        <v>10.61</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>587.7430000000001</v>
+        <v>1148.023</v>
       </c>
       <c r="C43">
-        <v>587.7430000000001</v>
+        <v>1148.023</v>
       </c>
       <c r="D43">
-        <v>8.605</v>
+        <v>-1.913</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>394.41</v>
+        <v>850</v>
       </c>
       <c r="C44">
-        <v>394.41</v>
+        <v>850</v>
       </c>
       <c r="D44">
-        <v>16.344</v>
+        <v>19.908</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>51.954</v>
+        <v>0.134</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>445.223</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>445.223</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>53.567</v>
+        <v>43.127</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>353.761</v>
+        <v>656.622</v>
       </c>
       <c r="C47">
-        <v>353.761</v>
+        <v>656.622</v>
       </c>
       <c r="D47">
-        <v>47.517</v>
+        <v>40.549</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>321.397</v>
+        <v>678.408</v>
       </c>
       <c r="C48">
-        <v>321.397</v>
+        <v>678.408</v>
       </c>
       <c r="D48">
-        <v>27.03</v>
+        <v>25.459</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>424.482</v>
+        <v>759.649</v>
       </c>
       <c r="C49">
-        <v>424.482</v>
+        <v>759.649</v>
       </c>
       <c r="D49">
-        <v>5.277</v>
+        <v>1.084</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>363.239</v>
+        <v>695.598</v>
       </c>
       <c r="C50">
-        <v>363.239</v>
+        <v>695.598</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>38.694</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>700</v>
+        <v>540.229</v>
       </c>
       <c r="C51">
-        <v>700</v>
+        <v>540.229</v>
       </c>
       <c r="D51">
-        <v>-12.157</v>
+        <v>29.622</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>726.126</v>
+        <v>552.071</v>
       </c>
       <c r="C52">
-        <v>726.126</v>
+        <v>552.071</v>
       </c>
       <c r="D52">
-        <v>-24.043</v>
+        <v>45.473</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>1047.736</v>
+        <v>467.68</v>
       </c>
       <c r="C53">
-        <v>1047.736</v>
+        <v>467.68</v>
       </c>
       <c r="D53">
-        <v>-5.728</v>
+        <v>37.286</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>959.27</v>
+        <v>566.2190000000001</v>
       </c>
       <c r="C54">
-        <v>959.27</v>
+        <v>566.2190000000001</v>
       </c>
       <c r="D54">
-        <v>-5.743</v>
+        <v>44.143</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>334.944</v>
+        <v>259.895</v>
       </c>
       <c r="C55">
-        <v>334.944</v>
+        <v>259.895</v>
       </c>
       <c r="D55">
-        <v>23.198</v>
+        <v>91.61</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>384.586</v>
+        <v>628.312</v>
       </c>
       <c r="C56">
-        <v>384.586</v>
+        <v>628.312</v>
       </c>
       <c r="D56">
-        <v>22.813</v>
+        <v>101.228</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>354.63</v>
+        <v>681</v>
       </c>
       <c r="C57">
-        <v>354.63</v>
+        <v>681</v>
       </c>
       <c r="D57">
-        <v>14.146</v>
+        <v>41.533</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>227.413</v>
+        <v>1167.357</v>
       </c>
       <c r="C58">
-        <v>227.413</v>
+        <v>1167.357</v>
       </c>
       <c r="D58">
-        <v>7.312</v>
+        <v>-49.109</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>318.294</v>
+        <v>1200.115</v>
       </c>
       <c r="C59">
-        <v>318.294</v>
+        <v>1200.115</v>
       </c>
       <c r="D59">
-        <v>24.498</v>
+        <v>-72.97199999999999</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>331.591</v>
+        <v>1383.93</v>
       </c>
       <c r="C60">
-        <v>331.591</v>
+        <v>1383.93</v>
       </c>
       <c r="D60">
-        <v>40.314</v>
+        <v>-125.453</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>426</v>
+        <v>3599.902</v>
       </c>
       <c r="C61">
-        <v>426</v>
+        <v>3599.902</v>
       </c>
       <c r="D61">
-        <v>11.328</v>
+        <v>-129.088</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>404.88</v>
+        <v>1860.042</v>
       </c>
       <c r="C62">
-        <v>404.88</v>
+        <v>1860.042</v>
       </c>
       <c r="D62">
-        <v>85.307</v>
+        <v>-162.723</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>147.917</v>
+        <v>1457.494</v>
       </c>
       <c r="C63">
-        <v>147.917</v>
+        <v>1457.494</v>
       </c>
       <c r="D63">
-        <v>53.426</v>
+        <v>-82.645</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>256.257</v>
+        <v>1461.989</v>
       </c>
       <c r="C64">
-        <v>256.257</v>
+        <v>1461.989</v>
       </c>
       <c r="D64">
-        <v>20.421</v>
+        <v>-49.391</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>256</v>
+        <v>1494.037</v>
       </c>
       <c r="C65">
-        <v>256</v>
+        <v>1494.037</v>
       </c>
       <c r="D65">
-        <v>6.145</v>
+        <v>-80.122</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>1481.764</v>
+        <v>248.707</v>
       </c>
       <c r="C66">
-        <v>1481.764</v>
+        <v>248.707</v>
       </c>
       <c r="D66">
-        <v>13.723</v>
+        <v>70.545</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>1662.066</v>
+        <v>667.283</v>
       </c>
       <c r="C67">
-        <v>1662.066</v>
+        <v>667.283</v>
       </c>
       <c r="D67">
-        <v>-8.884</v>
+        <v>50.468</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>2157.882</v>
+        <v>1836.072</v>
       </c>
       <c r="C68">
-        <v>2157.882</v>
+        <v>1836.072</v>
       </c>
       <c r="D68">
-        <v>-34.947</v>
+        <v>-7.898</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>1722.852</v>
+        <v>1832.361</v>
       </c>
       <c r="C69">
-        <v>1722.852</v>
+        <v>1832.361</v>
       </c>
       <c r="D69">
-        <v>-61.721</v>
+        <v>-20.891</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>1800.5</v>
+        <v>660.7329999999999</v>
       </c>
       <c r="C70">
-        <v>1800.5</v>
+        <v>660.7329999999999</v>
       </c>
       <c r="D70">
-        <v>-31.878</v>
+        <v>19.059</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>1772.951</v>
+        <v>675.854</v>
       </c>
       <c r="C71">
-        <v>1772.951</v>
+        <v>675.854</v>
       </c>
       <c r="D71">
-        <v>-76.758</v>
+        <v>28.69</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>1741.541</v>
+        <v>700</v>
       </c>
       <c r="C72">
-        <v>1741.541</v>
+        <v>700</v>
       </c>
       <c r="D72">
-        <v>-77.07899999999999</v>
+        <v>18.338</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>1740.447</v>
+        <v>1251.844</v>
       </c>
       <c r="C73">
-        <v>1740.447</v>
+        <v>1251.844</v>
       </c>
       <c r="D73">
-        <v>-102.295</v>
+        <v>-3.07</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>1719.256</v>
+        <v>2172.924</v>
       </c>
       <c r="C74">
-        <v>1719.256</v>
+        <v>2172.924</v>
       </c>
       <c r="D74">
-        <v>-52.524</v>
+        <v>12.464</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>1732.089</v>
+        <v>751</v>
       </c>
       <c r="C75">
-        <v>1732.089</v>
+        <v>751</v>
       </c>
       <c r="D75">
-        <v>-26.469</v>
+        <v>0.547</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>650</v>
+        <v>2084.259</v>
       </c>
       <c r="C76">
-        <v>650</v>
+        <v>2084.259</v>
       </c>
       <c r="D76">
-        <v>3.964</v>
+        <v>11.463</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="D77">
-        <v>44.13</v>
+        <v>11.662</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="D78">
-        <v>42.809</v>
+        <v>17.072</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="D79">
-        <v>46.024</v>
+        <v>1.251</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>278.654</v>
+        <v>1006.061</v>
       </c>
       <c r="C80">
-        <v>278.654</v>
+        <v>1006.061</v>
       </c>
       <c r="D80">
-        <v>29.173</v>
+        <v>-15.768</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>284.075</v>
+        <v>1180.973</v>
       </c>
       <c r="C81">
-        <v>284.075</v>
+        <v>1180.973</v>
       </c>
       <c r="D81">
-        <v>18.75</v>
+        <v>-29.314</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>1679.725</v>
+        <v>2364.432</v>
       </c>
       <c r="C82">
-        <v>1679.725</v>
+        <v>2364.432</v>
       </c>
       <c r="D82">
-        <v>-17.024</v>
+        <v>-53.432</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>1534.78</v>
+        <v>1547.96</v>
       </c>
       <c r="C83">
-        <v>1534.78</v>
+        <v>1547.96</v>
       </c>
       <c r="D83">
-        <v>-49.458</v>
+        <v>-50.644</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>1310.617</v>
+        <v>1933.177</v>
       </c>
       <c r="C84">
-        <v>1310.617</v>
+        <v>1933.177</v>
       </c>
       <c r="D84">
-        <v>-34.663</v>
+        <v>-24.01</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>1480.335</v>
+        <v>2300.251</v>
       </c>
       <c r="C85">
-        <v>1480.335</v>
+        <v>2300.251</v>
       </c>
       <c r="D85">
-        <v>-3.444</v>
+        <v>-21.093</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>1513.824</v>
+        <v>5683.187</v>
       </c>
       <c r="C86">
-        <v>1513.824</v>
+        <v>5683.187</v>
       </c>
       <c r="D86">
-        <v>-16.67</v>
+        <v>-55.057</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>647.23</v>
+        <v>2713.961</v>
       </c>
       <c r="C87">
-        <v>647.23</v>
+        <v>2713.961</v>
       </c>
       <c r="D87">
-        <v>5.415</v>
+        <v>-32.088</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>896.381</v>
+        <v>1935.564</v>
       </c>
       <c r="C88">
-        <v>896.381</v>
+        <v>1935.564</v>
       </c>
       <c r="D88">
-        <v>18.992</v>
+        <v>-5.046</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>539.866</v>
+        <v>1960.919</v>
       </c>
       <c r="C89">
-        <v>539.866</v>
+        <v>1960.919</v>
       </c>
       <c r="D89">
-        <v>22.7</v>
+        <v>-7.752</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>1392.312</v>
+        <v>2678.907</v>
       </c>
       <c r="C90">
-        <v>1392.312</v>
+        <v>2678.907</v>
       </c>
       <c r="D90">
-        <v>-8.829000000000001</v>
+        <v>-38.564</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>1369.085</v>
+        <v>3473.561</v>
       </c>
       <c r="C91">
-        <v>1369.085</v>
+        <v>3473.561</v>
       </c>
       <c r="D91">
-        <v>-13.998</v>
+        <v>-28.986</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>1554.984</v>
+        <v>2009.815</v>
       </c>
       <c r="C92">
-        <v>1554.984</v>
+        <v>2009.815</v>
       </c>
       <c r="D92">
-        <v>-19.27</v>
+        <v>-13.502</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>1778.546</v>
+        <v>2627.895</v>
       </c>
       <c r="C93">
-        <v>1778.546</v>
+        <v>2627.895</v>
       </c>
       <c r="D93">
-        <v>-13.822</v>
+        <v>-48.061</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>1459.414</v>
+        <v>6392.022</v>
       </c>
       <c r="C94">
-        <v>1459.414</v>
+        <v>6392.022</v>
       </c>
       <c r="D94">
-        <v>-15.46</v>
+        <v>-57.998</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>1365.919</v>
+        <v>3007.91</v>
       </c>
       <c r="C95">
-        <v>1365.919</v>
+        <v>3007.91</v>
       </c>
       <c r="D95">
-        <v>-1.225</v>
+        <v>-82.78400000000001</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>625.229</v>
+        <v>1854.535</v>
       </c>
       <c r="C96">
-        <v>625.229</v>
+        <v>1854.535</v>
       </c>
       <c r="D96">
-        <v>2.621</v>
+        <v>-65.989</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>1185.28</v>
+        <v>1870.533</v>
       </c>
       <c r="C97">
-        <v>1185.28</v>
+        <v>1870.533</v>
       </c>
       <c r="D97">
-        <v>-5.607</v>
+        <v>-93.422</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>1189.414</v>
+        <v>1957.114</v>
       </c>
       <c r="C98">
-        <v>1189.414</v>
+        <v>1957.114</v>
       </c>
       <c r="D98">
-        <v>6.727</v>
+        <v>-26.968</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>1197.919</v>
+        <v>1876.128</v>
       </c>
       <c r="C99">
-        <v>1197.919</v>
+        <v>1876.128</v>
       </c>
       <c r="D99">
-        <v>-0.594</v>
+        <v>-45.165</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>1212.581</v>
+        <v>1912.265</v>
       </c>
       <c r="C100">
-        <v>1212.581</v>
+        <v>1912.265</v>
       </c>
       <c r="D100">
-        <v>3.793</v>
+        <v>-29.381</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>576.062</v>
+        <v>1862.685</v>
       </c>
       <c r="C101">
-        <v>576.062</v>
+        <v>1862.685</v>
       </c>
       <c r="D101">
-        <v>6.776</v>
+        <v>-4.077</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>1398.409</v>
+        <v>1696.631</v>
       </c>
       <c r="C102">
-        <v>1398.409</v>
+        <v>1696.631</v>
       </c>
       <c r="D102">
-        <v>-11.349</v>
+        <v>-17.312</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>1282.675</v>
+        <v>1736.958</v>
       </c>
       <c r="C103">
-        <v>1282.675</v>
+        <v>1736.958</v>
       </c>
       <c r="D103">
-        <v>-2.047</v>
+        <v>-9.055</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>1710.128</v>
+        <v>1488.261</v>
       </c>
       <c r="C104">
-        <v>1710.128</v>
+        <v>1488.261</v>
       </c>
       <c r="D104">
-        <v>-30.428</v>
+        <v>-13.878</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>1624.357</v>
+        <v>619.3680000000001</v>
       </c>
       <c r="C105">
-        <v>1624.357</v>
+        <v>619.3680000000001</v>
       </c>
       <c r="D105">
-        <v>-17.68</v>
+        <v>29.815</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>1289.337</v>
+        <v>659.895</v>
       </c>
       <c r="C106">
-        <v>1289.337</v>
+        <v>659.895</v>
       </c>
       <c r="D106">
-        <v>-18.223</v>
+        <v>54.19</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>1530.773</v>
+        <v>863.131</v>
       </c>
       <c r="C107">
-        <v>1530.773</v>
+        <v>863.131</v>
       </c>
       <c r="D107">
-        <v>-23.219</v>
+        <v>65.09099999999999</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>1676.315</v>
+        <v>882.1</v>
       </c>
       <c r="C108">
-        <v>1676.315</v>
+        <v>882.1</v>
       </c>
       <c r="D108">
-        <v>-23.034</v>
+        <v>54.355</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>2889.547</v>
+        <v>950</v>
       </c>
       <c r="C109">
-        <v>2889.547</v>
+        <v>950</v>
       </c>
       <c r="D109">
-        <v>-39.953</v>
+        <v>3.177</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>6675.689</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>6675.689</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>-53.128</v>
+        <v>21.099</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>1778.315</v>
+        <v>934.365</v>
       </c>
       <c r="C111">
-        <v>1778.315</v>
+        <v>934.365</v>
       </c>
       <c r="D111">
-        <v>-76.47499999999999</v>
+        <v>1.375</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>1580.683</v>
+        <v>1344.509</v>
       </c>
       <c r="C112">
-        <v>1580.683</v>
+        <v>1344.509</v>
       </c>
       <c r="D112">
-        <v>-59.522</v>
+        <v>-9.002000000000001</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>2082.256</v>
+        <v>1396.761</v>
       </c>
       <c r="C113">
-        <v>2082.256</v>
+        <v>1396.761</v>
       </c>
       <c r="D113">
-        <v>-86.377</v>
+        <v>-25.857</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>1603.593</v>
+        <v>1687.954</v>
       </c>
       <c r="C114">
-        <v>1603.593</v>
+        <v>1687.954</v>
       </c>
       <c r="D114">
-        <v>-24.885</v>
+        <v>-29.725</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>1605.088</v>
+        <v>1625.18</v>
       </c>
       <c r="C115">
-        <v>1605.088</v>
+        <v>1625.18</v>
       </c>
       <c r="D115">
-        <v>-44.922</v>
+        <v>-27.546</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>1619.1</v>
+        <v>1616.305</v>
       </c>
       <c r="C116">
-        <v>1619.1</v>
+        <v>1616.305</v>
       </c>
       <c r="D116">
-        <v>-18.935</v>
+        <v>-38.732</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>1600.85</v>
+        <v>1698.146</v>
       </c>
       <c r="C117">
-        <v>1600.85</v>
+        <v>1698.146</v>
       </c>
       <c r="D117">
-        <v>-31.027</v>
+        <v>-5.011</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>1857.021</v>
+        <v>850</v>
       </c>
       <c r="C118">
-        <v>1857.021</v>
+        <v>850</v>
       </c>
       <c r="D118">
-        <v>-49.41</v>
+        <v>13.87</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>2137.141</v>
+        <v>825.698</v>
       </c>
       <c r="C119">
-        <v>2137.141</v>
+        <v>825.698</v>
       </c>
       <c r="D119">
-        <v>-72.113</v>
+        <v>29.861</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>1896.678</v>
+        <v>850</v>
       </c>
       <c r="C120">
-        <v>1896.678</v>
+        <v>850</v>
       </c>
       <c r="D120">
-        <v>-35.84</v>
+        <v>52.915</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>1877.101</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1877.101</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>-43.871</v>
+        <v>41.557</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>2039.275</v>
+        <v>453.103</v>
       </c>
       <c r="C122">
-        <v>2039.275</v>
+        <v>453.103</v>
       </c>
       <c r="D122">
-        <v>-20.874</v>
+        <v>86.553</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>621</v>
+        <v>545.14</v>
       </c>
       <c r="C123">
-        <v>621</v>
+        <v>545.14</v>
       </c>
       <c r="D123">
-        <v>25.274</v>
+        <v>138.416</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>292.537</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>292.537</v>
       </c>
       <c r="D124">
-        <v>37.772</v>
+        <v>106.367</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>278.541</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>278.541</v>
       </c>
       <c r="D125">
-        <v>10.666</v>
+        <v>114.819</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>753.125</v>
+        <v>277.81</v>
       </c>
       <c r="C126">
-        <v>753.125</v>
+        <v>277.81</v>
       </c>
       <c r="D126">
-        <v>19.861</v>
+        <v>62.889</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>755</v>
+        <v>299.49</v>
       </c>
       <c r="C127">
-        <v>755</v>
+        <v>299.49</v>
       </c>
       <c r="D127">
-        <v>0.623</v>
+        <v>64.605</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>753.648</v>
+        <v>281.175</v>
       </c>
       <c r="C128">
-        <v>753.648</v>
+        <v>281.175</v>
       </c>
       <c r="D128">
-        <v>41.176</v>
+        <v>68.315</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>766.667</v>
+        <v>257.299</v>
       </c>
       <c r="C129">
-        <v>766.667</v>
+        <v>257.299</v>
       </c>
       <c r="D129">
-        <v>7.312</v>
+        <v>70.755</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>3114.377</v>
+        <v>1765.81</v>
       </c>
       <c r="C130">
-        <v>3114.377</v>
+        <v>1765.81</v>
       </c>
       <c r="D130">
-        <v>-38.566</v>
+        <v>-60.827</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>4633.006</v>
+        <v>1856.666</v>
       </c>
       <c r="C131">
-        <v>4633.006</v>
+        <v>1856.666</v>
       </c>
       <c r="D131">
-        <v>-26.901</v>
+        <v>-42.1</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>636.206</v>
+        <v>1569.922</v>
       </c>
       <c r="C132">
-        <v>636.206</v>
+        <v>1569.922</v>
       </c>
       <c r="D132">
-        <v>4.051</v>
+        <v>-61.145</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>528.413</v>
+        <v>1590.943</v>
       </c>
       <c r="C133">
-        <v>528.413</v>
+        <v>1590.943</v>
       </c>
       <c r="D133">
-        <v>16.123</v>
+        <v>-51.298</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1728.721</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1728.721</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>-93.98</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46304.38541666666</v>
+        <v>46305.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1322.315</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1322.315</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>-69.943</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46304.39583333334</v>
+        <v>46305.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>1333.322</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1333.322</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>-68.128</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46304.40625</v>
+        <v>46305.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>1319.604</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1319.604</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>-57.556</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46304.41666666666</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>1266.63</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1266.63</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>-14.29</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46304.42708333334</v>
+        <v>46305.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>336.136</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>336.136</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>31.27</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46304.4375</v>
+        <v>46305.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>312.697</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>312.697</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>54.385</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46304.44791666666</v>
+        <v>46305.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>-2265.124</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>-2265.124</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>51.178</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46304.45833333334</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1296.637</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1296.637</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>-22.202</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,7 +4390,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46304.46875</v>
+        <v>46305.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3823,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>2.996</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46304.47916666666</v>
+        <v>46305.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>1177.503</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1177.503</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>-93.43899999999999</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46304.48958333334</v>
+        <v>46305.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>1261.104</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1261.104</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>-63.216</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46304.5</v>
+        <v>46305.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>1267.19</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1267.19</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>-21.723</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46304.51041666666</v>
+        <v>46305.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1250.25</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1250.25</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>-32.464</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46304.52083333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>1503.921</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1503.921</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>-42.348</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46304.53125</v>
+        <v>46305.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>1353.5</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1353.5</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>-37.172</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46304.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>1354.607</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1354.607</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>-33.898</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46304.55208333334</v>
+        <v>46305.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>1172.823</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1172.823</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>-56.6</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46304.5625</v>
+        <v>46305.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>972.4059999999999</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>972.4059999999999</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>-53.944</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46304.57291666666</v>
+        <v>46305.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>929.605</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>929.605</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>-36.526</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46304.58333333334</v>
+        <v>46305.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>999.356</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>999.356</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>-42.641</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4630,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46304.59375</v>
+        <v>46305.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1024.069</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1024.069</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>-28.798</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46304.60416666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>545.253</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>545.253</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>-0.876</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46304.61458333334</v>
+        <v>46305.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>398.497</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>398.497</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>7.624</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46304.625</v>
+        <v>46305.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>234.935</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>234.935</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>24.13</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46304.63541666666</v>
+        <v>46305.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>1167.699</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1167.699</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>-13.43</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46304.64583333334</v>
+        <v>46305.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>1550.625</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1550.625</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>-29.92</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46304.65625</v>
+        <v>46305.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>1944.704</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1944.704</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>-57.069</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46304.66666666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>1709.393</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1709.393</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46304.67708333334</v>
+        <v>46305.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>1783.59</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1783.59</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>-25.692</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46304.6875</v>
+        <v>46305.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>2021.785</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>2021.785</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>-38.301</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46304.69791666666</v>
+        <v>46305.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>2710.288</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>2710.288</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>-45.26</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46304.70833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>2054.65</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>2054.65</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>-51.28</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46304.71875</v>
+        <v>46305.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>2256.472</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>2256.472</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>-49.859</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46304.72916666666</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>2030.375</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>2030.375</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>-26.9</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46304.73958333334</v>
+        <v>46305.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>2033.641</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>2033.641</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>-27.656</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46304.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>2137.636</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>2137.636</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>-81.697</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46304.76041666666</v>
+        <v>46305.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>1925.38</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1925.38</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>-49.213</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46304.77083333334</v>
+        <v>46305.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>1937.292</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1937.292</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>-43.66</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46304.78125</v>
+        <v>46305.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>1948.631</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1948.631</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>-52.607</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46304.79166666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>2074.701</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>2074.701</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>-40.286</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46304.80208333334</v>
+        <v>46305.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>2086.57</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>2086.57</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>-13.141</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46304.8125</v>
+        <v>46305.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>2082.971</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>2082.971</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>-28.797</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46304.82291666666</v>
+        <v>46305.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>2058.278</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>2058.278</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>-28.696</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46304.83333333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>1667.054</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1667.054</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>-26.617</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46304.84375</v>
+        <v>46305.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>1573.121</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1573.121</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>-10.257</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46304.85416666666</v>
+        <v>46305.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>1686.474</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1686.474</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>-12.157</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46304.86458333334</v>
+        <v>46305.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>1627.1</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1627.1</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>-14.802</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46304.875</v>
+        <v>46305.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>2083.995</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>2083.995</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>-22.412</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46304.88541666666</v>
+        <v>46305.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>1619.122</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1619.122</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>-28.27</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46304.89583333334</v>
+        <v>46305.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1754.431</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1754.431</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>-20.168</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46304.90625</v>
+        <v>46305.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>1605.158</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>1605.158</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>-14.025</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46304.91666666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>2814.881</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>2814.881</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>-32.206</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46304.92708333334</v>
+        <v>46305.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>4304.771</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>4304.771</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>-30.547</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46304.9375</v>
+        <v>46305.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>1990.629</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1990.629</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>-1.869</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46304.94791666666</v>
+        <v>46305.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>1962.662</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1962.662</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>-19.544</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46304.95833333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1666.524</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1666.524</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>-25.866</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46304.96875</v>
+        <v>46305.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1484.437</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1484.437</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>-7.208</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46304.97916666666</v>
+        <v>46305.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>1483.161</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1483.161</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>-5.17</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46304.98958333334</v>
+        <v>46305.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>1394.555</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1394.555</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>-5.354</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>1568.155</v>
+      </c>
+      <c r="C194">
+        <v>1568.155</v>
+      </c>
+      <c r="D194">
+        <v>-47.183</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>1590.172</v>
+      </c>
+      <c r="C195">
+        <v>1590.172</v>
+      </c>
+      <c r="D195">
+        <v>-9.252000000000001</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>741.198</v>
+      </c>
+      <c r="C196">
+        <v>741.198</v>
+      </c>
+      <c r="D196">
+        <v>12.277</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>1486.292</v>
+      </c>
+      <c r="C197">
+        <v>1486.292</v>
+      </c>
+      <c r="D197">
+        <v>-20.504</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1307.782</v>
+      </c>
+      <c r="C198">
+        <v>1307.782</v>
+      </c>
+      <c r="D198">
+        <v>-33.088</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1490.044</v>
+      </c>
+      <c r="C199">
+        <v>1490.044</v>
+      </c>
+      <c r="D199">
+        <v>-37.152</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>1652.138</v>
+      </c>
+      <c r="C200">
+        <v>1652.138</v>
+      </c>
+      <c r="D200">
+        <v>-32.18</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1161.841</v>
+      </c>
+      <c r="C201">
+        <v>1161.841</v>
+      </c>
+      <c r="D201">
+        <v>-14.409</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1223.735</v>
+      </c>
+      <c r="C202">
+        <v>1223.735</v>
+      </c>
+      <c r="D202">
+        <v>-64.745</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>1069.565</v>
+      </c>
+      <c r="C203">
+        <v>1069.565</v>
+      </c>
+      <c r="D203">
+        <v>-54.713</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1331.342</v>
+      </c>
+      <c r="C204">
+        <v>1331.342</v>
+      </c>
+      <c r="D204">
+        <v>-62.973</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1177.103</v>
+      </c>
+      <c r="C205">
+        <v>1177.103</v>
+      </c>
+      <c r="D205">
+        <v>-11.426</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>1493.055</v>
+      </c>
+      <c r="C206">
+        <v>1493.055</v>
+      </c>
+      <c r="D206">
+        <v>-60.091</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1258.306</v>
+      </c>
+      <c r="C207">
+        <v>1258.306</v>
+      </c>
+      <c r="D207">
+        <v>-54.609</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1361.389</v>
+      </c>
+      <c r="C208">
+        <v>1361.389</v>
+      </c>
+      <c r="D208">
+        <v>-43.773</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>1558.685</v>
+      </c>
+      <c r="C209">
+        <v>1558.685</v>
+      </c>
+      <c r="D209">
+        <v>-73.749</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1511.465</v>
+      </c>
+      <c r="C210">
+        <v>1511.465</v>
+      </c>
+      <c r="D210">
+        <v>-37.068</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1509.085</v>
+      </c>
+      <c r="C211">
+        <v>1509.085</v>
+      </c>
+      <c r="D211">
+        <v>-37.914</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>1653.237</v>
+      </c>
+      <c r="C212">
+        <v>1653.237</v>
+      </c>
+      <c r="D212">
+        <v>-79.685</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1460.64</v>
+      </c>
+      <c r="C213">
+        <v>1460.64</v>
+      </c>
+      <c r="D213">
+        <v>-157.726</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1537.42</v>
+      </c>
+      <c r="C214">
+        <v>1537.42</v>
+      </c>
+      <c r="D214">
+        <v>-103.869</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>1542.142</v>
+      </c>
+      <c r="C215">
+        <v>1542.142</v>
+      </c>
+      <c r="D215">
+        <v>-58.686</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1543.191</v>
+      </c>
+      <c r="C216">
+        <v>1543.191</v>
+      </c>
+      <c r="D216">
+        <v>-96.181</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>1549.16</v>
+      </c>
+      <c r="C217">
+        <v>1549.16</v>
+      </c>
+      <c r="D217">
+        <v>-101.564</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>1539.359</v>
+      </c>
+      <c r="C218">
+        <v>1539.359</v>
+      </c>
+      <c r="D218">
+        <v>-133.829</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>1586.172</v>
+      </c>
+      <c r="C219">
+        <v>1586.172</v>
+      </c>
+      <c r="D219">
+        <v>-117.627</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>1602.424</v>
+      </c>
+      <c r="C220">
+        <v>1602.424</v>
+      </c>
+      <c r="D220">
+        <v>-66.43600000000001</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>1601.39</v>
+      </c>
+      <c r="C221">
+        <v>1601.39</v>
+      </c>
+      <c r="D221">
+        <v>-96.026</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>1613.029</v>
+      </c>
+      <c r="C222">
+        <v>1613.029</v>
+      </c>
+      <c r="D222">
+        <v>-106.199</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1583.09</v>
+      </c>
+      <c r="C223">
+        <v>1583.09</v>
+      </c>
+      <c r="D223">
+        <v>-93.712</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>1614.53</v>
+      </c>
+      <c r="C224">
+        <v>1614.53</v>
+      </c>
+      <c r="D224">
+        <v>-54.797</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>701</v>
+      </c>
+      <c r="C225">
+        <v>701</v>
+      </c>
+      <c r="D225">
+        <v>16.823</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1461.43</v>
+      </c>
+      <c r="C226">
+        <v>1461.43</v>
+      </c>
+      <c r="D226">
+        <v>-34.42</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>1466.75</v>
+      </c>
+      <c r="C227">
+        <v>1466.75</v>
+      </c>
+      <c r="D227">
+        <v>-6.236</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1182.051</v>
+      </c>
+      <c r="C228">
+        <v>1182.051</v>
+      </c>
+      <c r="D228">
+        <v>-50.621</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1347.322</v>
+      </c>
+      <c r="C229">
+        <v>1347.322</v>
+      </c>
+      <c r="D229">
+        <v>-12.535</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>1420.078</v>
+      </c>
+      <c r="C230">
+        <v>1420.078</v>
+      </c>
+      <c r="D230">
+        <v>-49.351</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1551.987</v>
+      </c>
+      <c r="C231">
+        <v>1551.987</v>
+      </c>
+      <c r="D231">
+        <v>-27.608</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>358.722</v>
+      </c>
+      <c r="C232">
+        <v>358.722</v>
+      </c>
+      <c r="D232">
+        <v>7.42</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>238.998</v>
+      </c>
+      <c r="C233">
+        <v>238.998</v>
+      </c>
+      <c r="D233">
+        <v>65.244</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>184.406</v>
+      </c>
+      <c r="C234">
+        <v>184.406</v>
+      </c>
+      <c r="D234">
+        <v>93.25</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>-2569.955</v>
+      </c>
+      <c r="C235">
+        <v>-2569.955</v>
+      </c>
+      <c r="D235">
+        <v>116.52</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>45.119</v>
+      </c>
+      <c r="C236">
+        <v>45.119</v>
+      </c>
+      <c r="D236">
+        <v>83.864</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>41.096</v>
+      </c>
+      <c r="C237">
+        <v>41.096</v>
+      </c>
+      <c r="D237">
+        <v>88.49299999999999</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>11.494</v>
+      </c>
+      <c r="C238">
+        <v>11.494</v>
+      </c>
+      <c r="D238">
+        <v>30.24</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>4.406</v>
+      </c>
+      <c r="C239">
+        <v>4.406</v>
+      </c>
+      <c r="D239">
+        <v>22.829</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>260.995</v>
+      </c>
+      <c r="C240">
+        <v>260.995</v>
+      </c>
+      <c r="D240">
+        <v>21.376</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>750</v>
+      </c>
+      <c r="C241">
+        <v>750</v>
+      </c>
+      <c r="D241">
+        <v>-3.123</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>261.188</v>
+      </c>
+      <c r="C242">
+        <v>261.188</v>
+      </c>
+      <c r="D242">
+        <v>21.848</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>261.259</v>
+      </c>
+      <c r="C243">
+        <v>261.259</v>
+      </c>
+      <c r="D243">
+        <v>0.579</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>275.229</v>
+      </c>
+      <c r="C244">
+        <v>275.229</v>
+      </c>
+      <c r="D244">
+        <v>15.216</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>277.895</v>
+      </c>
+      <c r="C245">
+        <v>277.895</v>
+      </c>
+      <c r="D245">
+        <v>31.49</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>277.488</v>
+      </c>
+      <c r="C246">
+        <v>277.488</v>
+      </c>
+      <c r="D246">
+        <v>27.704</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>281.467</v>
+      </c>
+      <c r="C247">
+        <v>281.467</v>
+      </c>
+      <c r="D247">
+        <v>31.418</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>292.913</v>
+      </c>
+      <c r="C248">
+        <v>292.913</v>
+      </c>
+      <c r="D248">
+        <v>8.356999999999999</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>659.4589999999999</v>
+      </c>
+      <c r="C249">
+        <v>659.4589999999999</v>
+      </c>
+      <c r="D249">
+        <v>-23.062</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1172.109</v>
+      </c>
+      <c r="C250">
+        <v>1172.109</v>
+      </c>
+      <c r="D250">
+        <v>-2.045</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>1487.629</v>
+      </c>
+      <c r="C251">
+        <v>1487.629</v>
+      </c>
+      <c r="D251">
+        <v>-28.979</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3902.046</v>
+      </c>
+      <c r="C252">
+        <v>3902.046</v>
+      </c>
+      <c r="D252">
+        <v>-73.226</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>3183.164</v>
+      </c>
+      <c r="C253">
+        <v>3183.164</v>
+      </c>
+      <c r="D253">
+        <v>-97.126</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>1261.475</v>
+      </c>
+      <c r="C254">
+        <v>1261.475</v>
+      </c>
+      <c r="D254">
+        <v>-112.769</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1405.968</v>
+      </c>
+      <c r="C255">
+        <v>1405.968</v>
+      </c>
+      <c r="D255">
+        <v>-103.159</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1334.583</v>
+      </c>
+      <c r="C256">
+        <v>1334.583</v>
+      </c>
+      <c r="D256">
+        <v>-99.03400000000001</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>1259.638</v>
+      </c>
+      <c r="C257">
+        <v>1259.638</v>
+      </c>
+      <c r="D257">
+        <v>-112.72</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1353.983</v>
+      </c>
+      <c r="C258">
+        <v>1353.983</v>
+      </c>
+      <c r="D258">
+        <v>-28.968</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1357.099</v>
+      </c>
+      <c r="C259">
+        <v>1357.099</v>
+      </c>
+      <c r="D259">
+        <v>-0.611</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>1395.746</v>
+      </c>
+      <c r="C260">
+        <v>1395.746</v>
+      </c>
+      <c r="D260">
+        <v>-32.392</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>830</v>
+      </c>
+      <c r="C261">
+        <v>830</v>
+      </c>
+      <c r="D261">
+        <v>14.994</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>528.228</v>
+      </c>
+      <c r="C262">
+        <v>528.228</v>
+      </c>
+      <c r="D262">
+        <v>53.631</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>844.278</v>
+      </c>
+      <c r="C263">
+        <v>844.278</v>
+      </c>
+      <c r="D263">
+        <v>81.57299999999999</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>850</v>
+      </c>
+      <c r="C264">
+        <v>850</v>
+      </c>
+      <c r="D264">
+        <v>12.762</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>1401.823</v>
+      </c>
+      <c r="C265">
+        <v>1401.823</v>
+      </c>
+      <c r="D265">
+        <v>-25.196</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>1351.812</v>
+      </c>
+      <c r="C266">
+        <v>1351.812</v>
+      </c>
+      <c r="D266">
+        <v>12.323</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>1611.82</v>
+      </c>
+      <c r="C267">
+        <v>1611.82</v>
+      </c>
+      <c r="D267">
+        <v>-27.179</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>850</v>
+      </c>
+      <c r="C268">
+        <v>850</v>
+      </c>
+      <c r="D268">
+        <v>5.472</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>800.013</v>
+      </c>
+      <c r="C269">
+        <v>800.013</v>
+      </c>
+      <c r="D269">
+        <v>22.677</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>2321.376</v>
+      </c>
+      <c r="C270">
+        <v>2321.376</v>
+      </c>
+      <c r="D270">
+        <v>-9.198</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>850</v>
+      </c>
+      <c r="C271">
+        <v>850</v>
+      </c>
+      <c r="D271">
+        <v>85.505</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>75.895</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>541.518</v>
+      </c>
+      <c r="C273">
+        <v>541.518</v>
+      </c>
+      <c r="D273">
+        <v>33.881</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>517.8390000000001</v>
+      </c>
+      <c r="C274">
+        <v>517.8390000000001</v>
+      </c>
+      <c r="D274">
+        <v>59.569</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>471.943</v>
+      </c>
+      <c r="C275">
+        <v>471.943</v>
+      </c>
+      <c r="D275">
+        <v>20.442</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>567.393</v>
+      </c>
+      <c r="C276">
+        <v>567.393</v>
+      </c>
+      <c r="D276">
+        <v>14.705</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>652.349</v>
+      </c>
+      <c r="C277">
+        <v>652.349</v>
+      </c>
+      <c r="D277">
+        <v>0.867</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>676.549</v>
+      </c>
+      <c r="C278">
+        <v>676.549</v>
+      </c>
+      <c r="D278">
+        <v>29.086</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>683.086</v>
+      </c>
+      <c r="C279">
+        <v>683.086</v>
+      </c>
+      <c r="D279">
+        <v>67.251</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>442.255</v>
+      </c>
+      <c r="C280">
+        <v>442.255</v>
+      </c>
+      <c r="D280">
+        <v>45.243</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>477.068</v>
+      </c>
+      <c r="C281">
+        <v>477.068</v>
+      </c>
+      <c r="D281">
+        <v>28.774</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>543.211</v>
+      </c>
+      <c r="C282">
+        <v>543.211</v>
+      </c>
+      <c r="D282">
+        <v>56.412</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>525.047</v>
+      </c>
+      <c r="C283">
+        <v>525.047</v>
+      </c>
+      <c r="D283">
+        <v>36.19</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>526.633</v>
+      </c>
+      <c r="C284">
+        <v>526.633</v>
+      </c>
+      <c r="D284">
+        <v>54.289</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>524.41</v>
+      </c>
+      <c r="C285">
+        <v>524.41</v>
+      </c>
+      <c r="D285">
+        <v>28.165</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1394.67</v>
+      </c>
+      <c r="C286">
+        <v>1394.67</v>
+      </c>
+      <c r="D286">
+        <v>-18.266</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>1114.215</v>
+      </c>
+      <c r="C287">
+        <v>1114.215</v>
+      </c>
+      <c r="D287">
+        <v>-51.949</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1524.788</v>
+      </c>
+      <c r="C288">
+        <v>1524.788</v>
+      </c>
+      <c r="D288">
+        <v>-74.377</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1741.939</v>
+      </c>
+      <c r="C289">
+        <v>1741.939</v>
+      </c>
+      <c r="D289">
+        <v>-59.786</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>1304.727</v>
+      </c>
+      <c r="C290">
+        <v>1304.727</v>
+      </c>
+      <c r="D290">
+        <v>-91.902</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>1521.893</v>
+      </c>
+      <c r="C291">
+        <v>1521.893</v>
+      </c>
+      <c r="D291">
+        <v>-83.819</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>1516.897</v>
+      </c>
+      <c r="C292">
+        <v>1516.897</v>
+      </c>
+      <c r="D292">
+        <v>-51.576</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>605</v>
+      </c>
+      <c r="C293">
+        <v>605</v>
+      </c>
+      <c r="D293">
+        <v>6.282</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>64.367</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>63.754</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>103.245</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>566.39</v>
+      </c>
+      <c r="C297">
+        <v>566.39</v>
+      </c>
+      <c r="D297">
+        <v>93.142</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>436.47</v>
+      </c>
+      <c r="C298">
+        <v>436.47</v>
+      </c>
+      <c r="D298">
+        <v>83.11799999999999</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>126.049</v>
+      </c>
+      <c r="C299">
+        <v>126.049</v>
+      </c>
+      <c r="D299">
+        <v>36.611</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>236.685</v>
+      </c>
+      <c r="C300">
+        <v>236.685</v>
+      </c>
+      <c r="D300">
+        <v>81.708</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>288.57</v>
+      </c>
+      <c r="C301">
+        <v>288.57</v>
+      </c>
+      <c r="D301">
+        <v>58.179</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>291.989</v>
+      </c>
+      <c r="C302">
+        <v>291.989</v>
+      </c>
+      <c r="D302">
+        <v>61.479</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>157.247</v>
+      </c>
+      <c r="C303">
+        <v>157.247</v>
+      </c>
+      <c r="D303">
+        <v>73.65300000000001</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>-1508.793</v>
+      </c>
+      <c r="C304">
+        <v>-1508.793</v>
+      </c>
+      <c r="D304">
+        <v>120.411</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>-909.562</v>
+      </c>
+      <c r="C305">
+        <v>-909.562</v>
+      </c>
+      <c r="D305">
+        <v>166.506</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>-35.042</v>
+      </c>
+      <c r="C306">
+        <v>-35.042</v>
+      </c>
+      <c r="D306">
+        <v>180.794</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>-853.627</v>
+      </c>
+      <c r="C307">
+        <v>-853.627</v>
+      </c>
+      <c r="D307">
+        <v>150.487</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>-999.474</v>
+      </c>
+      <c r="C308">
+        <v>-999.474</v>
+      </c>
+      <c r="D308">
+        <v>108.62</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>-1000</v>
+      </c>
+      <c r="C309">
+        <v>-1000</v>
+      </c>
+      <c r="D309">
+        <v>100.862</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>262.526</v>
+      </c>
+      <c r="C310">
+        <v>262.526</v>
+      </c>
+      <c r="D310">
+        <v>152.087</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>205.527</v>
+      </c>
+      <c r="C311">
+        <v>205.527</v>
+      </c>
+      <c r="D311">
+        <v>164.088</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>200</v>
+      </c>
+      <c r="C312">
+        <v>200</v>
+      </c>
+      <c r="D312">
+        <v>129.885</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>71.21899999999999</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>275</v>
+      </c>
+      <c r="C314">
+        <v>275</v>
+      </c>
+      <c r="D314">
+        <v>54.207</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>277</v>
+      </c>
+      <c r="C315">
+        <v>277</v>
+      </c>
+      <c r="D315">
+        <v>4.89</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>5835.997</v>
+      </c>
+      <c r="C316">
+        <v>5835.997</v>
+      </c>
+      <c r="D316">
+        <v>-38.517</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>5652.547</v>
+      </c>
+      <c r="C317">
+        <v>5652.547</v>
+      </c>
+      <c r="D317">
+        <v>-62.624</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>4624.004</v>
+      </c>
+      <c r="C318">
+        <v>4624.004</v>
+      </c>
+      <c r="D318">
+        <v>-115.384</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>5486.419</v>
+      </c>
+      <c r="C319">
+        <v>5486.419</v>
+      </c>
+      <c r="D319">
+        <v>-155.543</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>2348.835</v>
+      </c>
+      <c r="C320">
+        <v>2348.835</v>
+      </c>
+      <c r="D320">
+        <v>-132.177</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>2085.882</v>
+      </c>
+      <c r="C321">
+        <v>2085.882</v>
+      </c>
+      <c r="D321">
+        <v>-106.859</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1916.511</v>
+      </c>
+      <c r="C322">
+        <v>1916.511</v>
+      </c>
+      <c r="D322">
+        <v>-52.737</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>1915.936</v>
+      </c>
+      <c r="C323">
+        <v>1915.936</v>
+      </c>
+      <c r="D323">
+        <v>-65.937</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1911.077</v>
+      </c>
+      <c r="C324">
+        <v>1911.077</v>
+      </c>
+      <c r="D324">
+        <v>-69.233</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>1917.587</v>
+      </c>
+      <c r="C325">
+        <v>1917.587</v>
+      </c>
+      <c r="D325">
+        <v>-48.931</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>1662.234</v>
+      </c>
+      <c r="C326">
+        <v>1662.234</v>
+      </c>
+      <c r="D326">
+        <v>-40.029</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>1583.39</v>
+      </c>
+      <c r="C327">
+        <v>1583.39</v>
+      </c>
+      <c r="D327">
+        <v>-49.735</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46307.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46307.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46307.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46307.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46307.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46307.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46307.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46307.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46307.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46307.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46307.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46307.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46307.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46307.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46307.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46307.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46307.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46307.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46307.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46307.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46307.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46307.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46307.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46307.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46307.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46307.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46307.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46307.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46307.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46307.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46307.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46307.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46307.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46307.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46307.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46307.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46307.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46307.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46307.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46307.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46307.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46307.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46307.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46307.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46307.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46307.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46307.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46307.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46307.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
+  </si>
+  <si>
+    <t>14.10.202660</t>
+  </si>
+  <si>
+    <t>14.10.202661</t>
+  </si>
+  <si>
+    <t>14.10.202662</t>
+  </si>
+  <si>
+    <t>14.10.202663</t>
+  </si>
+  <si>
+    <t>14.10.202664</t>
+  </si>
+  <si>
+    <t>14.10.202665</t>
+  </si>
+  <si>
+    <t>14.10.202666</t>
+  </si>
+  <si>
+    <t>14.10.202667</t>
+  </si>
+  <si>
+    <t>14.10.202668</t>
+  </si>
+  <si>
+    <t>14.10.202669</t>
+  </si>
+  <si>
+    <t>14.10.202670</t>
+  </si>
+  <si>
+    <t>14.10.202671</t>
+  </si>
+  <si>
+    <t>14.10.202672</t>
+  </si>
+  <si>
+    <t>14.10.202673</t>
+  </si>
+  <si>
+    <t>14.10.202674</t>
+  </si>
+  <si>
+    <t>14.10.202675</t>
+  </si>
+  <si>
+    <t>14.10.202676</t>
+  </si>
+  <si>
+    <t>14.10.202677</t>
+  </si>
+  <si>
+    <t>14.10.202678</t>
+  </si>
+  <si>
+    <t>14.10.202679</t>
+  </si>
+  <si>
+    <t>14.10.202680</t>
+  </si>
+  <si>
+    <t>14.10.202681</t>
+  </si>
+  <si>
+    <t>14.10.202682</t>
+  </si>
+  <si>
+    <t>14.10.202683</t>
+  </si>
+  <si>
+    <t>14.10.202684</t>
+  </si>
+  <si>
+    <t>14.10.202685</t>
+  </si>
+  <si>
+    <t>14.10.202686</t>
+  </si>
+  <si>
+    <t>14.10.202687</t>
+  </si>
+  <si>
+    <t>14.10.202688</t>
+  </si>
+  <si>
+    <t>14.10.202689</t>
+  </si>
+  <si>
+    <t>14.10.202690</t>
+  </si>
+  <si>
+    <t>14.10.202691</t>
+  </si>
+  <si>
+    <t>14.10.202692</t>
+  </si>
+  <si>
+    <t>14.10.202693</t>
+  </si>
+  <si>
+    <t>14.10.202694</t>
+  </si>
+  <si>
+    <t>14.10.202695</t>
+  </si>
+  <si>
+    <t>14.10.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>1304.727</v>
+        <v>550.539</v>
       </c>
       <c r="C2">
-        <v>1304.727</v>
+        <v>550.539</v>
       </c>
       <c r="D2">
-        <v>-91.902</v>
+        <v>111.471</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>1521.893</v>
+        <v>503.822</v>
       </c>
       <c r="C3">
-        <v>1521.893</v>
+        <v>503.822</v>
       </c>
       <c r="D3">
-        <v>-83.819</v>
+        <v>112.883</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>1516.897</v>
+        <v>301.848</v>
       </c>
       <c r="C4">
-        <v>1516.897</v>
+        <v>301.848</v>
       </c>
       <c r="D4">
-        <v>-51.576</v>
+        <v>54.947</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>605</v>
+        <v>284.831</v>
       </c>
       <c r="C5">
-        <v>605</v>
+        <v>284.831</v>
       </c>
       <c r="D5">
-        <v>6.282</v>
+        <v>15.056</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1928.442</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1928.442</v>
       </c>
       <c r="D6">
-        <v>64.367</v>
+        <v>-12.796</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D7">
-        <v>63.754</v>
+        <v>1.691</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1455.668</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1455.668</v>
       </c>
       <c r="D8">
-        <v>103.245</v>
+        <v>-6.784</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>566.39</v>
+        <v>1578.362</v>
       </c>
       <c r="C9">
-        <v>566.39</v>
+        <v>1578.362</v>
       </c>
       <c r="D9">
-        <v>93.142</v>
+        <v>-24.031</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>436.47</v>
+        <v>681</v>
       </c>
       <c r="C10">
-        <v>436.47</v>
+        <v>681</v>
       </c>
       <c r="D10">
-        <v>83.11799999999999</v>
+        <v>7.493</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>126.049</v>
+        <v>1392.718</v>
       </c>
       <c r="C11">
-        <v>126.049</v>
+        <v>1392.718</v>
       </c>
       <c r="D11">
-        <v>36.611</v>
+        <v>-10.51</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>236.685</v>
+        <v>1194.672</v>
       </c>
       <c r="C12">
-        <v>236.685</v>
+        <v>1194.672</v>
       </c>
       <c r="D12">
-        <v>81.708</v>
+        <v>-7.227</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>288.57</v>
+        <v>609.409</v>
       </c>
       <c r="C13">
-        <v>288.57</v>
+        <v>609.409</v>
       </c>
       <c r="D13">
-        <v>58.179</v>
+        <v>2.783</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>291.989</v>
+        <v>1312.882</v>
       </c>
       <c r="C14">
-        <v>291.989</v>
+        <v>1312.882</v>
       </c>
       <c r="D14">
-        <v>61.479</v>
+        <v>-3.612</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>157.247</v>
+        <v>1189.158</v>
       </c>
       <c r="C15">
-        <v>157.247</v>
+        <v>1189.158</v>
       </c>
       <c r="D15">
-        <v>73.65300000000001</v>
+        <v>-16.595</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>-1508.793</v>
+        <v>610.681</v>
       </c>
       <c r="C16">
-        <v>-1508.793</v>
+        <v>610.681</v>
       </c>
       <c r="D16">
-        <v>120.411</v>
+        <v>7.92</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>-909.562</v>
+        <v>634.321</v>
       </c>
       <c r="C17">
-        <v>-909.562</v>
+        <v>634.321</v>
       </c>
       <c r="D17">
-        <v>166.506</v>
+        <v>0.119</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>-35.042</v>
+        <v>624.202</v>
       </c>
       <c r="C18">
-        <v>-35.042</v>
+        <v>624.202</v>
       </c>
       <c r="D18">
-        <v>180.794</v>
+        <v>26.316</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>-853.627</v>
+        <v>653.879</v>
       </c>
       <c r="C19">
-        <v>-853.627</v>
+        <v>653.879</v>
       </c>
       <c r="D19">
-        <v>150.487</v>
+        <v>10.505</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>-999.474</v>
+        <v>681</v>
       </c>
       <c r="C20">
-        <v>-999.474</v>
+        <v>681</v>
       </c>
       <c r="D20">
-        <v>108.62</v>
+        <v>5.916</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>-1000</v>
+        <v>1310.45</v>
       </c>
       <c r="C21">
-        <v>-1000</v>
+        <v>1310.45</v>
       </c>
       <c r="D21">
-        <v>100.862</v>
+        <v>-2.16</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>262.526</v>
+        <v>1198.065</v>
       </c>
       <c r="C22">
-        <v>262.526</v>
+        <v>1198.065</v>
       </c>
       <c r="D22">
-        <v>152.087</v>
+        <v>-6.191</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>205.527</v>
+        <v>509.615</v>
       </c>
       <c r="C23">
-        <v>205.527</v>
+        <v>509.615</v>
       </c>
       <c r="D23">
-        <v>164.088</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>200</v>
+        <v>538.737</v>
       </c>
       <c r="C24">
-        <v>200</v>
+        <v>538.737</v>
       </c>
       <c r="D24">
-        <v>129.885</v>
+        <v>35.522</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>598.997</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>598.997</v>
       </c>
       <c r="D25">
-        <v>71.21899999999999</v>
+        <v>44.211</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>275</v>
+        <v>-3571.686</v>
       </c>
       <c r="C26">
-        <v>275</v>
+        <v>-3571.686</v>
       </c>
       <c r="D26">
-        <v>54.207</v>
+        <v>76.175</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>277</v>
+        <v>592.057</v>
       </c>
       <c r="C27">
-        <v>277</v>
+        <v>592.057</v>
       </c>
       <c r="D27">
-        <v>4.89</v>
+        <v>66.428</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>5835.997</v>
+        <v>681</v>
       </c>
       <c r="C28">
-        <v>5835.997</v>
+        <v>681</v>
       </c>
       <c r="D28">
-        <v>-38.517</v>
+        <v>37.998</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>5652.547</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>5652.547</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>-62.624</v>
+        <v>44.531</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>4624.004</v>
+        <v>613.064</v>
       </c>
       <c r="C30">
-        <v>4624.004</v>
+        <v>613.064</v>
       </c>
       <c r="D30">
-        <v>-115.384</v>
+        <v>87.55500000000001</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>5486.419</v>
+        <v>681</v>
       </c>
       <c r="C31">
-        <v>5486.419</v>
+        <v>681</v>
       </c>
       <c r="D31">
-        <v>-155.543</v>
+        <v>80.956</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>2348.835</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>2348.835</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>-132.177</v>
+        <v>71.003</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>2085.882</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>2085.882</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>-106.859</v>
+        <v>112.985</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>1916.511</v>
+        <v>275.208</v>
       </c>
       <c r="C34">
-        <v>1916.511</v>
+        <v>275.208</v>
       </c>
       <c r="D34">
-        <v>-52.737</v>
+        <v>120.068</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>1915.936</v>
+        <v>275.164</v>
       </c>
       <c r="C35">
-        <v>1915.936</v>
+        <v>275.164</v>
       </c>
       <c r="D35">
-        <v>-65.937</v>
+        <v>90.285</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>1911.077</v>
+        <v>288.7</v>
       </c>
       <c r="C36">
-        <v>1911.077</v>
+        <v>288.7</v>
       </c>
       <c r="D36">
-        <v>-69.233</v>
+        <v>129.537</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>1917.587</v>
+        <v>286.962</v>
       </c>
       <c r="C37">
-        <v>1917.587</v>
+        <v>286.962</v>
       </c>
       <c r="D37">
-        <v>-48.931</v>
+        <v>128.964</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>1662.234</v>
+        <v>298.674</v>
       </c>
       <c r="C38">
-        <v>1662.234</v>
+        <v>298.674</v>
       </c>
       <c r="D38">
-        <v>-40.029</v>
+        <v>70.12</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>1583.39</v>
+        <v>303.318</v>
       </c>
       <c r="C39">
-        <v>1583.39</v>
+        <v>303.318</v>
       </c>
       <c r="D39">
-        <v>-49.735</v>
+        <v>35.823</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>1662.919</v>
+        <v>295.701</v>
       </c>
       <c r="C40">
-        <v>1662.919</v>
+        <v>295.701</v>
       </c>
       <c r="D40">
-        <v>-24.173</v>
+        <v>36.345</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>1663.459</v>
+        <v>266.913</v>
       </c>
       <c r="C41">
-        <v>1663.459</v>
+        <v>266.913</v>
       </c>
       <c r="D41">
-        <v>-56.032</v>
+        <v>36.676</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>600.258</v>
+        <v>1135.551</v>
       </c>
       <c r="C42">
-        <v>600.258</v>
+        <v>1135.551</v>
       </c>
       <c r="D42">
-        <v>-56.485</v>
+        <v>-26.954</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>1172.449</v>
+        <v>1292.982</v>
       </c>
       <c r="C43">
-        <v>1172.449</v>
+        <v>1292.982</v>
       </c>
       <c r="D43">
-        <v>-71.873</v>
+        <v>-25.401</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>1511.418</v>
+        <v>1096.537</v>
       </c>
       <c r="C44">
-        <v>1511.418</v>
+        <v>1096.537</v>
       </c>
       <c r="D44">
-        <v>-82.767</v>
+        <v>-6.972</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>1501.046</v>
+        <v>295.074</v>
       </c>
       <c r="C45">
-        <v>1501.046</v>
+        <v>295.074</v>
       </c>
       <c r="D45">
-        <v>-49.753</v>
+        <v>17.796</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>1544.633</v>
+        <v>300.358</v>
       </c>
       <c r="C46">
-        <v>1544.633</v>
+        <v>300.358</v>
       </c>
       <c r="D46">
-        <v>-79.194</v>
+        <v>18.732</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>1544.611</v>
+        <v>338.636</v>
       </c>
       <c r="C47">
-        <v>1544.611</v>
+        <v>338.636</v>
       </c>
       <c r="D47">
-        <v>-100.107</v>
+        <v>81.175</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>1544.72</v>
+        <v>268.74</v>
       </c>
       <c r="C48">
-        <v>1544.72</v>
+        <v>268.74</v>
       </c>
       <c r="D48">
-        <v>-57.586</v>
+        <v>115.249</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>208.048</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>208.048</v>
       </c>
       <c r="D49">
-        <v>-32.227</v>
+        <v>148.26</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>1541.4</v>
+        <v>16.242</v>
       </c>
       <c r="C50">
-        <v>1541.4</v>
+        <v>16.242</v>
       </c>
       <c r="D50">
-        <v>-34.182</v>
+        <v>107.039</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>480.556</v>
+        <v>55.571</v>
       </c>
       <c r="C51">
-        <v>480.556</v>
+        <v>55.571</v>
       </c>
       <c r="D51">
-        <v>1.222</v>
+        <v>75.267</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>248.528</v>
+        <v>-99</v>
       </c>
       <c r="C52">
-        <v>248.528</v>
+        <v>-99</v>
       </c>
       <c r="D52">
-        <v>29.104</v>
+        <v>49.613</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>405.705</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>405.705</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>45.45</v>
+        <v>18.17</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>-45.199</v>
+        <v>1490.405</v>
       </c>
       <c r="C54">
-        <v>-45.199</v>
+        <v>1490.405</v>
       </c>
       <c r="D54">
-        <v>67.815</v>
+        <v>-11.895</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>241.537</v>
+        <v>1695.851</v>
       </c>
       <c r="C55">
-        <v>241.537</v>
+        <v>1695.851</v>
       </c>
       <c r="D55">
-        <v>11.997</v>
+        <v>-14.061</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>267.355</v>
+        <v>1767.855</v>
       </c>
       <c r="C56">
-        <v>267.355</v>
+        <v>1767.855</v>
       </c>
       <c r="D56">
-        <v>22.125</v>
+        <v>-51.42</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>3.567</v>
+        <v>1412.044</v>
       </c>
       <c r="C57">
-        <v>3.567</v>
+        <v>1412.044</v>
       </c>
       <c r="D57">
-        <v>70.23399999999999</v>
+        <v>-87.69799999999999</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>402.887</v>
+        <v>1600.459</v>
       </c>
       <c r="C58">
-        <v>402.887</v>
+        <v>1600.459</v>
       </c>
       <c r="D58">
-        <v>33.064</v>
+        <v>-48.466</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>605.508</v>
+        <v>1733.861</v>
       </c>
       <c r="C59">
-        <v>605.508</v>
+        <v>1733.861</v>
       </c>
       <c r="D59">
-        <v>41.409</v>
+        <v>-25.763</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>374.804</v>
+        <v>1358.012</v>
       </c>
       <c r="C60">
-        <v>374.804</v>
+        <v>1358.012</v>
       </c>
       <c r="D60">
-        <v>3.1</v>
+        <v>-24.106</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>999.869</v>
+        <v>1997.107</v>
       </c>
       <c r="C61">
-        <v>999.869</v>
+        <v>1997.107</v>
       </c>
       <c r="D61">
-        <v>-11.601</v>
+        <v>-23.704</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>1196.228</v>
+        <v>426.996</v>
       </c>
       <c r="C62">
-        <v>1196.228</v>
+        <v>426.996</v>
       </c>
       <c r="D62">
-        <v>-39.966</v>
+        <v>29.989</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>1304.65</v>
+        <v>503.263</v>
       </c>
       <c r="C63">
-        <v>1304.65</v>
+        <v>503.263</v>
       </c>
       <c r="D63">
-        <v>-56.038</v>
+        <v>78.41</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>1392.779</v>
+        <v>650</v>
       </c>
       <c r="C64">
-        <v>1392.779</v>
+        <v>650</v>
       </c>
       <c r="D64">
-        <v>-58.212</v>
+        <v>37.647</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>1306.559</v>
+        <v>2692.19</v>
       </c>
       <c r="C65">
-        <v>1306.559</v>
+        <v>2692.19</v>
       </c>
       <c r="D65">
-        <v>-102.89</v>
+        <v>-18.578</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>1000</v>
+        <v>681</v>
       </c>
       <c r="C66">
-        <v>1000</v>
+        <v>681</v>
       </c>
       <c r="D66">
-        <v>-5.339</v>
+        <v>75.17700000000001</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>9.832000000000001</v>
+        <v>37.064</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>1591.45</v>
+        <v>1820.551</v>
       </c>
       <c r="C68">
-        <v>1591.45</v>
+        <v>1820.551</v>
       </c>
       <c r="D68">
-        <v>-14.452</v>
+        <v>-2.656</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>1471.211</v>
+        <v>1983.348</v>
       </c>
       <c r="C69">
-        <v>1471.211</v>
+        <v>1983.348</v>
       </c>
       <c r="D69">
-        <v>-63.806</v>
+        <v>-42.369</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>1716.098</v>
+        <v>5417.274</v>
       </c>
       <c r="C70">
-        <v>1716.098</v>
+        <v>5417.274</v>
       </c>
       <c r="D70">
-        <v>-56.261</v>
+        <v>-97.78</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>2392.061</v>
+        <v>2256.256</v>
       </c>
       <c r="C71">
-        <v>2392.061</v>
+        <v>2256.256</v>
       </c>
       <c r="D71">
-        <v>-58.205</v>
+        <v>-93.5</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>2488.834</v>
+        <v>1837.854</v>
       </c>
       <c r="C72">
-        <v>2488.834</v>
+        <v>1837.854</v>
       </c>
       <c r="D72">
-        <v>-71.11</v>
+        <v>-73.27800000000001</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>2608.967</v>
+        <v>2032.956</v>
       </c>
       <c r="C73">
-        <v>2608.967</v>
+        <v>2032.956</v>
       </c>
       <c r="D73">
-        <v>-75.85899999999999</v>
+        <v>-78.82299999999999</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>1941.901</v>
+        <v>2070.94</v>
       </c>
       <c r="C74">
-        <v>1941.901</v>
+        <v>2070.94</v>
       </c>
       <c r="D74">
-        <v>-79.77800000000001</v>
+        <v>-106.672</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>2833.211</v>
+        <v>1914.275</v>
       </c>
       <c r="C75">
-        <v>2833.211</v>
+        <v>1914.275</v>
       </c>
       <c r="D75">
-        <v>-75.146</v>
+        <v>-62.418</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>3005.928</v>
+        <v>1904.198</v>
       </c>
       <c r="C76">
-        <v>3005.928</v>
+        <v>1904.198</v>
       </c>
       <c r="D76">
-        <v>-58.768</v>
+        <v>-28.257</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>1780.533</v>
+        <v>1857.263</v>
       </c>
       <c r="C77">
-        <v>1780.533</v>
+        <v>1857.263</v>
       </c>
       <c r="D77">
-        <v>-43.929</v>
+        <v>-56.062</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>1932.475</v>
+        <v>1923.192</v>
       </c>
       <c r="C78">
-        <v>1932.475</v>
+        <v>1923.192</v>
       </c>
       <c r="D78">
-        <v>-8.339</v>
+        <v>-66.337</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>1939.332</v>
+        <v>1898.023</v>
       </c>
       <c r="C79">
-        <v>1939.332</v>
+        <v>1898.023</v>
       </c>
       <c r="D79">
-        <v>-6.18</v>
+        <v>-47.266</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>1939.807</v>
+        <v>1924.449</v>
       </c>
       <c r="C80">
-        <v>1939.807</v>
+        <v>1924.449</v>
       </c>
       <c r="D80">
-        <v>-31.027</v>
+        <v>-15.779</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>1941.11</v>
+        <v>1885.654</v>
       </c>
       <c r="C81">
-        <v>1941.11</v>
+        <v>1885.654</v>
       </c>
       <c r="D81">
-        <v>-5.402</v>
+        <v>-13.726</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>554.8440000000001</v>
+        <v>1460.333</v>
       </c>
       <c r="C82">
-        <v>554.8440000000001</v>
+        <v>1460.333</v>
       </c>
       <c r="D82">
-        <v>23.404</v>
+        <v>-0.03</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>601.647</v>
+        <v>1710.794</v>
       </c>
       <c r="C83">
-        <v>601.647</v>
+        <v>1710.794</v>
       </c>
       <c r="D83">
-        <v>15.48</v>
+        <v>-16.922</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>582.61</v>
+        <v>652.004</v>
       </c>
       <c r="C84">
-        <v>582.61</v>
+        <v>652.004</v>
       </c>
       <c r="D84">
-        <v>78.003</v>
+        <v>4.774</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>502.007</v>
+        <v>662.9690000000001</v>
       </c>
       <c r="C85">
-        <v>502.007</v>
+        <v>662.9690000000001</v>
       </c>
       <c r="D85">
-        <v>77.095</v>
+        <v>9.807</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>560.721</v>
+        <v>1702.7</v>
       </c>
       <c r="C86">
-        <v>560.721</v>
+        <v>1702.7</v>
       </c>
       <c r="D86">
-        <v>53.695</v>
+        <v>-5.012</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>366.221</v>
+        <v>1836.373</v>
       </c>
       <c r="C87">
-        <v>366.221</v>
+        <v>1836.373</v>
       </c>
       <c r="D87">
-        <v>39.661</v>
+        <v>-26.675</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>320.309</v>
+        <v>1730.58</v>
       </c>
       <c r="C88">
-        <v>320.309</v>
+        <v>1730.58</v>
       </c>
       <c r="D88">
-        <v>60.463</v>
+        <v>-7.835</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>340.001</v>
+        <v>1448.235</v>
       </c>
       <c r="C89">
-        <v>340.001</v>
+        <v>1448.235</v>
       </c>
       <c r="D89">
-        <v>43.972</v>
+        <v>-2.019</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>317.144</v>
+        <v>1172.727</v>
       </c>
       <c r="C90">
-        <v>317.144</v>
+        <v>1172.727</v>
       </c>
       <c r="D90">
-        <v>17.317</v>
+        <v>-56.641</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>294.092</v>
+        <v>2300.801</v>
       </c>
       <c r="C91">
-        <v>294.092</v>
+        <v>2300.801</v>
       </c>
       <c r="D91">
-        <v>1.585</v>
+        <v>-54.799</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>1701.56</v>
+        <v>3431.056</v>
       </c>
       <c r="C92">
-        <v>1701.56</v>
+        <v>3431.056</v>
       </c>
       <c r="D92">
-        <v>-26.542</v>
+        <v>-73.976</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>1179.293</v>
+        <v>1679.219</v>
       </c>
       <c r="C93">
-        <v>1179.293</v>
+        <v>1679.219</v>
       </c>
       <c r="D93">
-        <v>-36.657</v>
+        <v>-65.747</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>1261.603</v>
+        <v>1870.729</v>
       </c>
       <c r="C94">
-        <v>1261.603</v>
+        <v>1870.729</v>
       </c>
       <c r="D94">
-        <v>-17.01</v>
+        <v>-86.279</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>1239.127</v>
+        <v>1646.064</v>
       </c>
       <c r="C95">
-        <v>1239.127</v>
+        <v>1646.064</v>
       </c>
       <c r="D95">
-        <v>-6.828</v>
+        <v>-107.992</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>654.756</v>
+        <v>1546.256</v>
       </c>
       <c r="C96">
-        <v>654.756</v>
+        <v>1546.256</v>
       </c>
       <c r="D96">
-        <v>32.676</v>
+        <v>-88.663</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>510.815</v>
+        <v>1492.666</v>
       </c>
       <c r="C97">
-        <v>510.815</v>
+        <v>1492.666</v>
       </c>
       <c r="D97">
-        <v>93.226</v>
+        <v>-74.547</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>550.539</v>
+        <v>1670.518</v>
       </c>
       <c r="C98">
-        <v>550.539</v>
+        <v>1670.518</v>
       </c>
       <c r="D98">
-        <v>111.471</v>
+        <v>-85.44199999999999</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>503.822</v>
+        <v>1406.506</v>
       </c>
       <c r="C99">
-        <v>503.822</v>
+        <v>1406.506</v>
       </c>
       <c r="D99">
-        <v>112.883</v>
+        <v>-49.888</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>301.848</v>
+        <v>1389.235</v>
       </c>
       <c r="C100">
-        <v>301.848</v>
+        <v>1389.235</v>
       </c>
       <c r="D100">
-        <v>54.947</v>
+        <v>-65.432</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>284.831</v>
+        <v>1423.343</v>
       </c>
       <c r="C101">
-        <v>284.831</v>
+        <v>1423.343</v>
       </c>
       <c r="D101">
-        <v>15.056</v>
+        <v>-51.219</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>1928.442</v>
+        <v>1438.733</v>
       </c>
       <c r="C102">
-        <v>1928.442</v>
+        <v>1438.733</v>
       </c>
       <c r="D102">
-        <v>-12.796</v>
+        <v>-10.1</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>285</v>
+        <v>1697.92</v>
       </c>
       <c r="C103">
-        <v>285</v>
+        <v>1697.92</v>
       </c>
       <c r="D103">
-        <v>1.691</v>
+        <v>-64.321</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>1455.668</v>
+        <v>1854.461</v>
       </c>
       <c r="C104">
-        <v>1455.668</v>
+        <v>1854.461</v>
       </c>
       <c r="D104">
-        <v>-6.784</v>
+        <v>-48.373</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>1578.362</v>
+        <v>1442.835</v>
       </c>
       <c r="C105">
-        <v>1578.362</v>
+        <v>1442.835</v>
       </c>
       <c r="D105">
-        <v>-24.031</v>
+        <v>-55.098</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>681</v>
+        <v>1547.239</v>
       </c>
       <c r="C106">
-        <v>681</v>
+        <v>1547.239</v>
       </c>
       <c r="D106">
-        <v>7.493</v>
+        <v>-41.342</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>1392.718</v>
+        <v>1447.423</v>
       </c>
       <c r="C107">
-        <v>1392.718</v>
+        <v>1447.423</v>
       </c>
       <c r="D107">
-        <v>-10.51</v>
+        <v>-13.711</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>1194.672</v>
+        <v>604.588</v>
       </c>
       <c r="C108">
-        <v>1194.672</v>
+        <v>604.588</v>
       </c>
       <c r="D108">
-        <v>-7.227</v>
+        <v>5.419</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>609.409</v>
+        <v>502.609</v>
       </c>
       <c r="C109">
-        <v>609.409</v>
+        <v>502.609</v>
       </c>
       <c r="D109">
-        <v>2.783</v>
+        <v>24.291</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>1312.882</v>
+        <v>681</v>
       </c>
       <c r="C110">
-        <v>1312.882</v>
+        <v>681</v>
       </c>
       <c r="D110">
-        <v>-3.612</v>
+        <v>26.737</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>1189.158</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1189.158</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>-16.595</v>
+        <v>13.064</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>610.681</v>
+        <v>1355.054</v>
       </c>
       <c r="C112">
-        <v>610.681</v>
+        <v>1355.054</v>
       </c>
       <c r="D112">
-        <v>7.92</v>
+        <v>-12.796</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>634.321</v>
+        <v>681</v>
       </c>
       <c r="C113">
-        <v>634.321</v>
+        <v>681</v>
       </c>
       <c r="D113">
-        <v>0.119</v>
+        <v>7.135</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>624.202</v>
+        <v>1478.723</v>
       </c>
       <c r="C114">
-        <v>624.202</v>
+        <v>1478.723</v>
       </c>
       <c r="D114">
-        <v>26.316</v>
+        <v>-14.289</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>653.879</v>
+        <v>1400.792</v>
       </c>
       <c r="C115">
-        <v>653.879</v>
+        <v>1400.792</v>
       </c>
       <c r="D115">
-        <v>10.505</v>
+        <v>-9.702999999999999</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>681</v>
+        <v>1760.947</v>
       </c>
       <c r="C116">
-        <v>681</v>
+        <v>1760.947</v>
       </c>
       <c r="D116">
-        <v>5.916</v>
+        <v>-25.625</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>1310.45</v>
+        <v>1356.272</v>
       </c>
       <c r="C117">
-        <v>1310.45</v>
+        <v>1356.272</v>
       </c>
       <c r="D117">
-        <v>-2.16</v>
+        <v>2.866</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>1198.065</v>
+        <v>1866.664</v>
       </c>
       <c r="C118">
-        <v>1198.065</v>
+        <v>1866.664</v>
       </c>
       <c r="D118">
-        <v>-6.191</v>
+        <v>-35.409</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>509.615</v>
+        <v>1892.399</v>
       </c>
       <c r="C119">
-        <v>509.615</v>
+        <v>1892.399</v>
       </c>
       <c r="D119">
-        <v>8.476000000000001</v>
+        <v>-33.876</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>538.737</v>
+        <v>1480.914</v>
       </c>
       <c r="C120">
-        <v>538.737</v>
+        <v>1480.914</v>
       </c>
       <c r="D120">
-        <v>35.522</v>
+        <v>-41.464</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>598.997</v>
+        <v>1553.953</v>
       </c>
       <c r="C121">
-        <v>598.997</v>
+        <v>1553.953</v>
       </c>
       <c r="D121">
-        <v>44.211</v>
+        <v>-54.429</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>-3571.686</v>
+        <v>2686.238</v>
       </c>
       <c r="C122">
-        <v>-3571.686</v>
+        <v>2686.238</v>
       </c>
       <c r="D122">
-        <v>76.175</v>
+        <v>-75.79900000000001</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>592.057</v>
+        <v>2069.009</v>
       </c>
       <c r="C123">
-        <v>592.057</v>
+        <v>2069.009</v>
       </c>
       <c r="D123">
-        <v>66.428</v>
+        <v>-69.52500000000001</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>681</v>
+        <v>1715.476</v>
       </c>
       <c r="C124">
-        <v>681</v>
+        <v>1715.476</v>
       </c>
       <c r="D124">
-        <v>37.998</v>
+        <v>-48.799</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>1706.044</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1706.044</v>
       </c>
       <c r="D125">
-        <v>44.531</v>
+        <v>-51.821</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>613.064</v>
+        <v>1879.545</v>
       </c>
       <c r="C126">
-        <v>613.064</v>
+        <v>1879.545</v>
       </c>
       <c r="D126">
-        <v>87.55500000000001</v>
+        <v>-25.595</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
         <v>681</v>
@@ -3503,7 +3503,7 @@
         <v>681</v>
       </c>
       <c r="D127">
-        <v>80.956</v>
+        <v>4.022</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>71.003</v>
+        <v>100.824</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>112.985</v>
+        <v>128.11</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>275.208</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>275.208</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>120.068</v>
+        <v>178.8</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>275.164</v>
+        <v>295.992</v>
       </c>
       <c r="C131">
-        <v>275.164</v>
+        <v>295.992</v>
       </c>
       <c r="D131">
-        <v>90.285</v>
+        <v>163.508</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>288.7</v>
+        <v>243.962</v>
       </c>
       <c r="C132">
-        <v>288.7</v>
+        <v>243.962</v>
       </c>
       <c r="D132">
-        <v>129.537</v>
+        <v>154.673</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>286.962</v>
+        <v>315.284</v>
       </c>
       <c r="C133">
-        <v>286.962</v>
+        <v>315.284</v>
       </c>
       <c r="D133">
-        <v>128.964</v>
+        <v>103.634</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>298.674</v>
+        <v>526.85</v>
       </c>
       <c r="C134">
-        <v>298.674</v>
+        <v>526.85</v>
       </c>
       <c r="D134">
-        <v>70.12</v>
+        <v>92.212</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>303.318</v>
+        <v>312.374</v>
       </c>
       <c r="C135">
-        <v>303.318</v>
+        <v>312.374</v>
       </c>
       <c r="D135">
-        <v>35.823</v>
+        <v>19.956</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>295.701</v>
+        <v>149.243</v>
       </c>
       <c r="C136">
-        <v>295.701</v>
+        <v>149.243</v>
       </c>
       <c r="D136">
-        <v>36.345</v>
+        <v>41.064</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>266.913</v>
+        <v>393.827</v>
       </c>
       <c r="C137">
-        <v>266.913</v>
+        <v>393.827</v>
       </c>
       <c r="D137">
-        <v>36.676</v>
+        <v>16.893</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>1135.551</v>
+        <v>1000</v>
       </c>
       <c r="C138">
-        <v>1135.551</v>
+        <v>1000</v>
       </c>
       <c r="D138">
-        <v>-26.954</v>
+        <v>-28.03</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>1292.982</v>
+        <v>314.36</v>
       </c>
       <c r="C139">
-        <v>1292.982</v>
+        <v>314.36</v>
       </c>
       <c r="D139">
-        <v>-25.401</v>
+        <v>16.831</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>1096.537</v>
+        <v>376.061</v>
       </c>
       <c r="C140">
-        <v>1096.537</v>
+        <v>376.061</v>
       </c>
       <c r="D140">
-        <v>-6.972</v>
+        <v>12.094</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>295.074</v>
+        <v>122.47</v>
       </c>
       <c r="C141">
-        <v>295.074</v>
+        <v>122.47</v>
       </c>
       <c r="D141">
-        <v>17.796</v>
+        <v>54.41</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>300.358</v>
+        <v>462.413</v>
       </c>
       <c r="C142">
-        <v>300.358</v>
+        <v>462.413</v>
       </c>
       <c r="D142">
-        <v>18.732</v>
+        <v>38.875</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>338.636</v>
+        <v>333.666</v>
       </c>
       <c r="C143">
-        <v>338.636</v>
+        <v>333.666</v>
       </c>
       <c r="D143">
-        <v>81.175</v>
+        <v>56.806</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>268.74</v>
+        <v>154.07</v>
       </c>
       <c r="C144">
-        <v>268.74</v>
+        <v>154.07</v>
       </c>
       <c r="D144">
-        <v>115.249</v>
+        <v>78.15600000000001</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>208.048</v>
+        <v>-2295.313</v>
       </c>
       <c r="C145">
-        <v>208.048</v>
+        <v>-2295.313</v>
       </c>
       <c r="D145">
-        <v>148.26</v>
+        <v>83.209</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>16.242</v>
+        <v>-482.392</v>
       </c>
       <c r="C146">
-        <v>16.242</v>
+        <v>-482.392</v>
       </c>
       <c r="D146">
-        <v>107.039</v>
+        <v>57.193</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>55.571</v>
+        <v>-5162.061</v>
       </c>
       <c r="C147">
-        <v>55.571</v>
+        <v>-5162.061</v>
       </c>
       <c r="D147">
-        <v>75.267</v>
+        <v>99.886</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>-99</v>
+        <v>-4891.002</v>
       </c>
       <c r="C148">
-        <v>-99</v>
+        <v>-4891.002</v>
       </c>
       <c r="D148">
-        <v>49.613</v>
+        <v>177.686</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>-714.748</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>-714.748</v>
       </c>
       <c r="D149">
-        <v>18.17</v>
+        <v>189.326</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +3954,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>1490.405</v>
+        <v>-185.556</v>
       </c>
       <c r="C150">
-        <v>1490.405</v>
+        <v>-185.556</v>
       </c>
       <c r="D150">
-        <v>-11.895</v>
+        <v>211.789</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +3974,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>1695.851</v>
+        <v>-269.859</v>
       </c>
       <c r="C151">
-        <v>1695.851</v>
+        <v>-269.859</v>
       </c>
       <c r="D151">
-        <v>-14.061</v>
+        <v>195.864</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>-234.163</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>-234.163</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>213.822</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4014,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>-953.986</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>-953.986</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>239.321</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4034,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>-937.284</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>-937.284</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>225.806</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4054,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>-232.812</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>-232.812</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>239.916</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46308.92708333334</v>
+        <v>46309.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46308.9375</v>
+        <v>46309.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46308.94791666666</v>
+        <v>46309.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46308.95833333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46308.96875</v>
+        <v>46309.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46308.97916666666</v>
+        <v>46309.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46308.98958333334</v>
+        <v>46309.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
-  </si>
-  <si>
-    <t>14.10.202660</t>
-  </si>
-  <si>
-    <t>14.10.202661</t>
-  </si>
-  <si>
-    <t>14.10.202662</t>
-  </si>
-  <si>
-    <t>14.10.202663</t>
-  </si>
-  <si>
-    <t>14.10.202664</t>
-  </si>
-  <si>
-    <t>14.10.202665</t>
-  </si>
-  <si>
-    <t>14.10.202666</t>
-  </si>
-  <si>
-    <t>14.10.202667</t>
-  </si>
-  <si>
-    <t>14.10.202668</t>
-  </si>
-  <si>
-    <t>14.10.202669</t>
-  </si>
-  <si>
-    <t>14.10.202670</t>
-  </si>
-  <si>
-    <t>14.10.202671</t>
-  </si>
-  <si>
-    <t>14.10.202672</t>
-  </si>
-  <si>
-    <t>14.10.202673</t>
-  </si>
-  <si>
-    <t>14.10.202674</t>
-  </si>
-  <si>
-    <t>14.10.202675</t>
-  </si>
-  <si>
-    <t>14.10.202676</t>
-  </si>
-  <si>
-    <t>14.10.202677</t>
-  </si>
-  <si>
-    <t>14.10.202678</t>
-  </si>
-  <si>
-    <t>14.10.202679</t>
-  </si>
-  <si>
-    <t>14.10.202680</t>
-  </si>
-  <si>
-    <t>14.10.202681</t>
-  </si>
-  <si>
-    <t>14.10.202682</t>
-  </si>
-  <si>
-    <t>14.10.202683</t>
-  </si>
-  <si>
-    <t>14.10.202684</t>
-  </si>
-  <si>
-    <t>14.10.202685</t>
-  </si>
-  <si>
-    <t>14.10.202686</t>
-  </si>
-  <si>
-    <t>14.10.202687</t>
-  </si>
-  <si>
-    <t>14.10.202688</t>
-  </si>
-  <si>
-    <t>14.10.202689</t>
-  </si>
-  <si>
-    <t>14.10.202690</t>
-  </si>
-  <si>
-    <t>14.10.202691</t>
-  </si>
-  <si>
-    <t>14.10.202692</t>
-  </si>
-  <si>
-    <t>14.10.202693</t>
-  </si>
-  <si>
-    <t>14.10.202694</t>
-  </si>
-  <si>
-    <t>14.10.202695</t>
-  </si>
-  <si>
-    <t>14.10.202696</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
+  </si>
+  <si>
+    <t>16.10.202653</t>
+  </si>
+  <si>
+    <t>16.10.202654</t>
+  </si>
+  <si>
+    <t>16.10.202655</t>
+  </si>
+  <si>
+    <t>16.10.202656</t>
+  </si>
+  <si>
+    <t>16.10.202657</t>
+  </si>
+  <si>
+    <t>16.10.202658</t>
+  </si>
+  <si>
+    <t>16.10.202659</t>
+  </si>
+  <si>
+    <t>16.10.202660</t>
+  </si>
+  <si>
+    <t>16.10.202661</t>
+  </si>
+  <si>
+    <t>16.10.202662</t>
+  </si>
+  <si>
+    <t>16.10.202663</t>
+  </si>
+  <si>
+    <t>16.10.202664</t>
+  </si>
+  <si>
+    <t>16.10.202665</t>
+  </si>
+  <si>
+    <t>16.10.202666</t>
+  </si>
+  <si>
+    <t>16.10.202667</t>
+  </si>
+  <si>
+    <t>16.10.202668</t>
+  </si>
+  <si>
+    <t>16.10.202669</t>
+  </si>
+  <si>
+    <t>16.10.202670</t>
+  </si>
+  <si>
+    <t>16.10.202671</t>
+  </si>
+  <si>
+    <t>16.10.202672</t>
+  </si>
+  <si>
+    <t>16.10.202673</t>
+  </si>
+  <si>
+    <t>16.10.202674</t>
+  </si>
+  <si>
+    <t>16.10.202675</t>
+  </si>
+  <si>
+    <t>16.10.202676</t>
+  </si>
+  <si>
+    <t>16.10.202677</t>
+  </si>
+  <si>
+    <t>16.10.202678</t>
+  </si>
+  <si>
+    <t>16.10.202679</t>
+  </si>
+  <si>
+    <t>16.10.202680</t>
+  </si>
+  <si>
+    <t>16.10.202681</t>
+  </si>
+  <si>
+    <t>16.10.202682</t>
+  </si>
+  <si>
+    <t>16.10.202683</t>
+  </si>
+  <si>
+    <t>16.10.202684</t>
+  </si>
+  <si>
+    <t>16.10.202685</t>
+  </si>
+  <si>
+    <t>16.10.202686</t>
+  </si>
+  <si>
+    <t>16.10.202687</t>
+  </si>
+  <si>
+    <t>16.10.202688</t>
+  </si>
+  <si>
+    <t>16.10.202689</t>
+  </si>
+  <si>
+    <t>16.10.202690</t>
+  </si>
+  <si>
+    <t>16.10.202691</t>
+  </si>
+  <si>
+    <t>16.10.202692</t>
+  </si>
+  <si>
+    <t>16.10.202693</t>
+  </si>
+  <si>
+    <t>16.10.202694</t>
+  </si>
+  <si>
+    <t>16.10.202695</t>
+  </si>
+  <si>
+    <t>16.10.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>550.539</v>
+        <v>1619.626</v>
       </c>
       <c r="C2">
-        <v>550.539</v>
+        <v>1619.626</v>
       </c>
       <c r="D2">
-        <v>111.471</v>
+        <v>-38.058</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>503.822</v>
+        <v>1531.013</v>
       </c>
       <c r="C3">
-        <v>503.822</v>
+        <v>1531.013</v>
       </c>
       <c r="D3">
-        <v>112.883</v>
+        <v>-34.793</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>301.848</v>
+        <v>1526.31</v>
       </c>
       <c r="C4">
-        <v>301.848</v>
+        <v>1526.31</v>
       </c>
       <c r="D4">
-        <v>54.947</v>
+        <v>-21.726</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>284.831</v>
+        <v>1518.203</v>
       </c>
       <c r="C5">
-        <v>284.831</v>
+        <v>1518.203</v>
       </c>
       <c r="D5">
-        <v>15.056</v>
+        <v>-41.374</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>1928.442</v>
+        <v>1467.453</v>
       </c>
       <c r="C6">
-        <v>1928.442</v>
+        <v>1467.453</v>
       </c>
       <c r="D6">
-        <v>-12.796</v>
+        <v>-0.407</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>285</v>
+        <v>1594.629</v>
       </c>
       <c r="C7">
-        <v>285</v>
+        <v>1594.629</v>
       </c>
       <c r="D7">
-        <v>1.691</v>
+        <v>-13.805</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>1455.668</v>
+        <v>614.032</v>
       </c>
       <c r="C8">
-        <v>1455.668</v>
+        <v>614.032</v>
       </c>
       <c r="D8">
-        <v>-6.784</v>
+        <v>44.486</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>1578.362</v>
+        <v>645.357</v>
       </c>
       <c r="C9">
-        <v>1578.362</v>
+        <v>645.357</v>
       </c>
       <c r="D9">
-        <v>-24.031</v>
+        <v>51.741</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>681</v>
+        <v>588.064</v>
       </c>
       <c r="C10">
-        <v>681</v>
+        <v>588.064</v>
       </c>
       <c r="D10">
-        <v>7.493</v>
+        <v>55.501</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>1392.718</v>
+        <v>594.521</v>
       </c>
       <c r="C11">
-        <v>1392.718</v>
+        <v>594.521</v>
       </c>
       <c r="D11">
-        <v>-10.51</v>
+        <v>22.35</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>1194.672</v>
+        <v>1287.418</v>
       </c>
       <c r="C12">
-        <v>1194.672</v>
+        <v>1287.418</v>
       </c>
       <c r="D12">
-        <v>-7.227</v>
+        <v>-3.253</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>609.409</v>
+        <v>1560.977</v>
       </c>
       <c r="C13">
-        <v>609.409</v>
+        <v>1560.977</v>
       </c>
       <c r="D13">
-        <v>2.783</v>
+        <v>-30.828</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>1312.882</v>
+        <v>1601.614</v>
       </c>
       <c r="C14">
-        <v>1312.882</v>
+        <v>1601.614</v>
       </c>
       <c r="D14">
-        <v>-3.612</v>
+        <v>7.16</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>1189.158</v>
+        <v>652.353</v>
       </c>
       <c r="C15">
-        <v>1189.158</v>
+        <v>652.353</v>
       </c>
       <c r="D15">
-        <v>-16.595</v>
+        <v>9.284000000000001</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>610.681</v>
+        <v>655.818</v>
       </c>
       <c r="C16">
-        <v>610.681</v>
+        <v>655.818</v>
       </c>
       <c r="D16">
-        <v>7.92</v>
+        <v>93.96899999999999</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>634.321</v>
+        <v>671.088</v>
       </c>
       <c r="C17">
-        <v>634.321</v>
+        <v>671.088</v>
       </c>
       <c r="D17">
-        <v>0.119</v>
+        <v>115.103</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>624.202</v>
+        <v>567.274</v>
       </c>
       <c r="C18">
-        <v>624.202</v>
+        <v>567.274</v>
       </c>
       <c r="D18">
-        <v>26.316</v>
+        <v>151.703</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>653.879</v>
+        <v>453.52</v>
       </c>
       <c r="C19">
-        <v>653.879</v>
+        <v>453.52</v>
       </c>
       <c r="D19">
-        <v>10.505</v>
+        <v>83.36199999999999</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>681</v>
+        <v>505.941</v>
       </c>
       <c r="C20">
-        <v>681</v>
+        <v>505.941</v>
       </c>
       <c r="D20">
-        <v>5.916</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>1310.45</v>
+        <v>623.284</v>
       </c>
       <c r="C21">
-        <v>1310.45</v>
+        <v>623.284</v>
       </c>
       <c r="D21">
-        <v>-2.16</v>
+        <v>1.338</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>1198.065</v>
+        <v>1665.961</v>
       </c>
       <c r="C22">
-        <v>1198.065</v>
+        <v>1665.961</v>
       </c>
       <c r="D22">
-        <v>-6.191</v>
+        <v>-21.248</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>509.615</v>
+        <v>1682.32</v>
       </c>
       <c r="C23">
-        <v>509.615</v>
+        <v>1682.32</v>
       </c>
       <c r="D23">
-        <v>8.476000000000001</v>
+        <v>-29.106</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>538.737</v>
+        <v>1822.971</v>
       </c>
       <c r="C24">
-        <v>538.737</v>
+        <v>1822.971</v>
       </c>
       <c r="D24">
-        <v>35.522</v>
+        <v>-36.969</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>598.997</v>
+        <v>4086.221</v>
       </c>
       <c r="C25">
-        <v>598.997</v>
+        <v>4086.221</v>
       </c>
       <c r="D25">
-        <v>44.211</v>
+        <v>-46.421</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>-3571.686</v>
+        <v>1856.195</v>
       </c>
       <c r="C26">
-        <v>-3571.686</v>
+        <v>1856.195</v>
       </c>
       <c r="D26">
-        <v>76.175</v>
+        <v>6.02</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>592.057</v>
+        <v>2685.674</v>
       </c>
       <c r="C27">
-        <v>592.057</v>
+        <v>2685.674</v>
       </c>
       <c r="D27">
-        <v>66.428</v>
+        <v>-40.611</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>681</v>
+        <v>1922.785</v>
       </c>
       <c r="C28">
-        <v>681</v>
+        <v>1922.785</v>
       </c>
       <c r="D28">
-        <v>37.998</v>
+        <v>-52.965</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1910.008</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1910.008</v>
       </c>
       <c r="D29">
-        <v>44.531</v>
+        <v>-16.557</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>613.064</v>
+        <v>1946.277</v>
       </c>
       <c r="C30">
-        <v>613.064</v>
+        <v>1946.277</v>
       </c>
       <c r="D30">
-        <v>87.55500000000001</v>
+        <v>-47.413</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>681</v>
+        <v>1981.04</v>
       </c>
       <c r="C31">
-        <v>681</v>
+        <v>1981.04</v>
       </c>
       <c r="D31">
-        <v>80.956</v>
+        <v>-59.086</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2216.433</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>2216.433</v>
       </c>
       <c r="D32">
-        <v>71.003</v>
+        <v>-47.64</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2305.279</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2305.279</v>
       </c>
       <c r="D33">
-        <v>112.985</v>
+        <v>-44.199</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>275.208</v>
+        <v>5862.061</v>
       </c>
       <c r="C34">
-        <v>275.208</v>
+        <v>5862.061</v>
       </c>
       <c r="D34">
-        <v>120.068</v>
+        <v>-145.291</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>275.164</v>
+        <v>4966.22</v>
       </c>
       <c r="C35">
-        <v>275.164</v>
+        <v>4966.22</v>
       </c>
       <c r="D35">
-        <v>90.285</v>
+        <v>-179.152</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>288.7</v>
+        <v>3356.238</v>
       </c>
       <c r="C36">
-        <v>288.7</v>
+        <v>3356.238</v>
       </c>
       <c r="D36">
-        <v>129.537</v>
+        <v>-186.838</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>286.962</v>
+        <v>2115.788</v>
       </c>
       <c r="C37">
-        <v>286.962</v>
+        <v>2115.788</v>
       </c>
       <c r="D37">
-        <v>128.964</v>
+        <v>-18.871</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>298.674</v>
+        <v>1724.679</v>
       </c>
       <c r="C38">
-        <v>298.674</v>
+        <v>1724.679</v>
       </c>
       <c r="D38">
-        <v>70.12</v>
+        <v>-122.253</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>303.318</v>
+        <v>1727.146</v>
       </c>
       <c r="C39">
-        <v>303.318</v>
+        <v>1727.146</v>
       </c>
       <c r="D39">
-        <v>35.823</v>
+        <v>-83.961</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>295.701</v>
+        <v>1726.572</v>
       </c>
       <c r="C40">
-        <v>295.701</v>
+        <v>1726.572</v>
       </c>
       <c r="D40">
-        <v>36.345</v>
+        <v>-49.104</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>266.913</v>
+        <v>1725.386</v>
       </c>
       <c r="C41">
-        <v>266.913</v>
+        <v>1725.386</v>
       </c>
       <c r="D41">
-        <v>36.676</v>
+        <v>-61.599</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>1135.551</v>
+        <v>3458.472</v>
       </c>
       <c r="C42">
-        <v>1135.551</v>
+        <v>3458.472</v>
       </c>
       <c r="D42">
-        <v>-26.954</v>
+        <v>-207.524</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>1292.982</v>
+        <v>3917.006</v>
       </c>
       <c r="C43">
-        <v>1292.982</v>
+        <v>3917.006</v>
       </c>
       <c r="D43">
-        <v>-25.401</v>
+        <v>-205.845</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>1096.537</v>
+        <v>2999.41</v>
       </c>
       <c r="C44">
-        <v>1096.537</v>
+        <v>2999.41</v>
       </c>
       <c r="D44">
-        <v>-6.972</v>
+        <v>-257.164</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>295.074</v>
+        <v>2291.648</v>
       </c>
       <c r="C45">
-        <v>295.074</v>
+        <v>2291.648</v>
       </c>
       <c r="D45">
-        <v>17.796</v>
+        <v>-241.353</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>300.358</v>
+        <v>1457.539</v>
       </c>
       <c r="C46">
-        <v>300.358</v>
+        <v>1457.539</v>
       </c>
       <c r="D46">
-        <v>18.732</v>
+        <v>-143.092</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>338.636</v>
+        <v>1457.466</v>
       </c>
       <c r="C47">
-        <v>338.636</v>
+        <v>1457.466</v>
       </c>
       <c r="D47">
-        <v>81.175</v>
+        <v>-38.133</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>268.74</v>
+        <v>681</v>
       </c>
       <c r="C48">
-        <v>268.74</v>
+        <v>681</v>
       </c>
       <c r="D48">
-        <v>115.249</v>
+        <v>14.998</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>208.048</v>
+        <v>647.204</v>
       </c>
       <c r="C49">
-        <v>208.048</v>
+        <v>647.204</v>
       </c>
       <c r="D49">
-        <v>148.26</v>
+        <v>87.605</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>16.242</v>
+        <v>698.0410000000001</v>
       </c>
       <c r="C50">
-        <v>16.242</v>
+        <v>698.0410000000001</v>
       </c>
       <c r="D50">
-        <v>107.039</v>
+        <v>128.793</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>55.571</v>
+        <v>739.958</v>
       </c>
       <c r="C51">
-        <v>55.571</v>
+        <v>739.958</v>
       </c>
       <c r="D51">
-        <v>75.267</v>
+        <v>143.858</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>-99</v>
+        <v>750.136</v>
       </c>
       <c r="C52">
-        <v>-99</v>
+        <v>750.136</v>
       </c>
       <c r="D52">
-        <v>49.613</v>
+        <v>162.29</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="D53">
-        <v>18.17</v>
+        <v>47.69</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>1490.405</v>
+        <v>751</v>
       </c>
       <c r="C54">
-        <v>1490.405</v>
+        <v>751</v>
       </c>
       <c r="D54">
-        <v>-11.895</v>
+        <v>82.773</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>1695.851</v>
+        <v>257.461</v>
       </c>
       <c r="C55">
-        <v>1695.851</v>
+        <v>257.461</v>
       </c>
       <c r="D55">
-        <v>-14.061</v>
+        <v>64.628</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>1767.855</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>1767.855</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>-51.42</v>
+        <v>26.518</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>1412.044</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1412.044</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>-87.69799999999999</v>
+        <v>29.739</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>1600.459</v>
+        <v>257.114</v>
       </c>
       <c r="C58">
-        <v>1600.459</v>
+        <v>257.114</v>
       </c>
       <c r="D58">
-        <v>-48.466</v>
+        <v>53.728</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>1733.861</v>
+        <v>256.647</v>
       </c>
       <c r="C59">
-        <v>1733.861</v>
+        <v>256.647</v>
       </c>
       <c r="D59">
-        <v>-25.763</v>
+        <v>18.447</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>1358.012</v>
+        <v>1516.643</v>
       </c>
       <c r="C60">
-        <v>1358.012</v>
+        <v>1516.643</v>
       </c>
       <c r="D60">
-        <v>-24.106</v>
+        <v>10.753</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>1997.107</v>
+        <v>720</v>
       </c>
       <c r="C61">
-        <v>1997.107</v>
+        <v>720</v>
       </c>
       <c r="D61">
-        <v>-23.704</v>
+        <v>9.699</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>426.996</v>
+        <v>334.674</v>
       </c>
       <c r="C62">
-        <v>426.996</v>
+        <v>334.674</v>
       </c>
       <c r="D62">
-        <v>29.989</v>
+        <v>218.528</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>503.263</v>
+        <v>751</v>
       </c>
       <c r="C63">
-        <v>503.263</v>
+        <v>751</v>
       </c>
       <c r="D63">
-        <v>78.41</v>
+        <v>149.778</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>650</v>
+        <v>2.741</v>
       </c>
       <c r="C64">
-        <v>650</v>
+        <v>2.741</v>
       </c>
       <c r="D64">
-        <v>37.647</v>
+        <v>59.025</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>2692.19</v>
+        <v>256</v>
       </c>
       <c r="C65">
-        <v>2692.19</v>
+        <v>256</v>
       </c>
       <c r="D65">
-        <v>-18.578</v>
+        <v>17.769</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>681</v>
+        <v>292.145</v>
       </c>
       <c r="C66">
-        <v>681</v>
+        <v>292.145</v>
       </c>
       <c r="D66">
-        <v>75.17700000000001</v>
+        <v>165.225</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>292.321</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>292.321</v>
       </c>
       <c r="D67">
-        <v>37.064</v>
+        <v>95.008</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>1820.551</v>
+        <v>293</v>
       </c>
       <c r="C68">
-        <v>1820.551</v>
+        <v>293</v>
       </c>
       <c r="D68">
-        <v>-2.656</v>
+        <v>17.421</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>1983.348</v>
+        <v>2618.012</v>
       </c>
       <c r="C69">
-        <v>1983.348</v>
+        <v>2618.012</v>
       </c>
       <c r="D69">
-        <v>-42.369</v>
+        <v>-1.335</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>5417.274</v>
+        <v>293</v>
       </c>
       <c r="C70">
-        <v>5417.274</v>
+        <v>293</v>
       </c>
       <c r="D70">
-        <v>-97.78</v>
+        <v>19.291</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>2256.256</v>
+        <v>3012.845</v>
       </c>
       <c r="C71">
-        <v>2256.256</v>
+        <v>3012.845</v>
       </c>
       <c r="D71">
-        <v>-93.5</v>
+        <v>-29.537</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>1837.854</v>
+        <v>3282.319</v>
       </c>
       <c r="C72">
-        <v>1837.854</v>
+        <v>3282.319</v>
       </c>
       <c r="D72">
-        <v>-73.27800000000001</v>
+        <v>-45.381</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>2032.956</v>
+        <v>686.167</v>
       </c>
       <c r="C73">
-        <v>2032.956</v>
+        <v>686.167</v>
       </c>
       <c r="D73">
-        <v>-78.82299999999999</v>
+        <v>3.349</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>2070.94</v>
+        <v>2128.022</v>
       </c>
       <c r="C74">
-        <v>2070.94</v>
+        <v>2128.022</v>
       </c>
       <c r="D74">
-        <v>-106.672</v>
+        <v>-23.9</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>1914.275</v>
+        <v>2131.755</v>
       </c>
       <c r="C75">
-        <v>1914.275</v>
+        <v>2131.755</v>
       </c>
       <c r="D75">
-        <v>-62.418</v>
+        <v>-1.914</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>1904.198</v>
+        <v>751</v>
       </c>
       <c r="C76">
-        <v>1904.198</v>
+        <v>751</v>
       </c>
       <c r="D76">
-        <v>-28.257</v>
+        <v>2.73</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>1857.263</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1857.263</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>-56.062</v>
+        <v>1.24</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>1923.192</v>
+        <v>1852.929</v>
       </c>
       <c r="C78">
-        <v>1923.192</v>
+        <v>1852.929</v>
       </c>
       <c r="D78">
-        <v>-66.337</v>
+        <v>-15.788</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>1898.023</v>
+        <v>1388.008</v>
       </c>
       <c r="C79">
-        <v>1898.023</v>
+        <v>1388.008</v>
       </c>
       <c r="D79">
-        <v>-47.266</v>
+        <v>-15.837</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>1924.449</v>
+        <v>1895.056</v>
       </c>
       <c r="C80">
-        <v>1924.449</v>
+        <v>1895.056</v>
       </c>
       <c r="D80">
-        <v>-15.779</v>
+        <v>-7.662</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>1885.654</v>
+        <v>750.627</v>
       </c>
       <c r="C81">
-        <v>1885.654</v>
+        <v>750.627</v>
       </c>
       <c r="D81">
-        <v>-13.726</v>
+        <v>11.646</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>1460.333</v>
+        <v>697.298</v>
       </c>
       <c r="C82">
-        <v>1460.333</v>
+        <v>697.298</v>
       </c>
       <c r="D82">
-        <v>-0.03</v>
+        <v>18.364</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>1710.794</v>
+        <v>732.313</v>
       </c>
       <c r="C83">
-        <v>1710.794</v>
+        <v>732.313</v>
       </c>
       <c r="D83">
-        <v>-16.922</v>
+        <v>28.197</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>652.004</v>
+        <v>687.361</v>
       </c>
       <c r="C84">
-        <v>652.004</v>
+        <v>687.361</v>
       </c>
       <c r="D84">
-        <v>4.774</v>
+        <v>30.934</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>662.9690000000001</v>
+        <v>709.575</v>
       </c>
       <c r="C85">
-        <v>662.9690000000001</v>
+        <v>709.575</v>
       </c>
       <c r="D85">
-        <v>9.807</v>
+        <v>26.937</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>1702.7</v>
+        <v>1198.01</v>
       </c>
       <c r="C86">
-        <v>1702.7</v>
+        <v>1198.01</v>
       </c>
       <c r="D86">
-        <v>-5.012</v>
+        <v>-1.234</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>1836.373</v>
+        <v>755</v>
       </c>
       <c r="C87">
-        <v>1836.373</v>
+        <v>755</v>
       </c>
       <c r="D87">
-        <v>-26.675</v>
+        <v>16.726</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>1730.58</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1730.58</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>-7.835</v>
+        <v>9.919</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>1448.235</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1448.235</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>-2.019</v>
+        <v>7.43</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>1172.727</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1172.727</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>-56.641</v>
+        <v>3.139</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>2300.801</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>2300.801</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>-54.799</v>
+        <v>19.404</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>3431.056</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>3431.056</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>-73.976</v>
+        <v>20.664</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>1679.219</v>
+        <v>699.61</v>
       </c>
       <c r="C93">
-        <v>1679.219</v>
+        <v>699.61</v>
       </c>
       <c r="D93">
-        <v>-65.747</v>
+        <v>28.012</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>1870.729</v>
+        <v>602.854</v>
       </c>
       <c r="C94">
-        <v>1870.729</v>
+        <v>602.854</v>
       </c>
       <c r="D94">
-        <v>-86.279</v>
+        <v>63.291</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>1646.064</v>
+        <v>551.5700000000001</v>
       </c>
       <c r="C95">
-        <v>1646.064</v>
+        <v>551.5700000000001</v>
       </c>
       <c r="D95">
-        <v>-107.992</v>
+        <v>100.939</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>1546.256</v>
+        <v>683.468</v>
       </c>
       <c r="C96">
-        <v>1546.256</v>
+        <v>683.468</v>
       </c>
       <c r="D96">
-        <v>-88.663</v>
+        <v>137.034</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>1492.666</v>
+        <v>728.5309999999999</v>
       </c>
       <c r="C97">
-        <v>1492.666</v>
+        <v>728.5309999999999</v>
       </c>
       <c r="D97">
-        <v>-74.547</v>
+        <v>140.108</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>1670.518</v>
+        <v>1413.497</v>
       </c>
       <c r="C98">
-        <v>1670.518</v>
+        <v>1413.497</v>
       </c>
       <c r="D98">
-        <v>-85.44199999999999</v>
+        <v>38.501</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>1406.506</v>
+        <v>1470.799</v>
       </c>
       <c r="C99">
-        <v>1406.506</v>
+        <v>1470.799</v>
       </c>
       <c r="D99">
-        <v>-49.888</v>
+        <v>-9.423</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>1389.235</v>
+        <v>1871.377</v>
       </c>
       <c r="C100">
-        <v>1389.235</v>
+        <v>1871.377</v>
       </c>
       <c r="D100">
-        <v>-65.432</v>
+        <v>-36.413</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>1423.343</v>
+        <v>732.8440000000001</v>
       </c>
       <c r="C101">
-        <v>1423.343</v>
+        <v>732.8440000000001</v>
       </c>
       <c r="D101">
-        <v>-51.219</v>
+        <v>11.558</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>1438.733</v>
+        <v>727.593</v>
       </c>
       <c r="C102">
-        <v>1438.733</v>
+        <v>727.593</v>
       </c>
       <c r="D102">
-        <v>-10.1</v>
+        <v>3.576</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>1697.92</v>
+        <v>621.8440000000001</v>
       </c>
       <c r="C103">
-        <v>1697.92</v>
+        <v>621.8440000000001</v>
       </c>
       <c r="D103">
-        <v>-64.321</v>
+        <v>37.923</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>1854.461</v>
+        <v>700.133</v>
       </c>
       <c r="C104">
-        <v>1854.461</v>
+        <v>700.133</v>
       </c>
       <c r="D104">
-        <v>-48.373</v>
+        <v>105.934</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>1442.835</v>
+        <v>579.841</v>
       </c>
       <c r="C105">
-        <v>1442.835</v>
+        <v>579.841</v>
       </c>
       <c r="D105">
-        <v>-55.098</v>
+        <v>130.306</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>1547.239</v>
+        <v>707.009</v>
       </c>
       <c r="C106">
-        <v>1547.239</v>
+        <v>707.009</v>
       </c>
       <c r="D106">
-        <v>-41.342</v>
+        <v>127.951</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>1447.423</v>
+        <v>605.271</v>
       </c>
       <c r="C107">
-        <v>1447.423</v>
+        <v>605.271</v>
       </c>
       <c r="D107">
-        <v>-13.711</v>
+        <v>77.80500000000001</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>604.588</v>
+        <v>520.721</v>
       </c>
       <c r="C108">
-        <v>604.588</v>
+        <v>520.721</v>
       </c>
       <c r="D108">
-        <v>5.419</v>
+        <v>57.986</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>502.609</v>
+        <v>649.4059999999999</v>
       </c>
       <c r="C109">
-        <v>502.609</v>
+        <v>649.4059999999999</v>
       </c>
       <c r="D109">
-        <v>24.291</v>
+        <v>38.66</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>681</v>
+        <v>755</v>
       </c>
       <c r="C110">
-        <v>681</v>
+        <v>755</v>
       </c>
       <c r="D110">
-        <v>26.737</v>
+        <v>4.823</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1453.497</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1453.497</v>
       </c>
       <c r="D111">
-        <v>13.064</v>
+        <v>-11.402</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>1355.054</v>
+        <v>755</v>
       </c>
       <c r="C112">
-        <v>1355.054</v>
+        <v>755</v>
       </c>
       <c r="D112">
-        <v>-12.796</v>
+        <v>7.944</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>681</v>
+        <v>1380.014</v>
       </c>
       <c r="C113">
-        <v>681</v>
+        <v>1380.014</v>
       </c>
       <c r="D113">
-        <v>7.135</v>
+        <v>-1.175</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>1478.723</v>
+        <v>728.415</v>
       </c>
       <c r="C114">
-        <v>1478.723</v>
+        <v>728.415</v>
       </c>
       <c r="D114">
-        <v>-14.289</v>
+        <v>44.057</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>1400.792</v>
+        <v>755</v>
       </c>
       <c r="C115">
-        <v>1400.792</v>
+        <v>755</v>
       </c>
       <c r="D115">
-        <v>-9.702999999999999</v>
+        <v>30.026</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>1760.947</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>1760.947</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>-25.625</v>
+        <v>36.025</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>1356.272</v>
+        <v>680.731</v>
       </c>
       <c r="C117">
-        <v>1356.272</v>
+        <v>680.731</v>
       </c>
       <c r="D117">
-        <v>2.866</v>
+        <v>47.585</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>1866.664</v>
+        <v>546.0359999999999</v>
       </c>
       <c r="C118">
-        <v>1866.664</v>
+        <v>546.0359999999999</v>
       </c>
       <c r="D118">
-        <v>-35.409</v>
+        <v>35.304</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>1892.399</v>
+        <v>755</v>
       </c>
       <c r="C119">
-        <v>1892.399</v>
+        <v>755</v>
       </c>
       <c r="D119">
-        <v>-33.876</v>
+        <v>34.921</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>1480.914</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>1480.914</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>-41.464</v>
+        <v>58.753</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>1553.953</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1553.953</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>-54.429</v>
+        <v>53.52</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>2686.238</v>
+        <v>460.893</v>
       </c>
       <c r="C122">
-        <v>2686.238</v>
+        <v>460.893</v>
       </c>
       <c r="D122">
-        <v>-75.79900000000001</v>
+        <v>103.845</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>2069.009</v>
+        <v>755</v>
       </c>
       <c r="C123">
-        <v>2069.009</v>
+        <v>755</v>
       </c>
       <c r="D123">
-        <v>-69.52500000000001</v>
+        <v>91.52800000000001</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>1715.476</v>
+        <v>667.5069999999999</v>
       </c>
       <c r="C124">
-        <v>1715.476</v>
+        <v>667.5069999999999</v>
       </c>
       <c r="D124">
-        <v>-48.799</v>
+        <v>97.982</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>1706.044</v>
+        <v>626.794</v>
       </c>
       <c r="C125">
-        <v>1706.044</v>
+        <v>626.794</v>
       </c>
       <c r="D125">
-        <v>-51.821</v>
+        <v>78.624</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>1879.545</v>
+        <v>693.614</v>
       </c>
       <c r="C126">
-        <v>1879.545</v>
+        <v>693.614</v>
       </c>
       <c r="D126">
-        <v>-25.595</v>
+        <v>38.314</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>681</v>
+        <v>693.707</v>
       </c>
       <c r="C127">
-        <v>681</v>
+        <v>693.707</v>
       </c>
       <c r="D127">
-        <v>4.022</v>
+        <v>20.851</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>685.544</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>685.544</v>
       </c>
       <c r="D128">
-        <v>100.824</v>
+        <v>27.466</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>695.389</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>695.389</v>
       </c>
       <c r="D129">
-        <v>128.11</v>
+        <v>22.088</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1820.191</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1820.191</v>
       </c>
       <c r="D130">
-        <v>178.8</v>
+        <v>-25.847</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>295.992</v>
+        <v>1286.23</v>
       </c>
       <c r="C131">
-        <v>295.992</v>
+        <v>1286.23</v>
       </c>
       <c r="D131">
-        <v>163.508</v>
+        <v>-1.396</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>243.962</v>
+        <v>479.746</v>
       </c>
       <c r="C132">
-        <v>243.962</v>
+        <v>479.746</v>
       </c>
       <c r="D132">
-        <v>154.673</v>
+        <v>1.246</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>315.284</v>
+        <v>394.245</v>
       </c>
       <c r="C133">
-        <v>315.284</v>
+        <v>394.245</v>
       </c>
       <c r="D133">
-        <v>103.634</v>
+        <v>82.592</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>526.85</v>
+        <v>494.289</v>
       </c>
       <c r="C134">
-        <v>526.85</v>
+        <v>494.289</v>
       </c>
       <c r="D134">
-        <v>92.212</v>
+        <v>45.106</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>312.374</v>
+        <v>530.7910000000001</v>
       </c>
       <c r="C135">
-        <v>312.374</v>
+        <v>530.7910000000001</v>
       </c>
       <c r="D135">
-        <v>19.956</v>
+        <v>91.851</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>149.243</v>
+        <v>241.963</v>
       </c>
       <c r="C136">
-        <v>149.243</v>
+        <v>241.963</v>
       </c>
       <c r="D136">
-        <v>41.064</v>
+        <v>124.709</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>393.827</v>
+        <v>-567.073</v>
       </c>
       <c r="C137">
-        <v>393.827</v>
+        <v>-567.073</v>
       </c>
       <c r="D137">
-        <v>16.893</v>
+        <v>76.426</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>1000</v>
+        <v>1172.087</v>
       </c>
       <c r="C138">
-        <v>1000</v>
+        <v>1172.087</v>
       </c>
       <c r="D138">
-        <v>-28.03</v>
+        <v>-23.81</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>314.36</v>
+        <v>993.284</v>
       </c>
       <c r="C139">
-        <v>314.36</v>
+        <v>993.284</v>
       </c>
       <c r="D139">
-        <v>16.831</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>376.061</v>
+        <v>348.908</v>
       </c>
       <c r="C140">
-        <v>376.061</v>
+        <v>348.908</v>
       </c>
       <c r="D140">
-        <v>12.094</v>
+        <v>11.512</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>122.47</v>
+        <v>1388.091</v>
       </c>
       <c r="C141">
-        <v>122.47</v>
+        <v>1388.091</v>
       </c>
       <c r="D141">
-        <v>54.41</v>
+        <v>-44.41</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>462.413</v>
+        <v>963.978</v>
       </c>
       <c r="C142">
-        <v>462.413</v>
+        <v>963.978</v>
       </c>
       <c r="D142">
-        <v>38.875</v>
+        <v>-32.559</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>333.666</v>
+        <v>817.164</v>
       </c>
       <c r="C143">
-        <v>333.666</v>
+        <v>817.164</v>
       </c>
       <c r="D143">
-        <v>56.806</v>
+        <v>-5.048</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>154.07</v>
+        <v>1162.67</v>
       </c>
       <c r="C144">
-        <v>154.07</v>
+        <v>1162.67</v>
       </c>
       <c r="D144">
-        <v>78.15600000000001</v>
+        <v>-13.683</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>-2295.313</v>
+        <v>0.667</v>
       </c>
       <c r="C145">
-        <v>-2295.313</v>
+        <v>0.667</v>
       </c>
       <c r="D145">
-        <v>83.209</v>
+        <v>56.245</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>-482.392</v>
+        <v>61.765</v>
       </c>
       <c r="C146">
-        <v>-482.392</v>
+        <v>61.765</v>
       </c>
       <c r="D146">
-        <v>57.193</v>
+        <v>112.244</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>-5162.061</v>
+        <v>151.024</v>
       </c>
       <c r="C147">
-        <v>-5162.061</v>
+        <v>151.024</v>
       </c>
       <c r="D147">
-        <v>99.886</v>
+        <v>56.615</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>-4891.002</v>
+        <v>260.609</v>
       </c>
       <c r="C148">
-        <v>-4891.002</v>
+        <v>260.609</v>
       </c>
       <c r="D148">
-        <v>177.686</v>
+        <v>10.48</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
-        <v>-714.748</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>-714.748</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>189.326</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +3954,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B150">
-        <v>-185.556</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>-185.556</v>
+        <v>0</v>
       </c>
       <c r="D150">
-        <v>211.789</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +3974,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B151">
-        <v>-269.859</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>-269.859</v>
+        <v>0</v>
       </c>
       <c r="D151">
-        <v>195.864</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B152">
-        <v>-234.163</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>-234.163</v>
+        <v>0</v>
       </c>
       <c r="D152">
-        <v>213.822</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4014,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B153">
-        <v>-953.986</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>-953.986</v>
+        <v>0</v>
       </c>
       <c r="D153">
-        <v>239.321</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4034,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B154">
-        <v>-937.284</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>-937.284</v>
+        <v>0</v>
       </c>
       <c r="D154">
-        <v>225.806</v>
+        <v>0</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4054,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B155">
-        <v>-232.812</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>-232.812</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>239.916</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46309.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46309.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46309.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46309.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46309.96875</v>
+        <v>46311.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46309.97916666666</v>
+        <v>46311.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46309.98958333334</v>
+        <v>46311.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
-  </si>
-  <si>
-    <t>16.10.202653</t>
-  </si>
-  <si>
-    <t>16.10.202654</t>
-  </si>
-  <si>
-    <t>16.10.202655</t>
-  </si>
-  <si>
-    <t>16.10.202656</t>
-  </si>
-  <si>
-    <t>16.10.202657</t>
-  </si>
-  <si>
-    <t>16.10.202658</t>
-  </si>
-  <si>
-    <t>16.10.202659</t>
-  </si>
-  <si>
-    <t>16.10.202660</t>
-  </si>
-  <si>
-    <t>16.10.202661</t>
-  </si>
-  <si>
-    <t>16.10.202662</t>
-  </si>
-  <si>
-    <t>16.10.202663</t>
-  </si>
-  <si>
-    <t>16.10.202664</t>
-  </si>
-  <si>
-    <t>16.10.202665</t>
-  </si>
-  <si>
-    <t>16.10.202666</t>
-  </si>
-  <si>
-    <t>16.10.202667</t>
-  </si>
-  <si>
-    <t>16.10.202668</t>
-  </si>
-  <si>
-    <t>16.10.202669</t>
-  </si>
-  <si>
-    <t>16.10.202670</t>
-  </si>
-  <si>
-    <t>16.10.202671</t>
-  </si>
-  <si>
-    <t>16.10.202672</t>
-  </si>
-  <si>
-    <t>16.10.202673</t>
-  </si>
-  <si>
-    <t>16.10.202674</t>
-  </si>
-  <si>
-    <t>16.10.202675</t>
-  </si>
-  <si>
-    <t>16.10.202676</t>
-  </si>
-  <si>
-    <t>16.10.202677</t>
-  </si>
-  <si>
-    <t>16.10.202678</t>
-  </si>
-  <si>
-    <t>16.10.202679</t>
-  </si>
-  <si>
-    <t>16.10.202680</t>
-  </si>
-  <si>
-    <t>16.10.202681</t>
-  </si>
-  <si>
-    <t>16.10.202682</t>
-  </si>
-  <si>
-    <t>16.10.202683</t>
-  </si>
-  <si>
-    <t>16.10.202684</t>
-  </si>
-  <si>
-    <t>16.10.202685</t>
-  </si>
-  <si>
-    <t>16.10.202686</t>
-  </si>
-  <si>
-    <t>16.10.202687</t>
-  </si>
-  <si>
-    <t>16.10.202688</t>
-  </si>
-  <si>
-    <t>16.10.202689</t>
-  </si>
-  <si>
-    <t>16.10.202690</t>
-  </si>
-  <si>
-    <t>16.10.202691</t>
-  </si>
-  <si>
-    <t>16.10.202692</t>
-  </si>
-  <si>
-    <t>16.10.202693</t>
-  </si>
-  <si>
-    <t>16.10.202694</t>
-  </si>
-  <si>
-    <t>16.10.202695</t>
-  </si>
-  <si>
-    <t>16.10.202696</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
+  </si>
+  <si>
+    <t>21.10.202636</t>
+  </si>
+  <si>
+    <t>21.10.202637</t>
+  </si>
+  <si>
+    <t>21.10.202638</t>
+  </si>
+  <si>
+    <t>21.10.202639</t>
+  </si>
+  <si>
+    <t>21.10.202640</t>
+  </si>
+  <si>
+    <t>21.10.202641</t>
+  </si>
+  <si>
+    <t>21.10.202642</t>
+  </si>
+  <si>
+    <t>21.10.202643</t>
+  </si>
+  <si>
+    <t>21.10.202644</t>
+  </si>
+  <si>
+    <t>21.10.202645</t>
+  </si>
+  <si>
+    <t>21.10.202646</t>
+  </si>
+  <si>
+    <t>21.10.202647</t>
+  </si>
+  <si>
+    <t>21.10.202648</t>
+  </si>
+  <si>
+    <t>21.10.202649</t>
+  </si>
+  <si>
+    <t>21.10.202650</t>
+  </si>
+  <si>
+    <t>21.10.202651</t>
+  </si>
+  <si>
+    <t>21.10.202652</t>
+  </si>
+  <si>
+    <t>21.10.202653</t>
+  </si>
+  <si>
+    <t>21.10.202654</t>
+  </si>
+  <si>
+    <t>21.10.202655</t>
+  </si>
+  <si>
+    <t>21.10.202656</t>
+  </si>
+  <si>
+    <t>21.10.202657</t>
+  </si>
+  <si>
+    <t>21.10.202658</t>
+  </si>
+  <si>
+    <t>21.10.202659</t>
+  </si>
+  <si>
+    <t>21.10.202660</t>
+  </si>
+  <si>
+    <t>21.10.202661</t>
+  </si>
+  <si>
+    <t>21.10.202662</t>
+  </si>
+  <si>
+    <t>21.10.202663</t>
+  </si>
+  <si>
+    <t>21.10.202664</t>
+  </si>
+  <si>
+    <t>21.10.202665</t>
+  </si>
+  <si>
+    <t>21.10.202666</t>
+  </si>
+  <si>
+    <t>21.10.202667</t>
+  </si>
+  <si>
+    <t>21.10.202668</t>
+  </si>
+  <si>
+    <t>21.10.202669</t>
+  </si>
+  <si>
+    <t>21.10.202670</t>
+  </si>
+  <si>
+    <t>21.10.202671</t>
+  </si>
+  <si>
+    <t>21.10.202672</t>
+  </si>
+  <si>
+    <t>21.10.202673</t>
+  </si>
+  <si>
+    <t>21.10.202674</t>
+  </si>
+  <si>
+    <t>21.10.202675</t>
+  </si>
+  <si>
+    <t>21.10.202676</t>
+  </si>
+  <si>
+    <t>21.10.202677</t>
+  </si>
+  <si>
+    <t>21.10.202678</t>
+  </si>
+  <si>
+    <t>21.10.202679</t>
+  </si>
+  <si>
+    <t>21.10.202680</t>
+  </si>
+  <si>
+    <t>21.10.202681</t>
+  </si>
+  <si>
+    <t>21.10.202682</t>
+  </si>
+  <si>
+    <t>21.10.202683</t>
+  </si>
+  <si>
+    <t>21.10.202684</t>
+  </si>
+  <si>
+    <t>21.10.202685</t>
+  </si>
+  <si>
+    <t>21.10.202686</t>
+  </si>
+  <si>
+    <t>21.10.202687</t>
+  </si>
+  <si>
+    <t>21.10.202688</t>
+  </si>
+  <si>
+    <t>21.10.202689</t>
+  </si>
+  <si>
+    <t>21.10.202690</t>
+  </si>
+  <si>
+    <t>21.10.202691</t>
+  </si>
+  <si>
+    <t>21.10.202692</t>
+  </si>
+  <si>
+    <t>21.10.202693</t>
+  </si>
+  <si>
+    <t>21.10.202694</t>
+  </si>
+  <si>
+    <t>21.10.202695</t>
+  </si>
+  <si>
+    <t>21.10.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>1619.626</v>
+        <v>616.747</v>
       </c>
       <c r="C2">
-        <v>1619.626</v>
+        <v>616.747</v>
       </c>
       <c r="D2">
-        <v>-38.058</v>
+        <v>63.333</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>1531.013</v>
+        <v>174.35</v>
       </c>
       <c r="C3">
-        <v>1531.013</v>
+        <v>174.35</v>
       </c>
       <c r="D3">
-        <v>-34.793</v>
+        <v>50.831</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>1526.31</v>
+        <v>486.587</v>
       </c>
       <c r="C4">
-        <v>1526.31</v>
+        <v>486.587</v>
       </c>
       <c r="D4">
-        <v>-21.726</v>
+        <v>79.85899999999999</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>1518.203</v>
+        <v>704.181</v>
       </c>
       <c r="C5">
-        <v>1518.203</v>
+        <v>704.181</v>
       </c>
       <c r="D5">
-        <v>-41.374</v>
+        <v>20.851</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>1467.453</v>
+        <v>2080.88</v>
       </c>
       <c r="C6">
-        <v>1467.453</v>
+        <v>2080.88</v>
       </c>
       <c r="D6">
-        <v>-0.407</v>
+        <v>-45.759</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>1594.629</v>
+        <v>2005.247</v>
       </c>
       <c r="C7">
-        <v>1594.629</v>
+        <v>2005.247</v>
       </c>
       <c r="D7">
-        <v>-13.805</v>
+        <v>-85.96299999999999</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>614.032</v>
+        <v>1967.617</v>
       </c>
       <c r="C8">
-        <v>614.032</v>
+        <v>1967.617</v>
       </c>
       <c r="D8">
-        <v>44.486</v>
+        <v>-69.70999999999999</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>645.357</v>
+        <v>1983.258</v>
       </c>
       <c r="C9">
-        <v>645.357</v>
+        <v>1983.258</v>
       </c>
       <c r="D9">
-        <v>51.741</v>
+        <v>-60.088</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>588.064</v>
+        <v>720</v>
       </c>
       <c r="C10">
-        <v>588.064</v>
+        <v>720</v>
       </c>
       <c r="D10">
-        <v>55.501</v>
+        <v>32.834</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>594.521</v>
+        <v>712.924</v>
       </c>
       <c r="C11">
-        <v>594.521</v>
+        <v>712.924</v>
       </c>
       <c r="D11">
-        <v>22.35</v>
+        <v>53.182</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>1287.418</v>
+        <v>715.901</v>
       </c>
       <c r="C12">
-        <v>1287.418</v>
+        <v>715.901</v>
       </c>
       <c r="D12">
-        <v>-3.253</v>
+        <v>70.956</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>1560.977</v>
+        <v>710.482</v>
       </c>
       <c r="C13">
-        <v>1560.977</v>
+        <v>710.482</v>
       </c>
       <c r="D13">
-        <v>-30.828</v>
+        <v>36.992</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>1601.614</v>
+        <v>706.913</v>
       </c>
       <c r="C14">
-        <v>1601.614</v>
+        <v>706.913</v>
       </c>
       <c r="D14">
-        <v>7.16</v>
+        <v>59.679</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>652.353</v>
+        <v>707.266</v>
       </c>
       <c r="C15">
-        <v>652.353</v>
+        <v>707.266</v>
       </c>
       <c r="D15">
-        <v>9.284000000000001</v>
+        <v>63.197</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>655.818</v>
+        <v>702.109</v>
       </c>
       <c r="C16">
-        <v>655.818</v>
+        <v>702.109</v>
       </c>
       <c r="D16">
-        <v>93.96899999999999</v>
+        <v>18.141</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>671.088</v>
+        <v>1912.835</v>
       </c>
       <c r="C17">
-        <v>671.088</v>
+        <v>1912.835</v>
       </c>
       <c r="D17">
-        <v>115.103</v>
+        <v>-11.281</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>567.274</v>
+        <v>705.45</v>
       </c>
       <c r="C18">
-        <v>567.274</v>
+        <v>705.45</v>
       </c>
       <c r="D18">
-        <v>151.703</v>
+        <v>6.627</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>453.52</v>
+        <v>1804.727</v>
       </c>
       <c r="C19">
-        <v>453.52</v>
+        <v>1804.727</v>
       </c>
       <c r="D19">
-        <v>83.36199999999999</v>
+        <v>-14.216</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>505.941</v>
+        <v>705.1849999999999</v>
       </c>
       <c r="C20">
-        <v>505.941</v>
+        <v>705.1849999999999</v>
       </c>
       <c r="D20">
-        <v>64.04000000000001</v>
+        <v>7.753</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>623.284</v>
+        <v>704.276</v>
       </c>
       <c r="C21">
-        <v>623.284</v>
+        <v>704.276</v>
       </c>
       <c r="D21">
-        <v>1.338</v>
+        <v>0.456</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>1665.961</v>
+        <v>672.665</v>
       </c>
       <c r="C22">
-        <v>1665.961</v>
+        <v>672.665</v>
       </c>
       <c r="D22">
-        <v>-21.248</v>
+        <v>48.492</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>1682.32</v>
+        <v>705.155</v>
       </c>
       <c r="C23">
-        <v>1682.32</v>
+        <v>705.155</v>
       </c>
       <c r="D23">
-        <v>-29.106</v>
+        <v>31.426</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>1822.971</v>
+        <v>720</v>
       </c>
       <c r="C24">
-        <v>1822.971</v>
+        <v>720</v>
       </c>
       <c r="D24">
-        <v>-36.969</v>
+        <v>39.567</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>4086.221</v>
+        <v>718.754</v>
       </c>
       <c r="C25">
-        <v>4086.221</v>
+        <v>718.754</v>
       </c>
       <c r="D25">
-        <v>-46.421</v>
+        <v>28.314</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>1856.195</v>
+        <v>686.3390000000001</v>
       </c>
       <c r="C26">
-        <v>1856.195</v>
+        <v>686.3390000000001</v>
       </c>
       <c r="D26">
-        <v>6.02</v>
+        <v>24.069</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>2685.674</v>
+        <v>720</v>
       </c>
       <c r="C27">
-        <v>2685.674</v>
+        <v>720</v>
       </c>
       <c r="D27">
-        <v>-40.611</v>
+        <v>47.052</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>1922.785</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1922.785</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>-52.965</v>
+        <v>1.777</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>1910.008</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1910.008</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>-16.557</v>
+        <v>11.105</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>1946.277</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>1946.277</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>-47.413</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>1981.04</v>
+        <v>706.66</v>
       </c>
       <c r="C31">
-        <v>1981.04</v>
+        <v>706.66</v>
       </c>
       <c r="D31">
-        <v>-59.086</v>
+        <v>48.701</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>2216.433</v>
+        <v>721.2859999999999</v>
       </c>
       <c r="C32">
-        <v>2216.433</v>
+        <v>721.2859999999999</v>
       </c>
       <c r="D32">
-        <v>-47.64</v>
+        <v>22.569</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>2305.279</v>
+        <v>718.705</v>
       </c>
       <c r="C33">
-        <v>2305.279</v>
+        <v>718.705</v>
       </c>
       <c r="D33">
-        <v>-44.199</v>
+        <v>39.065</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>5862.061</v>
+        <v>712.497</v>
       </c>
       <c r="C34">
-        <v>5862.061</v>
+        <v>712.497</v>
       </c>
       <c r="D34">
-        <v>-145.291</v>
+        <v>26.352</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>4966.22</v>
+        <v>729.337</v>
       </c>
       <c r="C35">
-        <v>4966.22</v>
+        <v>729.337</v>
       </c>
       <c r="D35">
-        <v>-179.152</v>
+        <v>18.808</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>3356.238</v>
+        <v>3586.837</v>
       </c>
       <c r="C36">
-        <v>3356.238</v>
+        <v>3586.837</v>
       </c>
       <c r="D36">
-        <v>-186.838</v>
+        <v>-27.512</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>2115.788</v>
+        <v>705.283</v>
       </c>
       <c r="C37">
-        <v>2115.788</v>
+        <v>705.283</v>
       </c>
       <c r="D37">
-        <v>-18.871</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>1724.679</v>
+        <v>1696.691</v>
       </c>
       <c r="C38">
-        <v>1724.679</v>
+        <v>1696.691</v>
       </c>
       <c r="D38">
-        <v>-122.253</v>
+        <v>-7.898</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>1727.146</v>
+        <v>1655.484</v>
       </c>
       <c r="C39">
-        <v>1727.146</v>
+        <v>1655.484</v>
       </c>
       <c r="D39">
-        <v>-83.961</v>
+        <v>10.781</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>1726.572</v>
+        <v>720</v>
       </c>
       <c r="C40">
-        <v>1726.572</v>
+        <v>720</v>
       </c>
       <c r="D40">
-        <v>-49.104</v>
+        <v>39.541</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>1725.386</v>
+        <v>703.881</v>
       </c>
       <c r="C41">
-        <v>1725.386</v>
+        <v>703.881</v>
       </c>
       <c r="D41">
-        <v>-61.599</v>
+        <v>128.981</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>3458.472</v>
+        <v>710.836</v>
       </c>
       <c r="C42">
-        <v>3458.472</v>
+        <v>710.836</v>
       </c>
       <c r="D42">
-        <v>-207.524</v>
+        <v>133.689</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>3917.006</v>
+        <v>725</v>
       </c>
       <c r="C43">
-        <v>3917.006</v>
+        <v>725</v>
       </c>
       <c r="D43">
-        <v>-205.845</v>
+        <v>177.595</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>2999.41</v>
+        <v>301.174</v>
       </c>
       <c r="C44">
-        <v>2999.41</v>
+        <v>301.174</v>
       </c>
       <c r="D44">
-        <v>-257.164</v>
+        <v>208.053</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>2291.648</v>
+        <v>309.756</v>
       </c>
       <c r="C45">
-        <v>2291.648</v>
+        <v>309.756</v>
       </c>
       <c r="D45">
-        <v>-241.353</v>
+        <v>246.8</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>1457.539</v>
+        <v>1.173</v>
       </c>
       <c r="C46">
-        <v>1457.539</v>
+        <v>1.173</v>
       </c>
       <c r="D46">
-        <v>-143.092</v>
+        <v>234.143</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>1457.466</v>
+        <v>12.16</v>
       </c>
       <c r="C47">
-        <v>1457.466</v>
+        <v>12.16</v>
       </c>
       <c r="D47">
-        <v>-38.133</v>
+        <v>182.441</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>681</v>
+        <v>725.014</v>
       </c>
       <c r="C48">
-        <v>681</v>
+        <v>725.014</v>
       </c>
       <c r="D48">
-        <v>14.998</v>
+        <v>241.868</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>647.204</v>
+        <v>445.996</v>
       </c>
       <c r="C49">
-        <v>647.204</v>
+        <v>445.996</v>
       </c>
       <c r="D49">
-        <v>87.605</v>
+        <v>226.008</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>698.0410000000001</v>
+        <v>39.242</v>
       </c>
       <c r="C50">
-        <v>698.0410000000001</v>
+        <v>39.242</v>
       </c>
       <c r="D50">
-        <v>128.793</v>
+        <v>167.389</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>739.958</v>
+        <v>3.315</v>
       </c>
       <c r="C51">
-        <v>739.958</v>
+        <v>3.315</v>
       </c>
       <c r="D51">
-        <v>143.858</v>
+        <v>85.53700000000001</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>750.136</v>
+        <v>8.773</v>
       </c>
       <c r="C52">
-        <v>750.136</v>
+        <v>8.773</v>
       </c>
       <c r="D52">
-        <v>162.29</v>
+        <v>79.482</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>-100</v>
+        <v>10.425</v>
       </c>
       <c r="C53">
-        <v>-100</v>
+        <v>10.425</v>
       </c>
       <c r="D53">
-        <v>47.69</v>
+        <v>109.487</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>751</v>
+        <v>260.853</v>
       </c>
       <c r="C54">
-        <v>751</v>
+        <v>260.853</v>
       </c>
       <c r="D54">
-        <v>82.773</v>
+        <v>138.882</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>257.461</v>
+        <v>258.071</v>
       </c>
       <c r="C55">
-        <v>257.461</v>
+        <v>258.071</v>
       </c>
       <c r="D55">
-        <v>64.628</v>
+        <v>117.53</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>257.628</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>257.628</v>
       </c>
       <c r="D56">
-        <v>26.518</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>257.743</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>257.743</v>
       </c>
       <c r="D57">
-        <v>29.739</v>
+        <v>75.274</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>257.114</v>
+        <v>266.647</v>
       </c>
       <c r="C58">
-        <v>257.114</v>
+        <v>266.647</v>
       </c>
       <c r="D58">
-        <v>53.728</v>
+        <v>133.395</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>256.647</v>
+        <v>257.649</v>
       </c>
       <c r="C59">
-        <v>256.647</v>
+        <v>257.649</v>
       </c>
       <c r="D59">
-        <v>18.447</v>
+        <v>82.77200000000001</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>1516.643</v>
+        <v>264.969</v>
       </c>
       <c r="C60">
-        <v>1516.643</v>
+        <v>264.969</v>
       </c>
       <c r="D60">
-        <v>10.753</v>
+        <v>46.106</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>720</v>
+        <v>252.656</v>
       </c>
       <c r="C61">
-        <v>720</v>
+        <v>252.656</v>
       </c>
       <c r="D61">
-        <v>9.699</v>
+        <v>40.102</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>334.674</v>
+        <v>298.241</v>
       </c>
       <c r="C62">
-        <v>334.674</v>
+        <v>298.241</v>
       </c>
       <c r="D62">
-        <v>218.528</v>
+        <v>55.47</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>751</v>
+        <v>297.885</v>
       </c>
       <c r="C63">
-        <v>751</v>
+        <v>297.885</v>
       </c>
       <c r="D63">
-        <v>149.778</v>
+        <v>32.468</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>2.741</v>
+        <v>301</v>
       </c>
       <c r="C64">
-        <v>2.741</v>
+        <v>301</v>
       </c>
       <c r="D64">
-        <v>59.025</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>256</v>
+        <v>3980.197</v>
       </c>
       <c r="C65">
-        <v>256</v>
+        <v>3980.197</v>
       </c>
       <c r="D65">
-        <v>17.769</v>
+        <v>-11.541</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>292.145</v>
+        <v>301</v>
       </c>
       <c r="C66">
-        <v>292.145</v>
+        <v>301</v>
       </c>
       <c r="D66">
-        <v>165.225</v>
+        <v>29.865</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>292.321</v>
+        <v>2524.367</v>
       </c>
       <c r="C67">
-        <v>292.321</v>
+        <v>2524.367</v>
       </c>
       <c r="D67">
-        <v>95.008</v>
+        <v>-15.939</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>293</v>
+        <v>3180.593</v>
       </c>
       <c r="C68">
-        <v>293</v>
+        <v>3180.593</v>
       </c>
       <c r="D68">
-        <v>17.421</v>
+        <v>-31.252</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>2618.012</v>
+        <v>3585.764</v>
       </c>
       <c r="C69">
-        <v>2618.012</v>
+        <v>3585.764</v>
       </c>
       <c r="D69">
-        <v>-1.335</v>
+        <v>-42.432</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>293</v>
+        <v>810</v>
       </c>
       <c r="C70">
-        <v>293</v>
+        <v>810</v>
       </c>
       <c r="D70">
-        <v>19.291</v>
+        <v>13.752</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>3012.845</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>3012.845</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>-29.537</v>
+        <v>6.265</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>3282.319</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>3282.319</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>-45.381</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>686.167</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>686.167</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>3.349</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>2128.022</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>2128.022</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>-23.9</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>2131.755</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>2131.755</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>-1.914</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>1852.929</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>1852.929</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>-15.788</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>1388.008</v>
+        <v>2779.087</v>
       </c>
       <c r="C79">
-        <v>1388.008</v>
+        <v>2779.087</v>
       </c>
       <c r="D79">
-        <v>-15.837</v>
+        <v>-35.941</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>1895.056</v>
+        <v>2672.219</v>
       </c>
       <c r="C80">
-        <v>1895.056</v>
+        <v>2672.219</v>
       </c>
       <c r="D80">
-        <v>-7.662</v>
+        <v>-44.005</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>750.627</v>
+        <v>6903.772</v>
       </c>
       <c r="C81">
-        <v>750.627</v>
+        <v>6903.772</v>
       </c>
       <c r="D81">
-        <v>11.646</v>
+        <v>-58.856</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>697.298</v>
+        <v>5662.555</v>
       </c>
       <c r="C82">
-        <v>697.298</v>
+        <v>5662.555</v>
       </c>
       <c r="D82">
-        <v>18.364</v>
+        <v>-96.58499999999999</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>732.313</v>
+        <v>3405.511</v>
       </c>
       <c r="C83">
-        <v>732.313</v>
+        <v>3405.511</v>
       </c>
       <c r="D83">
-        <v>28.197</v>
+        <v>-68.96899999999999</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>687.361</v>
+        <v>2205.347</v>
       </c>
       <c r="C84">
-        <v>687.361</v>
+        <v>2205.347</v>
       </c>
       <c r="D84">
-        <v>30.934</v>
+        <v>-20.744</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>709.575</v>
+        <v>2204.127</v>
       </c>
       <c r="C85">
-        <v>709.575</v>
+        <v>2204.127</v>
       </c>
       <c r="D85">
-        <v>26.937</v>
+        <v>-60.61</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>1198.01</v>
+        <v>2569.648</v>
       </c>
       <c r="C86">
-        <v>1198.01</v>
+        <v>2569.648</v>
       </c>
       <c r="D86">
-        <v>-1.234</v>
+        <v>-79.83799999999999</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>755</v>
+        <v>2531.79</v>
       </c>
       <c r="C87">
-        <v>755</v>
+        <v>2531.79</v>
       </c>
       <c r="D87">
-        <v>16.726</v>
+        <v>-75.52500000000001</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>6730.249</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>6730.249</v>
       </c>
       <c r="D88">
-        <v>9.919</v>
+        <v>-72.72199999999999</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>6311.919</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>6311.919</v>
       </c>
       <c r="D89">
-        <v>7.43</v>
+        <v>-70.001</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>2020.085</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>2020.085</v>
       </c>
       <c r="D90">
-        <v>3.139</v>
+        <v>-44.332</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>2022.01</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>2022.01</v>
       </c>
       <c r="D91">
-        <v>19.404</v>
+        <v>-16.822</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>20.664</v>
+        <v>-12.494</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>699.61</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>699.61</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>28.012</v>
+        <v>-19.991</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>602.854</v>
+        <v>535.044</v>
       </c>
       <c r="C94">
-        <v>602.854</v>
+        <v>535.044</v>
       </c>
       <c r="D94">
-        <v>63.291</v>
+        <v>48.896</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>551.5700000000001</v>
+        <v>702.872</v>
       </c>
       <c r="C95">
-        <v>551.5700000000001</v>
+        <v>702.872</v>
       </c>
       <c r="D95">
-        <v>100.939</v>
+        <v>32.576</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>683.468</v>
+        <v>671.446</v>
       </c>
       <c r="C96">
-        <v>683.468</v>
+        <v>671.446</v>
       </c>
       <c r="D96">
-        <v>137.034</v>
+        <v>34.718</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>728.5309999999999</v>
+        <v>476.07</v>
       </c>
       <c r="C97">
-        <v>728.5309999999999</v>
+        <v>476.07</v>
       </c>
       <c r="D97">
-        <v>140.108</v>
+        <v>39.67</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>1413.497</v>
+        <v>151.877</v>
       </c>
       <c r="C98">
-        <v>1413.497</v>
+        <v>151.877</v>
       </c>
       <c r="D98">
-        <v>38.501</v>
+        <v>5.674</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>1470.799</v>
+        <v>708.293</v>
       </c>
       <c r="C99">
-        <v>1470.799</v>
+        <v>708.293</v>
       </c>
       <c r="D99">
-        <v>-9.423</v>
+        <v>14.481</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>1871.377</v>
+        <v>1165.682</v>
       </c>
       <c r="C100">
-        <v>1871.377</v>
+        <v>1165.682</v>
       </c>
       <c r="D100">
-        <v>-36.413</v>
+        <v>-9.412000000000001</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>732.8440000000001</v>
+        <v>1552.629</v>
       </c>
       <c r="C101">
-        <v>732.8440000000001</v>
+        <v>1552.629</v>
       </c>
       <c r="D101">
-        <v>11.558</v>
+        <v>-23.359</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>727.593</v>
+        <v>765.367</v>
       </c>
       <c r="C102">
-        <v>727.593</v>
+        <v>765.367</v>
       </c>
       <c r="D102">
-        <v>3.576</v>
+        <v>11.99</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>621.8440000000001</v>
+        <v>1021.169</v>
       </c>
       <c r="C103">
-        <v>621.8440000000001</v>
+        <v>1021.169</v>
       </c>
       <c r="D103">
-        <v>37.923</v>
+        <v>-29.407</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>700.133</v>
+        <v>1342.946</v>
       </c>
       <c r="C104">
-        <v>700.133</v>
+        <v>1342.946</v>
       </c>
       <c r="D104">
-        <v>105.934</v>
+        <v>1.069</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>579.841</v>
+        <v>1406.331</v>
       </c>
       <c r="C105">
-        <v>579.841</v>
+        <v>1406.331</v>
       </c>
       <c r="D105">
-        <v>130.306</v>
+        <v>-25.037</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>707.009</v>
+        <v>1441.311</v>
       </c>
       <c r="C106">
-        <v>707.009</v>
+        <v>1441.311</v>
       </c>
       <c r="D106">
-        <v>127.951</v>
+        <v>-12.678</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>605.271</v>
+        <v>1746.323</v>
       </c>
       <c r="C107">
-        <v>605.271</v>
+        <v>1746.323</v>
       </c>
       <c r="D107">
-        <v>77.80500000000001</v>
+        <v>-5.62</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>520.721</v>
+        <v>1740.024</v>
       </c>
       <c r="C108">
-        <v>520.721</v>
+        <v>1740.024</v>
       </c>
       <c r="D108">
-        <v>57.986</v>
+        <v>-38.572</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>649.4059999999999</v>
+        <v>1746.95</v>
       </c>
       <c r="C109">
-        <v>649.4059999999999</v>
+        <v>1746.95</v>
       </c>
       <c r="D109">
-        <v>38.66</v>
+        <v>-14.006</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>755</v>
+        <v>1742.993</v>
       </c>
       <c r="C110">
-        <v>755</v>
+        <v>1742.993</v>
       </c>
       <c r="D110">
-        <v>4.823</v>
+        <v>-24.721</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>1453.497</v>
+        <v>1851.308</v>
       </c>
       <c r="C111">
-        <v>1453.497</v>
+        <v>1851.308</v>
       </c>
       <c r="D111">
-        <v>-11.402</v>
+        <v>-61.832</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>755</v>
+        <v>1743.012</v>
       </c>
       <c r="C112">
-        <v>755</v>
+        <v>1743.012</v>
       </c>
       <c r="D112">
-        <v>7.944</v>
+        <v>-39.584</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>1380.014</v>
+        <v>1749.059</v>
       </c>
       <c r="C113">
-        <v>1380.014</v>
+        <v>1749.059</v>
       </c>
       <c r="D113">
-        <v>-1.175</v>
+        <v>-13.102</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>728.415</v>
+        <v>1671.785</v>
       </c>
       <c r="C114">
-        <v>728.415</v>
+        <v>1671.785</v>
       </c>
       <c r="D114">
-        <v>44.057</v>
+        <v>-33.943</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>755</v>
+        <v>733.439</v>
       </c>
       <c r="C115">
-        <v>755</v>
+        <v>733.439</v>
       </c>
       <c r="D115">
-        <v>30.026</v>
+        <v>16.329</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>717.5839999999999</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>717.5839999999999</v>
       </c>
       <c r="D116">
-        <v>36.025</v>
+        <v>5.465</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>680.731</v>
+        <v>750</v>
       </c>
       <c r="C117">
-        <v>680.731</v>
+        <v>750</v>
       </c>
       <c r="D117">
-        <v>47.585</v>
+        <v>54.179</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>546.0359999999999</v>
+        <v>678.687</v>
       </c>
       <c r="C118">
-        <v>546.0359999999999</v>
+        <v>678.687</v>
       </c>
       <c r="D118">
-        <v>35.304</v>
+        <v>34.318</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>755</v>
+        <v>707.001</v>
       </c>
       <c r="C119">
-        <v>755</v>
+        <v>707.001</v>
       </c>
       <c r="D119">
-        <v>34.921</v>
+        <v>15.737</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>3968.356</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>3968.356</v>
       </c>
       <c r="D120">
-        <v>58.753</v>
+        <v>-38.169</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>3105.456</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>3105.456</v>
       </c>
       <c r="D121">
-        <v>53.52</v>
+        <v>-40.283</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>460.893</v>
+        <v>1895.225</v>
       </c>
       <c r="C122">
-        <v>460.893</v>
+        <v>1895.225</v>
       </c>
       <c r="D122">
-        <v>103.845</v>
+        <v>-2.024</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>755</v>
+        <v>1925.946</v>
       </c>
       <c r="C123">
-        <v>755</v>
+        <v>1925.946</v>
       </c>
       <c r="D123">
-        <v>91.52800000000001</v>
+        <v>-29.692</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>667.5069999999999</v>
+        <v>1800.298</v>
       </c>
       <c r="C124">
-        <v>667.5069999999999</v>
+        <v>1800.298</v>
       </c>
       <c r="D124">
-        <v>97.982</v>
+        <v>-22.651</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>626.794</v>
+        <v>1935.157</v>
       </c>
       <c r="C125">
-        <v>626.794</v>
+        <v>1935.157</v>
       </c>
       <c r="D125">
-        <v>78.624</v>
+        <v>-32.993</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>693.614</v>
+        <v>724.943</v>
       </c>
       <c r="C126">
-        <v>693.614</v>
+        <v>724.943</v>
       </c>
       <c r="D126">
-        <v>38.314</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>693.707</v>
+        <v>750</v>
       </c>
       <c r="C127">
-        <v>693.707</v>
+        <v>750</v>
       </c>
       <c r="D127">
-        <v>20.851</v>
+        <v>0.228</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>685.544</v>
+        <v>722.246</v>
       </c>
       <c r="C128">
-        <v>685.544</v>
+        <v>722.246</v>
       </c>
       <c r="D128">
-        <v>27.466</v>
+        <v>17.062</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>695.389</v>
+        <v>1334.425</v>
       </c>
       <c r="C129">
-        <v>695.389</v>
+        <v>1334.425</v>
       </c>
       <c r="D129">
-        <v>22.088</v>
+        <v>-15.289</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>1820.191</v>
+        <v>1803.248</v>
       </c>
       <c r="C130">
-        <v>1820.191</v>
+        <v>1803.248</v>
       </c>
       <c r="D130">
-        <v>-25.847</v>
+        <v>-51.391</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>1286.23</v>
+        <v>2575.863</v>
       </c>
       <c r="C131">
-        <v>1286.23</v>
+        <v>2575.863</v>
       </c>
       <c r="D131">
-        <v>-1.396</v>
+        <v>-61.905</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>479.746</v>
+        <v>1964.383</v>
       </c>
       <c r="C132">
-        <v>479.746</v>
+        <v>1964.383</v>
       </c>
       <c r="D132">
-        <v>1.246</v>
+        <v>-79.06399999999999</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B133">
-        <v>394.245</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>394.245</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>82.592</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B134">
-        <v>494.289</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>494.289</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>45.106</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B135">
-        <v>530.7910000000001</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>530.7910000000001</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>91.851</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B136">
-        <v>241.963</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>241.963</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>124.709</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B137">
-        <v>-567.073</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>-567.073</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>76.426</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B138">
-        <v>1172.087</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>1172.087</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>-23.81</v>
+        <v>0</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B139">
-        <v>993.284</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>993.284</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>-0.8149999999999999</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B140">
-        <v>348.908</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>348.908</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>11.512</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B141">
-        <v>1388.091</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>1388.091</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>-44.41</v>
+        <v>0</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B142">
-        <v>963.978</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>963.978</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>-32.559</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B143">
-        <v>817.164</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>817.164</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>-5.048</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B144">
-        <v>1162.67</v>
+        <v>0</v>
       </c>
       <c r="C144">
-        <v>1162.67</v>
+        <v>0</v>
       </c>
       <c r="D144">
-        <v>-13.683</v>
+        <v>0</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B145">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>56.245</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B146">
-        <v>61.765</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>61.765</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>112.244</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B147">
-        <v>151.024</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>151.024</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>56.615</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B148">
-        <v>260.609</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>260.609</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>10.48</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46311.95833333334</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46311.96875</v>
+        <v>46316.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46311.97916666666</v>
+        <v>46316.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46311.98958333334</v>
+        <v>46316.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="198">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
-  </si>
-  <si>
-    <t>21.10.202636</t>
-  </si>
-  <si>
-    <t>21.10.202637</t>
-  </si>
-  <si>
-    <t>21.10.202638</t>
-  </si>
-  <si>
-    <t>21.10.202639</t>
-  </si>
-  <si>
-    <t>21.10.202640</t>
-  </si>
-  <si>
-    <t>21.10.202641</t>
-  </si>
-  <si>
-    <t>21.10.202642</t>
-  </si>
-  <si>
-    <t>21.10.202643</t>
-  </si>
-  <si>
-    <t>21.10.202644</t>
-  </si>
-  <si>
-    <t>21.10.202645</t>
-  </si>
-  <si>
-    <t>21.10.202646</t>
-  </si>
-  <si>
-    <t>21.10.202647</t>
-  </si>
-  <si>
-    <t>21.10.202648</t>
-  </si>
-  <si>
-    <t>21.10.202649</t>
-  </si>
-  <si>
-    <t>21.10.202650</t>
-  </si>
-  <si>
-    <t>21.10.202651</t>
-  </si>
-  <si>
-    <t>21.10.202652</t>
-  </si>
-  <si>
-    <t>21.10.202653</t>
-  </si>
-  <si>
-    <t>21.10.202654</t>
-  </si>
-  <si>
-    <t>21.10.202655</t>
-  </si>
-  <si>
-    <t>21.10.202656</t>
-  </si>
-  <si>
-    <t>21.10.202657</t>
-  </si>
-  <si>
-    <t>21.10.202658</t>
-  </si>
-  <si>
-    <t>21.10.202659</t>
-  </si>
-  <si>
-    <t>21.10.202660</t>
-  </si>
-  <si>
-    <t>21.10.202661</t>
-  </si>
-  <si>
-    <t>21.10.202662</t>
-  </si>
-  <si>
-    <t>21.10.202663</t>
-  </si>
-  <si>
-    <t>21.10.202664</t>
-  </si>
-  <si>
-    <t>21.10.202665</t>
-  </si>
-  <si>
-    <t>21.10.202666</t>
-  </si>
-  <si>
-    <t>21.10.202667</t>
-  </si>
-  <si>
-    <t>21.10.202668</t>
-  </si>
-  <si>
-    <t>21.10.202669</t>
-  </si>
-  <si>
-    <t>21.10.202670</t>
-  </si>
-  <si>
-    <t>21.10.202671</t>
-  </si>
-  <si>
-    <t>21.10.202672</t>
-  </si>
-  <si>
-    <t>21.10.202673</t>
-  </si>
-  <si>
-    <t>21.10.202674</t>
-  </si>
-  <si>
-    <t>21.10.202675</t>
-  </si>
-  <si>
-    <t>21.10.202676</t>
-  </si>
-  <si>
-    <t>21.10.202677</t>
-  </si>
-  <si>
-    <t>21.10.202678</t>
-  </si>
-  <si>
-    <t>21.10.202679</t>
-  </si>
-  <si>
-    <t>21.10.202680</t>
-  </si>
-  <si>
-    <t>21.10.202681</t>
-  </si>
-  <si>
-    <t>21.10.202682</t>
-  </si>
-  <si>
-    <t>21.10.202683</t>
-  </si>
-  <si>
-    <t>21.10.202684</t>
-  </si>
-  <si>
-    <t>21.10.202685</t>
-  </si>
-  <si>
-    <t>21.10.202686</t>
-  </si>
-  <si>
-    <t>21.10.202687</t>
-  </si>
-  <si>
-    <t>21.10.202688</t>
-  </si>
-  <si>
-    <t>21.10.202689</t>
-  </si>
-  <si>
-    <t>21.10.202690</t>
-  </si>
-  <si>
-    <t>21.10.202691</t>
-  </si>
-  <si>
-    <t>21.10.202692</t>
-  </si>
-  <si>
-    <t>21.10.202693</t>
-  </si>
-  <si>
-    <t>21.10.202694</t>
-  </si>
-  <si>
-    <t>21.10.202695</t>
-  </si>
-  <si>
-    <t>21.10.202696</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
+  </si>
+  <si>
+    <t>25.10.202638</t>
+  </si>
+  <si>
+    <t>25.10.202639</t>
+  </si>
+  <si>
+    <t>25.10.202640</t>
+  </si>
+  <si>
+    <t>25.10.202641</t>
+  </si>
+  <si>
+    <t>25.10.202642</t>
+  </si>
+  <si>
+    <t>25.10.202643</t>
+  </si>
+  <si>
+    <t>25.10.202644</t>
+  </si>
+  <si>
+    <t>25.10.202645</t>
+  </si>
+  <si>
+    <t>25.10.202646</t>
+  </si>
+  <si>
+    <t>25.10.202647</t>
+  </si>
+  <si>
+    <t>25.10.202648</t>
+  </si>
+  <si>
+    <t>25.10.202649</t>
+  </si>
+  <si>
+    <t>25.10.202650</t>
+  </si>
+  <si>
+    <t>25.10.202651</t>
+  </si>
+  <si>
+    <t>25.10.202652</t>
+  </si>
+  <si>
+    <t>25.10.202653</t>
+  </si>
+  <si>
+    <t>25.10.202654</t>
+  </si>
+  <si>
+    <t>25.10.202655</t>
+  </si>
+  <si>
+    <t>25.10.202656</t>
+  </si>
+  <si>
+    <t>25.10.202657</t>
+  </si>
+  <si>
+    <t>25.10.202658</t>
+  </si>
+  <si>
+    <t>25.10.202659</t>
+  </si>
+  <si>
+    <t>25.10.202660</t>
+  </si>
+  <si>
+    <t>25.10.202661</t>
+  </si>
+  <si>
+    <t>25.10.202662</t>
+  </si>
+  <si>
+    <t>25.10.202663</t>
+  </si>
+  <si>
+    <t>25.10.202664</t>
+  </si>
+  <si>
+    <t>25.10.202665</t>
+  </si>
+  <si>
+    <t>25.10.202666</t>
+  </si>
+  <si>
+    <t>25.10.202667</t>
+  </si>
+  <si>
+    <t>25.10.202668</t>
+  </si>
+  <si>
+    <t>25.10.202669</t>
+  </si>
+  <si>
+    <t>25.10.202670</t>
+  </si>
+  <si>
+    <t>25.10.202671</t>
+  </si>
+  <si>
+    <t>25.10.202672</t>
+  </si>
+  <si>
+    <t>25.10.202673</t>
+  </si>
+  <si>
+    <t>25.10.202674</t>
+  </si>
+  <si>
+    <t>25.10.202675</t>
+  </si>
+  <si>
+    <t>25.10.202676</t>
+  </si>
+  <si>
+    <t>25.10.202677</t>
+  </si>
+  <si>
+    <t>25.10.202678</t>
+  </si>
+  <si>
+    <t>25.10.202679</t>
+  </si>
+  <si>
+    <t>25.10.202680</t>
+  </si>
+  <si>
+    <t>25.10.202681</t>
+  </si>
+  <si>
+    <t>25.10.202682</t>
+  </si>
+  <si>
+    <t>25.10.202683</t>
+  </si>
+  <si>
+    <t>25.10.202684</t>
+  </si>
+  <si>
+    <t>25.10.202685</t>
+  </si>
+  <si>
+    <t>25.10.202686</t>
+  </si>
+  <si>
+    <t>25.10.202687</t>
+  </si>
+  <si>
+    <t>25.10.202688</t>
+  </si>
+  <si>
+    <t>25.10.202689</t>
+  </si>
+  <si>
+    <t>25.10.202690</t>
+  </si>
+  <si>
+    <t>25.10.202691</t>
+  </si>
+  <si>
+    <t>25.10.202692</t>
+  </si>
+  <si>
+    <t>25.10.202693</t>
+  </si>
+  <si>
+    <t>25.10.202694</t>
+  </si>
+  <si>
+    <t>25.10.202695</t>
+  </si>
+  <si>
+    <t>25.10.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>616.747</v>
+        <v>692.335</v>
       </c>
       <c r="C2">
-        <v>616.747</v>
+        <v>692.335</v>
       </c>
       <c r="D2">
-        <v>63.333</v>
+        <v>59.021</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>174.35</v>
+        <v>701</v>
       </c>
       <c r="C3">
-        <v>174.35</v>
+        <v>701</v>
       </c>
       <c r="D3">
-        <v>50.831</v>
+        <v>104.986</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>486.587</v>
+        <v>320.553</v>
       </c>
       <c r="C4">
-        <v>486.587</v>
+        <v>320.553</v>
       </c>
       <c r="D4">
-        <v>79.85899999999999</v>
+        <v>121.109</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>704.181</v>
+        <v>311.093</v>
       </c>
       <c r="C5">
-        <v>704.181</v>
+        <v>311.093</v>
       </c>
       <c r="D5">
-        <v>20.851</v>
+        <v>110.371</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>2080.88</v>
+        <v>18.363</v>
       </c>
       <c r="C6">
-        <v>2080.88</v>
+        <v>18.363</v>
       </c>
       <c r="D6">
-        <v>-45.759</v>
+        <v>119.143</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>2005.247</v>
+        <v>35.43</v>
       </c>
       <c r="C7">
-        <v>2005.247</v>
+        <v>35.43</v>
       </c>
       <c r="D7">
-        <v>-85.96299999999999</v>
+        <v>89.279</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>1967.617</v>
+        <v>29.98</v>
       </c>
       <c r="C8">
-        <v>1967.617</v>
+        <v>29.98</v>
       </c>
       <c r="D8">
-        <v>-69.70999999999999</v>
+        <v>83.318</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>1983.258</v>
+        <v>1.982</v>
       </c>
       <c r="C9">
-        <v>1983.258</v>
+        <v>1.982</v>
       </c>
       <c r="D9">
-        <v>-60.088</v>
+        <v>54.202</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>720</v>
+        <v>17.721</v>
       </c>
       <c r="C10">
-        <v>720</v>
+        <v>17.721</v>
       </c>
       <c r="D10">
-        <v>32.834</v>
+        <v>63.595</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>712.924</v>
+        <v>12.77</v>
       </c>
       <c r="C11">
-        <v>712.924</v>
+        <v>12.77</v>
       </c>
       <c r="D11">
-        <v>53.182</v>
+        <v>41.984</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>715.901</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>715.901</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>70.956</v>
+        <v>41.833</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>710.482</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>710.482</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>36.992</v>
+        <v>37.067</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>706.913</v>
+        <v>302</v>
       </c>
       <c r="C14">
-        <v>706.913</v>
+        <v>302</v>
       </c>
       <c r="D14">
-        <v>59.679</v>
+        <v>53.753</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>707.266</v>
+        <v>1622.672</v>
       </c>
       <c r="C15">
-        <v>707.266</v>
+        <v>1622.672</v>
       </c>
       <c r="D15">
-        <v>63.197</v>
+        <v>-3.669</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>702.109</v>
+        <v>693.335</v>
       </c>
       <c r="C16">
-        <v>702.109</v>
+        <v>693.335</v>
       </c>
       <c r="D16">
-        <v>18.141</v>
+        <v>12.913</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>1912.835</v>
+        <v>623.8200000000001</v>
       </c>
       <c r="C17">
-        <v>1912.835</v>
+        <v>623.8200000000001</v>
       </c>
       <c r="D17">
-        <v>-11.281</v>
+        <v>45.012</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>705.45</v>
+        <v>561.864</v>
       </c>
       <c r="C18">
-        <v>705.45</v>
+        <v>561.864</v>
       </c>
       <c r="D18">
-        <v>6.627</v>
+        <v>110.064</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>1804.727</v>
+        <v>336.126</v>
       </c>
       <c r="C19">
-        <v>1804.727</v>
+        <v>336.126</v>
       </c>
       <c r="D19">
-        <v>-14.216</v>
+        <v>50.535</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>705.1849999999999</v>
+        <v>336.513</v>
       </c>
       <c r="C20">
-        <v>705.1849999999999</v>
+        <v>336.513</v>
       </c>
       <c r="D20">
-        <v>7.753</v>
+        <v>56.653</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>704.276</v>
+        <v>336.396</v>
       </c>
       <c r="C21">
-        <v>704.276</v>
+        <v>336.396</v>
       </c>
       <c r="D21">
-        <v>0.456</v>
+        <v>50.805</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>672.665</v>
+        <v>306.014</v>
       </c>
       <c r="C22">
-        <v>672.665</v>
+        <v>306.014</v>
       </c>
       <c r="D22">
-        <v>48.492</v>
+        <v>55.278</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>705.155</v>
+        <v>704.55</v>
       </c>
       <c r="C23">
-        <v>705.155</v>
+        <v>704.55</v>
       </c>
       <c r="D23">
-        <v>31.426</v>
+        <v>57.658</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>720</v>
+        <v>703.4109999999999</v>
       </c>
       <c r="C24">
-        <v>720</v>
+        <v>703.4109999999999</v>
       </c>
       <c r="D24">
-        <v>39.567</v>
+        <v>42.804</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>718.754</v>
+        <v>701.768</v>
       </c>
       <c r="C25">
-        <v>718.754</v>
+        <v>701.768</v>
       </c>
       <c r="D25">
-        <v>28.314</v>
+        <v>8.698</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>686.3390000000001</v>
+        <v>621.2670000000001</v>
       </c>
       <c r="C26">
-        <v>686.3390000000001</v>
+        <v>621.2670000000001</v>
       </c>
       <c r="D26">
-        <v>24.069</v>
+        <v>45.942</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>720</v>
+        <v>701.021</v>
       </c>
       <c r="C27">
-        <v>720</v>
+        <v>701.021</v>
       </c>
       <c r="D27">
-        <v>47.052</v>
+        <v>20.155</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>709.444</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>709.444</v>
       </c>
       <c r="D28">
-        <v>1.777</v>
+        <v>12.469</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1259.513</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1259.513</v>
       </c>
       <c r="D29">
-        <v>11.105</v>
+        <v>4.912</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>686.691</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>686.691</v>
       </c>
       <c r="D30">
-        <v>86.15000000000001</v>
+        <v>27.416</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>706.66</v>
+        <v>708.788</v>
       </c>
       <c r="C31">
-        <v>706.66</v>
+        <v>708.788</v>
       </c>
       <c r="D31">
-        <v>48.701</v>
+        <v>13.086</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>721.2859999999999</v>
+        <v>702.605</v>
       </c>
       <c r="C32">
-        <v>721.2859999999999</v>
+        <v>702.605</v>
       </c>
       <c r="D32">
-        <v>22.569</v>
+        <v>35.851</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>718.705</v>
+        <v>736.716</v>
       </c>
       <c r="C33">
-        <v>718.705</v>
+        <v>736.716</v>
       </c>
       <c r="D33">
-        <v>39.065</v>
+        <v>79.379</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>712.497</v>
+        <v>712.948</v>
       </c>
       <c r="C34">
-        <v>712.497</v>
+        <v>712.948</v>
       </c>
       <c r="D34">
-        <v>26.352</v>
+        <v>40.556</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>729.337</v>
+        <v>755</v>
       </c>
       <c r="C35">
-        <v>729.337</v>
+        <v>755</v>
       </c>
       <c r="D35">
-        <v>18.808</v>
+        <v>75.616</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>3586.837</v>
+        <v>307.969</v>
       </c>
       <c r="C36">
-        <v>3586.837</v>
+        <v>307.969</v>
       </c>
       <c r="D36">
-        <v>-27.512</v>
+        <v>49.186</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>705.283</v>
+        <v>308.972</v>
       </c>
       <c r="C37">
-        <v>705.283</v>
+        <v>308.972</v>
       </c>
       <c r="D37">
-        <v>8.204000000000001</v>
+        <v>29.283</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>1696.691</v>
+        <v>2490.664</v>
       </c>
       <c r="C38">
-        <v>1696.691</v>
+        <v>2490.664</v>
       </c>
       <c r="D38">
-        <v>-7.898</v>
+        <v>-96.325</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>1655.484</v>
+        <v>5160.691</v>
       </c>
       <c r="C39">
-        <v>1655.484</v>
+        <v>5160.691</v>
       </c>
       <c r="D39">
-        <v>10.781</v>
+        <v>-109.138</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>720</v>
+        <v>6789.337</v>
       </c>
       <c r="C40">
-        <v>720</v>
+        <v>6789.337</v>
       </c>
       <c r="D40">
-        <v>39.541</v>
+        <v>-104.165</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>703.881</v>
+        <v>1779.066</v>
       </c>
       <c r="C41">
-        <v>703.881</v>
+        <v>1779.066</v>
       </c>
       <c r="D41">
-        <v>128.981</v>
+        <v>-86.517</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>710.836</v>
+        <v>2704.162</v>
       </c>
       <c r="C42">
-        <v>710.836</v>
+        <v>2704.162</v>
       </c>
       <c r="D42">
-        <v>133.689</v>
+        <v>-113.373</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>725</v>
+        <v>1666.832</v>
       </c>
       <c r="C43">
-        <v>725</v>
+        <v>1666.832</v>
       </c>
       <c r="D43">
-        <v>177.595</v>
+        <v>-97.822</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>301.174</v>
+        <v>1539.79</v>
       </c>
       <c r="C44">
-        <v>301.174</v>
+        <v>1539.79</v>
       </c>
       <c r="D44">
-        <v>208.053</v>
+        <v>-25.927</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>309.756</v>
+        <v>582.542</v>
       </c>
       <c r="C45">
-        <v>309.756</v>
+        <v>582.542</v>
       </c>
       <c r="D45">
-        <v>246.8</v>
+        <v>71.378</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>1.173</v>
+        <v>553.884</v>
       </c>
       <c r="C46">
-        <v>1.173</v>
+        <v>553.884</v>
       </c>
       <c r="D46">
-        <v>234.143</v>
+        <v>57.655</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>12.16</v>
+        <v>545.523</v>
       </c>
       <c r="C47">
-        <v>12.16</v>
+        <v>545.523</v>
       </c>
       <c r="D47">
-        <v>182.441</v>
+        <v>46.66</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>725.014</v>
+        <v>639.395</v>
       </c>
       <c r="C48">
-        <v>725.014</v>
+        <v>639.395</v>
       </c>
       <c r="D48">
-        <v>241.868</v>
+        <v>14.112</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>445.996</v>
+        <v>755</v>
       </c>
       <c r="C49">
-        <v>445.996</v>
+        <v>755</v>
       </c>
       <c r="D49">
-        <v>226.008</v>
+        <v>3.78</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>39.242</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>39.242</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>167.389</v>
+        <v>9.246</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>3.315</v>
+        <v>712.987</v>
       </c>
       <c r="C51">
-        <v>3.315</v>
+        <v>712.987</v>
       </c>
       <c r="D51">
-        <v>85.53700000000001</v>
+        <v>8.558</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>8.773</v>
+        <v>734.4880000000001</v>
       </c>
       <c r="C52">
-        <v>8.773</v>
+        <v>734.4880000000001</v>
       </c>
       <c r="D52">
-        <v>79.482</v>
+        <v>4.337</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>10.425</v>
+        <v>749.306</v>
       </c>
       <c r="C53">
-        <v>10.425</v>
+        <v>749.306</v>
       </c>
       <c r="D53">
-        <v>109.487</v>
+        <v>-5.795</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>260.853</v>
+        <v>1000</v>
       </c>
       <c r="C54">
-        <v>260.853</v>
+        <v>1000</v>
       </c>
       <c r="D54">
-        <v>138.882</v>
+        <v>-44.777</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>258.071</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>258.071</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>117.53</v>
+        <v>-17.127</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>257.628</v>
+        <v>900</v>
       </c>
       <c r="C56">
-        <v>257.628</v>
+        <v>900</v>
       </c>
       <c r="D56">
-        <v>86.23999999999999</v>
+        <v>-17.326</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>257.743</v>
+        <v>459.104</v>
       </c>
       <c r="C57">
-        <v>257.743</v>
+        <v>459.104</v>
       </c>
       <c r="D57">
-        <v>75.274</v>
+        <v>10.815</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>266.647</v>
+        <v>195.638</v>
       </c>
       <c r="C58">
-        <v>266.647</v>
+        <v>195.638</v>
       </c>
       <c r="D58">
-        <v>133.395</v>
+        <v>30.482</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>257.649</v>
+        <v>161.395</v>
       </c>
       <c r="C59">
-        <v>257.649</v>
+        <v>161.395</v>
       </c>
       <c r="D59">
-        <v>82.77200000000001</v>
+        <v>25.47</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>264.969</v>
+        <v>62.305</v>
       </c>
       <c r="C60">
-        <v>264.969</v>
+        <v>62.305</v>
       </c>
       <c r="D60">
-        <v>46.106</v>
+        <v>48.609</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>252.656</v>
+        <v>-234.327</v>
       </c>
       <c r="C61">
-        <v>252.656</v>
+        <v>-234.327</v>
       </c>
       <c r="D61">
-        <v>40.102</v>
+        <v>80.54300000000001</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>298.241</v>
+        <v>148.342</v>
       </c>
       <c r="C62">
-        <v>298.241</v>
+        <v>148.342</v>
       </c>
       <c r="D62">
-        <v>55.47</v>
+        <v>89.033</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>297.885</v>
+        <v>117.684</v>
       </c>
       <c r="C63">
-        <v>297.885</v>
+        <v>117.684</v>
       </c>
       <c r="D63">
-        <v>32.468</v>
+        <v>48.331</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>301</v>
+        <v>302.426</v>
       </c>
       <c r="C64">
-        <v>301</v>
+        <v>302.426</v>
       </c>
       <c r="D64">
-        <v>9.015000000000001</v>
+        <v>6.319</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>3980.197</v>
+        <v>3043.734</v>
       </c>
       <c r="C65">
-        <v>3980.197</v>
+        <v>3043.734</v>
       </c>
       <c r="D65">
-        <v>-11.541</v>
+        <v>-31.678</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>301</v>
+        <v>1828.002</v>
       </c>
       <c r="C66">
-        <v>301</v>
+        <v>1828.002</v>
       </c>
       <c r="D66">
-        <v>29.865</v>
+        <v>21.224</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>2524.367</v>
+        <v>2525.592</v>
       </c>
       <c r="C67">
-        <v>2524.367</v>
+        <v>2525.592</v>
       </c>
       <c r="D67">
-        <v>-15.939</v>
+        <v>-45.925</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>3180.593</v>
+        <v>1929.278</v>
       </c>
       <c r="C68">
-        <v>3180.593</v>
+        <v>1929.278</v>
       </c>
       <c r="D68">
-        <v>-31.252</v>
+        <v>-53.904</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>3585.764</v>
+        <v>1938.218</v>
       </c>
       <c r="C69">
-        <v>3585.764</v>
+        <v>1938.218</v>
       </c>
       <c r="D69">
-        <v>-42.432</v>
+        <v>-76.28700000000001</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>810</v>
+        <v>2120.086</v>
       </c>
       <c r="C70">
-        <v>810</v>
+        <v>2120.086</v>
       </c>
       <c r="D70">
-        <v>13.752</v>
+        <v>-5.481</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>2037.951</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2037.951</v>
       </c>
       <c r="D71">
-        <v>6.265</v>
+        <v>-36.759</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>2152.407</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>2152.407</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>-43.151</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>2167.816</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2167.816</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>-46.298</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1920.385</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1920.385</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>-60.571</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1912.767</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1912.767</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>-56.955</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1901.242</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1901.242</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>-61.378</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1928.197</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1928.197</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>-71.863</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>2071.379</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2071.379</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>-40.108</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>2779.087</v>
+        <v>1804.783</v>
       </c>
       <c r="C79">
-        <v>2779.087</v>
+        <v>1804.783</v>
       </c>
       <c r="D79">
-        <v>-35.941</v>
+        <v>-47.101</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>2672.219</v>
+        <v>1942.068</v>
       </c>
       <c r="C80">
-        <v>2672.219</v>
+        <v>1942.068</v>
       </c>
       <c r="D80">
-        <v>-44.005</v>
+        <v>-33.379</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>6903.772</v>
+        <v>1577.773</v>
       </c>
       <c r="C81">
-        <v>6903.772</v>
+        <v>1577.773</v>
       </c>
       <c r="D81">
-        <v>-58.856</v>
+        <v>-33.25</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>5662.555</v>
+        <v>2023.783</v>
       </c>
       <c r="C82">
-        <v>5662.555</v>
+        <v>2023.783</v>
       </c>
       <c r="D82">
-        <v>-96.58499999999999</v>
+        <v>-28.813</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>3405.511</v>
+        <v>2723.754</v>
       </c>
       <c r="C83">
-        <v>3405.511</v>
+        <v>2723.754</v>
       </c>
       <c r="D83">
-        <v>-68.96899999999999</v>
+        <v>-36.371</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>2205.347</v>
+        <v>1951.719</v>
       </c>
       <c r="C84">
-        <v>2205.347</v>
+        <v>1951.719</v>
       </c>
       <c r="D84">
-        <v>-20.744</v>
+        <v>-29.429</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>2204.127</v>
+        <v>1782.699</v>
       </c>
       <c r="C85">
-        <v>2204.127</v>
+        <v>1782.699</v>
       </c>
       <c r="D85">
-        <v>-60.61</v>
+        <v>-20.078</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>2569.648</v>
+        <v>1809.514</v>
       </c>
       <c r="C86">
-        <v>2569.648</v>
+        <v>1809.514</v>
       </c>
       <c r="D86">
-        <v>-79.83799999999999</v>
+        <v>-18.71</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>2531.79</v>
+        <v>1886.015</v>
       </c>
       <c r="C87">
-        <v>2531.79</v>
+        <v>1886.015</v>
       </c>
       <c r="D87">
-        <v>-75.52500000000001</v>
+        <v>-24.958</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>6730.249</v>
+        <v>1532.418</v>
       </c>
       <c r="C88">
-        <v>6730.249</v>
+        <v>1532.418</v>
       </c>
       <c r="D88">
-        <v>-72.72199999999999</v>
+        <v>-5.848</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>6311.919</v>
+        <v>1286.87</v>
       </c>
       <c r="C89">
-        <v>6311.919</v>
+        <v>1286.87</v>
       </c>
       <c r="D89">
-        <v>-70.001</v>
+        <v>-12.796</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>2020.085</v>
+        <v>1998.926</v>
       </c>
       <c r="C90">
-        <v>2020.085</v>
+        <v>1998.926</v>
       </c>
       <c r="D90">
-        <v>-44.332</v>
+        <v>-26.154</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>2022.01</v>
+        <v>2195.315</v>
       </c>
       <c r="C91">
-        <v>2022.01</v>
+        <v>2195.315</v>
       </c>
       <c r="D91">
-        <v>-16.822</v>
+        <v>-31.206</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>2020.584</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>2020.584</v>
       </c>
       <c r="D92">
-        <v>-12.494</v>
+        <v>-26.277</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1985.277</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1985.277</v>
       </c>
       <c r="D93">
-        <v>-19.991</v>
+        <v>-43.11</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>535.044</v>
+        <v>3491.779</v>
       </c>
       <c r="C94">
-        <v>535.044</v>
+        <v>3491.779</v>
       </c>
       <c r="D94">
-        <v>48.896</v>
+        <v>-53.844</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>702.872</v>
+        <v>5066.98</v>
       </c>
       <c r="C95">
-        <v>702.872</v>
+        <v>5066.98</v>
       </c>
       <c r="D95">
-        <v>32.576</v>
+        <v>-54.537</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>671.446</v>
+        <v>3095.379</v>
       </c>
       <c r="C96">
-        <v>671.446</v>
+        <v>3095.379</v>
       </c>
       <c r="D96">
-        <v>34.718</v>
+        <v>-70.47199999999999</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>476.07</v>
+        <v>2211.601</v>
       </c>
       <c r="C97">
-        <v>476.07</v>
+        <v>2211.601</v>
       </c>
       <c r="D97">
-        <v>39.67</v>
+        <v>-62.221</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>151.877</v>
+        <v>1968.253</v>
       </c>
       <c r="C98">
-        <v>151.877</v>
+        <v>1968.253</v>
       </c>
       <c r="D98">
-        <v>5.674</v>
+        <v>-36.24</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>708.293</v>
+        <v>2118.096</v>
       </c>
       <c r="C99">
-        <v>708.293</v>
+        <v>2118.096</v>
       </c>
       <c r="D99">
-        <v>14.481</v>
+        <v>-32.533</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>1165.682</v>
+        <v>1594.023</v>
       </c>
       <c r="C100">
-        <v>1165.682</v>
+        <v>1594.023</v>
       </c>
       <c r="D100">
-        <v>-9.412000000000001</v>
+        <v>-55.584</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>1552.629</v>
+        <v>1376.222</v>
       </c>
       <c r="C101">
-        <v>1552.629</v>
+        <v>1376.222</v>
       </c>
       <c r="D101">
-        <v>-23.359</v>
+        <v>-35.666</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>765.367</v>
+        <v>2607.065</v>
       </c>
       <c r="C102">
-        <v>765.367</v>
+        <v>2607.065</v>
       </c>
       <c r="D102">
-        <v>11.99</v>
+        <v>-22.537</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>1021.169</v>
+        <v>1935.471</v>
       </c>
       <c r="C103">
-        <v>1021.169</v>
+        <v>1935.471</v>
       </c>
       <c r="D103">
-        <v>-29.407</v>
+        <v>-45.718</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>1342.946</v>
+        <v>1514.653</v>
       </c>
       <c r="C104">
-        <v>1342.946</v>
+        <v>1514.653</v>
       </c>
       <c r="D104">
-        <v>1.069</v>
+        <v>-64.51600000000001</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>1406.331</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>1406.331</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>-25.037</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>1441.311</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>1441.311</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>-12.678</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
-        <v>1746.323</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>1746.323</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>-5.62</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
-        <v>1740.024</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1740.024</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>-38.572</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
-        <v>1746.95</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>1746.95</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>-14.006</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>1742.993</v>
+        <v>1383.278</v>
       </c>
       <c r="C110">
-        <v>1742.993</v>
+        <v>1383.278</v>
       </c>
       <c r="D110">
-        <v>-24.721</v>
+        <v>-45.736</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>1851.308</v>
+        <v>1602.895</v>
       </c>
       <c r="C111">
-        <v>1851.308</v>
+        <v>1602.895</v>
       </c>
       <c r="D111">
-        <v>-61.832</v>
+        <v>-42.043</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>1743.012</v>
+        <v>1997.328</v>
       </c>
       <c r="C112">
-        <v>1743.012</v>
+        <v>1997.328</v>
       </c>
       <c r="D112">
-        <v>-39.584</v>
+        <v>-34.111</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>1749.059</v>
+        <v>1599.677</v>
       </c>
       <c r="C113">
-        <v>1749.059</v>
+        <v>1599.677</v>
       </c>
       <c r="D113">
-        <v>-13.102</v>
+        <v>-24.672</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>1671.785</v>
+        <v>1852.767</v>
       </c>
       <c r="C114">
-        <v>1671.785</v>
+        <v>1852.767</v>
       </c>
       <c r="D114">
-        <v>-33.943</v>
+        <v>-23.255</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>733.439</v>
+        <v>1930.28</v>
       </c>
       <c r="C115">
-        <v>733.439</v>
+        <v>1930.28</v>
       </c>
       <c r="D115">
-        <v>16.329</v>
+        <v>-24.342</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>717.5839999999999</v>
+        <v>2001.287</v>
       </c>
       <c r="C116">
-        <v>717.5839999999999</v>
+        <v>2001.287</v>
       </c>
       <c r="D116">
-        <v>5.465</v>
+        <v>-23.244</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>750</v>
+        <v>1798.226</v>
       </c>
       <c r="C117">
-        <v>750</v>
+        <v>1798.226</v>
       </c>
       <c r="D117">
-        <v>54.179</v>
+        <v>-16.913</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>678.687</v>
+        <v>2004.577</v>
       </c>
       <c r="C118">
-        <v>678.687</v>
+        <v>2004.577</v>
       </c>
       <c r="D118">
-        <v>34.318</v>
+        <v>-12.723</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>707.001</v>
+        <v>1990.037</v>
       </c>
       <c r="C119">
-        <v>707.001</v>
+        <v>1990.037</v>
       </c>
       <c r="D119">
-        <v>15.737</v>
+        <v>-19.542</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>3968.356</v>
+        <v>1955.863</v>
       </c>
       <c r="C120">
-        <v>3968.356</v>
+        <v>1955.863</v>
       </c>
       <c r="D120">
-        <v>-38.169</v>
+        <v>-24.451</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>3105.456</v>
+        <v>3595.436</v>
       </c>
       <c r="C121">
-        <v>3105.456</v>
+        <v>3595.436</v>
       </c>
       <c r="D121">
-        <v>-40.283</v>
+        <v>-22.967</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>1895.225</v>
+        <v>3441.268</v>
       </c>
       <c r="C122">
-        <v>1895.225</v>
+        <v>3441.268</v>
       </c>
       <c r="D122">
-        <v>-2.024</v>
+        <v>-28.67</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>1925.946</v>
+        <v>2001.896</v>
       </c>
       <c r="C123">
-        <v>1925.946</v>
+        <v>2001.896</v>
       </c>
       <c r="D123">
-        <v>-29.692</v>
+        <v>-23.576</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>1800.298</v>
+        <v>1999.276</v>
       </c>
       <c r="C124">
-        <v>1800.298</v>
+        <v>1999.276</v>
       </c>
       <c r="D124">
-        <v>-22.651</v>
+        <v>-21.125</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>1935.157</v>
+        <v>775</v>
       </c>
       <c r="C125">
-        <v>1935.157</v>
+        <v>775</v>
       </c>
       <c r="D125">
-        <v>-32.993</v>
+        <v>4.146</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>724.943</v>
+        <v>2022.839</v>
       </c>
       <c r="C126">
-        <v>724.943</v>
+        <v>2022.839</v>
       </c>
       <c r="D126">
-        <v>9.380000000000001</v>
+        <v>-25.51</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>750</v>
+        <v>1776.084</v>
       </c>
       <c r="C127">
-        <v>750</v>
+        <v>1776.084</v>
       </c>
       <c r="D127">
-        <v>0.228</v>
+        <v>-33.866</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>722.246</v>
+        <v>1741.912</v>
       </c>
       <c r="C128">
-        <v>722.246</v>
+        <v>1741.912</v>
       </c>
       <c r="D128">
-        <v>17.062</v>
+        <v>-8.673</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>1334.425</v>
+        <v>691.803</v>
       </c>
       <c r="C129">
-        <v>1334.425</v>
+        <v>691.803</v>
       </c>
       <c r="D129">
-        <v>-15.289</v>
+        <v>73.94799999999999</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>1803.248</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>1803.248</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>-51.391</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>2575.863</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>2575.863</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>-61.905</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>1964.383</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>1964.383</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>-79.06399999999999</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>26.007</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>28.019</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1533.347</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1533.347</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>-15.603</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46316.95833333334</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46316.96875</v>
+        <v>46320.92708333334</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46316.97916666666</v>
+        <v>46320.9375</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46316.98958333334</v>
+        <v>46320.94791666666</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4830,6 +4830,86 @@
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46320.95833333334</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46320.96875</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46320.97916666666</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46320.98958333334</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
